--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0497493-F73C-49B4-900A-17287FCC50E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204BA701-971E-45EE-A0A3-12A58EC657BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="427">
   <si>
     <t>OpCode</t>
   </si>
@@ -2255,12 +2277,21 @@
   <si>
     <t>Para cada puerto se entienede que es una funcion de Switch distinta. Para 3 puertos el switch tiene 3 funciones. Excepto en el Root Complex</t>
   </si>
+  <si>
+    <t>Hex</t>
+  </si>
+  <si>
+    <t>Instrucción</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2347,6 +2378,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3363,10 +3401,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="345">
+  <cellXfs count="350">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3974,6 +4013,429 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3983,24 +4445,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4010,398 +4454,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4681,7 +4736,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AI75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
     <col min="2" max="2" width="19.85546875" style="15" customWidth="1"/>
@@ -4717,64 +4772,64 @@
     <col min="36" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="276" t="s">
+    <row r="1" spans="2:35" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:35" ht="15.75" thickBot="1">
+      <c r="B2" s="291" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="285" t="s">
+      <c r="C2" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286"/>
-      <c r="E2" s="287" t="s">
+      <c r="D2" s="307"/>
+      <c r="E2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="287"/>
-      <c r="G2" s="288" t="s">
+      <c r="F2" s="308"/>
+      <c r="G2" s="309" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="287"/>
-      <c r="I2" s="287" t="s">
+      <c r="H2" s="308"/>
+      <c r="I2" s="308" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="287"/>
-      <c r="K2" s="289" t="s">
+      <c r="J2" s="308"/>
+      <c r="K2" s="310" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="290"/>
-      <c r="R2" s="293" t="s">
+      <c r="L2" s="308"/>
+      <c r="M2" s="308"/>
+      <c r="N2" s="308"/>
+      <c r="O2" s="308"/>
+      <c r="P2" s="311"/>
+      <c r="R2" s="287" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="245" t="s">
+      <c r="S2" s="285" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="297" t="s">
+      <c r="T2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="298"/>
-      <c r="V2" s="298"/>
-      <c r="W2" s="298"/>
-      <c r="X2" s="298"/>
-      <c r="Y2" s="298"/>
-      <c r="Z2" s="298"/>
-      <c r="AA2" s="298"/>
-      <c r="AB2" s="298" t="s">
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="279"/>
+      <c r="AB2" s="279" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="298"/>
-      <c r="AD2" s="298"/>
-      <c r="AE2" s="298"/>
-      <c r="AF2" s="298"/>
-      <c r="AG2" s="298"/>
-      <c r="AH2" s="298"/>
-      <c r="AI2" s="299"/>
-    </row>
-    <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="277"/>
+      <c r="AC2" s="279"/>
+      <c r="AD2" s="279"/>
+      <c r="AE2" s="279"/>
+      <c r="AF2" s="279"/>
+      <c r="AG2" s="279"/>
+      <c r="AH2" s="279"/>
+      <c r="AI2" s="280"/>
+    </row>
+    <row r="3" spans="2:35" ht="15.75" thickBot="1">
+      <c r="B3" s="292"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -4799,21 +4854,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="282"/>
-      <c r="L3" s="283"/>
-      <c r="M3" s="283"/>
-      <c r="N3" s="283"/>
-      <c r="O3" s="283"/>
-      <c r="P3" s="284"/>
-      <c r="R3" s="294"/>
-      <c r="S3" s="291"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="305"/>
+      <c r="M3" s="305"/>
+      <c r="N3" s="305"/>
+      <c r="O3" s="305"/>
+      <c r="P3" s="264"/>
+      <c r="R3" s="288"/>
+      <c r="S3" s="214"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="263" t="s">
+      <c r="U3" s="315" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="263"/>
+      <c r="V3" s="315"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -4826,10 +4881,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="296" t="s">
+      <c r="AA3" s="277" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="296"/>
+      <c r="AB3" s="277"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -4852,22 +4907,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="278"/>
+    <row r="4" spans="2:35" ht="15.75" thickBot="1">
+      <c r="B4" s="293"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="264" t="s">
+      <c r="E4" s="281" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="211"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="269"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -4877,20 +4932,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="264" t="s">
+      <c r="N4" s="281" t="s">
         <v>312</v>
       </c>
-      <c r="O4" s="210"/>
-      <c r="P4" s="211"/>
-      <c r="R4" s="295"/>
-      <c r="S4" s="292"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="269"/>
+      <c r="R4" s="289"/>
+      <c r="S4" s="286"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="264" t="s">
+      <c r="U4" s="281" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="265"/>
+      <c r="V4" s="282"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -4903,10 +4958,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="264" t="s">
+      <c r="AA4" s="281" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="265"/>
+      <c r="AB4" s="282"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -4929,7 +4984,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:35" ht="15.75" thickBot="1">
       <c r="B5" s="1">
         <v>0</v>
       </c>
@@ -4938,22 +4993,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="268"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="270"/>
+      <c r="E5" s="312"/>
+      <c r="F5" s="313"/>
+      <c r="G5" s="313"/>
+      <c r="H5" s="313"/>
+      <c r="I5" s="313"/>
+      <c r="J5" s="314"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="223" t="s">
+      <c r="N5" s="248" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="224"/>
-      <c r="P5" s="225"/>
+      <c r="O5" s="290"/>
+      <c r="P5" s="249"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -4963,10 +5018,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="266" t="s">
+      <c r="U5" s="283" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="267"/>
+      <c r="V5" s="284"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -4979,10 +5034,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="266" t="s">
+      <c r="AA5" s="283" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="267"/>
+      <c r="AB5" s="284"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5005,7 +5060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:35" ht="15.75" thickBot="1">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -5014,12 +5069,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="275"/>
-      <c r="F6" s="272"/>
-      <c r="G6" s="272"/>
-      <c r="H6" s="272"/>
-      <c r="I6" s="272"/>
-      <c r="J6" s="273"/>
+      <c r="E6" s="303"/>
+      <c r="F6" s="298"/>
+      <c r="G6" s="298"/>
+      <c r="H6" s="298"/>
+      <c r="I6" s="298"/>
+      <c r="J6" s="299"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5027,11 +5082,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="220" t="s">
+      <c r="N6" s="274" t="s">
         <v>313</v>
       </c>
-      <c r="O6" s="221"/>
-      <c r="P6" s="222"/>
+      <c r="O6" s="275"/>
+      <c r="P6" s="276"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5041,10 +5096,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="261" t="s">
+      <c r="U6" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="262"/>
+      <c r="V6" s="271"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5057,10 +5112,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="261" t="s">
+      <c r="AA6" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="262"/>
+      <c r="AB6" s="271"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5083,7 +5138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:35" ht="15.75" thickBot="1">
       <c r="B7" s="2">
         <v>2</v>
       </c>
@@ -5103,9 +5158,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="271"/>
-      <c r="I7" s="272"/>
-      <c r="J7" s="273"/>
+      <c r="H7" s="297"/>
+      <c r="I7" s="298"/>
+      <c r="J7" s="299"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5113,11 +5168,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="220" t="s">
+      <c r="N7" s="274" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="221"/>
-      <c r="P7" s="222"/>
+      <c r="O7" s="275"/>
+      <c r="P7" s="276"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5127,10 +5182,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="261" t="s">
+      <c r="U7" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="262"/>
+      <c r="V7" s="271"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5143,10 +5198,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="261" t="s">
+      <c r="AA7" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="262"/>
+      <c r="AB7" s="271"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5169,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:35" ht="15.75" thickBot="1">
       <c r="B8" s="2">
         <v>3</v>
       </c>
@@ -5189,9 +5244,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="271"/>
-      <c r="I8" s="272"/>
-      <c r="J8" s="273"/>
+      <c r="H8" s="297"/>
+      <c r="I8" s="298"/>
+      <c r="J8" s="299"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5199,11 +5254,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="220" t="s">
+      <c r="N8" s="274" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="221"/>
-      <c r="P8" s="222"/>
+      <c r="O8" s="275"/>
+      <c r="P8" s="276"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5213,10 +5268,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="261" t="s">
+      <c r="U8" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="262"/>
+      <c r="V8" s="271"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5229,10 +5284,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="261" t="s">
+      <c r="AA8" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="262"/>
+      <c r="AB8" s="271"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5255,7 +5310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:35" ht="15.75" thickBot="1">
       <c r="B9" s="1">
         <v>4</v>
       </c>
@@ -5275,9 +5330,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="271"/>
-      <c r="I9" s="272"/>
-      <c r="J9" s="273"/>
+      <c r="H9" s="297"/>
+      <c r="I9" s="298"/>
+      <c r="J9" s="299"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5285,11 +5340,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="220" t="s">
+      <c r="N9" s="274" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="221"/>
-      <c r="P9" s="222"/>
+      <c r="O9" s="275"/>
+      <c r="P9" s="276"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5299,10 +5354,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="261" t="s">
+      <c r="U9" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="262"/>
+      <c r="V9" s="271"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5315,10 +5370,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="261" t="s">
+      <c r="AA9" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="262"/>
+      <c r="AB9" s="271"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5341,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:35" ht="15.75" thickBot="1">
       <c r="B10" s="2">
         <v>5</v>
       </c>
@@ -5361,9 +5416,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="271"/>
-      <c r="I10" s="272"/>
-      <c r="J10" s="273"/>
+      <c r="H10" s="297"/>
+      <c r="I10" s="298"/>
+      <c r="J10" s="299"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5371,11 +5426,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="220" t="s">
+      <c r="N10" s="274" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="221"/>
-      <c r="P10" s="222"/>
+      <c r="O10" s="275"/>
+      <c r="P10" s="276"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5385,10 +5440,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="261" t="s">
+      <c r="U10" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="262"/>
+      <c r="V10" s="271"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5401,10 +5456,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="261" t="s">
+      <c r="AA10" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="262"/>
+      <c r="AB10" s="271"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5427,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:35" ht="15.75" thickBot="1">
       <c r="B11" s="2">
         <v>6</v>
       </c>
@@ -5447,9 +5502,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="271"/>
-      <c r="I11" s="272"/>
-      <c r="J11" s="273"/>
+      <c r="H11" s="297"/>
+      <c r="I11" s="298"/>
+      <c r="J11" s="299"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5457,11 +5512,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="220" t="s">
+      <c r="N11" s="274" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="221"/>
-      <c r="P11" s="222"/>
+      <c r="O11" s="275"/>
+      <c r="P11" s="276"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5471,10 +5526,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="261" t="s">
+      <c r="U11" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="262"/>
+      <c r="V11" s="271"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5487,10 +5542,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="261" t="s">
+      <c r="AA11" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="262"/>
+      <c r="AB11" s="271"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5513,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:35" ht="15.75" thickBot="1">
       <c r="B12" s="2">
         <v>7</v>
       </c>
@@ -5533,9 +5588,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="271"/>
-      <c r="I12" s="272"/>
-      <c r="J12" s="273"/>
+      <c r="H12" s="297"/>
+      <c r="I12" s="298"/>
+      <c r="J12" s="299"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5543,11 +5598,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="220" t="s">
+      <c r="N12" s="274" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="221"/>
-      <c r="P12" s="222"/>
+      <c r="O12" s="275"/>
+      <c r="P12" s="276"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5557,10 +5612,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="261" t="s">
+      <c r="U12" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="262"/>
+      <c r="V12" s="271"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5573,10 +5628,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="261" t="s">
+      <c r="AA12" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="262"/>
+      <c r="AB12" s="271"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -5599,7 +5654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:35" ht="15.75" thickBot="1">
       <c r="B13" s="1">
         <v>8</v>
       </c>
@@ -5619,9 +5674,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="271"/>
-      <c r="I13" s="272"/>
-      <c r="J13" s="273"/>
+      <c r="H13" s="297"/>
+      <c r="I13" s="298"/>
+      <c r="J13" s="299"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -5629,11 +5684,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="220" t="s">
+      <c r="N13" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="221"/>
-      <c r="P13" s="222"/>
+      <c r="O13" s="275"/>
+      <c r="P13" s="276"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -5643,10 +5698,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="261" t="s">
+      <c r="U13" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="262"/>
+      <c r="V13" s="271"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -5659,10 +5714,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="261" t="s">
+      <c r="AA13" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="262"/>
+      <c r="AB13" s="271"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -5685,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:35" ht="15.75" thickBot="1">
       <c r="B14" s="2">
         <v>9</v>
       </c>
@@ -5705,9 +5760,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="271"/>
-      <c r="I14" s="272"/>
-      <c r="J14" s="273"/>
+      <c r="H14" s="297"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="299"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -5715,11 +5770,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="220" t="s">
+      <c r="N14" s="274" t="s">
         <v>314</v>
       </c>
-      <c r="O14" s="221"/>
-      <c r="P14" s="222"/>
+      <c r="O14" s="275"/>
+      <c r="P14" s="276"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -5729,10 +5784,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="261" t="s">
+      <c r="U14" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="262"/>
+      <c r="V14" s="271"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -5745,10 +5800,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="261" t="s">
+      <c r="AA14" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="262"/>
+      <c r="AB14" s="271"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -5771,7 +5826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:35" ht="15.75" thickBot="1">
       <c r="B15" s="2">
         <v>10</v>
       </c>
@@ -5791,9 +5846,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="271"/>
-      <c r="I15" s="272"/>
-      <c r="J15" s="273"/>
+      <c r="H15" s="297"/>
+      <c r="I15" s="298"/>
+      <c r="J15" s="299"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -5801,11 +5856,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="220" t="s">
+      <c r="N15" s="274" t="s">
         <v>315</v>
       </c>
-      <c r="O15" s="221"/>
-      <c r="P15" s="222"/>
+      <c r="O15" s="275"/>
+      <c r="P15" s="276"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -5815,10 +5870,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="261" t="s">
+      <c r="U15" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="262"/>
+      <c r="V15" s="271"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -5831,10 +5886,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="261" t="s">
+      <c r="AA15" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="262"/>
+      <c r="AB15" s="271"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -5857,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:35" ht="15.75" thickBot="1">
       <c r="B16" s="2">
         <v>11</v>
       </c>
@@ -5871,21 +5926,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="271"/>
-      <c r="G16" s="272"/>
-      <c r="H16" s="272"/>
-      <c r="I16" s="272"/>
-      <c r="J16" s="273"/>
+      <c r="F16" s="297"/>
+      <c r="G16" s="298"/>
+      <c r="H16" s="298"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="299"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="220" t="s">
+      <c r="N16" s="274" t="s">
         <v>316</v>
       </c>
-      <c r="O16" s="221"/>
-      <c r="P16" s="222"/>
+      <c r="O16" s="275"/>
+      <c r="P16" s="276"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -5895,10 +5950,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="261" t="s">
+      <c r="U16" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="262"/>
+      <c r="V16" s="271"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -5911,10 +5966,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="261" t="s">
+      <c r="AA16" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="262"/>
+      <c r="AB16" s="271"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -5937,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:35" ht="15.75" thickBot="1">
       <c r="B17" s="2">
         <v>12</v>
       </c>
@@ -5952,22 +6007,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="274" t="s">
+      <c r="G17" s="304" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="221"/>
-      <c r="I17" s="221"/>
-      <c r="J17" s="222"/>
+      <c r="H17" s="275"/>
+      <c r="I17" s="275"/>
+      <c r="J17" s="276"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="220" t="s">
+      <c r="N17" s="274" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="221"/>
-      <c r="P17" s="222"/>
+      <c r="O17" s="275"/>
+      <c r="P17" s="276"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -5977,10 +6032,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="261" t="s">
+      <c r="U17" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="262"/>
+      <c r="V17" s="271"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -5993,10 +6048,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="261" t="s">
+      <c r="AA17" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="262"/>
+      <c r="AB17" s="271"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6019,7 +6074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:35" ht="15.75" thickBot="1">
       <c r="B18" s="2">
         <v>13</v>
       </c>
@@ -6034,12 +6089,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="274" t="s">
+      <c r="G18" s="304" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="221"/>
-      <c r="I18" s="221"/>
-      <c r="J18" s="222"/>
+      <c r="H18" s="275"/>
+      <c r="I18" s="275"/>
+      <c r="J18" s="276"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6047,11 +6102,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="220" t="s">
+      <c r="N18" s="274" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="221"/>
-      <c r="P18" s="222"/>
+      <c r="O18" s="275"/>
+      <c r="P18" s="276"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6061,10 +6116,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="261" t="s">
+      <c r="U18" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="262"/>
+      <c r="V18" s="271"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6077,10 +6132,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="261" t="s">
+      <c r="AA18" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="262"/>
+      <c r="AB18" s="271"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6103,7 +6158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:35" ht="15.75" thickBot="1">
       <c r="B19" s="2">
         <v>14</v>
       </c>
@@ -6116,20 +6171,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="271"/>
-      <c r="H19" s="272"/>
-      <c r="I19" s="272"/>
-      <c r="J19" s="273"/>
+      <c r="G19" s="297"/>
+      <c r="H19" s="298"/>
+      <c r="I19" s="298"/>
+      <c r="J19" s="299"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="220" t="s">
+      <c r="N19" s="274" t="s">
         <v>317</v>
       </c>
-      <c r="O19" s="221"/>
-      <c r="P19" s="222"/>
+      <c r="O19" s="275"/>
+      <c r="P19" s="276"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6139,10 +6194,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="261" t="s">
+      <c r="U19" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="262"/>
+      <c r="V19" s="271"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6155,10 +6210,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="261" t="s">
+      <c r="AA19" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="262"/>
+      <c r="AB19" s="271"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6181,7 +6236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:35" ht="15.75" thickBot="1">
       <c r="B20" s="2">
         <v>15</v>
       </c>
@@ -6196,20 +6251,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="271"/>
-      <c r="H20" s="272"/>
-      <c r="I20" s="272"/>
-      <c r="J20" s="273"/>
+      <c r="G20" s="297"/>
+      <c r="H20" s="298"/>
+      <c r="I20" s="298"/>
+      <c r="J20" s="299"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="220" t="s">
+      <c r="N20" s="274" t="s">
         <v>318</v>
       </c>
-      <c r="O20" s="221"/>
-      <c r="P20" s="222"/>
+      <c r="O20" s="275"/>
+      <c r="P20" s="276"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6219,10 +6274,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="261" t="s">
+      <c r="U20" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="262"/>
+      <c r="V20" s="271"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6235,10 +6290,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="261" t="s">
+      <c r="AA20" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="262"/>
+      <c r="AB20" s="271"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6261,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:35" ht="15.75" thickBot="1">
       <c r="B21" s="2">
         <v>16</v>
       </c>
@@ -6276,20 +6331,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="271"/>
-      <c r="H21" s="272"/>
-      <c r="I21" s="272"/>
-      <c r="J21" s="273"/>
+      <c r="G21" s="297"/>
+      <c r="H21" s="298"/>
+      <c r="I21" s="298"/>
+      <c r="J21" s="299"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="220" t="s">
+      <c r="N21" s="274" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="221"/>
-      <c r="P21" s="222"/>
+      <c r="O21" s="275"/>
+      <c r="P21" s="276"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6299,10 +6354,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="261" t="s">
+      <c r="U21" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="262"/>
+      <c r="V21" s="271"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6315,10 +6370,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="261" t="s">
+      <c r="AA21" s="270" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="262"/>
+      <c r="AB21" s="271"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6341,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:35" ht="15.75" thickBot="1">
       <c r="B22" s="2">
         <v>17</v>
       </c>
@@ -6352,22 +6407,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="275"/>
-      <c r="F22" s="272"/>
-      <c r="G22" s="272"/>
-      <c r="H22" s="272"/>
-      <c r="I22" s="272"/>
-      <c r="J22" s="273"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="298"/>
+      <c r="G22" s="298"/>
+      <c r="H22" s="298"/>
+      <c r="I22" s="298"/>
+      <c r="J22" s="299"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="220" t="s">
+      <c r="N22" s="274" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="221"/>
-      <c r="P22" s="222"/>
+      <c r="O22" s="275"/>
+      <c r="P22" s="276"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6377,10 +6432,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="261" t="s">
-        <v>69</v>
-      </c>
-      <c r="V22" s="262"/>
+      <c r="U22" s="270" t="s">
+        <v>88</v>
+      </c>
+      <c r="V22" s="271"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6393,10 +6448,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="261" t="s">
+      <c r="AA22" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="262"/>
+      <c r="AB22" s="271"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6407,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="AF22" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="34">
         <v>0</v>
@@ -6419,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:35" ht="15.75" thickBot="1">
       <c r="B23" s="2">
         <v>18</v>
       </c>
@@ -6436,22 +6491,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="274" t="s">
+      <c r="G23" s="304" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="221"/>
-      <c r="I23" s="221"/>
-      <c r="J23" s="222"/>
+      <c r="H23" s="275"/>
+      <c r="I23" s="275"/>
+      <c r="J23" s="276"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="220" t="s">
+      <c r="N23" s="274" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="221"/>
-      <c r="P23" s="222"/>
+      <c r="O23" s="275"/>
+      <c r="P23" s="276"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6461,10 +6516,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="261" t="s">
+      <c r="U23" s="270" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="262"/>
+      <c r="V23" s="271"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6477,10 +6532,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="261" t="s">
+      <c r="AA23" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="262"/>
+      <c r="AB23" s="271"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6503,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:35" ht="15.75" thickBot="1">
       <c r="B24" s="2">
         <v>19</v>
       </c>
@@ -6520,22 +6575,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="274" t="s">
+      <c r="G24" s="304" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="221"/>
-      <c r="I24" s="221"/>
-      <c r="J24" s="222"/>
+      <c r="H24" s="275"/>
+      <c r="I24" s="275"/>
+      <c r="J24" s="276"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="220" t="s">
+      <c r="N24" s="274" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="221"/>
-      <c r="P24" s="222"/>
+      <c r="O24" s="275"/>
+      <c r="P24" s="276"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6545,10 +6600,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="261" t="s">
+      <c r="U24" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="262"/>
+      <c r="V24" s="271"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6561,10 +6616,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="261" t="s">
+      <c r="AA24" s="270" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="262"/>
+      <c r="AB24" s="271"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6587,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:35" ht="15.75" thickBot="1">
       <c r="B25" s="2">
         <v>20</v>
       </c>
@@ -6602,10 +6657,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="271"/>
-      <c r="H25" s="272"/>
-      <c r="I25" s="272"/>
-      <c r="J25" s="273"/>
+      <c r="G25" s="297"/>
+      <c r="H25" s="298"/>
+      <c r="I25" s="298"/>
+      <c r="J25" s="299"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6613,11 +6668,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="220" t="s">
+      <c r="N25" s="274" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="221"/>
-      <c r="P25" s="222"/>
+      <c r="O25" s="275"/>
+      <c r="P25" s="276"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -6627,10 +6682,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="261" t="s">
+      <c r="U25" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="262"/>
+      <c r="V25" s="271"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -6643,10 +6698,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="261" t="s">
+      <c r="AA25" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="262"/>
+      <c r="AB25" s="271"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -6669,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:35" ht="15.75" thickBot="1">
       <c r="B26" s="2">
         <v>21</v>
       </c>
@@ -6684,10 +6739,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="271"/>
-      <c r="H26" s="272"/>
-      <c r="I26" s="272"/>
-      <c r="J26" s="273"/>
+      <c r="G26" s="297"/>
+      <c r="H26" s="298"/>
+      <c r="I26" s="298"/>
+      <c r="J26" s="299"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -6695,11 +6750,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="220" t="s">
+      <c r="N26" s="274" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="221"/>
-      <c r="P26" s="222"/>
+      <c r="O26" s="275"/>
+      <c r="P26" s="276"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -6709,10 +6764,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="261" t="s">
+      <c r="U26" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="262"/>
+      <c r="V26" s="271"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -6725,10 +6780,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="261" t="s">
+      <c r="AA26" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="262"/>
+      <c r="AB26" s="271"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -6751,7 +6806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:35" ht="15.75" thickBot="1">
       <c r="B27" s="3">
         <v>22</v>
       </c>
@@ -6760,22 +6815,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="275"/>
-      <c r="F27" s="272"/>
-      <c r="G27" s="272"/>
-      <c r="H27" s="272"/>
-      <c r="I27" s="272"/>
-      <c r="J27" s="273"/>
+      <c r="E27" s="303"/>
+      <c r="F27" s="298"/>
+      <c r="G27" s="298"/>
+      <c r="H27" s="298"/>
+      <c r="I27" s="298"/>
+      <c r="J27" s="299"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="220" t="s">
+      <c r="N27" s="274" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="221"/>
-      <c r="P27" s="222"/>
+      <c r="O27" s="275"/>
+      <c r="P27" s="276"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -6785,10 +6840,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="261" t="s">
+      <c r="U27" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="262"/>
+      <c r="V27" s="271"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -6801,10 +6856,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="261" t="s">
+      <c r="AA27" s="270" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="262"/>
+      <c r="AB27" s="271"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -6827,7 +6882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:35" ht="15.75" thickBot="1">
       <c r="B28" s="4">
         <v>23</v>
       </c>
@@ -6836,12 +6891,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="279"/>
-      <c r="F28" s="280"/>
-      <c r="G28" s="280"/>
-      <c r="H28" s="280"/>
-      <c r="I28" s="280"/>
-      <c r="J28" s="281"/>
+      <c r="E28" s="300"/>
+      <c r="F28" s="301"/>
+      <c r="G28" s="301"/>
+      <c r="H28" s="301"/>
+      <c r="I28" s="301"/>
+      <c r="J28" s="302"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -6849,11 +6904,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="217" t="s">
+      <c r="N28" s="294" t="s">
         <v>319</v>
       </c>
-      <c r="O28" s="218"/>
-      <c r="P28" s="219"/>
+      <c r="O28" s="295"/>
+      <c r="P28" s="296"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -6863,10 +6918,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="308" t="s">
+      <c r="U28" s="272" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="309"/>
+      <c r="V28" s="273"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -6879,10 +6934,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="308" t="s">
+      <c r="AA28" s="272" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="309"/>
+      <c r="AB28" s="273"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -6905,8 +6960,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:35" ht="15.75" thickBot="1"/>
+    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1">
       <c r="B30" s="66" t="s">
         <v>80</v>
       </c>
@@ -6959,20 +7014,29 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="244" t="s">
+      <c r="T30" s="329" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="244"/>
-      <c r="V30" s="244"/>
-      <c r="W30" s="244"/>
-      <c r="X30" s="244"/>
-      <c r="Y30" s="244"/>
-      <c r="Z30" s="244"/>
-      <c r="AA30" s="244"/>
-      <c r="AB30" s="244"/>
-      <c r="AC30" s="245"/>
-    </row>
-    <row r="31" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U30" s="329"/>
+      <c r="V30" s="329"/>
+      <c r="W30" s="329"/>
+      <c r="X30" s="329"/>
+      <c r="Y30" s="329"/>
+      <c r="Z30" s="329"/>
+      <c r="AA30" s="329"/>
+      <c r="AB30" s="329"/>
+      <c r="AC30" s="285"/>
+      <c r="AE30" s="267" t="s">
+        <v>425</v>
+      </c>
+      <c r="AF30" s="268"/>
+      <c r="AG30" s="267" t="s">
+        <v>426</v>
+      </c>
+      <c r="AH30" s="268"/>
+      <c r="AI30" s="269"/>
+    </row>
+    <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1">
       <c r="B31" s="67" t="s">
         <v>68</v>
       </c>
@@ -7011,20 +7075,30 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="223" t="s">
+      <c r="T31" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="224"/>
-      <c r="V31" s="224"/>
-      <c r="W31" s="224"/>
-      <c r="X31" s="224"/>
-      <c r="Y31" s="224"/>
-      <c r="Z31" s="224"/>
-      <c r="AA31" s="224"/>
-      <c r="AB31" s="224"/>
-      <c r="AC31" s="225"/>
-    </row>
-    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U31" s="290"/>
+      <c r="V31" s="290"/>
+      <c r="W31" s="290"/>
+      <c r="X31" s="290"/>
+      <c r="Y31" s="290"/>
+      <c r="Z31" s="290"/>
+      <c r="AA31" s="290"/>
+      <c r="AB31" s="290"/>
+      <c r="AC31" s="249"/>
+      <c r="AE31" s="324">
+        <v>2</v>
+      </c>
+      <c r="AF31" s="325"/>
+      <c r="AG31" s="326" t="str" cm="1">
+        <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
+        <v>No encontrado</v>
+      </c>
+      <c r="AH31" s="327"/>
+      <c r="AI31" s="328"/>
+    </row>
+    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="B32" s="4" t="s">
         <v>71</v>
       </c>
@@ -7046,20 +7120,20 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="220" t="s">
+      <c r="T32" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="221"/>
-      <c r="V32" s="221"/>
-      <c r="W32" s="221"/>
-      <c r="X32" s="221"/>
-      <c r="Y32" s="221"/>
-      <c r="Z32" s="221"/>
-      <c r="AA32" s="221"/>
-      <c r="AB32" s="221"/>
-      <c r="AC32" s="222"/>
-    </row>
-    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U32" s="275"/>
+      <c r="V32" s="275"/>
+      <c r="W32" s="275"/>
+      <c r="X32" s="275"/>
+      <c r="Y32" s="275"/>
+      <c r="Z32" s="275"/>
+      <c r="AA32" s="275"/>
+      <c r="AB32" s="275"/>
+      <c r="AC32" s="276"/>
+    </row>
+    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1">
       <c r="H33" s="84" t="s">
         <v>165</v>
       </c>
@@ -7093,31 +7167,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="220" t="s">
+      <c r="T33" s="274" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="221"/>
-      <c r="V33" s="221"/>
-      <c r="W33" s="221"/>
-      <c r="X33" s="221"/>
-      <c r="Y33" s="221"/>
-      <c r="Z33" s="221"/>
-      <c r="AA33" s="221"/>
-      <c r="AB33" s="221"/>
-      <c r="AC33" s="222"/>
-    </row>
-    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="306" t="s">
+      <c r="U33" s="275"/>
+      <c r="V33" s="275"/>
+      <c r="W33" s="275"/>
+      <c r="X33" s="275"/>
+      <c r="Y33" s="275"/>
+      <c r="Z33" s="275"/>
+      <c r="AA33" s="275"/>
+      <c r="AB33" s="275"/>
+      <c r="AC33" s="276"/>
+    </row>
+    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
+      <c r="B34" s="265" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="282" t="s">
+      <c r="C34" s="263" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="284"/>
-      <c r="E34" s="282" t="s">
+      <c r="D34" s="264"/>
+      <c r="E34" s="263" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="284"/>
+      <c r="F34" s="264"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7145,21 +7219,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="220" t="s">
+      <c r="T34" s="274" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="221"/>
-      <c r="V34" s="221"/>
-      <c r="W34" s="221"/>
-      <c r="X34" s="221"/>
-      <c r="Y34" s="221"/>
-      <c r="Z34" s="221"/>
-      <c r="AA34" s="221"/>
-      <c r="AB34" s="221"/>
-      <c r="AC34" s="222"/>
-    </row>
-    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="307"/>
+      <c r="U34" s="275"/>
+      <c r="V34" s="275"/>
+      <c r="W34" s="275"/>
+      <c r="X34" s="275"/>
+      <c r="Y34" s="275"/>
+      <c r="Z34" s="275"/>
+      <c r="AA34" s="275"/>
+      <c r="AB34" s="275"/>
+      <c r="AC34" s="276"/>
+    </row>
+    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
+      <c r="B35" s="266"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7178,20 +7252,20 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="220" t="s">
+      <c r="T35" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="221"/>
-      <c r="V35" s="221"/>
-      <c r="W35" s="221"/>
-      <c r="X35" s="221"/>
-      <c r="Y35" s="221"/>
-      <c r="Z35" s="221"/>
-      <c r="AA35" s="221"/>
-      <c r="AB35" s="221"/>
-      <c r="AC35" s="222"/>
-    </row>
-    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U35" s="275"/>
+      <c r="V35" s="275"/>
+      <c r="W35" s="275"/>
+      <c r="X35" s="275"/>
+      <c r="Y35" s="275"/>
+      <c r="Z35" s="275"/>
+      <c r="AA35" s="275"/>
+      <c r="AB35" s="275"/>
+      <c r="AC35" s="276"/>
+    </row>
+    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1">
       <c r="B36" s="1">
         <v>0</v>
       </c>
@@ -7240,20 +7314,20 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="220" t="s">
+      <c r="T36" s="274" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="221"/>
-      <c r="V36" s="221"/>
-      <c r="W36" s="221"/>
-      <c r="X36" s="221"/>
-      <c r="Y36" s="221"/>
-      <c r="Z36" s="221"/>
-      <c r="AA36" s="221"/>
-      <c r="AB36" s="221"/>
-      <c r="AC36" s="222"/>
-    </row>
-    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U36" s="275"/>
+      <c r="V36" s="275"/>
+      <c r="W36" s="275"/>
+      <c r="X36" s="275"/>
+      <c r="Y36" s="275"/>
+      <c r="Z36" s="275"/>
+      <c r="AA36" s="275"/>
+      <c r="AB36" s="275"/>
+      <c r="AC36" s="276"/>
+    </row>
+    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1">
       <c r="B37" s="2">
         <v>1</v>
       </c>
@@ -7294,20 +7368,20 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="220" t="s">
+      <c r="T37" s="274" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="221"/>
-      <c r="V37" s="221"/>
-      <c r="W37" s="221"/>
-      <c r="X37" s="221"/>
-      <c r="Y37" s="221"/>
-      <c r="Z37" s="221"/>
-      <c r="AA37" s="221"/>
-      <c r="AB37" s="221"/>
-      <c r="AC37" s="222"/>
-    </row>
-    <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U37" s="275"/>
+      <c r="V37" s="275"/>
+      <c r="W37" s="275"/>
+      <c r="X37" s="275"/>
+      <c r="Y37" s="275"/>
+      <c r="Z37" s="275"/>
+      <c r="AA37" s="275"/>
+      <c r="AB37" s="275"/>
+      <c r="AC37" s="276"/>
+    </row>
+    <row r="38" spans="2:29" ht="15.75" thickBot="1">
       <c r="B38" s="2">
         <v>2</v>
       </c>
@@ -7326,23 +7400,23 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="246" t="s">
+      <c r="S38" s="316" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="248" t="s">
+      <c r="T38" s="318" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="249"/>
-      <c r="V38" s="249"/>
-      <c r="W38" s="249"/>
-      <c r="X38" s="249"/>
-      <c r="Y38" s="249"/>
-      <c r="Z38" s="249"/>
-      <c r="AA38" s="249"/>
-      <c r="AB38" s="249"/>
-      <c r="AC38" s="250"/>
-    </row>
-    <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U38" s="319"/>
+      <c r="V38" s="319"/>
+      <c r="W38" s="319"/>
+      <c r="X38" s="319"/>
+      <c r="Y38" s="319"/>
+      <c r="Z38" s="319"/>
+      <c r="AA38" s="319"/>
+      <c r="AB38" s="319"/>
+      <c r="AC38" s="320"/>
+    </row>
+    <row r="39" spans="2:29" ht="15" customHeight="1">
       <c r="B39" s="2">
         <v>3</v>
       </c>
@@ -7358,28 +7432,28 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="254" t="s">
+      <c r="G39" s="250" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="215"/>
-      <c r="I39" s="215"/>
-      <c r="J39" s="216"/>
+      <c r="H39" s="251"/>
+      <c r="I39" s="251"/>
+      <c r="J39" s="252"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="247"/>
-      <c r="T39" s="251"/>
-      <c r="U39" s="252"/>
-      <c r="V39" s="252"/>
-      <c r="W39" s="252"/>
-      <c r="X39" s="252"/>
-      <c r="Y39" s="252"/>
-      <c r="Z39" s="252"/>
-      <c r="AA39" s="252"/>
-      <c r="AB39" s="252"/>
-      <c r="AC39" s="253"/>
-    </row>
-    <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S39" s="317"/>
+      <c r="T39" s="321"/>
+      <c r="U39" s="322"/>
+      <c r="V39" s="322"/>
+      <c r="W39" s="322"/>
+      <c r="X39" s="322"/>
+      <c r="Y39" s="322"/>
+      <c r="Z39" s="322"/>
+      <c r="AA39" s="322"/>
+      <c r="AB39" s="322"/>
+      <c r="AC39" s="323"/>
+    </row>
+    <row r="40" spans="2:29" ht="37.5" customHeight="1">
       <c r="B40" s="2">
         <v>4</v>
       </c>
@@ -7395,30 +7469,30 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="258"/>
-      <c r="H40" s="259"/>
-      <c r="I40" s="259"/>
-      <c r="J40" s="260"/>
+      <c r="G40" s="253"/>
+      <c r="H40" s="254"/>
+      <c r="I40" s="254"/>
+      <c r="J40" s="255"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="220" t="s">
+      <c r="T40" s="274" t="s">
         <v>323</v>
       </c>
-      <c r="U40" s="221"/>
-      <c r="V40" s="221"/>
-      <c r="W40" s="221"/>
-      <c r="X40" s="221"/>
-      <c r="Y40" s="221"/>
-      <c r="Z40" s="221"/>
-      <c r="AA40" s="221"/>
-      <c r="AB40" s="221"/>
-      <c r="AC40" s="222"/>
-    </row>
-    <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U40" s="275"/>
+      <c r="V40" s="275"/>
+      <c r="W40" s="275"/>
+      <c r="X40" s="275"/>
+      <c r="Y40" s="275"/>
+      <c r="Z40" s="275"/>
+      <c r="AA40" s="275"/>
+      <c r="AB40" s="275"/>
+      <c r="AC40" s="276"/>
+    </row>
+    <row r="41" spans="2:29" ht="30" customHeight="1">
       <c r="B41" s="2">
         <v>5</v>
       </c>
@@ -7434,30 +7508,30 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="258"/>
-      <c r="H41" s="259"/>
-      <c r="I41" s="259"/>
-      <c r="J41" s="260"/>
+      <c r="G41" s="253"/>
+      <c r="H41" s="254"/>
+      <c r="I41" s="254"/>
+      <c r="J41" s="255"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="220" t="s">
+      <c r="T41" s="274" t="s">
         <v>326</v>
       </c>
-      <c r="U41" s="221"/>
-      <c r="V41" s="221"/>
-      <c r="W41" s="221"/>
-      <c r="X41" s="221"/>
-      <c r="Y41" s="221"/>
-      <c r="Z41" s="221"/>
-      <c r="AA41" s="221"/>
-      <c r="AB41" s="221"/>
-      <c r="AC41" s="222"/>
-    </row>
-    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U41" s="275"/>
+      <c r="V41" s="275"/>
+      <c r="W41" s="275"/>
+      <c r="X41" s="275"/>
+      <c r="Y41" s="275"/>
+      <c r="Z41" s="275"/>
+      <c r="AA41" s="275"/>
+      <c r="AB41" s="275"/>
+      <c r="AC41" s="276"/>
+    </row>
+    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1">
       <c r="B42" s="2">
         <v>6</v>
       </c>
@@ -7473,30 +7547,30 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="255"/>
-      <c r="H42" s="256"/>
-      <c r="I42" s="256"/>
-      <c r="J42" s="257"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="257"/>
+      <c r="I42" s="257"/>
+      <c r="J42" s="258"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="220" t="s">
+      <c r="T42" s="274" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="221"/>
-      <c r="V42" s="221"/>
-      <c r="W42" s="221"/>
-      <c r="X42" s="221"/>
-      <c r="Y42" s="221"/>
-      <c r="Z42" s="221"/>
-      <c r="AA42" s="221"/>
-      <c r="AB42" s="221"/>
-      <c r="AC42" s="222"/>
-    </row>
-    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U42" s="275"/>
+      <c r="V42" s="275"/>
+      <c r="W42" s="275"/>
+      <c r="X42" s="275"/>
+      <c r="Y42" s="275"/>
+      <c r="Z42" s="275"/>
+      <c r="AA42" s="275"/>
+      <c r="AB42" s="275"/>
+      <c r="AC42" s="276"/>
+    </row>
+    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1">
       <c r="B43" s="2">
         <v>7</v>
       </c>
@@ -7512,32 +7586,32 @@
       <c r="F43" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="G43" s="206" t="s">
+      <c r="G43" s="209" t="s">
         <v>330</v>
       </c>
-      <c r="H43" s="207"/>
-      <c r="I43" s="207"/>
-      <c r="J43" s="208"/>
+      <c r="H43" s="245"/>
+      <c r="I43" s="245"/>
+      <c r="J43" s="210"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="220" t="s">
+      <c r="T43" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="221"/>
-      <c r="V43" s="221"/>
-      <c r="W43" s="221"/>
-      <c r="X43" s="221"/>
-      <c r="Y43" s="221"/>
-      <c r="Z43" s="221"/>
-      <c r="AA43" s="221"/>
-      <c r="AB43" s="221"/>
-      <c r="AC43" s="222"/>
-    </row>
-    <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U43" s="275"/>
+      <c r="V43" s="275"/>
+      <c r="W43" s="275"/>
+      <c r="X43" s="275"/>
+      <c r="Y43" s="275"/>
+      <c r="Z43" s="275"/>
+      <c r="AA43" s="275"/>
+      <c r="AB43" s="275"/>
+      <c r="AC43" s="276"/>
+    </row>
+    <row r="44" spans="2:29" ht="45.75" thickBot="1">
       <c r="B44" s="2">
         <v>8</v>
       </c>
@@ -7556,23 +7630,23 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="246" t="s">
+      <c r="S44" s="316" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="248" t="s">
+      <c r="T44" s="318" t="s">
         <v>332</v>
       </c>
-      <c r="U44" s="249"/>
-      <c r="V44" s="249"/>
-      <c r="W44" s="249"/>
-      <c r="X44" s="249"/>
-      <c r="Y44" s="249"/>
-      <c r="Z44" s="249"/>
-      <c r="AA44" s="249"/>
-      <c r="AB44" s="249"/>
-      <c r="AC44" s="250"/>
-    </row>
-    <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U44" s="319"/>
+      <c r="V44" s="319"/>
+      <c r="W44" s="319"/>
+      <c r="X44" s="319"/>
+      <c r="Y44" s="319"/>
+      <c r="Z44" s="319"/>
+      <c r="AA44" s="319"/>
+      <c r="AB44" s="319"/>
+      <c r="AC44" s="320"/>
+    </row>
+    <row r="45" spans="2:29" ht="30.75" customHeight="1">
       <c r="B45" s="2">
         <v>9</v>
       </c>
@@ -7588,28 +7662,28 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="254" t="s">
+      <c r="G45" s="250" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="215"/>
-      <c r="I45" s="215"/>
-      <c r="J45" s="216"/>
+      <c r="H45" s="251"/>
+      <c r="I45" s="251"/>
+      <c r="J45" s="252"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="247"/>
-      <c r="T45" s="251"/>
-      <c r="U45" s="252"/>
-      <c r="V45" s="252"/>
-      <c r="W45" s="252"/>
-      <c r="X45" s="252"/>
-      <c r="Y45" s="252"/>
-      <c r="Z45" s="252"/>
-      <c r="AA45" s="252"/>
-      <c r="AB45" s="252"/>
-      <c r="AC45" s="253"/>
-    </row>
-    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S45" s="317"/>
+      <c r="T45" s="321"/>
+      <c r="U45" s="322"/>
+      <c r="V45" s="322"/>
+      <c r="W45" s="322"/>
+      <c r="X45" s="322"/>
+      <c r="Y45" s="322"/>
+      <c r="Z45" s="322"/>
+      <c r="AA45" s="322"/>
+      <c r="AB45" s="322"/>
+      <c r="AC45" s="323"/>
+    </row>
+    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1">
       <c r="B46" s="2">
         <v>10</v>
       </c>
@@ -7625,30 +7699,30 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="255"/>
-      <c r="H46" s="256"/>
-      <c r="I46" s="256"/>
-      <c r="J46" s="257"/>
+      <c r="G46" s="256"/>
+      <c r="H46" s="257"/>
+      <c r="I46" s="257"/>
+      <c r="J46" s="258"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="217" t="s">
+      <c r="T46" s="294" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="218"/>
-      <c r="V46" s="218"/>
-      <c r="W46" s="218"/>
-      <c r="X46" s="218"/>
-      <c r="Y46" s="218"/>
-      <c r="Z46" s="218"/>
-      <c r="AA46" s="218"/>
-      <c r="AB46" s="218"/>
-      <c r="AC46" s="219"/>
-    </row>
-    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U46" s="295"/>
+      <c r="V46" s="295"/>
+      <c r="W46" s="295"/>
+      <c r="X46" s="295"/>
+      <c r="Y46" s="295"/>
+      <c r="Z46" s="295"/>
+      <c r="AA46" s="295"/>
+      <c r="AB46" s="295"/>
+      <c r="AC46" s="296"/>
+    </row>
+    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1">
       <c r="B47" s="2">
         <v>11</v>
       </c>
@@ -7664,14 +7738,14 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="207" t="s">
+      <c r="G47" s="245" t="s">
         <v>334</v>
       </c>
-      <c r="H47" s="207"/>
-      <c r="I47" s="207"/>
-      <c r="J47" s="208"/>
-    </row>
-    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="210"/>
+    </row>
+    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1">
       <c r="B48" s="2">
         <v>12</v>
       </c>
@@ -7714,13 +7788,13 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="319" t="s">
+      <c r="AA48" s="203" t="s">
         <v>336</v>
       </c>
-      <c r="AB48" s="320"/>
-      <c r="AC48" s="321"/>
-    </row>
-    <row r="49" spans="2:29" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AB48" s="204"/>
+      <c r="AC48" s="205"/>
+    </row>
+    <row r="49" spans="2:29" ht="35.25" customHeight="1" thickBot="1">
       <c r="B49" s="2">
         <v>13</v>
       </c>
@@ -7736,12 +7810,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="254" t="s">
+      <c r="G49" s="250" t="s">
         <v>338</v>
       </c>
-      <c r="H49" s="215"/>
-      <c r="I49" s="215"/>
-      <c r="J49" s="216"/>
+      <c r="H49" s="251"/>
+      <c r="I49" s="251"/>
+      <c r="J49" s="252"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -7757,11 +7831,11 @@
       <c r="Z49" s="80" t="s">
         <v>298</v>
       </c>
-      <c r="AA49" s="322"/>
-      <c r="AB49" s="323"/>
-      <c r="AC49" s="324"/>
-    </row>
-    <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AA49" s="206"/>
+      <c r="AB49" s="207"/>
+      <c r="AC49" s="208"/>
+    </row>
+    <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1">
       <c r="B50" s="2">
         <v>14</v>
       </c>
@@ -7777,12 +7851,12 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="258"/>
-      <c r="H50" s="259"/>
-      <c r="I50" s="259"/>
-      <c r="J50" s="260"/>
-    </row>
-    <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G50" s="253"/>
+      <c r="H50" s="254"/>
+      <c r="I50" s="254"/>
+      <c r="J50" s="255"/>
+    </row>
+    <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1">
       <c r="B51" s="4">
         <v>15</v>
       </c>
@@ -7798,470 +7872,547 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="255"/>
-      <c r="H51" s="256"/>
-      <c r="I51" s="256"/>
-      <c r="J51" s="257"/>
-      <c r="R51" s="316" t="s">
+      <c r="G51" s="256"/>
+      <c r="H51" s="257"/>
+      <c r="I51" s="257"/>
+      <c r="J51" s="258"/>
+      <c r="R51" s="223" t="s">
         <v>301</v>
       </c>
-      <c r="S51" s="300" t="s">
+      <c r="S51" s="225" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="312" t="s">
+      <c r="T51" s="227" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="312"/>
-      <c r="V51" s="313"/>
-    </row>
-    <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="209" t="s">
+      <c r="U51" s="227"/>
+      <c r="V51" s="228"/>
+    </row>
+    <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B52" s="267" t="s">
         <v>339</v>
       </c>
-      <c r="C52" s="210"/>
-      <c r="D52" s="210"/>
-      <c r="E52" s="210"/>
-      <c r="F52" s="211"/>
-      <c r="R52" s="336"/>
-      <c r="S52" s="318"/>
-      <c r="T52" s="337"/>
-      <c r="U52" s="337"/>
-      <c r="V52" s="338"/>
-    </row>
-    <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="268"/>
+      <c r="D52" s="268"/>
+      <c r="E52" s="268"/>
+      <c r="F52" s="269"/>
+      <c r="R52" s="224"/>
+      <c r="S52" s="226"/>
+      <c r="T52" s="229"/>
+      <c r="U52" s="229"/>
+      <c r="V52" s="230"/>
+    </row>
+    <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1">
       <c r="R53" s="165" t="s">
         <v>195</v>
       </c>
       <c r="S53" s="166" t="s">
         <v>302</v>
       </c>
-      <c r="T53" s="331" t="s">
+      <c r="T53" s="218" t="s">
         <v>340</v>
       </c>
-      <c r="U53" s="331"/>
-      <c r="V53" s="332"/>
-    </row>
-    <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="302" t="s">
+      <c r="U53" s="218"/>
+      <c r="V53" s="219"/>
+    </row>
+    <row r="54" spans="2:29" ht="36.75" customHeight="1">
+      <c r="B54" s="261" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="300" t="s">
+      <c r="C54" s="225" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="312" t="s">
+      <c r="D54" s="227" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="313"/>
-      <c r="H54" s="316" t="s">
+      <c r="E54" s="228"/>
+      <c r="H54" s="223" t="s">
         <v>292</v>
       </c>
-      <c r="I54" s="300" t="s">
+      <c r="I54" s="225" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="325" t="s">
+      <c r="J54" s="211" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="326"/>
-      <c r="L54" s="327"/>
+      <c r="K54" s="212"/>
+      <c r="L54" s="213"/>
       <c r="R54" s="163" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="161" t="s">
         <v>303</v>
       </c>
-      <c r="T54" s="339" t="s">
+      <c r="T54" s="231" t="s">
         <v>309</v>
       </c>
-      <c r="U54" s="339"/>
-      <c r="V54" s="305"/>
-    </row>
-    <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="303"/>
-      <c r="C55" s="301"/>
-      <c r="D55" s="314"/>
-      <c r="E55" s="315"/>
-      <c r="H55" s="317"/>
-      <c r="I55" s="318"/>
-      <c r="J55" s="291"/>
-      <c r="K55" s="328"/>
-      <c r="L55" s="329"/>
+      <c r="U54" s="231"/>
+      <c r="V54" s="232"/>
+    </row>
+    <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1">
+      <c r="B55" s="262"/>
+      <c r="C55" s="260"/>
+      <c r="D55" s="246"/>
+      <c r="E55" s="247"/>
+      <c r="H55" s="259"/>
+      <c r="I55" s="226"/>
+      <c r="J55" s="214"/>
+      <c r="K55" s="215"/>
+      <c r="L55" s="216"/>
       <c r="R55" s="163" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="161" t="s">
         <v>304</v>
       </c>
-      <c r="T55" s="339" t="s">
+      <c r="T55" s="231" t="s">
         <v>341</v>
       </c>
-      <c r="U55" s="339"/>
-      <c r="V55" s="305"/>
-    </row>
-    <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U55" s="231"/>
+      <c r="V55" s="232"/>
+    </row>
+    <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1">
       <c r="B56" s="81">
         <v>0</v>
       </c>
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="223" t="s">
+      <c r="D56" s="248" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="225"/>
+      <c r="E56" s="249"/>
       <c r="H56" s="81" t="s">
         <v>295</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="J56" s="330" t="s">
+      <c r="J56" s="217" t="s">
         <v>293</v>
       </c>
-      <c r="K56" s="331"/>
-      <c r="L56" s="332"/>
-      <c r="M56" s="206" t="s">
+      <c r="K56" s="218"/>
+      <c r="L56" s="219"/>
+      <c r="M56" s="209" t="s">
         <v>342</v>
       </c>
-      <c r="N56" s="208"/>
+      <c r="N56" s="210"/>
       <c r="R56" s="163" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="161" t="s">
         <v>305</v>
       </c>
-      <c r="T56" s="339" t="s">
+      <c r="T56" s="231" t="s">
         <v>343</v>
       </c>
-      <c r="U56" s="339"/>
-      <c r="V56" s="305"/>
-    </row>
-    <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U56" s="231"/>
+      <c r="V56" s="232"/>
+    </row>
+    <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1">
       <c r="B57" s="82">
         <v>1</v>
       </c>
       <c r="C57" s="85" t="s">
         <v>288</v>
       </c>
-      <c r="D57" s="304" t="s">
+      <c r="D57" s="242" t="s">
         <v>289</v>
       </c>
-      <c r="E57" s="305"/>
-      <c r="F57" s="206" t="s">
+      <c r="E57" s="232"/>
+      <c r="F57" s="209" t="s">
         <v>344</v>
       </c>
-      <c r="G57" s="208"/>
+      <c r="G57" s="210"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>294</v>
       </c>
-      <c r="J57" s="333" t="s">
+      <c r="J57" s="220" t="s">
         <v>345</v>
       </c>
-      <c r="K57" s="334"/>
-      <c r="L57" s="335"/>
+      <c r="K57" s="221"/>
+      <c r="L57" s="222"/>
       <c r="R57" s="163" t="s">
         <v>229</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="T57" s="339" t="s">
+      <c r="T57" s="231" t="s">
         <v>346</v>
       </c>
-      <c r="U57" s="339"/>
-      <c r="V57" s="305"/>
-    </row>
-    <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U57" s="231"/>
+      <c r="V57" s="232"/>
+    </row>
+    <row r="58" spans="2:29" ht="60" customHeight="1">
       <c r="B58" s="82">
         <v>2</v>
       </c>
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="304" t="s">
+      <c r="D58" s="242" t="s">
         <v>347</v>
       </c>
-      <c r="E58" s="305"/>
+      <c r="E58" s="232"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>348</v>
       </c>
-      <c r="J58" s="333" t="s">
+      <c r="J58" s="220" t="s">
         <v>349</v>
       </c>
-      <c r="K58" s="334"/>
-      <c r="L58" s="335"/>
+      <c r="K58" s="221"/>
+      <c r="L58" s="222"/>
       <c r="R58" s="163" t="s">
         <v>230</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="T58" s="339" t="s">
+      <c r="T58" s="231" t="s">
         <v>350</v>
       </c>
-      <c r="U58" s="339"/>
-      <c r="V58" s="305"/>
-    </row>
-    <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U58" s="231"/>
+      <c r="V58" s="232"/>
+    </row>
+    <row r="59" spans="2:29" ht="61.5" customHeight="1">
       <c r="B59" s="82">
         <v>3</v>
       </c>
       <c r="C59" s="85" t="s">
         <v>351</v>
       </c>
-      <c r="D59" s="304" t="s">
+      <c r="D59" s="242" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="305"/>
+      <c r="E59" s="232"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>291</v>
       </c>
-      <c r="J59" s="333" t="s">
+      <c r="J59" s="220" t="s">
         <v>352</v>
       </c>
-      <c r="K59" s="334"/>
-      <c r="L59" s="335"/>
+      <c r="K59" s="221"/>
+      <c r="L59" s="222"/>
       <c r="R59" s="163" t="s">
         <v>231</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="T59" s="339" t="s">
+      <c r="T59" s="231" t="s">
         <v>353</v>
       </c>
-      <c r="U59" s="339"/>
-      <c r="V59" s="305"/>
+      <c r="U59" s="231"/>
+      <c r="V59" s="232"/>
       <c r="X59" s="167"/>
     </row>
-    <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:29" ht="45.75" customHeight="1">
       <c r="B60" s="82">
         <v>4</v>
       </c>
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="304" t="s">
+      <c r="D60" s="242" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="305"/>
+      <c r="E60" s="232"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="J60" s="333" t="s">
+      <c r="J60" s="220" t="s">
         <v>311</v>
       </c>
-      <c r="K60" s="334"/>
-      <c r="L60" s="335"/>
+      <c r="K60" s="221"/>
+      <c r="L60" s="222"/>
       <c r="R60" s="163" t="s">
         <v>232</v>
       </c>
       <c r="S60" s="161" t="s">
         <v>308</v>
       </c>
-      <c r="T60" s="340" t="s">
+      <c r="T60" s="233" t="s">
         <v>355</v>
       </c>
-      <c r="U60" s="341"/>
-      <c r="V60" s="342"/>
-    </row>
-    <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U60" s="234"/>
+      <c r="V60" s="235"/>
+    </row>
+    <row r="61" spans="2:29" ht="40.5" customHeight="1">
       <c r="B61" s="82">
         <v>5</v>
       </c>
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="304" t="s">
+      <c r="D61" s="242" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="305"/>
+      <c r="E61" s="232"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="333"/>
-      <c r="K61" s="334"/>
-      <c r="L61" s="335"/>
+      <c r="J61" s="220"/>
+      <c r="K61" s="221"/>
+      <c r="L61" s="222"/>
       <c r="R61" s="163" t="s">
         <v>233</v>
       </c>
       <c r="S61" s="161" t="s">
         <v>308</v>
       </c>
-      <c r="T61" s="343"/>
-      <c r="U61" s="230"/>
-      <c r="V61" s="231"/>
-    </row>
-    <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T61" s="236"/>
+      <c r="U61" s="237"/>
+      <c r="V61" s="238"/>
+    </row>
+    <row r="62" spans="2:29" ht="53.25" customHeight="1">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="304"/>
-      <c r="E62" s="305"/>
+      <c r="D62" s="242"/>
+      <c r="E62" s="232"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="333"/>
-      <c r="K62" s="334"/>
-      <c r="L62" s="335"/>
+      <c r="J62" s="220"/>
+      <c r="K62" s="221"/>
+      <c r="L62" s="222"/>
       <c r="R62" s="163" t="s">
         <v>265</v>
       </c>
       <c r="S62" s="161" t="s">
         <v>308</v>
       </c>
-      <c r="T62" s="343"/>
-      <c r="U62" s="230"/>
-      <c r="V62" s="231"/>
-    </row>
-    <row r="63" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T62" s="236"/>
+      <c r="U62" s="237"/>
+      <c r="V62" s="238"/>
+    </row>
+    <row r="63" spans="2:29" ht="36" customHeight="1" thickBot="1">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="304"/>
-      <c r="E63" s="305"/>
+      <c r="D63" s="242"/>
+      <c r="E63" s="232"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="333"/>
-      <c r="K63" s="334"/>
-      <c r="L63" s="335"/>
+      <c r="J63" s="220"/>
+      <c r="K63" s="221"/>
+      <c r="L63" s="222"/>
       <c r="R63" s="164" t="s">
         <v>354</v>
       </c>
       <c r="S63" s="162" t="s">
         <v>308</v>
       </c>
-      <c r="T63" s="344"/>
-      <c r="U63" s="233"/>
-      <c r="V63" s="234"/>
-    </row>
-    <row r="64" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T63" s="239"/>
+      <c r="U63" s="240"/>
+      <c r="V63" s="241"/>
+    </row>
+    <row r="64" spans="2:29" ht="40.5" customHeight="1">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="304"/>
-      <c r="E64" s="305"/>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="242"/>
+      <c r="E64" s="232"/>
+    </row>
+    <row r="65" spans="2:5">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="304"/>
-      <c r="E65" s="305"/>
-    </row>
-    <row r="66" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="242"/>
+      <c r="E65" s="232"/>
+    </row>
+    <row r="66" spans="2:5" ht="30" customHeight="1">
       <c r="B66" s="82">
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="304"/>
-      <c r="E66" s="305"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D66" s="242"/>
+      <c r="E66" s="232"/>
+    </row>
+    <row r="67" spans="2:5">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="304"/>
-      <c r="E67" s="305"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D67" s="242"/>
+      <c r="E67" s="232"/>
+    </row>
+    <row r="68" spans="2:5">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="304"/>
-      <c r="E68" s="305"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D68" s="242"/>
+      <c r="E68" s="232"/>
+    </row>
+    <row r="69" spans="2:5">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="304"/>
-      <c r="E69" s="305"/>
-    </row>
-    <row r="70" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D69" s="242"/>
+      <c r="E69" s="232"/>
+    </row>
+    <row r="70" spans="2:5" ht="30" customHeight="1">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="304"/>
-      <c r="E70" s="305"/>
-    </row>
-    <row r="71" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="242"/>
+      <c r="E70" s="232"/>
+    </row>
+    <row r="71" spans="2:5" ht="15.75" thickBot="1">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="310"/>
-      <c r="E71" s="311"/>
-    </row>
-    <row r="75" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D71" s="243"/>
+      <c r="E71" s="244"/>
+    </row>
+    <row r="75" spans="2:5" ht="72" customHeight="1"/>
   </sheetData>
-  <mergeCells count="183">
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
+  <mergeCells count="187">
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="D57:E57"/>
@@ -8286,128 +8437,55 @@
     <mergeCell ref="N20:P20"/>
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="AA5:AB20 U5:V20 U22:V22 V21 U24:V28 V23 AA25:AB28 AB21 AB22 AB23 AB24" numberStoredAsText="1"/>
+    <ignoredError sqref="AA5:AB20 U5:V20 V22 V21 U24:V28 V23 AA25:AB28 AB21 AB22 AB23 AB24" numberStoredAsText="1"/>
     <ignoredError sqref="D30" formula="1"/>
   </ignoredErrors>
 </worksheet>
@@ -8416,7 +8494,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CBBBEA-E421-4197-9F44-CA2E8EC0215F}">
   <dimension ref="B1:AB33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -8438,8 +8516,8 @@
     <col min="26" max="28" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:28" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1">
       <c r="B2" s="194" t="s">
         <v>358</v>
       </c>
@@ -8455,37 +8533,37 @@
       <c r="F2" s="188" t="s">
         <v>361</v>
       </c>
-      <c r="G2" s="215" t="s">
+      <c r="G2" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
-      <c r="J2" s="216"/>
-      <c r="L2" s="238" t="s">
+      <c r="H2" s="251"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="252"/>
+      <c r="L2" s="338" t="s">
         <v>276</v>
       </c>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="240"/>
+      <c r="M2" s="339"/>
+      <c r="N2" s="339"/>
+      <c r="O2" s="340"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="241" t="s">
+      <c r="Q2" s="341" t="s">
         <v>238</v>
       </c>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="243"/>
+      <c r="R2" s="342"/>
+      <c r="S2" s="342"/>
+      <c r="T2" s="343"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="235" t="s">
+      <c r="V2" s="335" t="s">
         <v>261</v>
       </c>
-      <c r="W2" s="236"/>
-      <c r="X2" s="236"/>
-      <c r="Y2" s="236"/>
-      <c r="Z2" s="236"/>
-      <c r="AA2" s="236"/>
-      <c r="AB2" s="237"/>
-    </row>
-    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W2" s="336"/>
+      <c r="X2" s="336"/>
+      <c r="Y2" s="336"/>
+      <c r="Z2" s="336"/>
+      <c r="AA2" s="336"/>
+      <c r="AB2" s="337"/>
+    </row>
+    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
       <c r="B3" s="195" t="s">
         <v>362</v>
       </c>
@@ -8504,11 +8582,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="223" t="s">
+      <c r="H3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
+      <c r="I3" s="290"/>
+      <c r="J3" s="249"/>
       <c r="L3" s="126" t="s">
         <v>224</v>
       </c>
@@ -8547,13 +8625,13 @@
       <c r="Y3" s="152" t="s">
         <v>227</v>
       </c>
-      <c r="Z3" s="226" t="s">
+      <c r="Z3" s="330" t="s">
         <v>266</v>
       </c>
-      <c r="AA3" s="227"/>
-      <c r="AB3" s="228"/>
-    </row>
-    <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA3" s="331"/>
+      <c r="AB3" s="332"/>
+    </row>
+    <row r="4" spans="2:28" ht="53.25" customHeight="1">
       <c r="B4" s="196" t="s">
         <v>367</v>
       </c>
@@ -8572,11 +8650,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="220">
+      <c r="H4" s="274">
         <v>63</v>
       </c>
-      <c r="I4" s="221"/>
-      <c r="J4" s="222"/>
+      <c r="I4" s="275"/>
+      <c r="J4" s="276"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -8615,13 +8693,13 @@
       <c r="Y4" s="119" t="s">
         <v>264</v>
       </c>
-      <c r="Z4" s="229" t="s">
+      <c r="Z4" s="333" t="s">
         <v>424</v>
       </c>
-      <c r="AA4" s="230"/>
-      <c r="AB4" s="231"/>
-    </row>
-    <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA4" s="237"/>
+      <c r="AB4" s="238"/>
+    </row>
+    <row r="5" spans="2:28" ht="47.25" customHeight="1">
       <c r="B5" s="197" t="s">
         <v>372</v>
       </c>
@@ -8640,11 +8718,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="220">
+      <c r="H5" s="274">
         <v>31</v>
       </c>
-      <c r="I5" s="221"/>
-      <c r="J5" s="222"/>
+      <c r="I5" s="275"/>
+      <c r="J5" s="276"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -8683,11 +8761,11 @@
       <c r="Y5" s="116" t="s">
         <v>241</v>
       </c>
-      <c r="Z5" s="229"/>
-      <c r="AA5" s="230"/>
-      <c r="AB5" s="231"/>
-    </row>
-    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z5" s="333"/>
+      <c r="AA5" s="237"/>
+      <c r="AB5" s="238"/>
+    </row>
+    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
       <c r="B6" s="196" t="s">
         <v>376</v>
       </c>
@@ -8706,11 +8784,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="217">
+      <c r="H6" s="294">
         <v>7</v>
       </c>
-      <c r="I6" s="218"/>
-      <c r="J6" s="219"/>
+      <c r="I6" s="295"/>
+      <c r="J6" s="296"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -8749,11 +8827,11 @@
       <c r="Y6" s="125" t="s">
         <v>263</v>
       </c>
-      <c r="Z6" s="232"/>
-      <c r="AA6" s="233"/>
-      <c r="AB6" s="234"/>
-    </row>
-    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z6" s="334"/>
+      <c r="AA6" s="240"/>
+      <c r="AB6" s="241"/>
+    </row>
+    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1">
       <c r="B7" s="197" t="s">
         <v>380</v>
       </c>
@@ -8772,12 +8850,12 @@
       <c r="G7" s="87" t="s">
         <v>223</v>
       </c>
-      <c r="H7" s="212" t="str">
+      <c r="H7" s="347" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="213"/>
-      <c r="J7" s="214"/>
+      <c r="I7" s="348"/>
+      <c r="J7" s="349"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -8805,7 +8883,7 @@
       </c>
       <c r="U7" s="114"/>
     </row>
-    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
       <c r="B8" s="196" t="s">
         <v>384</v>
       </c>
@@ -8824,18 +8902,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="212" t="str">
+      <c r="H8" s="347" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="213"/>
-      <c r="J8" s="214"/>
-      <c r="L8" s="206" t="s">
+      <c r="I8" s="348"/>
+      <c r="J8" s="349"/>
+      <c r="L8" s="209" t="s">
         <v>420</v>
       </c>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="208"/>
+      <c r="M8" s="245"/>
+      <c r="N8" s="245"/>
+      <c r="O8" s="210"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>233</v>
@@ -8854,7 +8932,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1">
       <c r="B9" s="196" t="s">
         <v>388</v>
       </c>
@@ -8889,7 +8967,7 @@
       </c>
       <c r="U9" s="114"/>
     </row>
-    <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1">
       <c r="B10" s="196" t="s">
         <v>393</v>
       </c>
@@ -8916,7 +8994,7 @@
       <c r="P10" s="114"/>
       <c r="U10" s="114"/>
     </row>
-    <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1">
       <c r="B11" s="196" t="s">
         <v>397</v>
       </c>
@@ -8941,15 +9019,15 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="203" t="s">
+      <c r="Q11" s="344" t="s">
         <v>260</v>
       </c>
-      <c r="R11" s="204"/>
-      <c r="S11" s="204"/>
-      <c r="T11" s="205"/>
+      <c r="R11" s="345"/>
+      <c r="S11" s="345"/>
+      <c r="T11" s="346"/>
       <c r="U11" s="114"/>
     </row>
-    <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1">
       <c r="B12" s="196" t="s">
         <v>401</v>
       </c>
@@ -8986,7 +9064,7 @@
       </c>
       <c r="U12" s="114"/>
     </row>
-    <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:28" ht="47.25" customHeight="1">
       <c r="B13" s="196" t="s">
         <v>404</v>
       </c>
@@ -9023,7 +9101,7 @@
       </c>
       <c r="U13" s="114"/>
     </row>
-    <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:28" ht="47.25" customHeight="1">
       <c r="B14" s="196" t="s">
         <v>407</v>
       </c>
@@ -9060,7 +9138,7 @@
       </c>
       <c r="U14" s="114"/>
     </row>
-    <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:28" ht="69" customHeight="1">
       <c r="B15" s="196" t="s">
         <v>410</v>
       </c>
@@ -9097,7 +9175,7 @@
       </c>
       <c r="U15" s="114"/>
     </row>
-    <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:28" ht="62.25" customHeight="1">
       <c r="B16" s="196" t="s">
         <v>413</v>
       </c>
@@ -9124,7 +9202,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" ht="69.75" customHeight="1" thickBot="1">
       <c r="B17" s="198" t="s">
         <v>416</v>
       </c>
@@ -9151,8 +9229,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" ht="51.75" customHeight="1" thickBot="1"/>
+    <row r="19" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B19" s="102" t="s">
         <v>178</v>
       </c>
@@ -9168,14 +9246,14 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="209" t="s">
+      <c r="G19" s="267" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="210"/>
-      <c r="I19" s="210"/>
-      <c r="J19" s="211"/>
-    </row>
-    <row r="20" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="268"/>
+      <c r="I19" s="268"/>
+      <c r="J19" s="269"/>
+    </row>
+    <row r="20" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B20" s="170" t="s">
         <v>183</v>
       </c>
@@ -9198,7 +9276,7 @@
       <c r="I20" s="175"/>
       <c r="J20" s="176"/>
     </row>
-    <row r="21" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B21" s="177"/>
       <c r="C21" s="178"/>
       <c r="D21" s="94" t="s">
@@ -9217,7 +9295,7 @@
       <c r="I21" s="172"/>
       <c r="J21" s="173"/>
     </row>
-    <row r="22" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B22" s="171"/>
       <c r="C22" s="169"/>
       <c r="D22" s="99" t="s">
@@ -9234,7 +9312,7 @@
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:20" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" ht="51.75" customHeight="1">
       <c r="B23" s="170" t="s">
         <v>193</v>
       </c>
@@ -9255,7 +9333,7 @@
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B24" s="171"/>
       <c r="C24" s="169"/>
       <c r="D24" s="99" t="s">
@@ -9272,7 +9350,7 @@
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="2:20" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" ht="51.75" customHeight="1">
       <c r="B25" s="170" t="s">
         <v>199</v>
       </c>
@@ -9293,7 +9371,7 @@
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B26" s="171"/>
       <c r="C26" s="169"/>
       <c r="D26" s="99" t="s">
@@ -9310,7 +9388,7 @@
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="2:20" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" ht="51.75" customHeight="1">
       <c r="B27" s="170" t="s">
         <v>204</v>
       </c>
@@ -9331,7 +9409,7 @@
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B28" s="171"/>
       <c r="C28" s="169"/>
       <c r="D28" s="99" t="s">
@@ -9348,7 +9426,7 @@
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="2:20" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
       <c r="B29" s="113" t="s">
         <v>208</v>
       </c>
@@ -9369,7 +9447,7 @@
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="2:20" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" ht="51.75" customHeight="1">
       <c r="B30" s="170" t="s">
         <v>187</v>
       </c>
@@ -9390,7 +9468,7 @@
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="2:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" ht="45.75" thickBot="1">
       <c r="B31" s="171"/>
       <c r="C31" s="169"/>
       <c r="D31" s="99" t="s">
@@ -9407,7 +9485,7 @@
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" ht="30">
       <c r="B32" s="170" t="s">
         <v>215</v>
       </c>
@@ -9428,7 +9506,7 @@
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
     </row>
-    <row r="33" spans="2:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" ht="57.75" thickBot="1">
       <c r="B33" s="171"/>
       <c r="C33" s="169"/>
       <c r="D33" s="99" t="s">
@@ -9447,11 +9525,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="V2:AB2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="Q2:T2"/>
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="L8:O8"/>
     <mergeCell ref="G19:J19"/>
@@ -9462,6 +9535,11 @@
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H7:J7"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="Z4:AB6"/>
+    <mergeCell ref="V2:AB2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="Q2:T2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204BA701-971E-45EE-A0A3-12A58EC657BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DDF818-0A77-4FDB-871D-E243F8A19FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
     <sheet name="MMIO" sheetId="2" r:id="rId2"/>
+    <sheet name="Perif Code" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="459">
   <si>
     <t>OpCode</t>
   </si>
@@ -824,9 +825,6 @@
   </si>
   <si>
     <t>Revision ID &amp; Class Code</t>
-  </si>
-  <si>
-    <t>Base-Sub-Prog IF-Revision</t>
   </si>
   <si>
     <t>00-00-00-00</t>
@@ -1109,9 +1107,6 @@
     <t>Notas:</t>
   </si>
   <si>
-    <t>,</t>
-  </si>
-  <si>
     <t>Bits para habilitar/deshabilitar características y Banderas de estado</t>
   </si>
   <si>
@@ -2283,6 +2278,108 @@
   <si>
     <t>Instrucción</t>
   </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t>TTY Controller</t>
+  </si>
+  <si>
+    <t>Dato 1</t>
+  </si>
+  <si>
+    <t>Dato 2</t>
+  </si>
+  <si>
+    <t>Dato 3</t>
+  </si>
+  <si>
+    <t>Descrip</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>Write_Addr</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>No hace nada (Estado por defecto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borra X cantidad de espacios </t>
+  </si>
+  <si>
+    <t>Limpia toda la pantalla</t>
+  </si>
+  <si>
+    <t>Letra</t>
+  </si>
+  <si>
+    <t>Escribe una letra X cantidad de veces</t>
+  </si>
+  <si>
+    <t>Cant</t>
+  </si>
+  <si>
+    <t>Addr</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribe los bytes de la direccion dicha </t>
+  </si>
+  <si>
+    <t>Comand</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Enable TTY</t>
+  </si>
+  <si>
+    <t>Enable DMA</t>
+  </si>
+  <si>
+    <t>Busy</t>
+  </si>
+  <si>
+    <t>Invalid Command</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>DMA Not Allowed</t>
+  </si>
+  <si>
+    <t>Devices</t>
+  </si>
+  <si>
+    <t>Descrpción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Bridges. Fuera del Root Complex </t>
+  </si>
+  <si>
+    <t>Root Complex Bridges</t>
+  </si>
+  <si>
+    <t>Base-Sub-Prog IF-Header Type</t>
+  </si>
 </sst>
 </file>
 
@@ -2291,7 +2388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2386,7 +2483,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2441,6 +2538,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="77">
     <border>
@@ -3405,7 +3508,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="350">
+  <cellXfs count="431">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3866,9 +3969,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3908,551 +4008,777 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="73" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4736,7 +5062,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AI75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
     <col min="2" max="2" width="19.85546875" style="15" customWidth="1"/>
@@ -4772,64 +5098,64 @@
     <col min="36" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:35" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B2" s="291" t="s">
+    <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="352" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="306" t="s">
+      <c r="C2" s="364" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="307"/>
-      <c r="E2" s="308" t="s">
+      <c r="D2" s="365"/>
+      <c r="E2" s="366" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="308"/>
-      <c r="G2" s="309" t="s">
+      <c r="F2" s="366"/>
+      <c r="G2" s="367" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="308"/>
-      <c r="I2" s="308" t="s">
+      <c r="H2" s="366"/>
+      <c r="I2" s="366" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="308"/>
-      <c r="K2" s="310" t="s">
+      <c r="J2" s="366"/>
+      <c r="K2" s="368" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="308"/>
-      <c r="M2" s="308"/>
-      <c r="N2" s="308"/>
-      <c r="O2" s="308"/>
-      <c r="P2" s="311"/>
-      <c r="R2" s="287" t="s">
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
+      <c r="N2" s="366"/>
+      <c r="O2" s="366"/>
+      <c r="P2" s="369"/>
+      <c r="R2" s="349" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="285" t="s">
+      <c r="S2" s="347" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="278" t="s">
+      <c r="T2" s="340" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="279"/>
-      <c r="AA2" s="279"/>
-      <c r="AB2" s="279" t="s">
+      <c r="U2" s="341"/>
+      <c r="V2" s="341"/>
+      <c r="W2" s="341"/>
+      <c r="X2" s="341"/>
+      <c r="Y2" s="341"/>
+      <c r="Z2" s="341"/>
+      <c r="AA2" s="341"/>
+      <c r="AB2" s="341" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="279"/>
-      <c r="AD2" s="279"/>
-      <c r="AE2" s="279"/>
-      <c r="AF2" s="279"/>
-      <c r="AG2" s="279"/>
-      <c r="AH2" s="279"/>
-      <c r="AI2" s="280"/>
-    </row>
-    <row r="3" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B3" s="292"/>
+      <c r="AC2" s="341"/>
+      <c r="AD2" s="341"/>
+      <c r="AE2" s="341"/>
+      <c r="AF2" s="341"/>
+      <c r="AG2" s="341"/>
+      <c r="AH2" s="341"/>
+      <c r="AI2" s="342"/>
+    </row>
+    <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="353"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -4854,21 +5180,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="263"/>
-      <c r="L3" s="305"/>
-      <c r="M3" s="305"/>
-      <c r="N3" s="305"/>
-      <c r="O3" s="305"/>
-      <c r="P3" s="264"/>
-      <c r="R3" s="288"/>
-      <c r="S3" s="214"/>
+      <c r="K3" s="331"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
+      <c r="N3" s="363"/>
+      <c r="O3" s="363"/>
+      <c r="P3" s="332"/>
+      <c r="R3" s="350"/>
+      <c r="S3" s="291"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="315" t="s">
+      <c r="U3" s="373" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="315"/>
+      <c r="V3" s="373"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -4881,10 +5207,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="277" t="s">
+      <c r="AA3" s="339" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="277"/>
+      <c r="AB3" s="339"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -4907,22 +5233,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B4" s="293"/>
+    <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="354"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="281" t="s">
+      <c r="E4" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="269"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="267"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -4932,20 +5258,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="281" t="s">
-        <v>312</v>
-      </c>
-      <c r="O4" s="268"/>
-      <c r="P4" s="269"/>
-      <c r="R4" s="289"/>
-      <c r="S4" s="286"/>
+      <c r="N4" s="343" t="s">
+        <v>310</v>
+      </c>
+      <c r="O4" s="266"/>
+      <c r="P4" s="267"/>
+      <c r="R4" s="351"/>
+      <c r="S4" s="348"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="281" t="s">
+      <c r="U4" s="343" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="282"/>
+      <c r="V4" s="344"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -4958,10 +5284,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="281" t="s">
+      <c r="AA4" s="343" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="282"/>
+      <c r="AB4" s="344"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -4984,7 +5310,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="2:35" ht="15.75" thickBot="1">
+    <row r="5" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>0</v>
       </c>
@@ -4993,22 +5319,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="312"/>
-      <c r="F5" s="313"/>
-      <c r="G5" s="313"/>
-      <c r="H5" s="313"/>
-      <c r="I5" s="313"/>
-      <c r="J5" s="314"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="371"/>
+      <c r="G5" s="371"/>
+      <c r="H5" s="371"/>
+      <c r="I5" s="371"/>
+      <c r="J5" s="372"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="248" t="s">
+      <c r="N5" s="279" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="290"/>
-      <c r="P5" s="249"/>
+      <c r="O5" s="280"/>
+      <c r="P5" s="281"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5018,10 +5344,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="283" t="s">
+      <c r="U5" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="284"/>
+      <c r="V5" s="346"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5034,10 +5360,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="283" t="s">
+      <c r="AA5" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="284"/>
+      <c r="AB5" s="346"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5060,7 +5386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:35" ht="15.75" thickBot="1">
+    <row r="6" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -5069,12 +5395,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="303"/>
-      <c r="F6" s="298"/>
-      <c r="G6" s="298"/>
-      <c r="H6" s="298"/>
-      <c r="I6" s="298"/>
-      <c r="J6" s="299"/>
+      <c r="E6" s="361"/>
+      <c r="F6" s="356"/>
+      <c r="G6" s="356"/>
+      <c r="H6" s="356"/>
+      <c r="I6" s="356"/>
+      <c r="J6" s="357"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5082,11 +5408,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="274" t="s">
-        <v>313</v>
-      </c>
-      <c r="O6" s="275"/>
-      <c r="P6" s="276"/>
+      <c r="N6" s="276" t="s">
+        <v>311</v>
+      </c>
+      <c r="O6" s="277"/>
+      <c r="P6" s="278"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5096,10 +5422,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="270" t="s">
+      <c r="U6" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="271"/>
+      <c r="V6" s="336"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5112,10 +5438,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="270" t="s">
+      <c r="AA6" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="271"/>
+      <c r="AB6" s="336"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5138,12 +5464,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:35" ht="15.75" thickBot="1">
+    <row r="7" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="159" t="s">
-        <v>280</v>
+      <c r="C7" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D7" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5158,9 +5484,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="297"/>
-      <c r="I7" s="298"/>
-      <c r="J7" s="299"/>
+      <c r="H7" s="355"/>
+      <c r="I7" s="356"/>
+      <c r="J7" s="357"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5168,11 +5494,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="274" t="s">
+      <c r="N7" s="276" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="275"/>
-      <c r="P7" s="276"/>
+      <c r="O7" s="277"/>
+      <c r="P7" s="278"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5182,10 +5508,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="270" t="s">
+      <c r="U7" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="271"/>
+      <c r="V7" s="336"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5198,10 +5524,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="270" t="s">
+      <c r="AA7" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="271"/>
+      <c r="AB7" s="336"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5224,12 +5550,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:35" ht="15.75" thickBot="1">
+    <row r="8" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="C8" s="159" t="s">
-        <v>280</v>
+      <c r="C8" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D8" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5244,9 +5570,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="297"/>
-      <c r="I8" s="298"/>
-      <c r="J8" s="299"/>
+      <c r="H8" s="355"/>
+      <c r="I8" s="356"/>
+      <c r="J8" s="357"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5254,11 +5580,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="274" t="s">
+      <c r="N8" s="276" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="275"/>
-      <c r="P8" s="276"/>
+      <c r="O8" s="277"/>
+      <c r="P8" s="278"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5268,10 +5594,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="270" t="s">
+      <c r="U8" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="271"/>
+      <c r="V8" s="336"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5284,10 +5610,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="270" t="s">
+      <c r="AA8" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="271"/>
+      <c r="AB8" s="336"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5310,12 +5636,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:35" ht="15.75" thickBot="1">
+    <row r="9" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="159" t="s">
-        <v>280</v>
+      <c r="C9" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D9" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5330,9 +5656,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="297"/>
-      <c r="I9" s="298"/>
-      <c r="J9" s="299"/>
+      <c r="H9" s="355"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="357"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5340,11 +5666,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="274" t="s">
+      <c r="N9" s="276" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="275"/>
-      <c r="P9" s="276"/>
+      <c r="O9" s="277"/>
+      <c r="P9" s="278"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5354,10 +5680,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="270" t="s">
+      <c r="U9" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="271"/>
+      <c r="V9" s="336"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5370,10 +5696,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="270" t="s">
+      <c r="AA9" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="271"/>
+      <c r="AB9" s="336"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5396,12 +5722,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:35" ht="15.75" thickBot="1">
+    <row r="10" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>5</v>
       </c>
-      <c r="C10" s="159" t="s">
-        <v>280</v>
+      <c r="C10" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D10" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5416,9 +5742,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="297"/>
-      <c r="I10" s="298"/>
-      <c r="J10" s="299"/>
+      <c r="H10" s="355"/>
+      <c r="I10" s="356"/>
+      <c r="J10" s="357"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5426,11 +5752,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="274" t="s">
+      <c r="N10" s="276" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="275"/>
-      <c r="P10" s="276"/>
+      <c r="O10" s="277"/>
+      <c r="P10" s="278"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5440,10 +5766,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="270" t="s">
+      <c r="U10" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="271"/>
+      <c r="V10" s="336"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5456,10 +5782,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="270" t="s">
+      <c r="AA10" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="271"/>
+      <c r="AB10" s="336"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5482,12 +5808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:35" ht="15.75" thickBot="1">
+    <row r="11" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>6</v>
       </c>
-      <c r="C11" s="159" t="s">
-        <v>280</v>
+      <c r="C11" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D11" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5502,9 +5828,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="297"/>
-      <c r="I11" s="298"/>
-      <c r="J11" s="299"/>
+      <c r="H11" s="355"/>
+      <c r="I11" s="356"/>
+      <c r="J11" s="357"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5512,11 +5838,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="274" t="s">
+      <c r="N11" s="276" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="275"/>
-      <c r="P11" s="276"/>
+      <c r="O11" s="277"/>
+      <c r="P11" s="278"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5526,10 +5852,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="270" t="s">
+      <c r="U11" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="271"/>
+      <c r="V11" s="336"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5542,10 +5868,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="270" t="s">
+      <c r="AA11" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="271"/>
+      <c r="AB11" s="336"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5568,12 +5894,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:35" ht="15.75" thickBot="1">
+    <row r="12" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>7</v>
       </c>
-      <c r="C12" s="159" t="s">
-        <v>280</v>
+      <c r="C12" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D12" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5588,9 +5914,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="297"/>
-      <c r="I12" s="298"/>
-      <c r="J12" s="299"/>
+      <c r="H12" s="355"/>
+      <c r="I12" s="356"/>
+      <c r="J12" s="357"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5598,11 +5924,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="274" t="s">
+      <c r="N12" s="276" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="275"/>
-      <c r="P12" s="276"/>
+      <c r="O12" s="277"/>
+      <c r="P12" s="278"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5612,10 +5938,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="270" t="s">
+      <c r="U12" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="271"/>
+      <c r="V12" s="336"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5628,10 +5954,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="270" t="s">
+      <c r="AA12" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="271"/>
+      <c r="AB12" s="336"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -5654,12 +5980,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:35" ht="15.75" thickBot="1">
+    <row r="13" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C13" s="159" t="s">
-        <v>280</v>
+      <c r="C13" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D13" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5674,9 +6000,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="297"/>
-      <c r="I13" s="298"/>
-      <c r="J13" s="299"/>
+      <c r="H13" s="355"/>
+      <c r="I13" s="356"/>
+      <c r="J13" s="357"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -5684,11 +6010,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="274" t="s">
+      <c r="N13" s="276" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="275"/>
-      <c r="P13" s="276"/>
+      <c r="O13" s="277"/>
+      <c r="P13" s="278"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -5698,10 +6024,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="270" t="s">
+      <c r="U13" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="271"/>
+      <c r="V13" s="336"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -5714,10 +6040,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="270" t="s">
+      <c r="AA13" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="271"/>
+      <c r="AB13" s="336"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -5740,12 +6066,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:35" ht="15.75" thickBot="1">
+    <row r="14" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>9</v>
       </c>
-      <c r="C14" s="159" t="s">
-        <v>280</v>
+      <c r="C14" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D14" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5760,9 +6086,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="297"/>
-      <c r="I14" s="298"/>
-      <c r="J14" s="299"/>
+      <c r="H14" s="355"/>
+      <c r="I14" s="356"/>
+      <c r="J14" s="357"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -5770,11 +6096,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="274" t="s">
-        <v>314</v>
-      </c>
-      <c r="O14" s="275"/>
-      <c r="P14" s="276"/>
+      <c r="N14" s="276" t="s">
+        <v>312</v>
+      </c>
+      <c r="O14" s="277"/>
+      <c r="P14" s="278"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -5784,10 +6110,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="270" t="s">
+      <c r="U14" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="271"/>
+      <c r="V14" s="336"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -5800,10 +6126,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="270" t="s">
+      <c r="AA14" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="271"/>
+      <c r="AB14" s="336"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -5826,12 +6152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:35" ht="15.75" thickBot="1">
+    <row r="15" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>10</v>
       </c>
-      <c r="C15" s="159" t="s">
-        <v>280</v>
+      <c r="C15" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D15" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5846,9 +6172,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="297"/>
-      <c r="I15" s="298"/>
-      <c r="J15" s="299"/>
+      <c r="H15" s="355"/>
+      <c r="I15" s="356"/>
+      <c r="J15" s="357"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -5856,11 +6182,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="274" t="s">
-        <v>315</v>
-      </c>
-      <c r="O15" s="275"/>
-      <c r="P15" s="276"/>
+      <c r="N15" s="276" t="s">
+        <v>313</v>
+      </c>
+      <c r="O15" s="277"/>
+      <c r="P15" s="278"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -5870,10 +6196,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="270" t="s">
+      <c r="U15" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="271"/>
+      <c r="V15" s="336"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -5886,10 +6212,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="270" t="s">
+      <c r="AA15" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="271"/>
+      <c r="AB15" s="336"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -5912,12 +6238,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:35" ht="15.75" thickBot="1">
+    <row r="16" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>11</v>
       </c>
-      <c r="C16" s="159" t="s">
-        <v>280</v>
+      <c r="C16" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D16" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5926,21 +6252,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="297"/>
-      <c r="G16" s="298"/>
-      <c r="H16" s="298"/>
-      <c r="I16" s="298"/>
-      <c r="J16" s="299"/>
+      <c r="F16" s="355"/>
+      <c r="G16" s="356"/>
+      <c r="H16" s="356"/>
+      <c r="I16" s="356"/>
+      <c r="J16" s="357"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="274" t="s">
-        <v>316</v>
-      </c>
-      <c r="O16" s="275"/>
-      <c r="P16" s="276"/>
+      <c r="N16" s="276" t="s">
+        <v>314</v>
+      </c>
+      <c r="O16" s="277"/>
+      <c r="P16" s="278"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -5950,10 +6276,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="270" t="s">
+      <c r="U16" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="271"/>
+      <c r="V16" s="336"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -5966,10 +6292,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="270" t="s">
+      <c r="AA16" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="271"/>
+      <c r="AB16" s="336"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -5992,12 +6318,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:35" ht="15.75" thickBot="1">
+    <row r="17" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>12</v>
       </c>
-      <c r="C17" s="159" t="s">
-        <v>281</v>
+      <c r="C17" s="158" t="s">
+        <v>279</v>
       </c>
       <c r="D17" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6007,22 +6333,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="304" t="s">
+      <c r="G17" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="275"/>
-      <c r="I17" s="275"/>
-      <c r="J17" s="276"/>
+      <c r="H17" s="277"/>
+      <c r="I17" s="277"/>
+      <c r="J17" s="278"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="274" t="s">
+      <c r="N17" s="276" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="275"/>
-      <c r="P17" s="276"/>
+      <c r="O17" s="277"/>
+      <c r="P17" s="278"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6032,10 +6358,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="270" t="s">
+      <c r="U17" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="271"/>
+      <c r="V17" s="336"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6048,10 +6374,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="270" t="s">
+      <c r="AA17" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="271"/>
+      <c r="AB17" s="336"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6074,12 +6400,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:35" ht="15.75" thickBot="1">
+    <row r="18" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>13</v>
       </c>
-      <c r="C18" s="159" t="s">
-        <v>280</v>
+      <c r="C18" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D18" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6089,12 +6415,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="304" t="s">
+      <c r="G18" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="275"/>
-      <c r="I18" s="275"/>
-      <c r="J18" s="276"/>
+      <c r="H18" s="277"/>
+      <c r="I18" s="277"/>
+      <c r="J18" s="278"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6102,11 +6428,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="274" t="s">
+      <c r="N18" s="276" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="275"/>
-      <c r="P18" s="276"/>
+      <c r="O18" s="277"/>
+      <c r="P18" s="278"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6116,10 +6442,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="270" t="s">
+      <c r="U18" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="271"/>
+      <c r="V18" s="336"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6132,10 +6458,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="270" t="s">
+      <c r="AA18" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="271"/>
+      <c r="AB18" s="336"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6158,7 +6484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:35" ht="15.75" thickBot="1">
+    <row r="19" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>14</v>
       </c>
@@ -6171,20 +6497,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="297"/>
-      <c r="H19" s="298"/>
-      <c r="I19" s="298"/>
-      <c r="J19" s="299"/>
+      <c r="G19" s="355"/>
+      <c r="H19" s="356"/>
+      <c r="I19" s="356"/>
+      <c r="J19" s="357"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="274" t="s">
-        <v>317</v>
-      </c>
-      <c r="O19" s="275"/>
-      <c r="P19" s="276"/>
+      <c r="N19" s="276" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="277"/>
+      <c r="P19" s="278"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6194,10 +6520,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="270" t="s">
+      <c r="U19" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="271"/>
+      <c r="V19" s="336"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6210,10 +6536,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="270" t="s">
+      <c r="AA19" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="271"/>
+      <c r="AB19" s="336"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6236,7 +6562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:35" ht="15.75" thickBot="1">
+    <row r="20" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>15</v>
       </c>
@@ -6251,20 +6577,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="297"/>
-      <c r="H20" s="298"/>
-      <c r="I20" s="298"/>
-      <c r="J20" s="299"/>
+      <c r="G20" s="355"/>
+      <c r="H20" s="356"/>
+      <c r="I20" s="356"/>
+      <c r="J20" s="357"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="274" t="s">
-        <v>318</v>
-      </c>
-      <c r="O20" s="275"/>
-      <c r="P20" s="276"/>
+      <c r="N20" s="276" t="s">
+        <v>316</v>
+      </c>
+      <c r="O20" s="277"/>
+      <c r="P20" s="278"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6274,10 +6600,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="270" t="s">
+      <c r="U20" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="271"/>
+      <c r="V20" s="336"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6290,10 +6616,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="270" t="s">
+      <c r="AA20" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="271"/>
+      <c r="AB20" s="336"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6316,12 +6642,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:35" ht="15.75" thickBot="1">
+    <row r="21" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D21" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6331,20 +6657,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="297"/>
-      <c r="H21" s="298"/>
-      <c r="I21" s="298"/>
-      <c r="J21" s="299"/>
+      <c r="G21" s="355"/>
+      <c r="H21" s="356"/>
+      <c r="I21" s="356"/>
+      <c r="J21" s="357"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="274" t="s">
+      <c r="N21" s="276" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="275"/>
-      <c r="P21" s="276"/>
+      <c r="O21" s="277"/>
+      <c r="P21" s="278"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6354,10 +6680,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="270" t="s">
+      <c r="U21" s="335" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="271"/>
+      <c r="V21" s="336"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6370,10 +6696,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="270" t="s">
+      <c r="AA21" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="271"/>
+      <c r="AB21" s="336"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6396,33 +6722,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:35" ht="15.75" thickBot="1">
+    <row r="22" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D22" s="23" t="str">
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="303"/>
-      <c r="F22" s="298"/>
-      <c r="G22" s="298"/>
-      <c r="H22" s="298"/>
-      <c r="I22" s="298"/>
-      <c r="J22" s="299"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="356"/>
+      <c r="G22" s="356"/>
+      <c r="H22" s="356"/>
+      <c r="I22" s="356"/>
+      <c r="J22" s="357"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="274" t="s">
+      <c r="N22" s="276" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="275"/>
-      <c r="P22" s="276"/>
+      <c r="O22" s="277"/>
+      <c r="P22" s="278"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6432,10 +6758,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="270" t="s">
+      <c r="U22" s="335" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="271"/>
+      <c r="V22" s="336"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6448,10 +6774,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="270" t="s">
+      <c r="AA22" s="335" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="271"/>
+      <c r="AB22" s="336"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6474,12 +6800,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:35" ht="15.75" thickBot="1">
+    <row r="23" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D23" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6491,22 +6817,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="304" t="s">
+      <c r="G23" s="362" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="275"/>
-      <c r="I23" s="275"/>
-      <c r="J23" s="276"/>
+      <c r="H23" s="277"/>
+      <c r="I23" s="277"/>
+      <c r="J23" s="278"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="274" t="s">
+      <c r="N23" s="276" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="275"/>
-      <c r="P23" s="276"/>
+      <c r="O23" s="277"/>
+      <c r="P23" s="278"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6516,10 +6842,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="270" t="s">
+      <c r="U23" s="335" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="271"/>
+      <c r="V23" s="336"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6532,10 +6858,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="270" t="s">
+      <c r="AA23" s="335" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="271"/>
+      <c r="AB23" s="336"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6558,12 +6884,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:35" ht="15.75" thickBot="1">
+    <row r="24" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D24" s="23" t="str">
         <f t="shared" si="0"/>
@@ -6575,22 +6901,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="304" t="s">
+      <c r="G24" s="362" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="275"/>
-      <c r="I24" s="275"/>
-      <c r="J24" s="276"/>
+      <c r="H24" s="277"/>
+      <c r="I24" s="277"/>
+      <c r="J24" s="278"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="274" t="s">
+      <c r="N24" s="276" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="275"/>
-      <c r="P24" s="276"/>
+      <c r="O24" s="277"/>
+      <c r="P24" s="278"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6600,10 +6926,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="270" t="s">
+      <c r="U24" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="271"/>
+      <c r="V24" s="336"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6616,10 +6942,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="270" t="s">
+      <c r="AA24" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="271"/>
+      <c r="AB24" s="336"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6642,7 +6968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:35" ht="15.75" thickBot="1">
+    <row r="25" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>20</v>
       </c>
@@ -6657,10 +6983,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="297"/>
-      <c r="H25" s="298"/>
-      <c r="I25" s="298"/>
-      <c r="J25" s="299"/>
+      <c r="G25" s="355"/>
+      <c r="H25" s="356"/>
+      <c r="I25" s="356"/>
+      <c r="J25" s="357"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6668,11 +6994,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="274" t="s">
+      <c r="N25" s="276" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="275"/>
-      <c r="P25" s="276"/>
+      <c r="O25" s="277"/>
+      <c r="P25" s="278"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -6682,10 +7008,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="270" t="s">
+      <c r="U25" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="271"/>
+      <c r="V25" s="336"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -6698,10 +7024,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="270" t="s">
+      <c r="AA25" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="271"/>
+      <c r="AB25" s="336"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -6724,7 +7050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:35" ht="15.75" thickBot="1">
+    <row r="26" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>21</v>
       </c>
@@ -6739,10 +7065,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="297"/>
-      <c r="H26" s="298"/>
-      <c r="I26" s="298"/>
-      <c r="J26" s="299"/>
+      <c r="G26" s="355"/>
+      <c r="H26" s="356"/>
+      <c r="I26" s="356"/>
+      <c r="J26" s="357"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -6750,11 +7076,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="274" t="s">
+      <c r="N26" s="276" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="275"/>
-      <c r="P26" s="276"/>
+      <c r="O26" s="277"/>
+      <c r="P26" s="278"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -6764,10 +7090,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="270" t="s">
+      <c r="U26" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="271"/>
+      <c r="V26" s="336"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -6780,10 +7106,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="270" t="s">
+      <c r="AA26" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="271"/>
+      <c r="AB26" s="336"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -6806,7 +7132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:35" ht="15.75" thickBot="1">
+    <row r="27" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>22</v>
       </c>
@@ -6815,22 +7141,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="303"/>
-      <c r="F27" s="298"/>
-      <c r="G27" s="298"/>
-      <c r="H27" s="298"/>
-      <c r="I27" s="298"/>
-      <c r="J27" s="299"/>
+      <c r="E27" s="361"/>
+      <c r="F27" s="356"/>
+      <c r="G27" s="356"/>
+      <c r="H27" s="356"/>
+      <c r="I27" s="356"/>
+      <c r="J27" s="357"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="274" t="s">
+      <c r="N27" s="276" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="275"/>
-      <c r="P27" s="276"/>
+      <c r="O27" s="277"/>
+      <c r="P27" s="278"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -6840,10 +7166,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="270" t="s">
+      <c r="U27" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="271"/>
+      <c r="V27" s="336"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -6856,10 +7182,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="270" t="s">
+      <c r="AA27" s="335" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="271"/>
+      <c r="AB27" s="336"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -6882,7 +7208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:35" ht="15.75" thickBot="1">
+    <row r="28" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>23</v>
       </c>
@@ -6891,12 +7217,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="300"/>
-      <c r="F28" s="301"/>
-      <c r="G28" s="301"/>
-      <c r="H28" s="301"/>
-      <c r="I28" s="301"/>
-      <c r="J28" s="302"/>
+      <c r="E28" s="358"/>
+      <c r="F28" s="359"/>
+      <c r="G28" s="359"/>
+      <c r="H28" s="359"/>
+      <c r="I28" s="359"/>
+      <c r="J28" s="360"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -6904,11 +7230,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="294" t="s">
-        <v>319</v>
-      </c>
-      <c r="O28" s="295"/>
-      <c r="P28" s="296"/>
+      <c r="N28" s="273" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" s="274"/>
+      <c r="P28" s="275"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -6918,10 +7244,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="272" t="s">
+      <c r="U28" s="337" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="273"/>
+      <c r="V28" s="338"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -6934,10 +7260,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="272" t="s">
+      <c r="AA28" s="337" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="273"/>
+      <c r="AB28" s="338"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -6960,8 +7286,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:35" ht="15.75" thickBot="1"/>
-    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1">
+    <row r="29" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="66" t="s">
         <v>80</v>
       </c>
@@ -7014,29 +7340,29 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="329" t="s">
+      <c r="T30" s="387" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="329"/>
-      <c r="V30" s="329"/>
-      <c r="W30" s="329"/>
-      <c r="X30" s="329"/>
-      <c r="Y30" s="329"/>
-      <c r="Z30" s="329"/>
-      <c r="AA30" s="329"/>
-      <c r="AB30" s="329"/>
-      <c r="AC30" s="285"/>
-      <c r="AE30" s="267" t="s">
-        <v>425</v>
-      </c>
-      <c r="AF30" s="268"/>
-      <c r="AG30" s="267" t="s">
-        <v>426</v>
-      </c>
-      <c r="AH30" s="268"/>
-      <c r="AI30" s="269"/>
-    </row>
-    <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1">
+      <c r="U30" s="387"/>
+      <c r="V30" s="387"/>
+      <c r="W30" s="387"/>
+      <c r="X30" s="387"/>
+      <c r="Y30" s="387"/>
+      <c r="Z30" s="387"/>
+      <c r="AA30" s="387"/>
+      <c r="AB30" s="387"/>
+      <c r="AC30" s="347"/>
+      <c r="AE30" s="265" t="s">
+        <v>423</v>
+      </c>
+      <c r="AF30" s="266"/>
+      <c r="AG30" s="265" t="s">
+        <v>424</v>
+      </c>
+      <c r="AH30" s="266"/>
+      <c r="AI30" s="267"/>
+    </row>
+    <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
         <v>68</v>
       </c>
@@ -7061,7 +7387,7 @@
       <c r="L31" s="79"/>
       <c r="M31" s="79"/>
       <c r="N31" s="79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O31" s="79" t="s">
         <v>151</v>
@@ -7075,30 +7401,30 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="248" t="s">
+      <c r="T31" s="279" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="290"/>
-      <c r="V31" s="290"/>
-      <c r="W31" s="290"/>
-      <c r="X31" s="290"/>
-      <c r="Y31" s="290"/>
-      <c r="Z31" s="290"/>
-      <c r="AA31" s="290"/>
-      <c r="AB31" s="290"/>
-      <c r="AC31" s="249"/>
-      <c r="AE31" s="324">
+      <c r="U31" s="280"/>
+      <c r="V31" s="280"/>
+      <c r="W31" s="280"/>
+      <c r="X31" s="280"/>
+      <c r="Y31" s="280"/>
+      <c r="Z31" s="280"/>
+      <c r="AA31" s="280"/>
+      <c r="AB31" s="280"/>
+      <c r="AC31" s="281"/>
+      <c r="AE31" s="382">
         <v>2</v>
       </c>
-      <c r="AF31" s="325"/>
-      <c r="AG31" s="326" t="str" cm="1">
+      <c r="AF31" s="383"/>
+      <c r="AG31" s="384" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="327"/>
-      <c r="AI31" s="328"/>
-    </row>
-    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
+      <c r="AH31" s="385"/>
+      <c r="AI31" s="386"/>
+    </row>
+    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>71</v>
       </c>
@@ -7120,20 +7446,20 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="274" t="s">
+      <c r="T32" s="276" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="275"/>
-      <c r="V32" s="275"/>
-      <c r="W32" s="275"/>
-      <c r="X32" s="275"/>
-      <c r="Y32" s="275"/>
-      <c r="Z32" s="275"/>
-      <c r="AA32" s="275"/>
-      <c r="AB32" s="275"/>
-      <c r="AC32" s="276"/>
-    </row>
-    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1">
+      <c r="U32" s="277"/>
+      <c r="V32" s="277"/>
+      <c r="W32" s="277"/>
+      <c r="X32" s="277"/>
+      <c r="Y32" s="277"/>
+      <c r="Z32" s="277"/>
+      <c r="AA32" s="277"/>
+      <c r="AB32" s="277"/>
+      <c r="AC32" s="278"/>
+    </row>
+    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
         <v>165</v>
       </c>
@@ -7167,31 +7493,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="274" t="s">
+      <c r="T33" s="276" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="275"/>
-      <c r="V33" s="275"/>
-      <c r="W33" s="275"/>
-      <c r="X33" s="275"/>
-      <c r="Y33" s="275"/>
-      <c r="Z33" s="275"/>
-      <c r="AA33" s="275"/>
-      <c r="AB33" s="275"/>
-      <c r="AC33" s="276"/>
-    </row>
-    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B34" s="265" t="s">
+      <c r="U33" s="277"/>
+      <c r="V33" s="277"/>
+      <c r="W33" s="277"/>
+      <c r="X33" s="277"/>
+      <c r="Y33" s="277"/>
+      <c r="Z33" s="277"/>
+      <c r="AA33" s="277"/>
+      <c r="AB33" s="277"/>
+      <c r="AC33" s="278"/>
+    </row>
+    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="333" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="263" t="s">
+      <c r="C34" s="331" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="264"/>
-      <c r="E34" s="263" t="s">
+      <c r="D34" s="332"/>
+      <c r="E34" s="331" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="264"/>
+      <c r="F34" s="332"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7199,7 +7525,7 @@
       <c r="J34" s="79"/>
       <c r="K34" s="79"/>
       <c r="L34" s="79" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M34" s="79" t="s">
         <v>169</v>
@@ -7219,21 +7545,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="274" t="s">
+      <c r="T34" s="276" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="275"/>
-      <c r="V34" s="275"/>
-      <c r="W34" s="275"/>
-      <c r="X34" s="275"/>
-      <c r="Y34" s="275"/>
-      <c r="Z34" s="275"/>
-      <c r="AA34" s="275"/>
-      <c r="AB34" s="275"/>
-      <c r="AC34" s="276"/>
-    </row>
-    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B35" s="266"/>
+      <c r="U34" s="277"/>
+      <c r="V34" s="277"/>
+      <c r="W34" s="277"/>
+      <c r="X34" s="277"/>
+      <c r="Y34" s="277"/>
+      <c r="Z34" s="277"/>
+      <c r="AA34" s="277"/>
+      <c r="AB34" s="277"/>
+      <c r="AC34" s="278"/>
+    </row>
+    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="334"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7252,20 +7578,20 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="274" t="s">
+      <c r="T35" s="276" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="275"/>
-      <c r="V35" s="275"/>
-      <c r="W35" s="275"/>
-      <c r="X35" s="275"/>
-      <c r="Y35" s="275"/>
-      <c r="Z35" s="275"/>
-      <c r="AA35" s="275"/>
-      <c r="AB35" s="275"/>
-      <c r="AC35" s="276"/>
-    </row>
-    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1">
+      <c r="U35" s="277"/>
+      <c r="V35" s="277"/>
+      <c r="W35" s="277"/>
+      <c r="X35" s="277"/>
+      <c r="Y35" s="277"/>
+      <c r="Z35" s="277"/>
+      <c r="AA35" s="277"/>
+      <c r="AB35" s="277"/>
+      <c r="AC35" s="278"/>
+    </row>
+    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>0</v>
       </c>
@@ -7282,7 +7608,7 @@
         <v>124</v>
       </c>
       <c r="H36" s="84" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I36" s="73">
         <v>7</v>
@@ -7314,20 +7640,20 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="274" t="s">
+      <c r="T36" s="276" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="275"/>
-      <c r="V36" s="275"/>
-      <c r="W36" s="275"/>
-      <c r="X36" s="275"/>
-      <c r="Y36" s="275"/>
-      <c r="Z36" s="275"/>
-      <c r="AA36" s="275"/>
-      <c r="AB36" s="275"/>
-      <c r="AC36" s="276"/>
-    </row>
-    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1">
+      <c r="U36" s="277"/>
+      <c r="V36" s="277"/>
+      <c r="W36" s="277"/>
+      <c r="X36" s="277"/>
+      <c r="Y36" s="277"/>
+      <c r="Z36" s="277"/>
+      <c r="AA36" s="277"/>
+      <c r="AB36" s="277"/>
+      <c r="AC36" s="278"/>
+    </row>
+    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>1</v>
       </c>
@@ -7350,17 +7676,17 @@
       <c r="J37" s="79"/>
       <c r="K37" s="79"/>
       <c r="L37" s="79"/>
-      <c r="M37" s="160" t="s">
-        <v>287</v>
+      <c r="M37" s="159" t="s">
+        <v>285</v>
       </c>
       <c r="N37" s="79" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O37" s="79" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P37" s="80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R37" s="2">
         <v>6</v>
@@ -7368,60 +7694,60 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="274" t="s">
+      <c r="T37" s="276" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="275"/>
-      <c r="V37" s="275"/>
-      <c r="W37" s="275"/>
-      <c r="X37" s="275"/>
-      <c r="Y37" s="275"/>
-      <c r="Z37" s="275"/>
-      <c r="AA37" s="275"/>
-      <c r="AB37" s="275"/>
-      <c r="AC37" s="276"/>
-    </row>
-    <row r="38" spans="2:29" ht="15.75" thickBot="1">
+      <c r="U37" s="277"/>
+      <c r="V37" s="277"/>
+      <c r="W37" s="277"/>
+      <c r="X37" s="277"/>
+      <c r="Y37" s="277"/>
+      <c r="Z37" s="277"/>
+      <c r="AA37" s="277"/>
+      <c r="AB37" s="277"/>
+      <c r="AC37" s="278"/>
+    </row>
+    <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>2</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>104</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="316" t="s">
+      <c r="S38" s="374" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="318" t="s">
+      <c r="T38" s="376" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="319"/>
-      <c r="V38" s="319"/>
-      <c r="W38" s="319"/>
-      <c r="X38" s="319"/>
-      <c r="Y38" s="319"/>
-      <c r="Z38" s="319"/>
-      <c r="AA38" s="319"/>
-      <c r="AB38" s="319"/>
-      <c r="AC38" s="320"/>
-    </row>
-    <row r="39" spans="2:29" ht="15" customHeight="1">
+      <c r="U38" s="377"/>
+      <c r="V38" s="377"/>
+      <c r="W38" s="377"/>
+      <c r="X38" s="377"/>
+      <c r="Y38" s="377"/>
+      <c r="Z38" s="377"/>
+      <c r="AA38" s="377"/>
+      <c r="AB38" s="377"/>
+      <c r="AC38" s="378"/>
+    </row>
+    <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>3</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D39" s="35" t="s">
         <v>118</v>
@@ -7432,33 +7758,33 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="250" t="s">
+      <c r="G39" s="320" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="251"/>
-      <c r="I39" s="251"/>
-      <c r="J39" s="252"/>
+      <c r="H39" s="271"/>
+      <c r="I39" s="271"/>
+      <c r="J39" s="272"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="317"/>
-      <c r="T39" s="321"/>
-      <c r="U39" s="322"/>
-      <c r="V39" s="322"/>
-      <c r="W39" s="322"/>
-      <c r="X39" s="322"/>
-      <c r="Y39" s="322"/>
-      <c r="Z39" s="322"/>
-      <c r="AA39" s="322"/>
-      <c r="AB39" s="322"/>
-      <c r="AC39" s="323"/>
-    </row>
-    <row r="40" spans="2:29" ht="37.5" customHeight="1">
+      <c r="S39" s="375"/>
+      <c r="T39" s="379"/>
+      <c r="U39" s="380"/>
+      <c r="V39" s="380"/>
+      <c r="W39" s="380"/>
+      <c r="X39" s="380"/>
+      <c r="Y39" s="380"/>
+      <c r="Z39" s="380"/>
+      <c r="AA39" s="380"/>
+      <c r="AB39" s="380"/>
+      <c r="AC39" s="381"/>
+    </row>
+    <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>4</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D40" s="69" t="s">
         <v>119</v>
@@ -7469,38 +7795,38 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="253"/>
-      <c r="H40" s="254"/>
-      <c r="I40" s="254"/>
-      <c r="J40" s="255"/>
+      <c r="G40" s="321"/>
+      <c r="H40" s="322"/>
+      <c r="I40" s="322"/>
+      <c r="J40" s="323"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="274" t="s">
-        <v>323</v>
-      </c>
-      <c r="U40" s="275"/>
-      <c r="V40" s="275"/>
-      <c r="W40" s="275"/>
-      <c r="X40" s="275"/>
-      <c r="Y40" s="275"/>
-      <c r="Z40" s="275"/>
-      <c r="AA40" s="275"/>
-      <c r="AB40" s="275"/>
-      <c r="AC40" s="276"/>
-    </row>
-    <row r="41" spans="2:29" ht="30" customHeight="1">
+      <c r="T40" s="276" t="s">
+        <v>321</v>
+      </c>
+      <c r="U40" s="277"/>
+      <c r="V40" s="277"/>
+      <c r="W40" s="277"/>
+      <c r="X40" s="277"/>
+      <c r="Y40" s="277"/>
+      <c r="Z40" s="277"/>
+      <c r="AA40" s="277"/>
+      <c r="AB40" s="277"/>
+      <c r="AC40" s="278"/>
+    </row>
+    <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
         <v>5</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D41" s="69" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>107</v>
@@ -7508,35 +7834,35 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="253"/>
-      <c r="H41" s="254"/>
-      <c r="I41" s="254"/>
-      <c r="J41" s="255"/>
+      <c r="G41" s="321"/>
+      <c r="H41" s="322"/>
+      <c r="I41" s="322"/>
+      <c r="J41" s="323"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="274" t="s">
-        <v>326</v>
-      </c>
-      <c r="U41" s="275"/>
-      <c r="V41" s="275"/>
-      <c r="W41" s="275"/>
-      <c r="X41" s="275"/>
-      <c r="Y41" s="275"/>
-      <c r="Z41" s="275"/>
-      <c r="AA41" s="275"/>
-      <c r="AB41" s="275"/>
-      <c r="AC41" s="276"/>
-    </row>
-    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1">
+      <c r="T41" s="276" t="s">
+        <v>324</v>
+      </c>
+      <c r="U41" s="277"/>
+      <c r="V41" s="277"/>
+      <c r="W41" s="277"/>
+      <c r="X41" s="277"/>
+      <c r="Y41" s="277"/>
+      <c r="Z41" s="277"/>
+      <c r="AA41" s="277"/>
+      <c r="AB41" s="277"/>
+      <c r="AC41" s="278"/>
+    </row>
+    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>6</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>149</v>
@@ -7547,30 +7873,30 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="256"/>
-      <c r="H42" s="257"/>
-      <c r="I42" s="257"/>
-      <c r="J42" s="258"/>
+      <c r="G42" s="324"/>
+      <c r="H42" s="325"/>
+      <c r="I42" s="325"/>
+      <c r="J42" s="326"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="274" t="s">
+      <c r="T42" s="276" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="275"/>
-      <c r="V42" s="275"/>
-      <c r="W42" s="275"/>
-      <c r="X42" s="275"/>
-      <c r="Y42" s="275"/>
-      <c r="Z42" s="275"/>
-      <c r="AA42" s="275"/>
-      <c r="AB42" s="275"/>
-      <c r="AC42" s="276"/>
-    </row>
-    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1">
+      <c r="U42" s="277"/>
+      <c r="V42" s="277"/>
+      <c r="W42" s="277"/>
+      <c r="X42" s="277"/>
+      <c r="Y42" s="277"/>
+      <c r="Z42" s="277"/>
+      <c r="AA42" s="277"/>
+      <c r="AB42" s="277"/>
+      <c r="AC42" s="278"/>
+    </row>
+    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>7</v>
       </c>
@@ -7578,40 +7904,40 @@
         <v>94</v>
       </c>
       <c r="D43" s="69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="G43" s="209" t="s">
-        <v>330</v>
-      </c>
-      <c r="H43" s="245"/>
-      <c r="I43" s="245"/>
-      <c r="J43" s="210"/>
+        <v>327</v>
+      </c>
+      <c r="G43" s="262" t="s">
+        <v>328</v>
+      </c>
+      <c r="H43" s="263"/>
+      <c r="I43" s="263"/>
+      <c r="J43" s="264"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="274" t="s">
+      <c r="T43" s="276" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="275"/>
-      <c r="V43" s="275"/>
-      <c r="W43" s="275"/>
-      <c r="X43" s="275"/>
-      <c r="Y43" s="275"/>
-      <c r="Z43" s="275"/>
-      <c r="AA43" s="275"/>
-      <c r="AB43" s="275"/>
-      <c r="AC43" s="276"/>
-    </row>
-    <row r="44" spans="2:29" ht="45.75" thickBot="1">
+      <c r="U43" s="277"/>
+      <c r="V43" s="277"/>
+      <c r="W43" s="277"/>
+      <c r="X43" s="277"/>
+      <c r="Y43" s="277"/>
+      <c r="Z43" s="277"/>
+      <c r="AA43" s="277"/>
+      <c r="AB43" s="277"/>
+      <c r="AC43" s="278"/>
+    </row>
+    <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>8</v>
       </c>
@@ -7619,34 +7945,34 @@
         <v>121</v>
       </c>
       <c r="D44" s="69" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>110</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="316" t="s">
+      <c r="S44" s="374" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="318" t="s">
-        <v>332</v>
-      </c>
-      <c r="U44" s="319"/>
-      <c r="V44" s="319"/>
-      <c r="W44" s="319"/>
-      <c r="X44" s="319"/>
-      <c r="Y44" s="319"/>
-      <c r="Z44" s="319"/>
-      <c r="AA44" s="319"/>
-      <c r="AB44" s="319"/>
-      <c r="AC44" s="320"/>
-    </row>
-    <row r="45" spans="2:29" ht="30.75" customHeight="1">
+      <c r="T44" s="376" t="s">
+        <v>330</v>
+      </c>
+      <c r="U44" s="377"/>
+      <c r="V44" s="377"/>
+      <c r="W44" s="377"/>
+      <c r="X44" s="377"/>
+      <c r="Y44" s="377"/>
+      <c r="Z44" s="377"/>
+      <c r="AA44" s="377"/>
+      <c r="AB44" s="377"/>
+      <c r="AC44" s="378"/>
+    </row>
+    <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
         <v>9</v>
       </c>
@@ -7662,28 +7988,28 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="250" t="s">
+      <c r="G45" s="320" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="251"/>
-      <c r="I45" s="251"/>
-      <c r="J45" s="252"/>
+      <c r="H45" s="271"/>
+      <c r="I45" s="271"/>
+      <c r="J45" s="272"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="317"/>
-      <c r="T45" s="321"/>
-      <c r="U45" s="322"/>
-      <c r="V45" s="322"/>
-      <c r="W45" s="322"/>
-      <c r="X45" s="322"/>
-      <c r="Y45" s="322"/>
-      <c r="Z45" s="322"/>
-      <c r="AA45" s="322"/>
-      <c r="AB45" s="322"/>
-      <c r="AC45" s="323"/>
-    </row>
-    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1">
+      <c r="S45" s="375"/>
+      <c r="T45" s="379"/>
+      <c r="U45" s="380"/>
+      <c r="V45" s="380"/>
+      <c r="W45" s="380"/>
+      <c r="X45" s="380"/>
+      <c r="Y45" s="380"/>
+      <c r="Z45" s="380"/>
+      <c r="AA45" s="380"/>
+      <c r="AB45" s="380"/>
+      <c r="AC45" s="381"/>
+    </row>
+    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>10</v>
       </c>
@@ -7699,30 +8025,30 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="256"/>
-      <c r="H46" s="257"/>
-      <c r="I46" s="257"/>
-      <c r="J46" s="258"/>
+      <c r="G46" s="324"/>
+      <c r="H46" s="325"/>
+      <c r="I46" s="325"/>
+      <c r="J46" s="326"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="294" t="s">
+      <c r="T46" s="273" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="295"/>
-      <c r="V46" s="295"/>
-      <c r="W46" s="295"/>
-      <c r="X46" s="295"/>
-      <c r="Y46" s="295"/>
-      <c r="Z46" s="295"/>
-      <c r="AA46" s="295"/>
-      <c r="AB46" s="295"/>
-      <c r="AC46" s="296"/>
-    </row>
-    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1">
+      <c r="U46" s="274"/>
+      <c r="V46" s="274"/>
+      <c r="W46" s="274"/>
+      <c r="X46" s="274"/>
+      <c r="Y46" s="274"/>
+      <c r="Z46" s="274"/>
+      <c r="AA46" s="274"/>
+      <c r="AB46" s="274"/>
+      <c r="AC46" s="275"/>
+    </row>
+    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>11</v>
       </c>
@@ -7730,7 +8056,7 @@
         <v>121</v>
       </c>
       <c r="D47" s="69" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>113</v>
@@ -7738,14 +8064,14 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="245" t="s">
-        <v>334</v>
-      </c>
-      <c r="H47" s="245"/>
-      <c r="I47" s="245"/>
-      <c r="J47" s="210"/>
-    </row>
-    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1">
+      <c r="G47" s="263" t="s">
+        <v>332</v>
+      </c>
+      <c r="H47" s="263"/>
+      <c r="I47" s="263"/>
+      <c r="J47" s="264"/>
+    </row>
+    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>12</v>
       </c>
@@ -7753,7 +8079,7 @@
         <v>121</v>
       </c>
       <c r="D48" s="69" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>114</v>
@@ -7762,7 +8088,7 @@
         <v>162</v>
       </c>
       <c r="R48" s="84" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S48" s="73">
         <v>7</v>
@@ -7788,13 +8114,13 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="203" t="s">
-        <v>336</v>
-      </c>
-      <c r="AB48" s="204"/>
-      <c r="AC48" s="205"/>
-    </row>
-    <row r="49" spans="2:29" ht="35.25" customHeight="1" thickBot="1">
+      <c r="AA48" s="282" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB48" s="283"/>
+      <c r="AC48" s="284"/>
+    </row>
+    <row r="49" spans="2:29" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>13</v>
       </c>
@@ -7802,7 +8128,7 @@
         <v>121</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>115</v>
@@ -7810,12 +8136,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="250" t="s">
-        <v>338</v>
-      </c>
-      <c r="H49" s="251"/>
-      <c r="I49" s="251"/>
-      <c r="J49" s="252"/>
+      <c r="G49" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="H49" s="271"/>
+      <c r="I49" s="271"/>
+      <c r="J49" s="272"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -7823,27 +8149,27 @@
       <c r="T49" s="79"/>
       <c r="U49" s="79"/>
       <c r="V49" s="79"/>
-      <c r="W49" s="160"/>
+      <c r="W49" s="159"/>
       <c r="X49" s="79"/>
       <c r="Y49" s="79" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Z49" s="80" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA49" s="206"/>
-      <c r="AB49" s="207"/>
-      <c r="AC49" s="208"/>
-    </row>
-    <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1">
+        <v>296</v>
+      </c>
+      <c r="AA49" s="285"/>
+      <c r="AB49" s="286"/>
+      <c r="AC49" s="287"/>
+    </row>
+    <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>14</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>116</v>
@@ -7851,12 +8177,12 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="253"/>
-      <c r="H50" s="254"/>
-      <c r="I50" s="254"/>
-      <c r="J50" s="255"/>
-    </row>
-    <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1">
+      <c r="G50" s="321"/>
+      <c r="H50" s="322"/>
+      <c r="I50" s="322"/>
+      <c r="J50" s="323"/>
+    </row>
+    <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>15</v>
       </c>
@@ -7864,7 +8190,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E51" s="63" t="s">
         <v>117</v>
@@ -7872,425 +8198,425 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="256"/>
-      <c r="H51" s="257"/>
-      <c r="I51" s="257"/>
-      <c r="J51" s="258"/>
-      <c r="R51" s="223" t="s">
+      <c r="G51" s="324"/>
+      <c r="H51" s="325"/>
+      <c r="I51" s="325"/>
+      <c r="J51" s="326"/>
+      <c r="R51" s="300" t="s">
+        <v>299</v>
+      </c>
+      <c r="S51" s="302" t="s">
+        <v>156</v>
+      </c>
+      <c r="T51" s="304" t="s">
+        <v>155</v>
+      </c>
+      <c r="U51" s="304"/>
+      <c r="V51" s="305"/>
+    </row>
+    <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="265" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" s="266"/>
+      <c r="D52" s="266"/>
+      <c r="E52" s="266"/>
+      <c r="F52" s="267"/>
+      <c r="R52" s="301"/>
+      <c r="S52" s="303"/>
+      <c r="T52" s="306"/>
+      <c r="U52" s="306"/>
+      <c r="V52" s="307"/>
+    </row>
+    <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R53" s="164" t="s">
+        <v>195</v>
+      </c>
+      <c r="S53" s="165" t="s">
+        <v>300</v>
+      </c>
+      <c r="T53" s="295" t="s">
+        <v>338</v>
+      </c>
+      <c r="U53" s="295"/>
+      <c r="V53" s="296"/>
+    </row>
+    <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="329" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="302" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" s="304" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="305"/>
+      <c r="H54" s="300" t="s">
+        <v>290</v>
+      </c>
+      <c r="I54" s="302" t="s">
+        <v>156</v>
+      </c>
+      <c r="J54" s="288" t="s">
+        <v>155</v>
+      </c>
+      <c r="K54" s="289"/>
+      <c r="L54" s="290"/>
+      <c r="R54" s="162" t="s">
+        <v>204</v>
+      </c>
+      <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="S51" s="225" t="s">
-        <v>156</v>
-      </c>
-      <c r="T51" s="227" t="s">
-        <v>155</v>
-      </c>
-      <c r="U51" s="227"/>
-      <c r="V51" s="228"/>
-    </row>
-    <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B52" s="267" t="s">
+      <c r="T54" s="308" t="s">
+        <v>307</v>
+      </c>
+      <c r="U54" s="308"/>
+      <c r="V54" s="309"/>
+    </row>
+    <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="330"/>
+      <c r="C55" s="328"/>
+      <c r="D55" s="318"/>
+      <c r="E55" s="319"/>
+      <c r="H55" s="327"/>
+      <c r="I55" s="303"/>
+      <c r="J55" s="291"/>
+      <c r="K55" s="292"/>
+      <c r="L55" s="293"/>
+      <c r="R55" s="162" t="s">
+        <v>190</v>
+      </c>
+      <c r="S55" s="160" t="s">
+        <v>302</v>
+      </c>
+      <c r="T55" s="308" t="s">
         <v>339</v>
       </c>
-      <c r="C52" s="268"/>
-      <c r="D52" s="268"/>
-      <c r="E52" s="268"/>
-      <c r="F52" s="269"/>
-      <c r="R52" s="224"/>
-      <c r="S52" s="226"/>
-      <c r="T52" s="229"/>
-      <c r="U52" s="229"/>
-      <c r="V52" s="230"/>
-    </row>
-    <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1">
-      <c r="R53" s="165" t="s">
-        <v>195</v>
-      </c>
-      <c r="S53" s="166" t="s">
-        <v>302</v>
-      </c>
-      <c r="T53" s="218" t="s">
-        <v>340</v>
-      </c>
-      <c r="U53" s="218"/>
-      <c r="V53" s="219"/>
-    </row>
-    <row r="54" spans="2:29" ht="36.75" customHeight="1">
-      <c r="B54" s="261" t="s">
-        <v>154</v>
-      </c>
-      <c r="C54" s="225" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" s="227" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="228"/>
-      <c r="H54" s="223" t="s">
-        <v>292</v>
-      </c>
-      <c r="I54" s="225" t="s">
-        <v>156</v>
-      </c>
-      <c r="J54" s="211" t="s">
-        <v>155</v>
-      </c>
-      <c r="K54" s="212"/>
-      <c r="L54" s="213"/>
-      <c r="R54" s="163" t="s">
-        <v>204</v>
-      </c>
-      <c r="S54" s="161" t="s">
-        <v>303</v>
-      </c>
-      <c r="T54" s="231" t="s">
-        <v>309</v>
-      </c>
-      <c r="U54" s="231"/>
-      <c r="V54" s="232"/>
-    </row>
-    <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1">
-      <c r="B55" s="262"/>
-      <c r="C55" s="260"/>
-      <c r="D55" s="246"/>
-      <c r="E55" s="247"/>
-      <c r="H55" s="259"/>
-      <c r="I55" s="226"/>
-      <c r="J55" s="214"/>
-      <c r="K55" s="215"/>
-      <c r="L55" s="216"/>
-      <c r="R55" s="163" t="s">
-        <v>190</v>
-      </c>
-      <c r="S55" s="161" t="s">
-        <v>304</v>
-      </c>
-      <c r="T55" s="231" t="s">
-        <v>341</v>
-      </c>
-      <c r="U55" s="231"/>
-      <c r="V55" s="232"/>
-    </row>
-    <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1">
+      <c r="U55" s="308"/>
+      <c r="V55" s="309"/>
+    </row>
+    <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <v>0</v>
       </c>
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="248" t="s">
+      <c r="D56" s="279" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="249"/>
+      <c r="E56" s="281"/>
       <c r="H56" s="81" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="J56" s="217" t="s">
-        <v>293</v>
-      </c>
-      <c r="K56" s="218"/>
-      <c r="L56" s="219"/>
-      <c r="M56" s="209" t="s">
-        <v>342</v>
-      </c>
-      <c r="N56" s="210"/>
-      <c r="R56" s="163" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" s="294" t="s">
+        <v>291</v>
+      </c>
+      <c r="K56" s="295"/>
+      <c r="L56" s="296"/>
+      <c r="M56" s="262" t="s">
+        <v>340</v>
+      </c>
+      <c r="N56" s="264"/>
+      <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
-      <c r="S56" s="161" t="s">
-        <v>305</v>
-      </c>
-      <c r="T56" s="231" t="s">
-        <v>343</v>
-      </c>
-      <c r="U56" s="231"/>
-      <c r="V56" s="232"/>
-    </row>
-    <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1">
+      <c r="S56" s="160" t="s">
+        <v>303</v>
+      </c>
+      <c r="T56" s="308" t="s">
+        <v>341</v>
+      </c>
+      <c r="U56" s="308"/>
+      <c r="V56" s="309"/>
+    </row>
+    <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
         <v>1</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>288</v>
-      </c>
-      <c r="D57" s="242" t="s">
-        <v>289</v>
-      </c>
-      <c r="E57" s="232"/>
-      <c r="F57" s="209" t="s">
+        <v>286</v>
+      </c>
+      <c r="D57" s="315" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57" s="309"/>
+      <c r="F57" s="262" t="s">
+        <v>342</v>
+      </c>
+      <c r="G57" s="264"/>
+      <c r="H57" s="82">
+        <v>0</v>
+      </c>
+      <c r="I57" s="85" t="s">
+        <v>292</v>
+      </c>
+      <c r="J57" s="297" t="s">
+        <v>343</v>
+      </c>
+      <c r="K57" s="298"/>
+      <c r="L57" s="299"/>
+      <c r="R57" s="162" t="s">
+        <v>228</v>
+      </c>
+      <c r="S57" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="T57" s="308" t="s">
         <v>344</v>
       </c>
-      <c r="G57" s="210"/>
-      <c r="H57" s="82">
-        <v>0</v>
-      </c>
-      <c r="I57" s="85" t="s">
-        <v>294</v>
-      </c>
-      <c r="J57" s="220" t="s">
-        <v>345</v>
-      </c>
-      <c r="K57" s="221"/>
-      <c r="L57" s="222"/>
-      <c r="R57" s="163" t="s">
-        <v>229</v>
-      </c>
-      <c r="S57" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="T57" s="231" t="s">
-        <v>346</v>
-      </c>
-      <c r="U57" s="231"/>
-      <c r="V57" s="232"/>
-    </row>
-    <row r="58" spans="2:29" ht="60" customHeight="1">
+      <c r="U57" s="308"/>
+      <c r="V57" s="309"/>
+    </row>
+    <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
         <v>2</v>
       </c>
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="242" t="s">
-        <v>347</v>
-      </c>
-      <c r="E58" s="232"/>
+      <c r="D58" s="315" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="309"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
+        <v>346</v>
+      </c>
+      <c r="J58" s="297" t="s">
+        <v>347</v>
+      </c>
+      <c r="K58" s="298"/>
+      <c r="L58" s="299"/>
+      <c r="R58" s="162" t="s">
+        <v>229</v>
+      </c>
+      <c r="S58" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="T58" s="308" t="s">
         <v>348</v>
       </c>
-      <c r="J58" s="220" t="s">
-        <v>349</v>
-      </c>
-      <c r="K58" s="221"/>
-      <c r="L58" s="222"/>
-      <c r="R58" s="163" t="s">
-        <v>230</v>
-      </c>
-      <c r="S58" s="36" t="s">
-        <v>306</v>
-      </c>
-      <c r="T58" s="231" t="s">
-        <v>350</v>
-      </c>
-      <c r="U58" s="231"/>
-      <c r="V58" s="232"/>
-    </row>
-    <row r="59" spans="2:29" ht="61.5" customHeight="1">
+      <c r="U58" s="308"/>
+      <c r="V58" s="309"/>
+    </row>
+    <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
         <v>3</v>
       </c>
       <c r="C59" s="85" t="s">
-        <v>351</v>
-      </c>
-      <c r="D59" s="242" t="s">
+        <v>349</v>
+      </c>
+      <c r="D59" s="315" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="232"/>
+      <c r="E59" s="309"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
-        <v>291</v>
-      </c>
-      <c r="J59" s="220" t="s">
-        <v>352</v>
-      </c>
-      <c r="K59" s="221"/>
-      <c r="L59" s="222"/>
-      <c r="R59" s="163" t="s">
-        <v>231</v>
+        <v>289</v>
+      </c>
+      <c r="J59" s="297" t="s">
+        <v>350</v>
+      </c>
+      <c r="K59" s="298"/>
+      <c r="L59" s="299"/>
+      <c r="R59" s="162" t="s">
+        <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="T59" s="231" t="s">
-        <v>353</v>
-      </c>
-      <c r="U59" s="231"/>
-      <c r="V59" s="232"/>
-      <c r="X59" s="167"/>
-    </row>
-    <row r="60" spans="2:29" ht="45.75" customHeight="1">
+        <v>305</v>
+      </c>
+      <c r="T59" s="308" t="s">
+        <v>351</v>
+      </c>
+      <c r="U59" s="308"/>
+      <c r="V59" s="309"/>
+      <c r="X59" s="166"/>
+    </row>
+    <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="82">
         <v>4</v>
       </c>
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="242" t="s">
+      <c r="D60" s="315" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="232"/>
+      <c r="E60" s="309"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="J60" s="220" t="s">
-        <v>311</v>
-      </c>
-      <c r="K60" s="221"/>
-      <c r="L60" s="222"/>
-      <c r="R60" s="163" t="s">
-        <v>232</v>
-      </c>
-      <c r="S60" s="161" t="s">
-        <v>308</v>
-      </c>
-      <c r="T60" s="233" t="s">
-        <v>355</v>
-      </c>
-      <c r="U60" s="234"/>
-      <c r="V60" s="235"/>
-    </row>
-    <row r="61" spans="2:29" ht="40.5" customHeight="1">
+        <v>294</v>
+      </c>
+      <c r="J60" s="297" t="s">
+        <v>309</v>
+      </c>
+      <c r="K60" s="298"/>
+      <c r="L60" s="299"/>
+      <c r="R60" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="S60" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T60" s="310" t="s">
+        <v>353</v>
+      </c>
+      <c r="U60" s="311"/>
+      <c r="V60" s="312"/>
+    </row>
+    <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
         <v>5</v>
       </c>
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="242" t="s">
+      <c r="D61" s="315" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="232"/>
+      <c r="E61" s="309"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="220"/>
-      <c r="K61" s="221"/>
-      <c r="L61" s="222"/>
-      <c r="R61" s="163" t="s">
-        <v>233</v>
-      </c>
-      <c r="S61" s="161" t="s">
-        <v>308</v>
-      </c>
-      <c r="T61" s="236"/>
-      <c r="U61" s="237"/>
-      <c r="V61" s="238"/>
-    </row>
-    <row r="62" spans="2:29" ht="53.25" customHeight="1">
+      <c r="J61" s="297"/>
+      <c r="K61" s="298"/>
+      <c r="L61" s="299"/>
+      <c r="R61" s="162" t="s">
+        <v>232</v>
+      </c>
+      <c r="S61" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T61" s="313"/>
+      <c r="U61" s="245"/>
+      <c r="V61" s="246"/>
+    </row>
+    <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="242"/>
-      <c r="E62" s="232"/>
+      <c r="D62" s="315"/>
+      <c r="E62" s="309"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="220"/>
-      <c r="K62" s="221"/>
-      <c r="L62" s="222"/>
-      <c r="R62" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="S62" s="161" t="s">
-        <v>308</v>
-      </c>
-      <c r="T62" s="236"/>
-      <c r="U62" s="237"/>
-      <c r="V62" s="238"/>
-    </row>
-    <row r="63" spans="2:29" ht="36" customHeight="1" thickBot="1">
+      <c r="J62" s="297"/>
+      <c r="K62" s="298"/>
+      <c r="L62" s="299"/>
+      <c r="R62" s="162" t="s">
+        <v>264</v>
+      </c>
+      <c r="S62" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T62" s="313"/>
+      <c r="U62" s="245"/>
+      <c r="V62" s="246"/>
+    </row>
+    <row r="63" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="242"/>
-      <c r="E63" s="232"/>
+      <c r="D63" s="315"/>
+      <c r="E63" s="309"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="220"/>
-      <c r="K63" s="221"/>
-      <c r="L63" s="222"/>
-      <c r="R63" s="164" t="s">
-        <v>354</v>
-      </c>
-      <c r="S63" s="162" t="s">
-        <v>308</v>
-      </c>
-      <c r="T63" s="239"/>
-      <c r="U63" s="240"/>
-      <c r="V63" s="241"/>
-    </row>
-    <row r="64" spans="2:29" ht="40.5" customHeight="1">
+      <c r="J63" s="297"/>
+      <c r="K63" s="298"/>
+      <c r="L63" s="299"/>
+      <c r="R63" s="163" t="s">
+        <v>352</v>
+      </c>
+      <c r="S63" s="161" t="s">
+        <v>306</v>
+      </c>
+      <c r="T63" s="314"/>
+      <c r="U63" s="248"/>
+      <c r="V63" s="249"/>
+    </row>
+    <row r="64" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="242"/>
-      <c r="E64" s="232"/>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="D64" s="315"/>
+      <c r="E64" s="309"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="242"/>
-      <c r="E65" s="232"/>
-    </row>
-    <row r="66" spans="2:5" ht="30" customHeight="1">
+      <c r="D65" s="315"/>
+      <c r="E65" s="309"/>
+    </row>
+    <row r="66" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="82">
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="242"/>
-      <c r="E66" s="232"/>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="D66" s="315"/>
+      <c r="E66" s="309"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="242"/>
-      <c r="E67" s="232"/>
-    </row>
-    <row r="68" spans="2:5">
+      <c r="D67" s="315"/>
+      <c r="E67" s="309"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="242"/>
-      <c r="E68" s="232"/>
-    </row>
-    <row r="69" spans="2:5">
+      <c r="D68" s="315"/>
+      <c r="E68" s="309"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="242"/>
-      <c r="E69" s="232"/>
-    </row>
-    <row r="70" spans="2:5" ht="30" customHeight="1">
+      <c r="D69" s="315"/>
+      <c r="E69" s="309"/>
+    </row>
+    <row r="70" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="242"/>
-      <c r="E70" s="232"/>
-    </row>
-    <row r="71" spans="2:5" ht="15.75" thickBot="1">
+      <c r="D70" s="315"/>
+      <c r="E70" s="309"/>
+    </row>
+    <row r="71" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="243"/>
-      <c r="E71" s="244"/>
-    </row>
-    <row r="75" spans="2:5" ht="72" customHeight="1"/>
+      <c r="D71" s="316"/>
+      <c r="E71" s="317"/>
+    </row>
+    <row r="75" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="187">
     <mergeCell ref="AE30:AF30"/>
@@ -8494,12 +8820,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CBBBEA-E421-4197-9F44-CA2E8EC0215F}">
   <dimension ref="B1:AB33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="10" width="10.140625" customWidth="1"/>
     <col min="12" max="12" width="10.140625" customWidth="1"/>
@@ -8510,443 +8836,449 @@
     <col min="17" max="19" width="18.42578125" customWidth="1"/>
     <col min="20" max="20" width="28.5703125" customWidth="1"/>
     <col min="21" max="21" width="8" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" customWidth="1"/>
     <col min="24" max="24" width="27.42578125" customWidth="1"/>
     <col min="25" max="25" width="48.140625" customWidth="1"/>
     <col min="26" max="28" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1">
-      <c r="B2" s="194" t="s">
+    <row r="1" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="185" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" s="180" t="s">
+        <v>357</v>
+      </c>
+      <c r="D2" s="178" t="s">
         <v>358</v>
       </c>
-      <c r="C2" s="189" t="s">
+      <c r="E2" s="178" t="s">
+        <v>417</v>
+      </c>
+      <c r="F2" s="179" t="s">
         <v>359</v>
       </c>
-      <c r="D2" s="187" t="s">
+      <c r="G2" s="271" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="L2" s="253" t="s">
+        <v>274</v>
+      </c>
+      <c r="M2" s="254"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="255"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="256" t="s">
+        <v>237</v>
+      </c>
+      <c r="R2" s="257"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="250" t="s">
+        <v>260</v>
+      </c>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="252"/>
+    </row>
+    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="186" t="s">
         <v>360</v>
       </c>
-      <c r="E2" s="187" t="s">
-        <v>419</v>
-      </c>
-      <c r="F2" s="188" t="s">
+      <c r="C3" s="181" t="s">
         <v>361</v>
       </c>
-      <c r="G2" s="251" t="s">
-        <v>171</v>
-      </c>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="252"/>
-      <c r="L2" s="338" t="s">
-        <v>276</v>
-      </c>
-      <c r="M2" s="339"/>
-      <c r="N2" s="339"/>
-      <c r="O2" s="340"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="341" t="s">
-        <v>238</v>
-      </c>
-      <c r="R2" s="342"/>
-      <c r="S2" s="342"/>
-      <c r="T2" s="343"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="335" t="s">
-        <v>261</v>
-      </c>
-      <c r="W2" s="336"/>
-      <c r="X2" s="336"/>
-      <c r="Y2" s="336"/>
-      <c r="Z2" s="336"/>
-      <c r="AA2" s="336"/>
-      <c r="AB2" s="337"/>
-    </row>
-    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B3" s="195" t="s">
+      <c r="D3" s="190" t="s">
         <v>362</v>
       </c>
-      <c r="C3" s="190" t="s">
+      <c r="E3" s="176" t="s">
         <v>363</v>
       </c>
-      <c r="D3" s="199" t="s">
+      <c r="F3" s="177" t="s">
         <v>364</v>
-      </c>
-      <c r="E3" s="185" t="s">
-        <v>365</v>
-      </c>
-      <c r="F3" s="186" t="s">
-        <v>366</v>
       </c>
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="248" t="s">
+      <c r="H3" s="279" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="290"/>
-      <c r="J3" s="249"/>
+      <c r="I3" s="280"/>
+      <c r="J3" s="281"/>
       <c r="L3" s="126" t="s">
+        <v>223</v>
+      </c>
+      <c r="M3" s="127" t="s">
         <v>224</v>
       </c>
-      <c r="M3" s="127" t="s">
+      <c r="N3" s="128" t="s">
         <v>225</v>
       </c>
-      <c r="N3" s="128" t="s">
+      <c r="O3" s="129" t="s">
         <v>226</v>
-      </c>
-      <c r="O3" s="129" t="s">
-        <v>227</v>
       </c>
       <c r="P3" s="114"/>
       <c r="Q3" s="150" t="s">
+        <v>223</v>
+      </c>
+      <c r="R3" s="151" t="s">
         <v>224</v>
       </c>
-      <c r="R3" s="151" t="s">
+      <c r="S3" s="151" t="s">
         <v>225</v>
       </c>
-      <c r="S3" s="151" t="s">
+      <c r="T3" s="152" t="s">
         <v>226</v>
-      </c>
-      <c r="T3" s="152" t="s">
-        <v>227</v>
       </c>
       <c r="U3" s="114"/>
       <c r="V3" s="150" t="s">
+        <v>223</v>
+      </c>
+      <c r="W3" s="153" t="s">
         <v>224</v>
       </c>
-      <c r="W3" s="153" t="s">
+      <c r="X3" s="151" t="s">
         <v>225</v>
       </c>
-      <c r="X3" s="151" t="s">
+      <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Y3" s="152" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z3" s="330" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA3" s="331"/>
-      <c r="AB3" s="332"/>
-    </row>
-    <row r="4" spans="2:28" ht="53.25" customHeight="1">
-      <c r="B4" s="196" t="s">
+      <c r="Z3" s="241" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA3" s="242"/>
+      <c r="AB3" s="243"/>
+    </row>
+    <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="187" t="s">
+        <v>365</v>
+      </c>
+      <c r="C4" s="182" t="s">
+        <v>366</v>
+      </c>
+      <c r="D4" s="191" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="191" t="s">
+      <c r="E4" s="171" t="s">
         <v>368</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="F4" s="172" t="s">
         <v>369</v>
-      </c>
-      <c r="E4" s="180" t="s">
-        <v>370</v>
-      </c>
-      <c r="F4" s="181" t="s">
-        <v>371</v>
       </c>
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="274">
+      <c r="H4" s="276">
         <v>63</v>
       </c>
-      <c r="I4" s="275"/>
-      <c r="J4" s="276"/>
+      <c r="I4" s="277"/>
+      <c r="J4" s="278"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
-      <c r="M4" s="158" t="s">
-        <v>228</v>
+      <c r="M4" s="157" t="s">
+        <v>227</v>
       </c>
       <c r="N4" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="O4" s="116" t="s">
         <v>269</v>
-      </c>
-      <c r="O4" s="116" t="s">
-        <v>271</v>
       </c>
       <c r="P4" s="114"/>
       <c r="Q4" s="144" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R4" s="120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S4" s="118" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T4" s="119" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U4" s="114"/>
       <c r="V4" s="144" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W4" s="120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X4" s="118" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Y4" s="119" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z4" s="333" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="238"/>
-    </row>
-    <row r="5" spans="2:28" ht="47.25" customHeight="1">
-      <c r="B5" s="197" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z4" s="244" t="s">
+        <v>422</v>
+      </c>
+      <c r="AA4" s="245"/>
+      <c r="AB4" s="246"/>
+    </row>
+    <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="188" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="182" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>371</v>
+      </c>
+      <c r="E5" s="171" t="s">
         <v>372</v>
       </c>
-      <c r="C5" s="191" t="s">
-        <v>363</v>
-      </c>
-      <c r="D5" s="200" t="s">
+      <c r="F5" s="172" t="s">
         <v>373</v>
-      </c>
-      <c r="E5" s="180" t="s">
-        <v>374</v>
-      </c>
-      <c r="F5" s="181" t="s">
-        <v>375</v>
       </c>
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="274">
+      <c r="H5" s="276">
         <v>31</v>
       </c>
-      <c r="I5" s="275"/>
-      <c r="J5" s="276"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="278"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
       <c r="M5" s="91" t="s">
-        <v>228</v>
-      </c>
-      <c r="N5" s="155" t="s">
-        <v>270</v>
+        <v>227</v>
+      </c>
+      <c r="N5" s="154" t="s">
+        <v>268</v>
       </c>
       <c r="O5" s="116" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P5" s="114"/>
       <c r="Q5" s="145" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R5" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S5" s="115" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="T5" s="116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U5" s="114"/>
       <c r="V5" s="145" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W5" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X5" s="115" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Y5" s="116" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z5" s="333"/>
-      <c r="AA5" s="237"/>
-      <c r="AB5" s="238"/>
-    </row>
-    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B6" s="196" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z5" s="244"/>
+      <c r="AA5" s="245"/>
+      <c r="AB5" s="246"/>
+    </row>
+    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="187" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="182" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="191" t="s">
+        <v>375</v>
+      </c>
+      <c r="E6" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="C6" s="191" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="200" t="s">
+      <c r="F6" s="172" t="s">
         <v>377</v>
-      </c>
-      <c r="E6" s="180" t="s">
-        <v>378</v>
-      </c>
-      <c r="F6" s="181" t="s">
-        <v>379</v>
       </c>
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="273">
         <v>7</v>
       </c>
-      <c r="I6" s="295"/>
-      <c r="J6" s="296"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="275"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
       <c r="M6" s="123" t="s">
+        <v>419</v>
+      </c>
+      <c r="N6" s="92" t="s">
         <v>421</v>
       </c>
-      <c r="N6" s="92" t="s">
-        <v>423</v>
-      </c>
       <c r="O6" s="116" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P6" s="114"/>
       <c r="Q6" s="145" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R6" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S6" s="115" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="T6" s="116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U6" s="114"/>
       <c r="V6" s="146" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W6" s="122" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X6" s="117" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Y6" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z6" s="334"/>
-      <c r="AA6" s="240"/>
-      <c r="AB6" s="241"/>
-    </row>
-    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1">
-      <c r="B7" s="197" t="s">
+      <c r="Z6" s="247"/>
+      <c r="AA6" s="248"/>
+      <c r="AB6" s="249"/>
+    </row>
+    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="188" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="182" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="191" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="171" t="s">
         <v>380</v>
       </c>
-      <c r="C7" s="191" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="200" t="s">
+      <c r="F7" s="172" t="s">
         <v>381</v>
       </c>
-      <c r="E7" s="180" t="s">
-        <v>382</v>
-      </c>
-      <c r="F7" s="181" t="s">
-        <v>383</v>
-      </c>
       <c r="G7" s="87" t="s">
-        <v>223</v>
-      </c>
-      <c r="H7" s="347" t="str">
+        <v>222</v>
+      </c>
+      <c r="H7" s="268" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="348"/>
-      <c r="J7" s="349"/>
+      <c r="I7" s="269"/>
+      <c r="J7" s="270"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
       <c r="M7" s="124" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N7" s="93" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="O7" s="125" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P7" s="114"/>
       <c r="Q7" s="145" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R7" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S7" s="115" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="T7" s="116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U7" s="114"/>
     </row>
-    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B8" s="196" t="s">
+    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="187" t="s">
+        <v>382</v>
+      </c>
+      <c r="C8" s="183" t="s">
+        <v>383</v>
+      </c>
+      <c r="D8" s="192" t="s">
         <v>384</v>
       </c>
-      <c r="C8" s="192" t="s">
+      <c r="E8" s="170" t="s">
+        <v>384</v>
+      </c>
+      <c r="F8" s="173" t="s">
         <v>385</v>
-      </c>
-      <c r="D8" s="201" t="s">
-        <v>386</v>
-      </c>
-      <c r="E8" s="179" t="s">
-        <v>386</v>
-      </c>
-      <c r="F8" s="182" t="s">
-        <v>387</v>
       </c>
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="347" t="str">
+      <c r="H8" s="268" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="348"/>
-      <c r="J8" s="349"/>
-      <c r="L8" s="209" t="s">
-        <v>420</v>
-      </c>
-      <c r="M8" s="245"/>
-      <c r="N8" s="245"/>
-      <c r="O8" s="210"/>
+      <c r="I8" s="269"/>
+      <c r="J8" s="270"/>
+      <c r="L8" s="262" t="s">
+        <v>418</v>
+      </c>
+      <c r="M8" s="263"/>
+      <c r="N8" s="263"/>
+      <c r="O8" s="264"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
+        <v>232</v>
+      </c>
+      <c r="R8" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="S8" s="115" t="s">
         <v>233</v>
       </c>
-      <c r="R8" s="121" t="s">
-        <v>228</v>
-      </c>
-      <c r="S8" s="115" t="s">
-        <v>234</v>
-      </c>
       <c r="T8" s="116" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U8" s="114"/>
-      <c r="X8" s="154" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1">
-      <c r="B9" s="196" t="s">
+      <c r="V8" s="231" t="s">
+        <v>454</v>
+      </c>
+      <c r="W8" s="237" t="s">
+        <v>455</v>
+      </c>
+      <c r="X8" s="238"/>
+      <c r="Y8" s="230"/>
+    </row>
+    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="187" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D9" s="191" t="s">
         <v>388</v>
       </c>
-      <c r="C9" s="191" t="s">
+      <c r="E9" s="171" t="s">
         <v>389</v>
       </c>
-      <c r="D9" s="200" t="s">
+      <c r="F9" s="172" t="s">
         <v>390</v>
-      </c>
-      <c r="E9" s="180" t="s">
-        <v>391</v>
-      </c>
-      <c r="F9" s="181" t="s">
-        <v>392</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
@@ -8954,34 +9286,41 @@
       <c r="J9" s="15"/>
       <c r="P9" s="114"/>
       <c r="Q9" s="146" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R9" s="122" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S9" s="117" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T9" s="125" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U9" s="114"/>
-    </row>
-    <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1">
-      <c r="B10" s="196" t="s">
+      <c r="V9" s="67">
+        <v>1</v>
+      </c>
+      <c r="W9" s="239" t="s">
+        <v>457</v>
+      </c>
+      <c r="X9" s="240"/>
+    </row>
+    <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="187" t="s">
+        <v>391</v>
+      </c>
+      <c r="C10" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="191" t="s">
+        <v>392</v>
+      </c>
+      <c r="E10" s="171" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D10" s="200" t="s">
+      <c r="F10" s="172" t="s">
         <v>394</v>
-      </c>
-      <c r="E10" s="180" t="s">
-        <v>395</v>
-      </c>
-      <c r="F10" s="181" t="s">
-        <v>396</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
@@ -8993,22 +9332,29 @@
       <c r="O10" s="114"/>
       <c r="P10" s="114"/>
       <c r="U10" s="114"/>
-    </row>
-    <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1">
-      <c r="B11" s="196" t="s">
+      <c r="V10" s="2">
+        <v>2</v>
+      </c>
+      <c r="W10" s="235" t="s">
+        <v>456</v>
+      </c>
+      <c r="X10" s="236"/>
+    </row>
+    <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="187" t="s">
+        <v>395</v>
+      </c>
+      <c r="C11" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D11" s="191" t="s">
+        <v>396</v>
+      </c>
+      <c r="E11" s="171" t="s">
         <v>397</v>
       </c>
-      <c r="C11" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D11" s="200" t="s">
+      <c r="F11" s="172" t="s">
         <v>398</v>
-      </c>
-      <c r="E11" s="180" t="s">
-        <v>399</v>
-      </c>
-      <c r="F11" s="181" t="s">
-        <v>400</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -9019,28 +9365,35 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="344" t="s">
-        <v>260</v>
-      </c>
-      <c r="R11" s="345"/>
-      <c r="S11" s="345"/>
-      <c r="T11" s="346"/>
+      <c r="Q11" s="259" t="s">
+        <v>259</v>
+      </c>
+      <c r="R11" s="260"/>
+      <c r="S11" s="260"/>
+      <c r="T11" s="261"/>
       <c r="U11" s="114"/>
-    </row>
-    <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1">
-      <c r="B12" s="196" t="s">
+      <c r="V11" s="1">
+        <v>3</v>
+      </c>
+      <c r="W11" s="235" t="s">
+        <v>426</v>
+      </c>
+      <c r="X11" s="236"/>
+    </row>
+    <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="187" t="s">
+        <v>399</v>
+      </c>
+      <c r="C12" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D12" s="191" t="s">
+        <v>400</v>
+      </c>
+      <c r="E12" s="171" t="s">
         <v>401</v>
       </c>
-      <c r="C12" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D12" s="200" t="s">
-        <v>402</v>
-      </c>
-      <c r="E12" s="180" t="s">
-        <v>403</v>
-      </c>
-      <c r="F12" s="181"/>
+      <c r="F12" s="172"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
@@ -9051,33 +9404,38 @@
       <c r="O12" s="114"/>
       <c r="P12" s="114"/>
       <c r="Q12" s="126" t="s">
-        <v>242</v>
-      </c>
-      <c r="R12" s="156" t="s">
+        <v>241</v>
+      </c>
+      <c r="R12" s="155" t="s">
+        <v>224</v>
+      </c>
+      <c r="S12" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="S12" s="156" t="s">
+      <c r="T12" s="156" t="s">
         <v>226</v>
       </c>
-      <c r="T12" s="157" t="s">
-        <v>227</v>
-      </c>
       <c r="U12" s="114"/>
-    </row>
-    <row r="13" spans="2:28" ht="47.25" customHeight="1">
-      <c r="B13" s="196" t="s">
+      <c r="V12" s="2">
+        <v>4</v>
+      </c>
+      <c r="W12" s="235"/>
+      <c r="X12" s="236"/>
+    </row>
+    <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="187" t="s">
+        <v>402</v>
+      </c>
+      <c r="C13" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D13" s="191" t="s">
+        <v>403</v>
+      </c>
+      <c r="E13" s="171" t="s">
         <v>404</v>
       </c>
-      <c r="C13" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D13" s="200" t="s">
-        <v>405</v>
-      </c>
-      <c r="E13" s="180" t="s">
-        <v>406</v>
-      </c>
-      <c r="F13" s="181"/>
+      <c r="F13" s="172"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
@@ -9088,33 +9446,38 @@
       <c r="O13" s="114"/>
       <c r="P13" s="114"/>
       <c r="Q13" s="147" t="s">
+        <v>242</v>
+      </c>
+      <c r="R13" s="141" t="s">
         <v>243</v>
       </c>
-      <c r="R13" s="141" t="s">
+      <c r="S13" s="142" t="s">
         <v>244</v>
       </c>
-      <c r="S13" s="142" t="s">
+      <c r="T13" s="143" t="s">
         <v>245</v>
       </c>
-      <c r="T13" s="143" t="s">
-        <v>246</v>
-      </c>
       <c r="U13" s="114"/>
-    </row>
-    <row r="14" spans="2:28" ht="47.25" customHeight="1">
-      <c r="B14" s="196" t="s">
+      <c r="V13" s="1">
+        <v>5</v>
+      </c>
+      <c r="W13" s="235"/>
+      <c r="X13" s="236"/>
+    </row>
+    <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="187" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" s="191" t="s">
+        <v>406</v>
+      </c>
+      <c r="E14" s="171" t="s">
         <v>407</v>
       </c>
-      <c r="C14" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D14" s="200" t="s">
-        <v>408</v>
-      </c>
-      <c r="E14" s="180" t="s">
-        <v>409</v>
-      </c>
-      <c r="F14" s="181"/>
+      <c r="F14" s="172"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
@@ -9125,33 +9488,38 @@
       <c r="O14" s="114"/>
       <c r="P14" s="114"/>
       <c r="Q14" s="148" t="s">
+        <v>246</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="S14" s="134" t="s">
         <v>247</v>
       </c>
-      <c r="R14" s="139" t="s">
-        <v>244</v>
-      </c>
-      <c r="S14" s="134" t="s">
+      <c r="T14" s="135" t="s">
         <v>248</v>
       </c>
-      <c r="T14" s="135" t="s">
-        <v>249</v>
-      </c>
       <c r="U14" s="114"/>
-    </row>
-    <row r="15" spans="2:28" ht="69" customHeight="1">
-      <c r="B15" s="196" t="s">
+      <c r="V14" s="2">
+        <v>6</v>
+      </c>
+      <c r="W14" s="235"/>
+      <c r="X14" s="236"/>
+    </row>
+    <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="187" t="s">
+        <v>408</v>
+      </c>
+      <c r="C15" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" s="191" t="s">
+        <v>409</v>
+      </c>
+      <c r="E15" s="171" t="s">
         <v>410</v>
       </c>
-      <c r="C15" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D15" s="200" t="s">
-        <v>411</v>
-      </c>
-      <c r="E15" s="180" t="s">
-        <v>412</v>
-      </c>
-      <c r="F15" s="181"/>
+      <c r="F15" s="172"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
@@ -9162,75 +9530,90 @@
       <c r="O15" s="114"/>
       <c r="P15" s="114"/>
       <c r="Q15" s="148" t="s">
+        <v>249</v>
+      </c>
+      <c r="R15" s="139" t="s">
         <v>250</v>
       </c>
-      <c r="R15" s="139" t="s">
+      <c r="S15" s="134" t="s">
         <v>251</v>
       </c>
-      <c r="S15" s="134" t="s">
+      <c r="T15" s="135" t="s">
         <v>252</v>
       </c>
-      <c r="T15" s="135" t="s">
+      <c r="U15" s="114"/>
+      <c r="V15" s="1">
+        <v>7</v>
+      </c>
+      <c r="W15" s="235"/>
+      <c r="X15" s="236"/>
+    </row>
+    <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="187" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="D16" s="191" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="171" t="s">
+        <v>413</v>
+      </c>
+      <c r="F16" s="172"/>
+      <c r="Q16" s="148" t="s">
         <v>253</v>
       </c>
-      <c r="U15" s="114"/>
-    </row>
-    <row r="16" spans="2:28" ht="62.25" customHeight="1">
-      <c r="B16" s="196" t="s">
-        <v>413</v>
-      </c>
-      <c r="C16" s="191" t="s">
-        <v>389</v>
-      </c>
-      <c r="D16" s="200" t="s">
+      <c r="R16" s="139" t="s">
+        <v>227</v>
+      </c>
+      <c r="S16" s="134" t="s">
+        <v>254</v>
+      </c>
+      <c r="T16" s="136" t="s">
+        <v>255</v>
+      </c>
+      <c r="V16" s="2">
+        <v>8</v>
+      </c>
+      <c r="W16" s="235"/>
+      <c r="X16" s="236"/>
+    </row>
+    <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="189" t="s">
         <v>414</v>
       </c>
-      <c r="E16" s="180" t="s">
+      <c r="C17" s="184" t="s">
+        <v>387</v>
+      </c>
+      <c r="D17" s="193" t="s">
         <v>415</v>
       </c>
-      <c r="F16" s="181"/>
-      <c r="Q16" s="148" t="s">
-        <v>254</v>
-      </c>
-      <c r="R16" s="139" t="s">
-        <v>228</v>
-      </c>
-      <c r="S16" s="134" t="s">
-        <v>255</v>
-      </c>
-      <c r="T16" s="136" t="s">
+      <c r="E17" s="174" t="s">
+        <v>416</v>
+      </c>
+      <c r="F17" s="175"/>
+      <c r="Q17" s="149" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="17" spans="2:20" ht="69.75" customHeight="1" thickBot="1">
-      <c r="B17" s="198" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="193" t="s">
-        <v>389</v>
-      </c>
-      <c r="D17" s="202" t="s">
-        <v>417</v>
-      </c>
-      <c r="E17" s="183" t="s">
-        <v>418</v>
-      </c>
-      <c r="F17" s="184"/>
-      <c r="Q17" s="149" t="s">
+      <c r="R17" s="140" t="s">
+        <v>250</v>
+      </c>
+      <c r="S17" s="137" t="s">
         <v>257</v>
       </c>
-      <c r="R17" s="140" t="s">
-        <v>251</v>
-      </c>
-      <c r="S17" s="137" t="s">
+      <c r="T17" s="138" t="s">
         <v>258</v>
       </c>
-      <c r="T17" s="138" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="51.75" customHeight="1" thickBot="1"/>
-    <row r="19" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
+      <c r="V17" s="232">
+        <v>9</v>
+      </c>
+      <c r="W17" s="233"/>
+      <c r="X17" s="234"/>
+    </row>
+    <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="102" t="s">
         <v>178</v>
       </c>
@@ -9246,18 +9629,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="267" t="s">
+      <c r="G19" s="265" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="268"/>
-      <c r="I19" s="268"/>
-      <c r="J19" s="269"/>
-    </row>
-    <row r="20" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B20" s="170" t="s">
+      <c r="H19" s="266"/>
+      <c r="I19" s="266"/>
+      <c r="J19" s="267"/>
+    </row>
+    <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="168" t="s">
+      <c r="C20" s="428" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9269,16 +9652,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="174" t="s">
-        <v>221</v>
-      </c>
-      <c r="H20" s="175"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="176"/>
-    </row>
-    <row r="21" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B21" s="177"/>
-      <c r="C21" s="178"/>
+      <c r="G20" s="425" t="s">
+        <v>458</v>
+      </c>
+      <c r="H20" s="426"/>
+      <c r="I20" s="426"/>
+      <c r="J20" s="427"/>
+    </row>
+    <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="169"/>
+      <c r="C21" s="429"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9288,16 +9671,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="H21" s="172"/>
-      <c r="I21" s="172"/>
-      <c r="J21" s="173"/>
-    </row>
-    <row r="22" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B22" s="171"/>
-      <c r="C22" s="169"/>
+      <c r="G21" s="268" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" s="269"/>
+      <c r="I21" s="269"/>
+      <c r="J21" s="270"/>
+    </row>
+    <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="168"/>
+      <c r="C22" s="430"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9312,11 +9695,11 @@
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B23" s="170" t="s">
+    <row r="23" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="168" t="s">
+      <c r="C23" s="428" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9333,9 +9716,9 @@
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B24" s="171"/>
-      <c r="C24" s="169"/>
+    <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="168"/>
+      <c r="C24" s="430"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9350,11 +9733,11 @@
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B25" s="170" t="s">
+    <row r="25" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="168" t="s">
+      <c r="C25" s="428" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9371,9 +9754,9 @@
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B26" s="171"/>
-      <c r="C26" s="169"/>
+    <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="168"/>
+      <c r="C26" s="430"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9388,11 +9771,11 @@
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B27" s="170" t="s">
+    <row r="27" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="168" t="s">
+      <c r="C27" s="428" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9409,9 +9792,9 @@
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B28" s="171"/>
-      <c r="C28" s="169"/>
+    <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="168"/>
+      <c r="C28" s="430"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9426,7 +9809,7 @@
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
+    <row r="29" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="113" t="s">
         <v>208</v>
       </c>
@@ -9447,11 +9830,11 @@
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B30" s="170" t="s">
+    <row r="30" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="168" t="s">
+      <c r="C30" s="428" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9468,9 +9851,9 @@
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="2:20" ht="45.75" thickBot="1">
-      <c r="B31" s="171"/>
-      <c r="C31" s="169"/>
+    <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="168"/>
+      <c r="C31" s="430"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9485,11 +9868,11 @@
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="2:20" ht="30">
-      <c r="B32" s="170" t="s">
+    <row r="32" spans="2:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="168" t="s">
+      <c r="C32" s="428" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9506,9 +9889,9 @@
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
     </row>
-    <row r="33" spans="2:10" ht="57.75" thickBot="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="169"/>
+    <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="168"/>
+      <c r="C33" s="430"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9524,9 +9907,15 @@
       <c r="J33" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="L8:O8"/>
+  <mergeCells count="33">
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="G2:J2"/>
@@ -9535,14 +9924,344 @@
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="Z4:AB6"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="Z4:AB6"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B07C92-48AD-46D8-AFE8-A66BE9216D0D}">
+  <dimension ref="B1:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="419" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2" s="420"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
+      <c r="G2" s="421"/>
+      <c r="H2" s="422"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="194" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" s="195" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="195" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" s="195" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="195" t="s">
+        <v>431</v>
+      </c>
+      <c r="G3" s="417" t="s">
+        <v>430</v>
+      </c>
+      <c r="H3" s="418"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="196">
+        <v>0</v>
+      </c>
+      <c r="C4" s="202"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="223" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="423" t="s">
+        <v>437</v>
+      </c>
+      <c r="H4" s="424"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="197">
+        <v>1</v>
+      </c>
+      <c r="C5" s="198" t="s">
+        <v>440</v>
+      </c>
+      <c r="D5" s="228"/>
+      <c r="E5" s="222" t="s">
+        <v>442</v>
+      </c>
+      <c r="F5" s="224" t="s">
+        <v>432</v>
+      </c>
+      <c r="G5" s="408" t="s">
+        <v>441</v>
+      </c>
+      <c r="H5" s="409"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="197">
+        <v>2</v>
+      </c>
+      <c r="C6" s="229"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="200" t="s">
+        <v>442</v>
+      </c>
+      <c r="F6" s="224" t="s">
+        <v>433</v>
+      </c>
+      <c r="G6" s="408" t="s">
+        <v>438</v>
+      </c>
+      <c r="H6" s="409"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="197">
+        <v>3</v>
+      </c>
+      <c r="C7" s="207"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="224" t="s">
+        <v>434</v>
+      </c>
+      <c r="G7" s="408" t="s">
+        <v>439</v>
+      </c>
+      <c r="H7" s="409"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="197">
+        <v>4</v>
+      </c>
+      <c r="C8" s="198" t="s">
+        <v>443</v>
+      </c>
+      <c r="D8" s="199" t="s">
+        <v>444</v>
+      </c>
+      <c r="E8" s="206"/>
+      <c r="F8" s="224" t="s">
+        <v>435</v>
+      </c>
+      <c r="G8" s="408" t="s">
+        <v>445</v>
+      </c>
+      <c r="H8" s="409"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="197">
+        <v>5</v>
+      </c>
+      <c r="C9" s="207"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="225" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="410"/>
+      <c r="H9" s="411"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="197">
+        <v>6</v>
+      </c>
+      <c r="C10" s="207"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="226" t="s">
+        <v>436</v>
+      </c>
+      <c r="G10" s="410"/>
+      <c r="H10" s="411"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="201">
+        <v>7</v>
+      </c>
+      <c r="C11" s="208"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="227" t="s">
+        <v>436</v>
+      </c>
+      <c r="G11" s="412"/>
+      <c r="H11" s="413"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="212" t="s">
+        <v>447</v>
+      </c>
+      <c r="C13" s="414" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="415"/>
+      <c r="E13" s="416"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="213">
+        <v>0</v>
+      </c>
+      <c r="C14" s="399" t="s">
+        <v>452</v>
+      </c>
+      <c r="D14" s="400"/>
+      <c r="E14" s="401"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="214">
+        <v>1</v>
+      </c>
+      <c r="C15" s="402" t="s">
+        <v>450</v>
+      </c>
+      <c r="D15" s="403"/>
+      <c r="E15" s="404"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="214">
+        <v>2</v>
+      </c>
+      <c r="C16" s="390" t="s">
+        <v>451</v>
+      </c>
+      <c r="D16" s="391"/>
+      <c r="E16" s="392"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="214">
+        <v>3</v>
+      </c>
+      <c r="C17" s="405" t="s">
+        <v>453</v>
+      </c>
+      <c r="D17" s="406"/>
+      <c r="E17" s="407"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="214">
+        <v>4</v>
+      </c>
+      <c r="C18" s="393"/>
+      <c r="D18" s="394"/>
+      <c r="E18" s="395"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="214">
+        <v>5</v>
+      </c>
+      <c r="C19" s="393"/>
+      <c r="D19" s="394"/>
+      <c r="E19" s="395"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="214">
+        <v>6</v>
+      </c>
+      <c r="C20" s="393"/>
+      <c r="D20" s="394"/>
+      <c r="E20" s="395"/>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="215">
+        <v>7</v>
+      </c>
+      <c r="C21" s="396"/>
+      <c r="D21" s="397"/>
+      <c r="E21" s="398"/>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="388" t="s">
+        <v>446</v>
+      </c>
+      <c r="C23" s="211">
+        <v>5</v>
+      </c>
+      <c r="D23" s="218">
+        <v>4</v>
+      </c>
+      <c r="E23" s="218">
+        <v>3</v>
+      </c>
+      <c r="F23" s="218">
+        <v>2</v>
+      </c>
+      <c r="G23" s="218">
+        <v>1</v>
+      </c>
+      <c r="H23" s="219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="389"/>
+      <c r="C24" s="220"/>
+      <c r="D24" s="221"/>
+      <c r="E24" s="221"/>
+      <c r="F24" s="221"/>
+      <c r="G24" s="216" t="s">
+        <v>449</v>
+      </c>
+      <c r="H24" s="217" t="s">
+        <v>448</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DDF818-0A77-4FDB-871D-E243F8A19FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787BD476-9523-4D51-AED7-9AF633FAF38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="462">
   <si>
     <t>OpCode</t>
   </si>
@@ -1424,9 +1424,6 @@
     <t>0x28</t>
   </si>
   <si>
-    <t>Valores que guardan las interrupciones en cola (mapa de bits). Se puede usar para generar una auto interrupción</t>
-  </si>
-  <si>
     <t>SP: Punto del stack</t>
   </si>
   <si>
@@ -2379,6 +2376,18 @@
   </si>
   <si>
     <t>Base-Sub-Prog IF-Header Type</t>
+  </si>
+  <si>
+    <t>0x2C</t>
+  </si>
+  <si>
+    <t>MSI Vector (32 bits)</t>
+  </si>
+  <si>
+    <t>Entrada para las insterrupciones MSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores que guardan las interrupciones en cola (mapa de bits). </t>
   </si>
 </sst>
 </file>
@@ -2545,7 +2554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="77">
+  <borders count="75">
     <border>
       <left/>
       <right/>
@@ -3481,34 +3490,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="431">
+  <cellXfs count="425">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4186,151 +4173,409 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4360,9 +4605,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4387,269 +4629,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4684,101 +4746,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5081,7 +5050,7 @@
     <col min="16" max="16" width="20" style="15" customWidth="1"/>
     <col min="17" max="17" width="9.140625" style="15" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" style="15" customWidth="1"/>
-    <col min="19" max="19" width="15.42578125" style="15" customWidth="1"/>
+    <col min="19" max="19" width="20.5703125" style="15" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="15" customWidth="1"/>
     <col min="21" max="21" width="8.85546875" style="15" customWidth="1"/>
     <col min="22" max="22" width="9.28515625" style="15" customWidth="1"/>
@@ -5100,62 +5069,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="352" t="s">
+      <c r="B2" s="325" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="364" t="s">
+      <c r="C2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="365"/>
-      <c r="E2" s="366" t="s">
+      <c r="D2" s="335"/>
+      <c r="E2" s="336" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="366"/>
-      <c r="G2" s="367" t="s">
+      <c r="F2" s="336"/>
+      <c r="G2" s="337" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="366"/>
-      <c r="I2" s="366" t="s">
+      <c r="H2" s="336"/>
+      <c r="I2" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="366"/>
-      <c r="K2" s="368" t="s">
+      <c r="J2" s="336"/>
+      <c r="K2" s="338" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="366"/>
-      <c r="M2" s="366"/>
-      <c r="N2" s="366"/>
-      <c r="O2" s="366"/>
-      <c r="P2" s="369"/>
-      <c r="R2" s="349" t="s">
+      <c r="L2" s="336"/>
+      <c r="M2" s="336"/>
+      <c r="N2" s="336"/>
+      <c r="O2" s="336"/>
+      <c r="P2" s="339"/>
+      <c r="R2" s="342" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="347" t="s">
+      <c r="S2" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="340" t="s">
+      <c r="T2" s="346" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="341"/>
-      <c r="V2" s="341"/>
-      <c r="W2" s="341"/>
-      <c r="X2" s="341"/>
-      <c r="Y2" s="341"/>
-      <c r="Z2" s="341"/>
-      <c r="AA2" s="341"/>
-      <c r="AB2" s="341" t="s">
+      <c r="U2" s="347"/>
+      <c r="V2" s="347"/>
+      <c r="W2" s="347"/>
+      <c r="X2" s="347"/>
+      <c r="Y2" s="347"/>
+      <c r="Z2" s="347"/>
+      <c r="AA2" s="347"/>
+      <c r="AB2" s="347" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="341"/>
-      <c r="AD2" s="341"/>
-      <c r="AE2" s="341"/>
-      <c r="AF2" s="341"/>
-      <c r="AG2" s="341"/>
-      <c r="AH2" s="341"/>
-      <c r="AI2" s="342"/>
+      <c r="AC2" s="347"/>
+      <c r="AD2" s="347"/>
+      <c r="AE2" s="347"/>
+      <c r="AF2" s="347"/>
+      <c r="AG2" s="347"/>
+      <c r="AH2" s="347"/>
+      <c r="AI2" s="348"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="353"/>
+      <c r="B3" s="326"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5181,20 +5150,20 @@
         <v>31</v>
       </c>
       <c r="K3" s="331"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
-      <c r="N3" s="363"/>
-      <c r="O3" s="363"/>
-      <c r="P3" s="332"/>
-      <c r="R3" s="350"/>
-      <c r="S3" s="291"/>
+      <c r="L3" s="332"/>
+      <c r="M3" s="332"/>
+      <c r="N3" s="332"/>
+      <c r="O3" s="332"/>
+      <c r="P3" s="333"/>
+      <c r="R3" s="343"/>
+      <c r="S3" s="340"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="373" t="s">
+      <c r="U3" s="312" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="373"/>
+      <c r="V3" s="312"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5207,10 +5176,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="339" t="s">
+      <c r="AA3" s="345" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="339"/>
+      <c r="AB3" s="345"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5234,21 +5203,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="354"/>
+      <c r="B4" s="327"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="343" t="s">
+      <c r="E4" s="313" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="267"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="244"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5258,20 +5227,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="343" t="s">
+      <c r="N4" s="313" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="266"/>
-      <c r="P4" s="267"/>
-      <c r="R4" s="351"/>
-      <c r="S4" s="348"/>
+      <c r="O4" s="243"/>
+      <c r="P4" s="244"/>
+      <c r="R4" s="344"/>
+      <c r="S4" s="341"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="343" t="s">
+      <c r="U4" s="313" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="344"/>
+      <c r="V4" s="314"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5284,10 +5253,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="343" t="s">
+      <c r="AA4" s="313" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="344"/>
+      <c r="AB4" s="314"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5319,22 +5288,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="370"/>
-      <c r="F5" s="371"/>
-      <c r="G5" s="371"/>
-      <c r="H5" s="371"/>
-      <c r="I5" s="371"/>
-      <c r="J5" s="372"/>
+      <c r="E5" s="317"/>
+      <c r="F5" s="318"/>
+      <c r="G5" s="318"/>
+      <c r="H5" s="318"/>
+      <c r="I5" s="318"/>
+      <c r="J5" s="319"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="279" t="s">
+      <c r="N5" s="253" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="280"/>
-      <c r="P5" s="281"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="255"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5344,10 +5313,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="345" t="s">
+      <c r="U5" s="315" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="346"/>
+      <c r="V5" s="316"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5360,10 +5329,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="345" t="s">
+      <c r="AA5" s="315" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="346"/>
+      <c r="AB5" s="316"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5395,12 +5364,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="361"/>
-      <c r="F6" s="356"/>
-      <c r="G6" s="356"/>
-      <c r="H6" s="356"/>
-      <c r="I6" s="356"/>
-      <c r="J6" s="357"/>
+      <c r="E6" s="324"/>
+      <c r="F6" s="321"/>
+      <c r="G6" s="321"/>
+      <c r="H6" s="321"/>
+      <c r="I6" s="321"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5408,11 +5377,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="276" t="s">
+      <c r="N6" s="250" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="277"/>
-      <c r="P6" s="278"/>
+      <c r="O6" s="251"/>
+      <c r="P6" s="252"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5422,10 +5391,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="335" t="s">
+      <c r="U6" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="336"/>
+      <c r="V6" s="311"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5438,10 +5407,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="335" t="s">
+      <c r="AA6" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="336"/>
+      <c r="AB6" s="311"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5484,9 +5453,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="355"/>
-      <c r="I7" s="356"/>
-      <c r="J7" s="357"/>
+      <c r="H7" s="320"/>
+      <c r="I7" s="321"/>
+      <c r="J7" s="322"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5494,11 +5463,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="276" t="s">
+      <c r="N7" s="250" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="277"/>
-      <c r="P7" s="278"/>
+      <c r="O7" s="251"/>
+      <c r="P7" s="252"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5508,10 +5477,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="335" t="s">
+      <c r="U7" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="336"/>
+      <c r="V7" s="311"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5524,10 +5493,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="335" t="s">
+      <c r="AA7" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="336"/>
+      <c r="AB7" s="311"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5570,9 +5539,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="355"/>
-      <c r="I8" s="356"/>
-      <c r="J8" s="357"/>
+      <c r="H8" s="320"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="322"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5580,11 +5549,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="276" t="s">
+      <c r="N8" s="250" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="277"/>
-      <c r="P8" s="278"/>
+      <c r="O8" s="251"/>
+      <c r="P8" s="252"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5594,10 +5563,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="335" t="s">
+      <c r="U8" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="336"/>
+      <c r="V8" s="311"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5610,10 +5579,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="335" t="s">
+      <c r="AA8" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="336"/>
+      <c r="AB8" s="311"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5656,9 +5625,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="355"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="357"/>
+      <c r="H9" s="320"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="322"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5666,11 +5635,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="276" t="s">
+      <c r="N9" s="250" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="277"/>
-      <c r="P9" s="278"/>
+      <c r="O9" s="251"/>
+      <c r="P9" s="252"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5680,10 +5649,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="335" t="s">
+      <c r="U9" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="336"/>
+      <c r="V9" s="311"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5696,10 +5665,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="335" t="s">
+      <c r="AA9" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="336"/>
+      <c r="AB9" s="311"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5742,9 +5711,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="355"/>
-      <c r="I10" s="356"/>
-      <c r="J10" s="357"/>
+      <c r="H10" s="320"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="322"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5752,11 +5721,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="276" t="s">
+      <c r="N10" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="277"/>
-      <c r="P10" s="278"/>
+      <c r="O10" s="251"/>
+      <c r="P10" s="252"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5766,10 +5735,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="335" t="s">
+      <c r="U10" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="336"/>
+      <c r="V10" s="311"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5782,10 +5751,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="335" t="s">
+      <c r="AA10" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="336"/>
+      <c r="AB10" s="311"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5828,9 +5797,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="355"/>
-      <c r="I11" s="356"/>
-      <c r="J11" s="357"/>
+      <c r="H11" s="320"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="322"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5838,11 +5807,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="276" t="s">
+      <c r="N11" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="277"/>
-      <c r="P11" s="278"/>
+      <c r="O11" s="251"/>
+      <c r="P11" s="252"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5852,10 +5821,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="335" t="s">
+      <c r="U11" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="336"/>
+      <c r="V11" s="311"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5868,10 +5837,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="335" t="s">
+      <c r="AA11" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="336"/>
+      <c r="AB11" s="311"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5914,9 +5883,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="355"/>
-      <c r="I12" s="356"/>
-      <c r="J12" s="357"/>
+      <c r="H12" s="320"/>
+      <c r="I12" s="321"/>
+      <c r="J12" s="322"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5924,11 +5893,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="276" t="s">
+      <c r="N12" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="277"/>
-      <c r="P12" s="278"/>
+      <c r="O12" s="251"/>
+      <c r="P12" s="252"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5938,10 +5907,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="335" t="s">
+      <c r="U12" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="336"/>
+      <c r="V12" s="311"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5954,10 +5923,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="335" t="s">
+      <c r="AA12" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="336"/>
+      <c r="AB12" s="311"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -6000,9 +5969,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="355"/>
-      <c r="I13" s="356"/>
-      <c r="J13" s="357"/>
+      <c r="H13" s="320"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="322"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -6010,11 +5979,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="276" t="s">
+      <c r="N13" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="277"/>
-      <c r="P13" s="278"/>
+      <c r="O13" s="251"/>
+      <c r="P13" s="252"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -6024,10 +5993,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="335" t="s">
+      <c r="U13" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="336"/>
+      <c r="V13" s="311"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6040,10 +6009,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="335" t="s">
+      <c r="AA13" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="336"/>
+      <c r="AB13" s="311"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6086,9 +6055,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="355"/>
-      <c r="I14" s="356"/>
-      <c r="J14" s="357"/>
+      <c r="H14" s="320"/>
+      <c r="I14" s="321"/>
+      <c r="J14" s="322"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6096,11 +6065,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="276" t="s">
+      <c r="N14" s="250" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="277"/>
-      <c r="P14" s="278"/>
+      <c r="O14" s="251"/>
+      <c r="P14" s="252"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6110,10 +6079,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="335" t="s">
+      <c r="U14" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="336"/>
+      <c r="V14" s="311"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6126,10 +6095,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="335" t="s">
+      <c r="AA14" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="336"/>
+      <c r="AB14" s="311"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6172,9 +6141,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="355"/>
-      <c r="I15" s="356"/>
-      <c r="J15" s="357"/>
+      <c r="H15" s="320"/>
+      <c r="I15" s="321"/>
+      <c r="J15" s="322"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6182,11 +6151,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="276" t="s">
+      <c r="N15" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="277"/>
-      <c r="P15" s="278"/>
+      <c r="O15" s="251"/>
+      <c r="P15" s="252"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6196,10 +6165,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="335" t="s">
+      <c r="U15" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="336"/>
+      <c r="V15" s="311"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6212,10 +6181,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="335" t="s">
+      <c r="AA15" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="336"/>
+      <c r="AB15" s="311"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6252,21 +6221,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="355"/>
-      <c r="G16" s="356"/>
-      <c r="H16" s="356"/>
-      <c r="I16" s="356"/>
-      <c r="J16" s="357"/>
+      <c r="F16" s="320"/>
+      <c r="G16" s="321"/>
+      <c r="H16" s="321"/>
+      <c r="I16" s="321"/>
+      <c r="J16" s="322"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="276" t="s">
+      <c r="N16" s="250" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="277"/>
-      <c r="P16" s="278"/>
+      <c r="O16" s="251"/>
+      <c r="P16" s="252"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6276,10 +6245,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="335" t="s">
+      <c r="U16" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="336"/>
+      <c r="V16" s="311"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6292,10 +6261,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="335" t="s">
+      <c r="AA16" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="336"/>
+      <c r="AB16" s="311"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6333,22 +6302,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="362" t="s">
+      <c r="G17" s="323" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="277"/>
-      <c r="I17" s="277"/>
-      <c r="J17" s="278"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="252"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="276" t="s">
+      <c r="N17" s="250" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="277"/>
-      <c r="P17" s="278"/>
+      <c r="O17" s="251"/>
+      <c r="P17" s="252"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6358,10 +6327,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="335" t="s">
+      <c r="U17" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="336"/>
+      <c r="V17" s="311"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6374,10 +6343,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="335" t="s">
+      <c r="AA17" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="336"/>
+      <c r="AB17" s="311"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6415,12 +6384,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="362" t="s">
+      <c r="G18" s="323" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="277"/>
-      <c r="I18" s="277"/>
-      <c r="J18" s="278"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="252"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6428,11 +6397,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="276" t="s">
+      <c r="N18" s="250" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="277"/>
-      <c r="P18" s="278"/>
+      <c r="O18" s="251"/>
+      <c r="P18" s="252"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6442,10 +6411,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="335" t="s">
+      <c r="U18" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="336"/>
+      <c r="V18" s="311"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6458,10 +6427,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="335" t="s">
+      <c r="AA18" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="336"/>
+      <c r="AB18" s="311"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6497,20 +6466,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="355"/>
-      <c r="H19" s="356"/>
-      <c r="I19" s="356"/>
-      <c r="J19" s="357"/>
+      <c r="G19" s="320"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="322"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="276" t="s">
+      <c r="N19" s="250" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="277"/>
-      <c r="P19" s="278"/>
+      <c r="O19" s="251"/>
+      <c r="P19" s="252"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6520,10 +6489,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="335" t="s">
+      <c r="U19" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="336"/>
+      <c r="V19" s="311"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6536,10 +6505,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="335" t="s">
+      <c r="AA19" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="336"/>
+      <c r="AB19" s="311"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6577,20 +6546,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="355"/>
-      <c r="H20" s="356"/>
-      <c r="I20" s="356"/>
-      <c r="J20" s="357"/>
+      <c r="G20" s="320"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="322"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="276" t="s">
+      <c r="N20" s="250" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="277"/>
-      <c r="P20" s="278"/>
+      <c r="O20" s="251"/>
+      <c r="P20" s="252"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6600,10 +6569,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="335" t="s">
+      <c r="U20" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="336"/>
+      <c r="V20" s="311"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6616,10 +6585,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="335" t="s">
+      <c r="AA20" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="336"/>
+      <c r="AB20" s="311"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6657,20 +6626,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="355"/>
-      <c r="H21" s="356"/>
-      <c r="I21" s="356"/>
-      <c r="J21" s="357"/>
+      <c r="G21" s="320"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="322"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="276" t="s">
+      <c r="N21" s="250" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="277"/>
-      <c r="P21" s="278"/>
+      <c r="O21" s="251"/>
+      <c r="P21" s="252"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6680,10 +6649,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="335" t="s">
+      <c r="U21" s="310" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="336"/>
+      <c r="V21" s="311"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6696,10 +6665,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="335" t="s">
+      <c r="AA21" s="310" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="336"/>
+      <c r="AB21" s="311"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6733,22 +6702,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="361"/>
-      <c r="F22" s="356"/>
-      <c r="G22" s="356"/>
-      <c r="H22" s="356"/>
-      <c r="I22" s="356"/>
-      <c r="J22" s="357"/>
+      <c r="E22" s="324"/>
+      <c r="F22" s="321"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="321"/>
+      <c r="I22" s="321"/>
+      <c r="J22" s="322"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="276" t="s">
+      <c r="N22" s="250" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="277"/>
-      <c r="P22" s="278"/>
+      <c r="O22" s="251"/>
+      <c r="P22" s="252"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6758,10 +6727,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="335" t="s">
+      <c r="U22" s="310" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="336"/>
+      <c r="V22" s="311"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6774,10 +6743,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="335" t="s">
+      <c r="AA22" s="310" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="336"/>
+      <c r="AB22" s="311"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6817,22 +6786,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="362" t="s">
+      <c r="G23" s="323" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="277"/>
-      <c r="I23" s="277"/>
-      <c r="J23" s="278"/>
+      <c r="H23" s="251"/>
+      <c r="I23" s="251"/>
+      <c r="J23" s="252"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="276" t="s">
+      <c r="N23" s="250" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="277"/>
-      <c r="P23" s="278"/>
+      <c r="O23" s="251"/>
+      <c r="P23" s="252"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6842,10 +6811,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="335" t="s">
+      <c r="U23" s="310" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="336"/>
+      <c r="V23" s="311"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6858,10 +6827,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="335" t="s">
+      <c r="AA23" s="310" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="336"/>
+      <c r="AB23" s="311"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6901,22 +6870,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="362" t="s">
+      <c r="G24" s="323" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="277"/>
-      <c r="I24" s="277"/>
-      <c r="J24" s="278"/>
+      <c r="H24" s="251"/>
+      <c r="I24" s="251"/>
+      <c r="J24" s="252"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="276" t="s">
+      <c r="N24" s="250" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="277"/>
-      <c r="P24" s="278"/>
+      <c r="O24" s="251"/>
+      <c r="P24" s="252"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6926,10 +6895,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="335" t="s">
+      <c r="U24" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="336"/>
+      <c r="V24" s="311"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6942,10 +6911,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="335" t="s">
+      <c r="AA24" s="310" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="336"/>
+      <c r="AB24" s="311"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6983,10 +6952,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="355"/>
-      <c r="H25" s="356"/>
-      <c r="I25" s="356"/>
-      <c r="J25" s="357"/>
+      <c r="G25" s="320"/>
+      <c r="H25" s="321"/>
+      <c r="I25" s="321"/>
+      <c r="J25" s="322"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6994,11 +6963,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="276" t="s">
+      <c r="N25" s="250" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="277"/>
-      <c r="P25" s="278"/>
+      <c r="O25" s="251"/>
+      <c r="P25" s="252"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -7008,10 +6977,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="335" t="s">
+      <c r="U25" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="336"/>
+      <c r="V25" s="311"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -7024,10 +6993,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="335" t="s">
+      <c r="AA25" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="336"/>
+      <c r="AB25" s="311"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7065,10 +7034,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="355"/>
-      <c r="H26" s="356"/>
-      <c r="I26" s="356"/>
-      <c r="J26" s="357"/>
+      <c r="G26" s="320"/>
+      <c r="H26" s="321"/>
+      <c r="I26" s="321"/>
+      <c r="J26" s="322"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7076,11 +7045,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="276" t="s">
+      <c r="N26" s="250" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="277"/>
-      <c r="P26" s="278"/>
+      <c r="O26" s="251"/>
+      <c r="P26" s="252"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7090,10 +7059,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="335" t="s">
+      <c r="U26" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="336"/>
+      <c r="V26" s="311"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7106,10 +7075,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="335" t="s">
+      <c r="AA26" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="336"/>
+      <c r="AB26" s="311"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7141,22 +7110,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="361"/>
-      <c r="F27" s="356"/>
-      <c r="G27" s="356"/>
-      <c r="H27" s="356"/>
-      <c r="I27" s="356"/>
-      <c r="J27" s="357"/>
+      <c r="E27" s="324"/>
+      <c r="F27" s="321"/>
+      <c r="G27" s="321"/>
+      <c r="H27" s="321"/>
+      <c r="I27" s="321"/>
+      <c r="J27" s="322"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="276" t="s">
+      <c r="N27" s="250" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="277"/>
-      <c r="P27" s="278"/>
+      <c r="O27" s="251"/>
+      <c r="P27" s="252"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7166,10 +7135,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="335" t="s">
+      <c r="U27" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="336"/>
+      <c r="V27" s="311"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7182,10 +7151,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="335" t="s">
+      <c r="AA27" s="310" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="336"/>
+      <c r="AB27" s="311"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7217,12 +7186,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="358"/>
-      <c r="F28" s="359"/>
-      <c r="G28" s="359"/>
-      <c r="H28" s="359"/>
-      <c r="I28" s="359"/>
-      <c r="J28" s="360"/>
+      <c r="E28" s="328"/>
+      <c r="F28" s="329"/>
+      <c r="G28" s="329"/>
+      <c r="H28" s="329"/>
+      <c r="I28" s="329"/>
+      <c r="J28" s="330"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7230,11 +7199,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="273" t="s">
+      <c r="N28" s="247" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="274"/>
-      <c r="P28" s="275"/>
+      <c r="O28" s="248"/>
+      <c r="P28" s="249"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7244,10 +7213,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="337" t="s">
+      <c r="U28" s="357" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="338"/>
+      <c r="V28" s="358"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7260,10 +7229,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="337" t="s">
+      <c r="AA28" s="357" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="338"/>
+      <c r="AB28" s="358"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7340,27 +7309,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="387" t="s">
+      <c r="T30" s="293" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="387"/>
-      <c r="V30" s="387"/>
-      <c r="W30" s="387"/>
-      <c r="X30" s="387"/>
-      <c r="Y30" s="387"/>
-      <c r="Z30" s="387"/>
-      <c r="AA30" s="387"/>
-      <c r="AB30" s="387"/>
-      <c r="AC30" s="347"/>
-      <c r="AE30" s="265" t="s">
+      <c r="U30" s="293"/>
+      <c r="V30" s="293"/>
+      <c r="W30" s="293"/>
+      <c r="X30" s="293"/>
+      <c r="Y30" s="293"/>
+      <c r="Z30" s="293"/>
+      <c r="AA30" s="293"/>
+      <c r="AB30" s="293"/>
+      <c r="AC30" s="294"/>
+      <c r="AE30" s="242" t="s">
+        <v>422</v>
+      </c>
+      <c r="AF30" s="243"/>
+      <c r="AG30" s="242" t="s">
         <v>423</v>
       </c>
-      <c r="AF30" s="266"/>
-      <c r="AG30" s="265" t="s">
-        <v>424</v>
-      </c>
-      <c r="AH30" s="266"/>
-      <c r="AI30" s="267"/>
+      <c r="AH30" s="243"/>
+      <c r="AI30" s="244"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7401,28 +7370,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="279" t="s">
+      <c r="T31" s="253" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="280"/>
-      <c r="V31" s="280"/>
-      <c r="W31" s="280"/>
-      <c r="X31" s="280"/>
-      <c r="Y31" s="280"/>
-      <c r="Z31" s="280"/>
-      <c r="AA31" s="280"/>
-      <c r="AB31" s="280"/>
-      <c r="AC31" s="281"/>
-      <c r="AE31" s="382">
+      <c r="U31" s="254"/>
+      <c r="V31" s="254"/>
+      <c r="W31" s="254"/>
+      <c r="X31" s="254"/>
+      <c r="Y31" s="254"/>
+      <c r="Z31" s="254"/>
+      <c r="AA31" s="254"/>
+      <c r="AB31" s="254"/>
+      <c r="AC31" s="255"/>
+      <c r="AE31" s="288">
         <v>2</v>
       </c>
-      <c r="AF31" s="383"/>
-      <c r="AG31" s="384" t="str" cm="1">
+      <c r="AF31" s="289"/>
+      <c r="AG31" s="290" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="385"/>
-      <c r="AI31" s="386"/>
+      <c r="AH31" s="291"/>
+      <c r="AI31" s="292"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7446,18 +7415,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="276" t="s">
+      <c r="T32" s="250" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="277"/>
-      <c r="V32" s="277"/>
-      <c r="W32" s="277"/>
-      <c r="X32" s="277"/>
-      <c r="Y32" s="277"/>
-      <c r="Z32" s="277"/>
-      <c r="AA32" s="277"/>
-      <c r="AB32" s="277"/>
-      <c r="AC32" s="278"/>
+      <c r="U32" s="251"/>
+      <c r="V32" s="251"/>
+      <c r="W32" s="251"/>
+      <c r="X32" s="251"/>
+      <c r="Y32" s="251"/>
+      <c r="Z32" s="251"/>
+      <c r="AA32" s="251"/>
+      <c r="AB32" s="251"/>
+      <c r="AC32" s="252"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7493,31 +7462,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="276" t="s">
+      <c r="T33" s="250" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="277"/>
-      <c r="V33" s="277"/>
-      <c r="W33" s="277"/>
-      <c r="X33" s="277"/>
-      <c r="Y33" s="277"/>
-      <c r="Z33" s="277"/>
-      <c r="AA33" s="277"/>
-      <c r="AB33" s="277"/>
-      <c r="AC33" s="278"/>
+      <c r="U33" s="251"/>
+      <c r="V33" s="251"/>
+      <c r="W33" s="251"/>
+      <c r="X33" s="251"/>
+      <c r="Y33" s="251"/>
+      <c r="Z33" s="251"/>
+      <c r="AA33" s="251"/>
+      <c r="AB33" s="251"/>
+      <c r="AC33" s="252"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="333" t="s">
+      <c r="B34" s="355" t="s">
         <v>95</v>
       </c>
       <c r="C34" s="331" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="332"/>
+      <c r="D34" s="333"/>
       <c r="E34" s="331" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="332"/>
+      <c r="F34" s="333"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7545,21 +7514,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="276" t="s">
+      <c r="T34" s="250" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="277"/>
-      <c r="V34" s="277"/>
-      <c r="W34" s="277"/>
-      <c r="X34" s="277"/>
-      <c r="Y34" s="277"/>
-      <c r="Z34" s="277"/>
-      <c r="AA34" s="277"/>
-      <c r="AB34" s="277"/>
-      <c r="AC34" s="278"/>
+      <c r="U34" s="251"/>
+      <c r="V34" s="251"/>
+      <c r="W34" s="251"/>
+      <c r="X34" s="251"/>
+      <c r="Y34" s="251"/>
+      <c r="Z34" s="251"/>
+      <c r="AA34" s="251"/>
+      <c r="AB34" s="251"/>
+      <c r="AC34" s="252"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="334"/>
+      <c r="B35" s="356"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7578,18 +7547,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="276" t="s">
+      <c r="T35" s="250" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="277"/>
-      <c r="V35" s="277"/>
-      <c r="W35" s="277"/>
-      <c r="X35" s="277"/>
-      <c r="Y35" s="277"/>
-      <c r="Z35" s="277"/>
-      <c r="AA35" s="277"/>
-      <c r="AB35" s="277"/>
-      <c r="AC35" s="278"/>
+      <c r="U35" s="251"/>
+      <c r="V35" s="251"/>
+      <c r="W35" s="251"/>
+      <c r="X35" s="251"/>
+      <c r="Y35" s="251"/>
+      <c r="Z35" s="251"/>
+      <c r="AA35" s="251"/>
+      <c r="AB35" s="251"/>
+      <c r="AC35" s="252"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7640,18 +7609,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="276" t="s">
+      <c r="T36" s="250" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="277"/>
-      <c r="V36" s="277"/>
-      <c r="W36" s="277"/>
-      <c r="X36" s="277"/>
-      <c r="Y36" s="277"/>
-      <c r="Z36" s="277"/>
-      <c r="AA36" s="277"/>
-      <c r="AB36" s="277"/>
-      <c r="AC36" s="278"/>
+      <c r="U36" s="251"/>
+      <c r="V36" s="251"/>
+      <c r="W36" s="251"/>
+      <c r="X36" s="251"/>
+      <c r="Y36" s="251"/>
+      <c r="Z36" s="251"/>
+      <c r="AA36" s="251"/>
+      <c r="AB36" s="251"/>
+      <c r="AC36" s="252"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7694,18 +7663,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="276" t="s">
+      <c r="T37" s="250" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="277"/>
-      <c r="V37" s="277"/>
-      <c r="W37" s="277"/>
-      <c r="X37" s="277"/>
-      <c r="Y37" s="277"/>
-      <c r="Z37" s="277"/>
-      <c r="AA37" s="277"/>
-      <c r="AB37" s="277"/>
-      <c r="AC37" s="278"/>
+      <c r="U37" s="251"/>
+      <c r="V37" s="251"/>
+      <c r="W37" s="251"/>
+      <c r="X37" s="251"/>
+      <c r="Y37" s="251"/>
+      <c r="Z37" s="251"/>
+      <c r="AA37" s="251"/>
+      <c r="AB37" s="251"/>
+      <c r="AC37" s="252"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7715,32 +7684,32 @@
         <v>318</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>104</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="374" t="s">
+      <c r="S38" s="295" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="376" t="s">
+      <c r="T38" s="297" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="377"/>
-      <c r="V38" s="377"/>
-      <c r="W38" s="377"/>
-      <c r="X38" s="377"/>
-      <c r="Y38" s="377"/>
-      <c r="Z38" s="377"/>
-      <c r="AA38" s="377"/>
-      <c r="AB38" s="377"/>
-      <c r="AC38" s="378"/>
+      <c r="U38" s="298"/>
+      <c r="V38" s="298"/>
+      <c r="W38" s="298"/>
+      <c r="X38" s="298"/>
+      <c r="Y38" s="298"/>
+      <c r="Z38" s="298"/>
+      <c r="AA38" s="298"/>
+      <c r="AB38" s="298"/>
+      <c r="AC38" s="299"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7758,26 +7727,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="320" t="s">
+      <c r="G39" s="303" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="271"/>
-      <c r="I39" s="271"/>
-      <c r="J39" s="272"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="246"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="375"/>
-      <c r="T39" s="379"/>
-      <c r="U39" s="380"/>
-      <c r="V39" s="380"/>
-      <c r="W39" s="380"/>
-      <c r="X39" s="380"/>
-      <c r="Y39" s="380"/>
-      <c r="Z39" s="380"/>
-      <c r="AA39" s="380"/>
-      <c r="AB39" s="380"/>
-      <c r="AC39" s="381"/>
+      <c r="S39" s="296"/>
+      <c r="T39" s="300"/>
+      <c r="U39" s="301"/>
+      <c r="V39" s="301"/>
+      <c r="W39" s="301"/>
+      <c r="X39" s="301"/>
+      <c r="Y39" s="301"/>
+      <c r="Z39" s="301"/>
+      <c r="AA39" s="301"/>
+      <c r="AB39" s="301"/>
+      <c r="AC39" s="302"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7795,28 +7764,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="321"/>
-      <c r="H40" s="322"/>
-      <c r="I40" s="322"/>
-      <c r="J40" s="323"/>
+      <c r="G40" s="307"/>
+      <c r="H40" s="308"/>
+      <c r="I40" s="308"/>
+      <c r="J40" s="309"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="276" t="s">
+      <c r="T40" s="250" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="277"/>
-      <c r="V40" s="277"/>
-      <c r="W40" s="277"/>
-      <c r="X40" s="277"/>
-      <c r="Y40" s="277"/>
-      <c r="Z40" s="277"/>
-      <c r="AA40" s="277"/>
-      <c r="AB40" s="277"/>
-      <c r="AC40" s="278"/>
+      <c r="U40" s="251"/>
+      <c r="V40" s="251"/>
+      <c r="W40" s="251"/>
+      <c r="X40" s="251"/>
+      <c r="Y40" s="251"/>
+      <c r="Z40" s="251"/>
+      <c r="AA40" s="251"/>
+      <c r="AB40" s="251"/>
+      <c r="AC40" s="252"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7834,28 +7803,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="321"/>
-      <c r="H41" s="322"/>
-      <c r="I41" s="322"/>
-      <c r="J41" s="323"/>
+      <c r="G41" s="307"/>
+      <c r="H41" s="308"/>
+      <c r="I41" s="308"/>
+      <c r="J41" s="309"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="276" t="s">
+      <c r="T41" s="250" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="277"/>
-      <c r="V41" s="277"/>
-      <c r="W41" s="277"/>
-      <c r="X41" s="277"/>
-      <c r="Y41" s="277"/>
-      <c r="Z41" s="277"/>
-      <c r="AA41" s="277"/>
-      <c r="AB41" s="277"/>
-      <c r="AC41" s="278"/>
+      <c r="U41" s="251"/>
+      <c r="V41" s="251"/>
+      <c r="W41" s="251"/>
+      <c r="X41" s="251"/>
+      <c r="Y41" s="251"/>
+      <c r="Z41" s="251"/>
+      <c r="AA41" s="251"/>
+      <c r="AB41" s="251"/>
+      <c r="AC41" s="252"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7873,28 +7842,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="324"/>
-      <c r="H42" s="325"/>
-      <c r="I42" s="325"/>
-      <c r="J42" s="326"/>
+      <c r="G42" s="304"/>
+      <c r="H42" s="305"/>
+      <c r="I42" s="305"/>
+      <c r="J42" s="306"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="276" t="s">
+      <c r="T42" s="250" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="277"/>
-      <c r="V42" s="277"/>
-      <c r="W42" s="277"/>
-      <c r="X42" s="277"/>
-      <c r="Y42" s="277"/>
-      <c r="Z42" s="277"/>
-      <c r="AA42" s="277"/>
-      <c r="AB42" s="277"/>
-      <c r="AC42" s="278"/>
+      <c r="U42" s="251"/>
+      <c r="V42" s="251"/>
+      <c r="W42" s="251"/>
+      <c r="X42" s="251"/>
+      <c r="Y42" s="251"/>
+      <c r="Z42" s="251"/>
+      <c r="AA42" s="251"/>
+      <c r="AB42" s="251"/>
+      <c r="AC42" s="252"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7912,30 +7881,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="262" t="s">
+      <c r="G43" s="268" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="263"/>
-      <c r="I43" s="263"/>
-      <c r="J43" s="264"/>
+      <c r="H43" s="269"/>
+      <c r="I43" s="269"/>
+      <c r="J43" s="270"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="276" t="s">
+      <c r="T43" s="250" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="277"/>
-      <c r="V43" s="277"/>
-      <c r="W43" s="277"/>
-      <c r="X43" s="277"/>
-      <c r="Y43" s="277"/>
-      <c r="Z43" s="277"/>
-      <c r="AA43" s="277"/>
-      <c r="AB43" s="277"/>
-      <c r="AC43" s="278"/>
+      <c r="U43" s="251"/>
+      <c r="V43" s="251"/>
+      <c r="W43" s="251"/>
+      <c r="X43" s="251"/>
+      <c r="Y43" s="251"/>
+      <c r="Z43" s="251"/>
+      <c r="AA43" s="251"/>
+      <c r="AB43" s="251"/>
+      <c r="AC43" s="252"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7956,21 +7925,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="374" t="s">
+      <c r="S44" s="295" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="376" t="s">
+      <c r="T44" s="297" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="377"/>
-      <c r="V44" s="377"/>
-      <c r="W44" s="377"/>
-      <c r="X44" s="377"/>
-      <c r="Y44" s="377"/>
-      <c r="Z44" s="377"/>
-      <c r="AA44" s="377"/>
-      <c r="AB44" s="377"/>
-      <c r="AC44" s="378"/>
+      <c r="U44" s="298"/>
+      <c r="V44" s="298"/>
+      <c r="W44" s="298"/>
+      <c r="X44" s="298"/>
+      <c r="Y44" s="298"/>
+      <c r="Z44" s="298"/>
+      <c r="AA44" s="298"/>
+      <c r="AB44" s="298"/>
+      <c r="AC44" s="299"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -7988,26 +7957,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="320" t="s">
+      <c r="G45" s="303" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="271"/>
-      <c r="I45" s="271"/>
-      <c r="J45" s="272"/>
+      <c r="H45" s="245"/>
+      <c r="I45" s="245"/>
+      <c r="J45" s="246"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="375"/>
-      <c r="T45" s="379"/>
-      <c r="U45" s="380"/>
-      <c r="V45" s="380"/>
-      <c r="W45" s="380"/>
-      <c r="X45" s="380"/>
-      <c r="Y45" s="380"/>
-      <c r="Z45" s="380"/>
-      <c r="AA45" s="380"/>
-      <c r="AB45" s="380"/>
-      <c r="AC45" s="381"/>
+      <c r="S45" s="296"/>
+      <c r="T45" s="300"/>
+      <c r="U45" s="301"/>
+      <c r="V45" s="301"/>
+      <c r="W45" s="301"/>
+      <c r="X45" s="301"/>
+      <c r="Y45" s="301"/>
+      <c r="Z45" s="301"/>
+      <c r="AA45" s="301"/>
+      <c r="AB45" s="301"/>
+      <c r="AC45" s="302"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -8025,28 +7994,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="324"/>
-      <c r="H46" s="325"/>
-      <c r="I46" s="325"/>
-      <c r="J46" s="326"/>
+      <c r="G46" s="304"/>
+      <c r="H46" s="305"/>
+      <c r="I46" s="305"/>
+      <c r="J46" s="306"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="273" t="s">
+      <c r="T46" s="247" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="274"/>
-      <c r="V46" s="274"/>
-      <c r="W46" s="274"/>
-      <c r="X46" s="274"/>
-      <c r="Y46" s="274"/>
-      <c r="Z46" s="274"/>
-      <c r="AA46" s="274"/>
-      <c r="AB46" s="274"/>
-      <c r="AC46" s="275"/>
+      <c r="U46" s="248"/>
+      <c r="V46" s="248"/>
+      <c r="W46" s="248"/>
+      <c r="X46" s="248"/>
+      <c r="Y46" s="248"/>
+      <c r="Z46" s="248"/>
+      <c r="AA46" s="248"/>
+      <c r="AB46" s="248"/>
+      <c r="AC46" s="249"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8064,12 +8033,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="263" t="s">
+      <c r="G47" s="269" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="263"/>
-      <c r="I47" s="263"/>
-      <c r="J47" s="264"/>
+      <c r="H47" s="269"/>
+      <c r="I47" s="269"/>
+      <c r="J47" s="270"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8114,13 +8083,13 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="282" t="s">
+      <c r="AA48" s="368" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="283"/>
-      <c r="AC48" s="284"/>
-    </row>
-    <row r="49" spans="2:29" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AB48" s="369"/>
+      <c r="AC48" s="370"/>
+    </row>
+    <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>13</v>
       </c>
@@ -8136,12 +8105,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="320" t="s">
+      <c r="G49" s="303" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
-      <c r="J49" s="272"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="246"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8157,16 +8126,16 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="285"/>
-      <c r="AB49" s="286"/>
-      <c r="AC49" s="287"/>
+      <c r="AA49" s="371"/>
+      <c r="AB49" s="372"/>
+      <c r="AC49" s="373"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>14</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D50" s="35" t="s">
         <v>335</v>
@@ -8177,10 +8146,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="321"/>
-      <c r="H50" s="322"/>
-      <c r="I50" s="322"/>
-      <c r="J50" s="323"/>
+      <c r="G50" s="307"/>
+      <c r="H50" s="308"/>
+      <c r="I50" s="308"/>
+      <c r="J50" s="309"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8198,35 +8167,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="324"/>
-      <c r="H51" s="325"/>
-      <c r="I51" s="325"/>
-      <c r="J51" s="326"/>
-      <c r="R51" s="300" t="s">
+      <c r="G51" s="304"/>
+      <c r="H51" s="305"/>
+      <c r="I51" s="305"/>
+      <c r="J51" s="306"/>
+      <c r="R51" s="365" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="302" t="s">
+      <c r="S51" s="349" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="304" t="s">
+      <c r="T51" s="361" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="304"/>
-      <c r="V51" s="305"/>
+      <c r="U51" s="361"/>
+      <c r="V51" s="362"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="265" t="s">
+      <c r="B52" s="242" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="266"/>
-      <c r="D52" s="266"/>
-      <c r="E52" s="266"/>
-      <c r="F52" s="267"/>
-      <c r="R52" s="301"/>
-      <c r="S52" s="303"/>
-      <c r="T52" s="306"/>
-      <c r="U52" s="306"/>
-      <c r="V52" s="307"/>
+      <c r="C52" s="243"/>
+      <c r="D52" s="243"/>
+      <c r="E52" s="243"/>
+      <c r="F52" s="244"/>
+      <c r="R52" s="385"/>
+      <c r="S52" s="350"/>
+      <c r="T52" s="363"/>
+      <c r="U52" s="363"/>
+      <c r="V52" s="364"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8235,67 +8204,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="295" t="s">
+      <c r="T53" s="380" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="295"/>
-      <c r="V53" s="296"/>
+      <c r="U53" s="380"/>
+      <c r="V53" s="381"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="329" t="s">
+      <c r="B54" s="351" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="302" t="s">
+      <c r="C54" s="349" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="304" t="s">
+      <c r="D54" s="361" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="305"/>
-      <c r="H54" s="300" t="s">
+      <c r="E54" s="362"/>
+      <c r="H54" s="365" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="302" t="s">
+      <c r="I54" s="349" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="288" t="s">
+      <c r="J54" s="374" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="289"/>
-      <c r="L54" s="290"/>
+      <c r="K54" s="375"/>
+      <c r="L54" s="376"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="308" t="s">
+      <c r="T54" s="386" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="308"/>
-      <c r="V54" s="309"/>
+      <c r="U54" s="386"/>
+      <c r="V54" s="354"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="330"/>
-      <c r="C55" s="328"/>
-      <c r="D55" s="318"/>
-      <c r="E55" s="319"/>
-      <c r="H55" s="327"/>
-      <c r="I55" s="303"/>
-      <c r="J55" s="291"/>
-      <c r="K55" s="292"/>
-      <c r="L55" s="293"/>
+      <c r="B55" s="352"/>
+      <c r="C55" s="350"/>
+      <c r="D55" s="363"/>
+      <c r="E55" s="364"/>
+      <c r="H55" s="366"/>
+      <c r="I55" s="367"/>
+      <c r="J55" s="340"/>
+      <c r="K55" s="377"/>
+      <c r="L55" s="378"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="308" t="s">
+      <c r="T55" s="386" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="308"/>
-      <c r="V55" s="309"/>
+      <c r="U55" s="386"/>
+      <c r="V55" s="354"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8304,36 +8273,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="279" t="s">
+      <c r="D56" s="253" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="281"/>
+      <c r="E56" s="255"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="294" t="s">
+      <c r="J56" s="379" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="295"/>
-      <c r="L56" s="296"/>
-      <c r="M56" s="262" t="s">
+      <c r="K56" s="380"/>
+      <c r="L56" s="381"/>
+      <c r="M56" s="268" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="264"/>
+      <c r="N56" s="270"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="308" t="s">
+      <c r="T56" s="386" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="308"/>
-      <c r="V56" s="309"/>
+      <c r="U56" s="386"/>
+      <c r="V56" s="354"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8342,36 +8311,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="315" t="s">
+      <c r="D57" s="353" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="309"/>
-      <c r="F57" s="262" t="s">
+      <c r="E57" s="354"/>
+      <c r="F57" s="268" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="264"/>
+      <c r="G57" s="270"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="297" t="s">
+      <c r="J57" s="382" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="298"/>
-      <c r="L57" s="299"/>
+      <c r="K57" s="383"/>
+      <c r="L57" s="384"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="308" t="s">
+      <c r="T57" s="386" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="308"/>
-      <c r="V57" s="309"/>
+      <c r="U57" s="386"/>
+      <c r="V57" s="354"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8380,32 +8349,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="315" t="s">
+      <c r="D58" s="353" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="309"/>
+      <c r="E58" s="354"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="297" t="s">
+      <c r="J58" s="382" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="298"/>
-      <c r="L58" s="299"/>
+      <c r="K58" s="383"/>
+      <c r="L58" s="384"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="308" t="s">
+      <c r="T58" s="386" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="308"/>
-      <c r="V58" s="309"/>
+      <c r="U58" s="386"/>
+      <c r="V58" s="354"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8414,32 +8383,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="315" t="s">
+      <c r="D59" s="353" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="309"/>
+      <c r="E59" s="354"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="297" t="s">
+      <c r="J59" s="382" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="298"/>
-      <c r="L59" s="299"/>
+      <c r="K59" s="383"/>
+      <c r="L59" s="384"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="308" t="s">
+      <c r="T59" s="386" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="308"/>
-      <c r="V59" s="309"/>
+      <c r="U59" s="386"/>
+      <c r="V59" s="354"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8449,32 +8418,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="315" t="s">
+      <c r="D60" s="353" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="309"/>
+      <c r="E60" s="354"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="297" t="s">
+      <c r="J60" s="382" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="298"/>
-      <c r="L60" s="299"/>
+      <c r="K60" s="383"/>
+      <c r="L60" s="384"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="310" t="s">
-        <v>353</v>
-      </c>
-      <c r="U60" s="311"/>
-      <c r="V60" s="312"/>
+      <c r="T60" s="386" t="s">
+        <v>461</v>
+      </c>
+      <c r="U60" s="386"/>
+      <c r="V60" s="354"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8483,166 +8452,294 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="315" t="s">
+      <c r="D61" s="353" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="309"/>
+      <c r="E61" s="354"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="297"/>
-      <c r="K61" s="298"/>
-      <c r="L61" s="299"/>
+      <c r="J61" s="382"/>
+      <c r="K61" s="383"/>
+      <c r="L61" s="384"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="313"/>
-      <c r="U61" s="245"/>
-      <c r="V61" s="246"/>
+      <c r="T61" s="386"/>
+      <c r="U61" s="386"/>
+      <c r="V61" s="354"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="315"/>
-      <c r="E62" s="309"/>
+      <c r="D62" s="353"/>
+      <c r="E62" s="354"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="297"/>
-      <c r="K62" s="298"/>
-      <c r="L62" s="299"/>
+      <c r="J62" s="382"/>
+      <c r="K62" s="383"/>
+      <c r="L62" s="384"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="313"/>
-      <c r="U62" s="245"/>
-      <c r="V62" s="246"/>
-    </row>
-    <row r="63" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T62" s="386"/>
+      <c r="U62" s="386"/>
+      <c r="V62" s="354"/>
+    </row>
+    <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="315"/>
-      <c r="E63" s="309"/>
+      <c r="D63" s="353"/>
+      <c r="E63" s="354"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="297"/>
-      <c r="K63" s="298"/>
-      <c r="L63" s="299"/>
-      <c r="R63" s="163" t="s">
+      <c r="J63" s="382"/>
+      <c r="K63" s="383"/>
+      <c r="L63" s="384"/>
+      <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
-      <c r="S63" s="161" t="s">
+      <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="314"/>
-      <c r="U63" s="248"/>
-      <c r="V63" s="249"/>
-    </row>
-    <row r="64" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T63" s="386"/>
+      <c r="U63" s="386"/>
+      <c r="V63" s="354"/>
+    </row>
+    <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="315"/>
-      <c r="E64" s="309"/>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="353"/>
+      <c r="E64" s="354"/>
+      <c r="R64" s="163" t="s">
+        <v>458</v>
+      </c>
+      <c r="S64" s="161" t="s">
+        <v>459</v>
+      </c>
+      <c r="T64" s="424" t="s">
+        <v>460</v>
+      </c>
+      <c r="U64" s="424"/>
+      <c r="V64" s="360"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="315"/>
-      <c r="E65" s="309"/>
-    </row>
-    <row r="66" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="353"/>
+      <c r="E65" s="354"/>
+      <c r="T65" s="166"/>
+    </row>
+    <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="82">
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="315"/>
-      <c r="E66" s="309"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D66" s="353"/>
+      <c r="E66" s="354"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="315"/>
-      <c r="E67" s="309"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D67" s="353"/>
+      <c r="E67" s="354"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="315"/>
-      <c r="E68" s="309"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D68" s="353"/>
+      <c r="E68" s="354"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="315"/>
-      <c r="E69" s="309"/>
-    </row>
-    <row r="70" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D69" s="353"/>
+      <c r="E69" s="354"/>
+    </row>
+    <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="315"/>
-      <c r="E70" s="309"/>
-    </row>
-    <row r="71" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="353"/>
+      <c r="E70" s="354"/>
+    </row>
+    <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="316"/>
-      <c r="E71" s="317"/>
-    </row>
-    <row r="75" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D71" s="359"/>
+      <c r="E71" s="360"/>
+    </row>
+    <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="187">
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
+  <mergeCells count="188">
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
     <mergeCell ref="AA20:AB20"/>
     <mergeCell ref="AA21:AB21"/>
     <mergeCell ref="AA22:AB22"/>
@@ -8667,145 +8764,30 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8846,74 +8828,74 @@
     <row r="1" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="185" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="180" t="s">
         <v>356</v>
       </c>
-      <c r="C2" s="180" t="s">
+      <c r="D2" s="178" t="s">
         <v>357</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="E2" s="178" t="s">
+        <v>416</v>
+      </c>
+      <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="E2" s="178" t="s">
-        <v>417</v>
-      </c>
-      <c r="F2" s="179" t="s">
-        <v>359</v>
-      </c>
-      <c r="G2" s="271" t="s">
+      <c r="G2" s="245" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="L2" s="253" t="s">
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="246"/>
+      <c r="L2" s="259" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="254"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="255"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="261"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="256" t="s">
+      <c r="Q2" s="262" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="257"/>
-      <c r="S2" s="257"/>
-      <c r="T2" s="258"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="250" t="s">
+      <c r="V2" s="256" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251"/>
-      <c r="AB2" s="252"/>
+      <c r="W2" s="257"/>
+      <c r="X2" s="257"/>
+      <c r="Y2" s="257"/>
+      <c r="Z2" s="257"/>
+      <c r="AA2" s="257"/>
+      <c r="AB2" s="258"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="181" t="s">
         <v>360</v>
       </c>
-      <c r="C3" s="181" t="s">
+      <c r="D3" s="190" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="190" t="s">
+      <c r="E3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="E3" s="176" t="s">
+      <c r="F3" s="177" t="s">
         <v>363</v>
-      </c>
-      <c r="F3" s="177" t="s">
-        <v>364</v>
       </c>
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="279" t="s">
+      <c r="H3" s="253" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="280"/>
-      <c r="J3" s="281"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="255"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8952,36 +8934,36 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="241" t="s">
+      <c r="Z3" s="277" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="242"/>
-      <c r="AB3" s="243"/>
+      <c r="AA3" s="278"/>
+      <c r="AB3" s="279"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="182" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="182" t="s">
+      <c r="D4" s="191" t="s">
         <v>366</v>
       </c>
-      <c r="D4" s="191" t="s">
+      <c r="E4" s="171" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="171" t="s">
+      <c r="F4" s="172" t="s">
         <v>368</v>
-      </c>
-      <c r="F4" s="172" t="s">
-        <v>369</v>
       </c>
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="276">
+      <c r="H4" s="250">
         <v>63</v>
       </c>
-      <c r="I4" s="277"/>
-      <c r="J4" s="278"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="252"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9020,36 +9002,36 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="244" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="246"/>
+      <c r="Z4" s="280" t="s">
+        <v>421</v>
+      </c>
+      <c r="AA4" s="281"/>
+      <c r="AB4" s="282"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="182" t="s">
+        <v>360</v>
+      </c>
+      <c r="D5" s="191" t="s">
         <v>370</v>
       </c>
-      <c r="C5" s="182" t="s">
-        <v>361</v>
-      </c>
-      <c r="D5" s="191" t="s">
+      <c r="E5" s="171" t="s">
         <v>371</v>
       </c>
-      <c r="E5" s="171" t="s">
+      <c r="F5" s="172" t="s">
         <v>372</v>
-      </c>
-      <c r="F5" s="172" t="s">
-        <v>373</v>
       </c>
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="276">
+      <c r="H5" s="250">
         <v>31</v>
       </c>
-      <c r="I5" s="277"/>
-      <c r="J5" s="278"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="252"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9088,42 +9070,42 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="244"/>
-      <c r="AA5" s="245"/>
-      <c r="AB5" s="246"/>
+      <c r="Z5" s="280"/>
+      <c r="AA5" s="281"/>
+      <c r="AB5" s="282"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="182" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="191" t="s">
         <v>374</v>
       </c>
-      <c r="C6" s="182" t="s">
-        <v>366</v>
-      </c>
-      <c r="D6" s="191" t="s">
+      <c r="E6" s="171" t="s">
         <v>375</v>
       </c>
-      <c r="E6" s="171" t="s">
+      <c r="F6" s="172" t="s">
         <v>376</v>
-      </c>
-      <c r="F6" s="172" t="s">
-        <v>377</v>
       </c>
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="273">
+      <c r="H6" s="247">
         <v>7</v>
       </c>
-      <c r="I6" s="274"/>
-      <c r="J6" s="275"/>
+      <c r="I6" s="248"/>
+      <c r="J6" s="249"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
       <c r="M6" s="123" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N6" s="92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O6" s="116" t="s">
         <v>236</v>
@@ -9154,40 +9136,40 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="247"/>
-      <c r="AA6" s="248"/>
-      <c r="AB6" s="249"/>
+      <c r="Z6" s="283"/>
+      <c r="AA6" s="284"/>
+      <c r="AB6" s="285"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="182" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="191" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="182" t="s">
-        <v>361</v>
-      </c>
-      <c r="D7" s="191" t="s">
+      <c r="E7" s="171" t="s">
         <v>379</v>
       </c>
-      <c r="E7" s="171" t="s">
+      <c r="F7" s="172" t="s">
         <v>380</v>
-      </c>
-      <c r="F7" s="172" t="s">
-        <v>381</v>
       </c>
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="268" t="str">
+      <c r="H7" s="235" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="269"/>
-      <c r="J7" s="270"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="237"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
       <c r="M7" s="124" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N7" s="93" t="s">
         <v>275</v>
@@ -9212,35 +9194,35 @@
     </row>
     <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="187" t="s">
+        <v>381</v>
+      </c>
+      <c r="C8" s="183" t="s">
         <v>382</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="D8" s="192" t="s">
         <v>383</v>
       </c>
-      <c r="D8" s="192" t="s">
+      <c r="E8" s="170" t="s">
+        <v>383</v>
+      </c>
+      <c r="F8" s="173" t="s">
         <v>384</v>
-      </c>
-      <c r="E8" s="170" t="s">
-        <v>384</v>
-      </c>
-      <c r="F8" s="173" t="s">
-        <v>385</v>
       </c>
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="268" t="str">
+      <c r="H8" s="235" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="269"/>
-      <c r="J8" s="270"/>
-      <c r="L8" s="262" t="s">
-        <v>418</v>
-      </c>
-      <c r="M8" s="263"/>
-      <c r="N8" s="263"/>
-      <c r="O8" s="264"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="237"/>
+      <c r="L8" s="268" t="s">
+        <v>417</v>
+      </c>
+      <c r="M8" s="269"/>
+      <c r="N8" s="269"/>
+      <c r="O8" s="270"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9256,29 +9238,29 @@
       </c>
       <c r="U8" s="114"/>
       <c r="V8" s="231" t="s">
+        <v>453</v>
+      </c>
+      <c r="W8" s="271" t="s">
         <v>454</v>
       </c>
-      <c r="W8" s="237" t="s">
-        <v>455</v>
-      </c>
-      <c r="X8" s="238"/>
+      <c r="X8" s="272"/>
       <c r="Y8" s="230"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="187" t="s">
+        <v>385</v>
+      </c>
+      <c r="C9" s="182" t="s">
         <v>386</v>
       </c>
-      <c r="C9" s="182" t="s">
+      <c r="D9" s="191" t="s">
         <v>387</v>
       </c>
-      <c r="D9" s="191" t="s">
+      <c r="E9" s="171" t="s">
         <v>388</v>
       </c>
-      <c r="E9" s="171" t="s">
+      <c r="F9" s="172" t="s">
         <v>389</v>
-      </c>
-      <c r="F9" s="172" t="s">
-        <v>390</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
@@ -9301,26 +9283,26 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="239" t="s">
-        <v>457</v>
-      </c>
-      <c r="X9" s="240"/>
+      <c r="W9" s="273" t="s">
+        <v>456</v>
+      </c>
+      <c r="X9" s="274"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="191" t="s">
         <v>391</v>
       </c>
-      <c r="C10" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D10" s="191" t="s">
+      <c r="E10" s="171" t="s">
         <v>392</v>
       </c>
-      <c r="E10" s="171" t="s">
+      <c r="F10" s="172" t="s">
         <v>393</v>
-      </c>
-      <c r="F10" s="172" t="s">
-        <v>394</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
@@ -9335,26 +9317,26 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="235" t="s">
-        <v>456</v>
-      </c>
-      <c r="X10" s="236"/>
+      <c r="W10" s="275" t="s">
+        <v>455</v>
+      </c>
+      <c r="X10" s="276"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="191" t="s">
         <v>395</v>
       </c>
-      <c r="C11" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D11" s="191" t="s">
+      <c r="E11" s="171" t="s">
         <v>396</v>
       </c>
-      <c r="E11" s="171" t="s">
+      <c r="F11" s="172" t="s">
         <v>397</v>
-      </c>
-      <c r="F11" s="172" t="s">
-        <v>398</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -9365,33 +9347,33 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="259" t="s">
+      <c r="Q11" s="265" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="260"/>
-      <c r="S11" s="260"/>
-      <c r="T11" s="261"/>
+      <c r="R11" s="266"/>
+      <c r="S11" s="266"/>
+      <c r="T11" s="267"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="235" t="s">
-        <v>426</v>
-      </c>
-      <c r="X11" s="236"/>
+      <c r="W11" s="275" t="s">
+        <v>425</v>
+      </c>
+      <c r="X11" s="276"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
+        <v>398</v>
+      </c>
+      <c r="C12" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="191" t="s">
         <v>399</v>
       </c>
-      <c r="C12" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D12" s="191" t="s">
+      <c r="E12" s="171" t="s">
         <v>400</v>
-      </c>
-      <c r="E12" s="171" t="s">
-        <v>401</v>
       </c>
       <c r="F12" s="172"/>
       <c r="G12" s="15"/>
@@ -9419,21 +9401,21 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="235"/>
-      <c r="X12" s="236"/>
+      <c r="W12" s="275"/>
+      <c r="X12" s="276"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D13" s="191" t="s">
         <v>402</v>
       </c>
-      <c r="C13" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D13" s="191" t="s">
+      <c r="E13" s="171" t="s">
         <v>403</v>
-      </c>
-      <c r="E13" s="171" t="s">
-        <v>404</v>
       </c>
       <c r="F13" s="172"/>
       <c r="G13" s="15"/>
@@ -9461,21 +9443,21 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="235"/>
-      <c r="X13" s="236"/>
+      <c r="W13" s="275"/>
+      <c r="X13" s="276"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
+        <v>404</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" s="191" t="s">
         <v>405</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D14" s="191" t="s">
+      <c r="E14" s="171" t="s">
         <v>406</v>
-      </c>
-      <c r="E14" s="171" t="s">
-        <v>407</v>
       </c>
       <c r="F14" s="172"/>
       <c r="G14" s="15"/>
@@ -9503,21 +9485,21 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="235"/>
-      <c r="X14" s="236"/>
+      <c r="W14" s="275"/>
+      <c r="X14" s="276"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
+        <v>407</v>
+      </c>
+      <c r="C15" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D15" s="191" t="s">
         <v>408</v>
       </c>
-      <c r="C15" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D15" s="191" t="s">
+      <c r="E15" s="171" t="s">
         <v>409</v>
-      </c>
-      <c r="E15" s="171" t="s">
-        <v>410</v>
       </c>
       <c r="F15" s="172"/>
       <c r="G15" s="15"/>
@@ -9545,21 +9527,21 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="235"/>
-      <c r="X15" s="236"/>
+      <c r="W15" s="275"/>
+      <c r="X15" s="276"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="191" t="s">
         <v>411</v>
       </c>
-      <c r="C16" s="182" t="s">
-        <v>387</v>
-      </c>
-      <c r="D16" s="191" t="s">
+      <c r="E16" s="171" t="s">
         <v>412</v>
-      </c>
-      <c r="E16" s="171" t="s">
-        <v>413</v>
       </c>
       <c r="F16" s="172"/>
       <c r="Q16" s="148" t="s">
@@ -9577,21 +9559,21 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="235"/>
-      <c r="X16" s="236"/>
+      <c r="W16" s="275"/>
+      <c r="X16" s="276"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="184" t="s">
+        <v>386</v>
+      </c>
+      <c r="D17" s="193" t="s">
         <v>414</v>
       </c>
-      <c r="C17" s="184" t="s">
-        <v>387</v>
-      </c>
-      <c r="D17" s="193" t="s">
+      <c r="E17" s="174" t="s">
         <v>415</v>
-      </c>
-      <c r="E17" s="174" t="s">
-        <v>416</v>
       </c>
       <c r="F17" s="175"/>
       <c r="Q17" s="149" t="s">
@@ -9609,8 +9591,8 @@
       <c r="V17" s="232">
         <v>9</v>
       </c>
-      <c r="W17" s="233"/>
-      <c r="X17" s="234"/>
+      <c r="W17" s="286"/>
+      <c r="X17" s="287"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9629,18 +9611,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="265" t="s">
+      <c r="G19" s="242" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="266"/>
-      <c r="I19" s="266"/>
-      <c r="J19" s="267"/>
+      <c r="H19" s="243"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="244"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="428" t="s">
+      <c r="C20" s="233" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9652,16 +9634,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="425" t="s">
-        <v>458</v>
-      </c>
-      <c r="H20" s="426"/>
-      <c r="I20" s="426"/>
-      <c r="J20" s="427"/>
+      <c r="G20" s="238" t="s">
+        <v>457</v>
+      </c>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="240"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="429"/>
+      <c r="C21" s="241"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9671,16 +9653,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="268" t="s">
+      <c r="G21" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="269"/>
-      <c r="I21" s="269"/>
-      <c r="J21" s="270"/>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="237"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="430"/>
+      <c r="C22" s="234"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9699,7 +9681,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="428" t="s">
+      <c r="C23" s="233" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9718,7 +9700,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="430"/>
+      <c r="C24" s="234"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9737,7 +9719,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="428" t="s">
+      <c r="C25" s="233" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9756,7 +9738,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="430"/>
+      <c r="C26" s="234"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9775,7 +9757,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="428" t="s">
+      <c r="C27" s="233" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9794,7 +9776,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="430"/>
+      <c r="C28" s="234"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9834,7 +9816,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="428" t="s">
+      <c r="C30" s="233" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9853,7 +9835,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="430"/>
+      <c r="C31" s="234"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9872,7 +9854,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="428" t="s">
+      <c r="C32" s="233" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9891,7 +9873,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="430"/>
+      <c r="C33" s="234"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9908,22 +9890,12 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9935,12 +9907,22 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9963,36 +9945,36 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="419" t="s">
-        <v>426</v>
-      </c>
-      <c r="C2" s="420"/>
-      <c r="D2" s="421"/>
-      <c r="E2" s="421"/>
-      <c r="F2" s="421"/>
-      <c r="G2" s="421"/>
-      <c r="H2" s="422"/>
+      <c r="B2" s="391" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2" s="392"/>
+      <c r="D2" s="393"/>
+      <c r="E2" s="393"/>
+      <c r="F2" s="393"/>
+      <c r="G2" s="393"/>
+      <c r="H2" s="394"/>
     </row>
     <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="194" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C3" s="195" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="195" t="s">
         <v>427</v>
       </c>
-      <c r="D3" s="195" t="s">
+      <c r="E3" s="195" t="s">
         <v>428</v>
       </c>
-      <c r="E3" s="195" t="s">
+      <c r="F3" s="195" t="s">
+        <v>430</v>
+      </c>
+      <c r="G3" s="389" t="s">
         <v>429</v>
       </c>
-      <c r="F3" s="195" t="s">
-        <v>431</v>
-      </c>
-      <c r="G3" s="417" t="s">
-        <v>430</v>
-      </c>
-      <c r="H3" s="418"/>
+      <c r="H3" s="390"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="196">
@@ -10004,29 +9986,29 @@
       <c r="F4" s="223" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="423" t="s">
-        <v>437</v>
-      </c>
-      <c r="H4" s="424"/>
+      <c r="G4" s="395" t="s">
+        <v>436</v>
+      </c>
+      <c r="H4" s="396"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="197">
         <v>1</v>
       </c>
       <c r="C5" s="198" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D5" s="228"/>
       <c r="E5" s="222" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F5" s="224" t="s">
-        <v>432</v>
-      </c>
-      <c r="G5" s="408" t="s">
-        <v>441</v>
-      </c>
-      <c r="H5" s="409"/>
+        <v>431</v>
+      </c>
+      <c r="G5" s="387" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" s="388"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="197">
@@ -10035,15 +10017,15 @@
       <c r="C6" s="229"/>
       <c r="D6" s="205"/>
       <c r="E6" s="200" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F6" s="224" t="s">
-        <v>433</v>
-      </c>
-      <c r="G6" s="408" t="s">
-        <v>438</v>
-      </c>
-      <c r="H6" s="409"/>
+        <v>432</v>
+      </c>
+      <c r="G6" s="387" t="s">
+        <v>437</v>
+      </c>
+      <c r="H6" s="388"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="197">
@@ -10053,31 +10035,31 @@
       <c r="D7" s="205"/>
       <c r="E7" s="206"/>
       <c r="F7" s="224" t="s">
-        <v>434</v>
-      </c>
-      <c r="G7" s="408" t="s">
-        <v>439</v>
-      </c>
-      <c r="H7" s="409"/>
+        <v>433</v>
+      </c>
+      <c r="G7" s="387" t="s">
+        <v>438</v>
+      </c>
+      <c r="H7" s="388"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="197">
         <v>4</v>
       </c>
       <c r="C8" s="198" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8" s="199" t="s">
         <v>443</v>
-      </c>
-      <c r="D8" s="199" t="s">
-        <v>444</v>
       </c>
       <c r="E8" s="206"/>
       <c r="F8" s="224" t="s">
-        <v>435</v>
-      </c>
-      <c r="G8" s="408" t="s">
-        <v>445</v>
-      </c>
-      <c r="H8" s="409"/>
+        <v>434</v>
+      </c>
+      <c r="G8" s="387" t="s">
+        <v>444</v>
+      </c>
+      <c r="H8" s="388"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="197">
@@ -10087,10 +10069,10 @@
       <c r="D9" s="205"/>
       <c r="E9" s="206"/>
       <c r="F9" s="225" t="s">
-        <v>436</v>
-      </c>
-      <c r="G9" s="410"/>
-      <c r="H9" s="411"/>
+        <v>435</v>
+      </c>
+      <c r="G9" s="406"/>
+      <c r="H9" s="407"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="197">
@@ -10100,10 +10082,10 @@
       <c r="D10" s="205"/>
       <c r="E10" s="206"/>
       <c r="F10" s="226" t="s">
-        <v>436</v>
-      </c>
-      <c r="G10" s="410"/>
-      <c r="H10" s="411"/>
+        <v>435</v>
+      </c>
+      <c r="G10" s="406"/>
+      <c r="H10" s="407"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="201">
@@ -10113,98 +10095,98 @@
       <c r="D11" s="209"/>
       <c r="E11" s="210"/>
       <c r="F11" s="227" t="s">
-        <v>436</v>
-      </c>
-      <c r="G11" s="412"/>
-      <c r="H11" s="413"/>
+        <v>435</v>
+      </c>
+      <c r="G11" s="408"/>
+      <c r="H11" s="409"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="212" t="s">
-        <v>447</v>
-      </c>
-      <c r="C13" s="414" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" s="410" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="415"/>
-      <c r="E13" s="416"/>
+      <c r="D13" s="411"/>
+      <c r="E13" s="412"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="213">
         <v>0</v>
       </c>
-      <c r="C14" s="399" t="s">
-        <v>452</v>
-      </c>
-      <c r="D14" s="400"/>
-      <c r="E14" s="401"/>
+      <c r="C14" s="397" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="398"/>
+      <c r="E14" s="399"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="214">
         <v>1</v>
       </c>
-      <c r="C15" s="402" t="s">
-        <v>450</v>
-      </c>
-      <c r="D15" s="403"/>
-      <c r="E15" s="404"/>
+      <c r="C15" s="400" t="s">
+        <v>449</v>
+      </c>
+      <c r="D15" s="401"/>
+      <c r="E15" s="402"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="214">
         <v>2</v>
       </c>
-      <c r="C16" s="390" t="s">
-        <v>451</v>
-      </c>
-      <c r="D16" s="391"/>
-      <c r="E16" s="392"/>
+      <c r="C16" s="415" t="s">
+        <v>450</v>
+      </c>
+      <c r="D16" s="416"/>
+      <c r="E16" s="417"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="214">
         <v>3</v>
       </c>
-      <c r="C17" s="405" t="s">
-        <v>453</v>
-      </c>
-      <c r="D17" s="406"/>
-      <c r="E17" s="407"/>
+      <c r="C17" s="403" t="s">
+        <v>452</v>
+      </c>
+      <c r="D17" s="404"/>
+      <c r="E17" s="405"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="214">
         <v>4</v>
       </c>
-      <c r="C18" s="393"/>
-      <c r="D18" s="394"/>
-      <c r="E18" s="395"/>
+      <c r="C18" s="418"/>
+      <c r="D18" s="419"/>
+      <c r="E18" s="420"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="214">
         <v>5</v>
       </c>
-      <c r="C19" s="393"/>
-      <c r="D19" s="394"/>
-      <c r="E19" s="395"/>
+      <c r="C19" s="418"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="420"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="214">
         <v>6</v>
       </c>
-      <c r="C20" s="393"/>
-      <c r="D20" s="394"/>
-      <c r="E20" s="395"/>
+      <c r="C20" s="418"/>
+      <c r="D20" s="419"/>
+      <c r="E20" s="420"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="215">
         <v>7</v>
       </c>
-      <c r="C21" s="396"/>
-      <c r="D21" s="397"/>
-      <c r="E21" s="398"/>
+      <c r="C21" s="421"/>
+      <c r="D21" s="422"/>
+      <c r="E21" s="423"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="388" t="s">
-        <v>446</v>
+      <c r="B23" s="413" t="s">
+        <v>445</v>
       </c>
       <c r="C23" s="211">
         <v>5</v>
@@ -10226,26 +10208,26 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="389"/>
+      <c r="B24" s="414"/>
       <c r="C24" s="220"/>
       <c r="D24" s="221"/>
       <c r="E24" s="221"/>
       <c r="F24" s="221"/>
       <c r="G24" s="216" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H24" s="217" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C17:E17"/>
@@ -10254,12 +10236,12 @@
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF8803C-73B8-4A22-BF06-2C9428F2D4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787BD476-9523-4D51-AED7-9AF633FAF38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
     <sheet name="MMIO" sheetId="2" r:id="rId2"/>
+    <sheet name="Perif Code" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="462">
   <si>
     <t>OpCode</t>
   </si>
@@ -66,9 +89,6 @@
     <t>Flags</t>
   </si>
   <si>
-    <t>Obsvervaciones</t>
-  </si>
-  <si>
     <t>NOP</t>
   </si>
   <si>
@@ -189,9 +209,6 @@
     <t>GOF</t>
   </si>
   <si>
-    <t>Recive el overflow o el carry de una operación anterior</t>
-  </si>
-  <si>
     <t>Operación nula, no hace nada</t>
   </si>
   <si>
@@ -216,12 +233,6 @@
     <t>Realiza la operación XOR con A, B y guarda en C</t>
   </si>
   <si>
-    <t>Shift logico a la derecha de A por lo que dice B, guarda en C</t>
-  </si>
-  <si>
-    <t>Shift logico a la izquierda de A por lo que dice B, guarda en C</t>
-  </si>
-  <si>
     <t>Suma un valor inmediato a A</t>
   </si>
   <si>
@@ -315,18 +326,6 @@
     <t>Viene de RAM</t>
   </si>
   <si>
-    <t>Vuelve del SO a la direccion guardada en el EPC</t>
-  </si>
-  <si>
-    <t>Salto incondicional al numero gaurdado en un registro</t>
-  </si>
-  <si>
-    <t>Salto condicional al numero gaurdado en un registro</t>
-  </si>
-  <si>
-    <t>Detiene al nucleo hasta recibir una interrupción o instrucción</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -342,21 +341,6 @@
     <t>Especial</t>
   </si>
   <si>
-    <t>Parametro 1</t>
-  </si>
-  <si>
-    <t>Parametro 2</t>
-  </si>
-  <si>
-    <t>Parametro 3</t>
-  </si>
-  <si>
-    <t>Parametro 4</t>
-  </si>
-  <si>
-    <t>Parametro 5</t>
-  </si>
-  <si>
     <t>Motivo de la llamada y Resultado</t>
   </si>
   <si>
@@ -369,9 +353,6 @@
     <t>EPC</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
     <t>PCID</t>
   </si>
   <si>
@@ -435,18 +416,12 @@
     <t>R15</t>
   </si>
   <si>
-    <t>Punto del stack</t>
-  </si>
-  <si>
     <t>ID de programa</t>
   </si>
   <si>
     <t>Base de la tabla de direcciones</t>
   </si>
   <si>
-    <t>Direccion virtual fallida</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -459,9 +434,6 @@
     <t>Eflags</t>
   </si>
   <si>
-    <t>El tamaño del putero si es un array, se define en el primer espacio, el puntero apunta al tramaño del array</t>
-  </si>
-  <si>
     <t>RE0</t>
   </si>
   <si>
@@ -474,33 +446,15 @@
     <t>A==E</t>
   </si>
   <si>
-    <t>Cuase</t>
-  </si>
-  <si>
-    <t>Causa de la exepción</t>
-  </si>
-  <si>
     <t>Lugar de regreso para el SRT</t>
   </si>
   <si>
     <t>TR</t>
   </si>
   <si>
-    <t>Direccion al TSS</t>
-  </si>
-  <si>
-    <t>Nota: Direccion al TSS que contiene los SP que se usan para las distintas cosas, concretamente tiene la direccion del (RSP0=SP del kernel) y los distintos IST</t>
-  </si>
-  <si>
     <t>RegE Kernel</t>
   </si>
   <si>
-    <t>Uso unico del kernel</t>
-  </si>
-  <si>
-    <t>Nota: Estos registros son de uso unico del kernel, son para no pisar datos en el guardado de contexto. El kernel debe copiar algunos registros aquí para luego hacer el guardado</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -543,21 +497,12 @@
     <t>Esta señal dicta como debe actuar la RAM ante un pedido de datos</t>
   </si>
   <si>
-    <t>Activa el subsistema que permite recuperar la direccion de la RAM</t>
-  </si>
-  <si>
-    <t>Congela el el nucleo hasta que alla  una interrupción</t>
-  </si>
-  <si>
     <t>Habilita el guardado en registros normales</t>
   </si>
   <si>
     <t>Habilita el guardado en registros especiales</t>
   </si>
   <si>
-    <t>Determina de donde viene el dato para su posterior envio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hace que el operando A sea igual al registro especial pedido </t>
   </si>
   <si>
@@ -588,9 +533,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>General Protection Fault</t>
-  </si>
-  <si>
     <t>Invalid Opcode</t>
   </si>
   <si>
@@ -606,24 +548,15 @@
     <t>Error lanzado cuando el procesador estaba resolviendo un fault y ocurre otro</t>
   </si>
   <si>
-    <t>Nota: Cause es el ID de la excepción, puede ser generado de maner aasincrona por cualquier subsistema</t>
-  </si>
-  <si>
     <t>SyS-JMP</t>
   </si>
   <si>
-    <t>Direccion de salto automatica para SCL</t>
-  </si>
-  <si>
     <t>Se activa cuando se requiere llamar al kernel, o regresar del kernel</t>
   </si>
   <si>
     <t>Alignment Fault</t>
   </si>
   <si>
-    <t>Error de aliniamiento en memoria, los accesos deben terminar en 00</t>
-  </si>
-  <si>
     <t>Flags de paginas</t>
   </si>
   <si>
@@ -642,21 +575,6 @@
     <t xml:space="preserve">No Excepción </t>
   </si>
   <si>
-    <t>Dispositivo</t>
-  </si>
-  <si>
-    <t>Bus Lógico</t>
-  </si>
-  <si>
-    <t>Dispositivo (ID)</t>
-  </si>
-  <si>
-    <t>Función</t>
-  </si>
-  <si>
-    <t>Offset ECAM (Hex)</t>
-  </si>
-  <si>
     <t>Dirección Base ECAM + (Bus &lt;&lt; 20) + (Device_X &lt;&lt; 15) + (Function_0 &lt;&lt; 12)</t>
   </si>
   <si>
@@ -676,36 +594,6 @@
   </si>
   <si>
     <t>Res Max</t>
-  </si>
-  <si>
-    <t>fff</t>
-  </si>
-  <si>
-    <t>Extensión 1</t>
-  </si>
-  <si>
-    <t>Extensión 2</t>
-  </si>
-  <si>
-    <t>Extensión 3</t>
-  </si>
-  <si>
-    <t>Extensión 4</t>
-  </si>
-  <si>
-    <t>Extensión 5</t>
-  </si>
-  <si>
-    <t>Extensión 6</t>
-  </si>
-  <si>
-    <t>Extensión 7</t>
-  </si>
-  <si>
-    <t>Extesión Rápida 1</t>
-  </si>
-  <si>
-    <t>Extesión Rápida 2</t>
   </si>
   <si>
     <t>Base Class (Hex)</t>
@@ -939,19 +827,10 @@
     <t>Revision ID &amp; Class Code</t>
   </si>
   <si>
-    <t>Base-Sub-Prog IF-Revision</t>
-  </si>
-  <si>
     <t>00-00-00-00</t>
   </si>
   <si>
     <t xml:space="preserve">Res </t>
-  </si>
-  <si>
-    <t>Switch A</t>
-  </si>
-  <si>
-    <t>Switch B</t>
   </si>
   <si>
     <t>Offset</t>
@@ -1228,12 +1107,6 @@
     <t>Notas:</t>
   </si>
   <si>
-    <t>Para cada puerto se entienede que es una funcion de Switch distinta. Para 3 puertos el switch tiene 3 funciones</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
     <t>Bits para habilitar/deshabilitar características y Banderas de estado</t>
   </si>
   <si>
@@ -1241,9 +1114,6 @@
   </si>
   <si>
     <t xml:space="preserve">Command (2B) &amp; Status (2B) </t>
-  </si>
-  <si>
-    <t>Class Code (4B)</t>
   </si>
   <si>
     <t xml:space="preserve">Indentificadores del dispositivo: Creador y dispositivo </t>
@@ -1300,9 +1170,6 @@
   </si>
   <si>
     <t>Header Type (1B)</t>
-  </si>
-  <si>
-    <t>Nota: defe es mi vendor ID y 0001 es el root complex</t>
   </si>
   <si>
     <r>
@@ -1344,9 +1211,6 @@
     <t>Especial Flags</t>
   </si>
   <si>
-    <t>Flags Especiales del Nucleo, como kernel previo o actual</t>
-  </si>
-  <si>
     <t>Actual Mode</t>
   </si>
   <si>
@@ -1365,9 +1229,6 @@
     <t>Lanzada en el momento exacto en el que la MMU detecta un error</t>
   </si>
   <si>
-    <t>Nota: El codigo de error especifico esta en la mitad alta de CR0</t>
-  </si>
-  <si>
     <t>IF</t>
   </si>
   <si>
@@ -1386,35 +1247,1157 @@
     <t>Bit 0 - Control</t>
   </si>
   <si>
-    <t>Nota: El bit "0" de la parte alta indentifica si el error fue de IF o MEM, los codigos reales empiezan a partir del bit 1</t>
-  </si>
-  <si>
-    <t>Privilege Violation</t>
-  </si>
-  <si>
     <t>Executable</t>
   </si>
   <si>
-    <t xml:space="preserve">Codigo para pagina no presente </t>
-  </si>
-  <si>
-    <t>Codigo para acceso restringido, solo permitido para el kernel</t>
-  </si>
-  <si>
-    <t>Codigo para acceso restringido de solo lectura</t>
-  </si>
-  <si>
-    <t>Codigo para intento de ejecutar zona no ejecutable</t>
-  </si>
-  <si>
     <t>Flush TLBs</t>
+  </si>
+  <si>
+    <t>En_LAPIC</t>
+  </si>
+  <si>
+    <t>En_Perif_IRQs</t>
+  </si>
+  <si>
+    <t>LAPIC Control</t>
+  </si>
+  <si>
+    <t>Registros LAPIC</t>
+  </si>
+  <si>
+    <t>Base Addr</t>
+  </si>
+  <si>
+    <t>LAPIC_ID</t>
+  </si>
+  <si>
+    <t>APIC_Config</t>
+  </si>
+  <si>
+    <t>TPR</t>
+  </si>
+  <si>
+    <t>Timer Config</t>
+  </si>
+  <si>
+    <t>Timer Limit</t>
+  </si>
+  <si>
+    <t>IRR (32 bits)</t>
+  </si>
+  <si>
+    <t>ID de la unidad. Es modificable</t>
+  </si>
+  <si>
+    <t>EOI</t>
+  </si>
+  <si>
+    <t>Código para intento de ejecutar zona no ejecutable</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Detiene al núcleo hasta recibir una interrupción o instrucción</t>
+  </si>
+  <si>
+    <t>Shift lógico a la derecha de A por lo que dice B, guarda en C</t>
+  </si>
+  <si>
+    <t>Shift lógico a la izquierda de A por lo que dice B, guarda en C</t>
+  </si>
+  <si>
+    <t>Recibe el overflow o el carry de una operación anterior</t>
+  </si>
+  <si>
+    <t>Salto incondicional al numero guardado en un registro</t>
+  </si>
+  <si>
+    <t>Salto condicional al numero guardado en un registro</t>
+  </si>
+  <si>
+    <t>Vuelve del SO a la dirección guardada en el EPC</t>
+  </si>
+  <si>
+    <t>Parámetro 1</t>
+  </si>
+  <si>
+    <t>Parámetro 2</t>
+  </si>
+  <si>
+    <t>Parámetro 3</t>
+  </si>
+  <si>
+    <t>Activa el subsistema que permite recuperar la dirección de la RAM</t>
+  </si>
+  <si>
+    <t>Parámetro 4</t>
+  </si>
+  <si>
+    <t>Dirección virtual fallida</t>
+  </si>
+  <si>
+    <t>Congela el  núcleo hasta que allá  una interrupción</t>
+  </si>
+  <si>
+    <t>Parámetro 5</t>
+  </si>
+  <si>
+    <t>Causa de la excepción</t>
+  </si>
+  <si>
+    <t>Cause</t>
+  </si>
+  <si>
+    <t>Nota: Cause es el ID de la excepción, puede ser generado de manera asíncrona por cualquier subsistema</t>
+  </si>
+  <si>
+    <t>Flags Especiales del Núcleo, como kernel previo o actual</t>
+  </si>
+  <si>
+    <t>Determina de donde viene el dato para su posterior envió</t>
+  </si>
+  <si>
+    <t>Dirección al TSS</t>
+  </si>
+  <si>
+    <t>Nota: Dirección al TSS que contiene los SP que se usan para las distintas cosas, concretamente tiene la dirección del (RSP0=SP del kernel) y los distintos IST</t>
+  </si>
+  <si>
+    <t>Dirección de salto automática para SCL</t>
+  </si>
+  <si>
+    <t>Nota: AL inicio el LAPIC esta configurado en fee. Una vez haces una escritura en 00 de esa dirección, se setea la dirección base</t>
+  </si>
+  <si>
+    <t>Uso único del kernel</t>
+  </si>
+  <si>
+    <t>Nota: Estos registros son de uso único del kernel, son para no pisar datos en el guardado de contexto. El kernel debe copiar algunos registros aquí para luego hacer el guardado</t>
+  </si>
+  <si>
+    <t>El tamaño del putero si es un array, se define en el primer espacio, el puntero apunta al tamaño del array</t>
+  </si>
+  <si>
+    <t>Indica la dirección física donde empieza el LAPIC. Por defecto viene en fee</t>
+  </si>
+  <si>
+    <t>Configuración de la unidad</t>
+  </si>
+  <si>
+    <t>Nota: El bit "0" de la parte alta identifica si el error fue de IF o MEM, los códigos reales empiezan a partir del bit 1</t>
+  </si>
+  <si>
+    <t>Usa los primeros 7 bits (6-0) para definir el valor mínimo de las IRQs que pasan</t>
+  </si>
+  <si>
+    <t>Nota: El código de error especifico esta en la mitad alta de CR0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código para pagina no presente </t>
+  </si>
+  <si>
+    <t>Se usa solo el bit de menor valor. Marca el fin de una interrupción</t>
+  </si>
+  <si>
+    <t>Error de alineamiento en memoria, los accesos deben terminar en 00</t>
+  </si>
+  <si>
+    <t>Privilege Violación</t>
+  </si>
+  <si>
+    <t>Código para acceso restringido, solo permitido para el kernel</t>
+  </si>
+  <si>
+    <t>Configuración del Timer. Se usa del 6-0 para marcar un numero de interrupción (0 por defecto) el bit numero 7 habilita el timer</t>
+  </si>
+  <si>
+    <t>General Protección Fault</t>
+  </si>
+  <si>
+    <t>Código para acceso restringido de solo lectura</t>
+  </si>
+  <si>
+    <t>La cantidad de ciclos que el timer deberá contar ante de lanzar una IRQ. Se debe configurar este valor primero</t>
+  </si>
+  <si>
+    <t>0x28</t>
+  </si>
+  <si>
+    <t>SP: Punto del stack</t>
+  </si>
+  <si>
+    <t>Undefined</t>
+  </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Tipo de Nodo</t>
+  </si>
+  <si>
+    <t>BDF</t>
+  </si>
+  <si>
+    <t>Función / Dispositivo Conectado</t>
+  </si>
+  <si>
+    <t>PUERTO RAÍZ 1</t>
+  </si>
+  <si>
+    <t>Puerto/Bridge (RC)</t>
+  </si>
+  <si>
+    <t>00:01.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0008000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0008FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Controla el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Aquí se conectará la GPU.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">└─ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>GPU</t>
+    </r>
+  </si>
+  <si>
+    <t>Tarjeta (Endpoint)</t>
+  </si>
+  <si>
+    <t>01:00.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0100000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0100FFF</t>
+    </r>
+  </si>
+  <si>
+    <t>Tarjeta Gráfica Principal.</t>
+  </si>
+  <si>
+    <t>PUERTO RAÍZ 2</t>
+  </si>
+  <si>
+    <t>00:1C.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE00E0000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE00E0FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Controla el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Aquí se conectará el almacenamiento.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">└─ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NVMe SSD</t>
+    </r>
+  </si>
+  <si>
+    <t>02:00.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0200000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0200FFF</t>
+    </r>
+  </si>
+  <si>
+    <t>Almacenamiento de estado sólido.</t>
+  </si>
+  <si>
+    <t>PUERTO RAÍZ 3</t>
+  </si>
+  <si>
+    <t>00:1C.1</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE00E1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE00E1FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abre la línea hacia el Chipset. Controla el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">└─ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CHIPSET (SWITCH)</t>
+    </r>
+  </si>
+  <si>
+    <t>Estructura Interna</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>El Chipset distribuye el tráfico en cascada:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upstream Port</t>
+    </r>
+  </si>
+  <si>
+    <t>Puerto/Bridge (Switch)</t>
+  </si>
+  <si>
+    <t>03:00.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0300000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0300FFF</t>
+    </r>
+  </si>
+  <si>
+    <t>Entrada al Chipset. Abre el espacio para sus puertos de salida (Buses 4 al 11).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 1 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:00.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0400000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0400FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Controla el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> \(\rightarrow \) Conectado a: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controladora USB (Teclado)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>05:00.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0500000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 2 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:01.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0408000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0408FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Controla el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> \(\rightarrow \) Conectado a: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controladora USB (Mouse)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>06:00.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0600000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 3 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:02.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0410000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0410FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 4 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:03.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0418000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0418FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 5 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:04.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0420000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0420FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 6 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:05.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0428000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0428FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 7 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:06.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0430000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0430FFF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   └── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Port 8 (Downstream)</t>
+    </r>
+  </si>
+  <si>
+    <t>04:07.0</t>
+  </si>
+  <si>
+    <r>
+      <t>0xE0438000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0xE0438FFF</t>
+    </r>
+  </si>
+  <si>
+    <t>Rango Dirección ECAM</t>
+  </si>
+  <si>
+    <t>Nota: 0x7A32 es mi vendor ID y 0001 es el root complex</t>
+  </si>
+  <si>
+    <t>3 Bytes</t>
+  </si>
+  <si>
+    <t>1 Bytes</t>
+  </si>
+  <si>
+    <t>Class Code (3B)</t>
+  </si>
+  <si>
+    <t>Para cada puerto se entienede que es una funcion de Switch distinta. Para 3 puertos el switch tiene 3 funciones. Excepto en el Root Complex</t>
+  </si>
+  <si>
+    <t>Hex</t>
+  </si>
+  <si>
+    <t>Instrucción</t>
+  </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t>TTY Controller</t>
+  </si>
+  <si>
+    <t>Dato 1</t>
+  </si>
+  <si>
+    <t>Dato 2</t>
+  </si>
+  <si>
+    <t>Dato 3</t>
+  </si>
+  <si>
+    <t>Descrip</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>Write_Addr</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>No hace nada (Estado por defecto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borra X cantidad de espacios </t>
+  </si>
+  <si>
+    <t>Limpia toda la pantalla</t>
+  </si>
+  <si>
+    <t>Letra</t>
+  </si>
+  <si>
+    <t>Escribe una letra X cantidad de veces</t>
+  </si>
+  <si>
+    <t>Cant</t>
+  </si>
+  <si>
+    <t>Addr</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribe los bytes de la direccion dicha </t>
+  </si>
+  <si>
+    <t>Comand</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Enable TTY</t>
+  </si>
+  <si>
+    <t>Enable DMA</t>
+  </si>
+  <si>
+    <t>Busy</t>
+  </si>
+  <si>
+    <t>Invalid Command</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>DMA Not Allowed</t>
+  </si>
+  <si>
+    <t>Devices</t>
+  </si>
+  <si>
+    <t>Descrpción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Bridges. Fuera del Root Complex </t>
+  </si>
+  <si>
+    <t>Root Complex Bridges</t>
+  </si>
+  <si>
+    <t>Base-Sub-Prog IF-Header Type</t>
+  </si>
+  <si>
+    <t>0x2C</t>
+  </si>
+  <si>
+    <t>MSI Vector (32 bits)</t>
+  </si>
+  <si>
+    <t>Entrada para las insterrupciones MSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores que guardan las interrupciones en cola (mapa de bits). </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1467,8 +2450,49 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1523,6 +2547,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="75">
     <border>
@@ -2461,10 +3491,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="425">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2727,18 +3758,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2747,15 +3766,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2763,39 +3773,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -2820,9 +3800,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -2979,9 +3956,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3000,12 +3974,628 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="73" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3013,9 +4603,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3042,377 +4629,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3692,7 +5031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AI75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
     <col min="2" max="2" width="19.85546875" style="15" customWidth="1"/>
@@ -3710,10 +5049,14 @@
     <col min="15" max="15" width="18.7109375" style="15" customWidth="1"/>
     <col min="16" max="16" width="20" style="15" customWidth="1"/>
     <col min="17" max="17" width="9.140625" style="15" customWidth="1"/>
-    <col min="18" max="19" width="22.28515625" style="15" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" style="15" customWidth="1"/>
-    <col min="21" max="22" width="7.7109375" style="15" customWidth="1"/>
-    <col min="23" max="26" width="10.7109375" style="15" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" style="15" customWidth="1"/>
+    <col min="19" max="19" width="20.5703125" style="15" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="15" customWidth="1"/>
+    <col min="21" max="21" width="8.85546875" style="15" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" style="15" customWidth="1"/>
+    <col min="23" max="24" width="10.7109375" style="15" customWidth="1"/>
+    <col min="25" max="25" width="15.28515625" style="15" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="15" customWidth="1"/>
     <col min="27" max="28" width="6" style="15" customWidth="1"/>
     <col min="29" max="29" width="15.140625" style="15" customWidth="1"/>
     <col min="30" max="30" width="13.28515625" style="15" customWidth="1"/>
@@ -3724,103 +5067,103 @@
     <col min="36" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:35" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B2" s="248" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="263" t="s">
+    <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="325" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="264"/>
-      <c r="E2" s="265" t="s">
+      <c r="D2" s="335"/>
+      <c r="E2" s="336" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="265"/>
-      <c r="G2" s="266" t="s">
+      <c r="F2" s="336"/>
+      <c r="G2" s="337" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="265"/>
-      <c r="I2" s="265" t="s">
+      <c r="H2" s="336"/>
+      <c r="I2" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="265"/>
-      <c r="K2" s="267" t="s">
+      <c r="J2" s="336"/>
+      <c r="K2" s="338" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="265"/>
-      <c r="M2" s="265"/>
-      <c r="N2" s="265"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="268"/>
-      <c r="R2" s="244" t="s">
-        <v>65</v>
-      </c>
-      <c r="S2" s="242" t="s">
-        <v>66</v>
-      </c>
-      <c r="T2" s="235" t="s">
+      <c r="L2" s="336"/>
+      <c r="M2" s="336"/>
+      <c r="N2" s="336"/>
+      <c r="O2" s="336"/>
+      <c r="P2" s="339"/>
+      <c r="R2" s="342" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="294" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="346" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="236"/>
-      <c r="V2" s="236"/>
-      <c r="W2" s="236"/>
-      <c r="X2" s="236"/>
-      <c r="Y2" s="236"/>
-      <c r="Z2" s="236"/>
-      <c r="AA2" s="236"/>
-      <c r="AB2" s="236" t="s">
+      <c r="U2" s="347"/>
+      <c r="V2" s="347"/>
+      <c r="W2" s="347"/>
+      <c r="X2" s="347"/>
+      <c r="Y2" s="347"/>
+      <c r="Z2" s="347"/>
+      <c r="AA2" s="347"/>
+      <c r="AB2" s="347" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="236"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="236"/>
-      <c r="AF2" s="236"/>
-      <c r="AG2" s="236"/>
-      <c r="AH2" s="236"/>
-      <c r="AI2" s="237"/>
-    </row>
-    <row r="3" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B3" s="249"/>
+      <c r="AC2" s="347"/>
+      <c r="AD2" s="347"/>
+      <c r="AE2" s="347"/>
+      <c r="AF2" s="347"/>
+      <c r="AG2" s="347"/>
+      <c r="AH2" s="347"/>
+      <c r="AI2" s="348"/>
+    </row>
+    <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="326"/>
       <c r="C3" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="220"/>
-      <c r="L3" s="262"/>
-      <c r="M3" s="262"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="221"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="184"/>
+        <v>31</v>
+      </c>
+      <c r="K3" s="331"/>
+      <c r="L3" s="332"/>
+      <c r="M3" s="332"/>
+      <c r="N3" s="332"/>
+      <c r="O3" s="332"/>
+      <c r="P3" s="333"/>
+      <c r="R3" s="343"/>
+      <c r="S3" s="340"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="272" t="s">
-        <v>83</v>
-      </c>
-      <c r="V3" s="272"/>
+      <c r="U3" s="312" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" s="312"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -3833,10 +5176,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="234" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB3" s="234"/>
+      <c r="AA3" s="345" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB3" s="345"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -3859,84 +5202,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:35" ht="15.75" thickBot="1">
-      <c r="B4" s="250"/>
+    <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="327"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="238" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="225"/>
-      <c r="G4" s="225"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="225"/>
-      <c r="J4" s="226"/>
+      <c r="E4" s="313" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="244"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="238" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="225"/>
-      <c r="P4" s="226"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="243"/>
+      <c r="N4" s="313" t="s">
+        <v>310</v>
+      </c>
+      <c r="O4" s="243"/>
+      <c r="P4" s="244"/>
+      <c r="R4" s="344"/>
+      <c r="S4" s="341"/>
       <c r="T4" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="U4" s="238" t="s">
-        <v>75</v>
-      </c>
-      <c r="V4" s="239"/>
+        <v>127</v>
+      </c>
+      <c r="U4" s="313" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="314"/>
       <c r="W4" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Y4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="313" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB4" s="314"/>
+      <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA4" s="238" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB4" s="239"/>
-      <c r="AC4" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="AD4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="AE4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF4" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="AG4" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="2:35" ht="15.75" thickBot="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>0</v>
       </c>
@@ -3945,35 +5288,35 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="269"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="271"/>
+      <c r="E5" s="317"/>
+      <c r="F5" s="318"/>
+      <c r="G5" s="318"/>
+      <c r="H5" s="318"/>
+      <c r="I5" s="318"/>
+      <c r="J5" s="319"/>
       <c r="K5" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="202" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="247"/>
-      <c r="P5" s="203"/>
+      <c r="N5" s="253" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="254"/>
+      <c r="P5" s="255"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
       <c r="S5" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="240" t="s">
-        <v>73</v>
-      </c>
-      <c r="V5" s="241"/>
+      <c r="U5" s="315" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="316"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -3986,10 +5329,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="240" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB5" s="241"/>
+      <c r="AA5" s="315" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" s="316"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -4012,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:35" ht="15.75" thickBot="1">
+    <row r="6" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -4021,37 +5364,37 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="260"/>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="255"/>
-      <c r="J6" s="256"/>
+      <c r="E6" s="324"/>
+      <c r="F6" s="321"/>
+      <c r="G6" s="321"/>
+      <c r="H6" s="321"/>
+      <c r="I6" s="321"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6" s="61" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="231" t="s">
-        <v>95</v>
-      </c>
-      <c r="O6" s="232"/>
-      <c r="P6" s="233"/>
+      <c r="N6" s="250" t="s">
+        <v>311</v>
+      </c>
+      <c r="O6" s="251"/>
+      <c r="P6" s="252"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V6" s="228"/>
+      <c r="U6" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" s="311"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -4064,10 +5407,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB6" s="228"/>
+      <c r="AA6" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB6" s="311"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -4090,54 +5433,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:35" ht="15.75" thickBot="1">
+    <row r="7" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="177" t="s">
-        <v>330</v>
+      <c r="C7" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D7" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00010</v>
       </c>
       <c r="E7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="254"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="256"/>
+      <c r="H7" s="320"/>
+      <c r="I7" s="321"/>
+      <c r="J7" s="322"/>
       <c r="K7" s="25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" s="38"/>
       <c r="M7" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N7" s="231" t="s">
-        <v>52</v>
-      </c>
-      <c r="O7" s="232"/>
-      <c r="P7" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N7" s="250" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="251"/>
+      <c r="P7" s="252"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V7" s="228"/>
+      <c r="U7" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="311"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -4150,10 +5493,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB7" s="228"/>
+      <c r="AA7" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB7" s="311"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -4176,54 +5519,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:35" ht="15.75" thickBot="1">
+    <row r="8" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="C8" s="177" t="s">
-        <v>330</v>
+      <c r="C8" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00011</v>
       </c>
       <c r="E8" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="254"/>
-      <c r="I8" s="255"/>
-      <c r="J8" s="256"/>
+      <c r="H8" s="320"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="322"/>
       <c r="K8" s="37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" s="38"/>
       <c r="M8" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N8" s="231" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="232"/>
-      <c r="P8" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N8" s="250" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" s="251"/>
+      <c r="P8" s="252"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
       <c r="S8" s="38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V8" s="228"/>
+      <c r="U8" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V8" s="311"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -4236,10 +5579,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB8" s="228"/>
+      <c r="AA8" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB8" s="311"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -4262,54 +5605,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:35" ht="15.75" thickBot="1">
+    <row r="9" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="177" t="s">
-        <v>330</v>
+      <c r="C9" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D9" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00100</v>
       </c>
       <c r="E9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="254"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="256"/>
+      <c r="H9" s="320"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="322"/>
       <c r="K9" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L9" s="38"/>
       <c r="M9" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N9" s="231" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="232"/>
-      <c r="P9" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N9" s="250" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="251"/>
+      <c r="P9" s="252"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
       <c r="S9" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V9" s="228"/>
+      <c r="U9" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V9" s="311"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -4322,10 +5665,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB9" s="228"/>
+      <c r="AA9" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB9" s="311"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -4348,54 +5691,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:35" ht="15.75" thickBot="1">
+    <row r="10" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>5</v>
       </c>
-      <c r="C10" s="177" t="s">
-        <v>330</v>
+      <c r="C10" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00101</v>
       </c>
       <c r="E10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="254"/>
-      <c r="I10" s="255"/>
-      <c r="J10" s="256"/>
+      <c r="H10" s="320"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="322"/>
       <c r="K10" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L10" s="38"/>
       <c r="M10" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N10" s="231" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="232"/>
-      <c r="P10" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N10" s="250" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" s="251"/>
+      <c r="P10" s="252"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
       <c r="S10" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V10" s="228"/>
+      <c r="U10" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V10" s="311"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -4408,10 +5751,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB10" s="228"/>
+      <c r="AA10" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB10" s="311"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -4434,54 +5777,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:35" ht="15.75" thickBot="1">
+    <row r="11" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>6</v>
       </c>
-      <c r="C11" s="177" t="s">
-        <v>330</v>
+      <c r="C11" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D11" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00110</v>
       </c>
       <c r="E11" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="254"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="256"/>
+      <c r="H11" s="320"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="322"/>
       <c r="K11" s="37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L11" s="38"/>
       <c r="M11" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N11" s="231" t="s">
-        <v>56</v>
-      </c>
-      <c r="O11" s="232"/>
-      <c r="P11" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N11" s="250" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="251"/>
+      <c r="P11" s="252"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
       <c r="S11" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V11" s="228"/>
+      <c r="U11" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="311"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -4494,10 +5837,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB11" s="228"/>
+      <c r="AA11" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB11" s="311"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -4520,54 +5863,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:35" ht="15.75" thickBot="1">
+    <row r="12" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>7</v>
       </c>
-      <c r="C12" s="177" t="s">
-        <v>330</v>
+      <c r="C12" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D12" s="23" t="str">
         <f t="shared" si="0"/>
         <v>00111</v>
       </c>
       <c r="E12" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="254"/>
-      <c r="I12" s="255"/>
-      <c r="J12" s="256"/>
+      <c r="H12" s="320"/>
+      <c r="I12" s="321"/>
+      <c r="J12" s="322"/>
       <c r="K12" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12" s="38"/>
       <c r="M12" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N12" s="231" t="s">
-        <v>57</v>
-      </c>
-      <c r="O12" s="232"/>
-      <c r="P12" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N12" s="250" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="251"/>
+      <c r="P12" s="252"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
       <c r="S12" s="38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V12" s="228"/>
+      <c r="U12" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V12" s="311"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -4580,10 +5923,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB12" s="228"/>
+      <c r="AA12" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" s="311"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -4606,54 +5949,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:35" ht="15.75" thickBot="1">
+    <row r="13" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C13" s="177" t="s">
-        <v>330</v>
+      <c r="C13" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D13" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01000</v>
       </c>
       <c r="E13" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="254"/>
-      <c r="I13" s="255"/>
-      <c r="J13" s="256"/>
+      <c r="H13" s="320"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="322"/>
       <c r="K13" s="37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" s="38"/>
       <c r="M13" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N13" s="231" t="s">
-        <v>58</v>
-      </c>
-      <c r="O13" s="232"/>
-      <c r="P13" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N13" s="250" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="251"/>
+      <c r="P13" s="252"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
       <c r="S13" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V13" s="228"/>
+      <c r="U13" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V13" s="311"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -4666,10 +6009,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB13" s="228"/>
+      <c r="AA13" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB13" s="311"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -4692,54 +6035,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:35" ht="15.75" thickBot="1">
+    <row r="14" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>9</v>
       </c>
-      <c r="C14" s="177" t="s">
-        <v>330</v>
+      <c r="C14" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D14" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01001</v>
       </c>
       <c r="E14" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="254"/>
-      <c r="I14" s="255"/>
-      <c r="J14" s="256"/>
+      <c r="H14" s="320"/>
+      <c r="I14" s="321"/>
+      <c r="J14" s="322"/>
       <c r="K14" s="37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L14" s="38"/>
       <c r="M14" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N14" s="231" t="s">
-        <v>59</v>
-      </c>
-      <c r="O14" s="232"/>
-      <c r="P14" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N14" s="250" t="s">
+        <v>312</v>
+      </c>
+      <c r="O14" s="251"/>
+      <c r="P14" s="252"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
       <c r="S14" s="38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V14" s="228"/>
+      <c r="U14" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V14" s="311"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -4752,10 +6095,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB14" s="228"/>
+      <c r="AA14" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB14" s="311"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -4778,54 +6121,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:35" ht="15.75" thickBot="1">
+    <row r="15" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>10</v>
       </c>
-      <c r="C15" s="177" t="s">
-        <v>330</v>
+      <c r="C15" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D15" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01010</v>
       </c>
       <c r="E15" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="254"/>
-      <c r="I15" s="255"/>
-      <c r="J15" s="256"/>
+      <c r="H15" s="320"/>
+      <c r="I15" s="321"/>
+      <c r="J15" s="322"/>
       <c r="K15" s="31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L15" s="38"/>
       <c r="M15" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N15" s="231" t="s">
-        <v>60</v>
-      </c>
-      <c r="O15" s="232"/>
-      <c r="P15" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N15" s="250" t="s">
+        <v>313</v>
+      </c>
+      <c r="O15" s="251"/>
+      <c r="P15" s="252"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
       <c r="S15" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V15" s="228"/>
+      <c r="U15" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V15" s="311"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -4838,10 +6181,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB15" s="228"/>
+      <c r="AA15" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB15" s="311"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -4864,48 +6207,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:35" ht="15.75" thickBot="1">
+    <row r="16" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>11</v>
       </c>
-      <c r="C16" s="177" t="s">
-        <v>330</v>
+      <c r="C16" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D16" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01011</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="254"/>
-      <c r="G16" s="255"/>
-      <c r="H16" s="255"/>
-      <c r="I16" s="255"/>
-      <c r="J16" s="256"/>
+        <v>27</v>
+      </c>
+      <c r="F16" s="320"/>
+      <c r="G16" s="321"/>
+      <c r="H16" s="321"/>
+      <c r="I16" s="321"/>
+      <c r="J16" s="322"/>
       <c r="K16" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="231" t="s">
-        <v>50</v>
-      </c>
-      <c r="O16" s="232"/>
-      <c r="P16" s="233"/>
+      <c r="N16" s="250" t="s">
+        <v>314</v>
+      </c>
+      <c r="O16" s="251"/>
+      <c r="P16" s="252"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
       <c r="S16" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V16" s="228"/>
+      <c r="U16" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V16" s="311"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -4918,10 +6261,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB16" s="228"/>
+      <c r="AA16" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" s="311"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -4944,50 +6287,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:35" ht="15.75" thickBot="1">
+    <row r="17" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>12</v>
       </c>
-      <c r="C17" s="177" t="s">
-        <v>331</v>
+      <c r="C17" s="158" t="s">
+        <v>279</v>
       </c>
       <c r="D17" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01100</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="261" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="232"/>
-      <c r="I17" s="232"/>
-      <c r="J17" s="233"/>
+      <c r="G17" s="323" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="252"/>
       <c r="K17" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="231" t="s">
-        <v>64</v>
-      </c>
-      <c r="O17" s="232"/>
-      <c r="P17" s="233"/>
+      <c r="N17" s="250" t="s">
+        <v>60</v>
+      </c>
+      <c r="O17" s="251"/>
+      <c r="P17" s="252"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
       <c r="S17" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V17" s="228"/>
+      <c r="U17" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V17" s="311"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -5000,10 +6343,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB17" s="228"/>
+      <c r="AA17" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" s="311"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -5026,52 +6369,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:35" ht="15.75" thickBot="1">
+    <row r="18" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>13</v>
       </c>
-      <c r="C18" s="177" t="s">
-        <v>330</v>
+      <c r="C18" s="158" t="s">
+        <v>278</v>
       </c>
       <c r="D18" s="23" t="str">
         <f t="shared" si="0"/>
         <v>01101</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="261" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="232"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="233"/>
+      <c r="G18" s="323" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="252"/>
       <c r="K18" s="40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L18" s="43"/>
       <c r="M18" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="N18" s="231" t="s">
-        <v>61</v>
-      </c>
-      <c r="O18" s="232"/>
-      <c r="P18" s="233"/>
+        <v>131</v>
+      </c>
+      <c r="N18" s="250" t="s">
+        <v>57</v>
+      </c>
+      <c r="O18" s="251"/>
+      <c r="P18" s="252"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
       <c r="S18" s="41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V18" s="228"/>
+      <c r="U18" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" s="311"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -5084,10 +6427,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB18" s="228"/>
+      <c r="AA18" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB18" s="311"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -5110,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:35" ht="15.75" thickBot="1">
+    <row r="19" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>14</v>
       </c>
@@ -5121,35 +6464,35 @@
       </c>
       <c r="E19" s="60"/>
       <c r="F19" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="254"/>
-      <c r="H19" s="255"/>
-      <c r="I19" s="255"/>
-      <c r="J19" s="256"/>
+        <v>28</v>
+      </c>
+      <c r="G19" s="320"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="322"/>
       <c r="K19" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="231" t="s">
-        <v>93</v>
-      </c>
-      <c r="O19" s="232"/>
-      <c r="P19" s="233"/>
+      <c r="N19" s="250" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="251"/>
+      <c r="P19" s="252"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
       <c r="S19" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V19" s="228"/>
+      <c r="U19" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" s="311"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -5162,10 +6505,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB19" s="228"/>
+      <c r="AA19" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB19" s="311"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -5188,7 +6531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:35" ht="15.75" thickBot="1">
+    <row r="20" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>15</v>
       </c>
@@ -5198,38 +6541,38 @@
         <v>01111</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="254"/>
-      <c r="H20" s="255"/>
-      <c r="I20" s="255"/>
-      <c r="J20" s="256"/>
+        <v>28</v>
+      </c>
+      <c r="G20" s="320"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="322"/>
       <c r="K20" s="37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="231" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="232"/>
-      <c r="P20" s="233"/>
+      <c r="N20" s="250" t="s">
+        <v>316</v>
+      </c>
+      <c r="O20" s="251"/>
+      <c r="P20" s="252"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
       <c r="S20" s="38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V20" s="228"/>
+      <c r="U20" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V20" s="311"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -5242,10 +6585,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB20" s="228"/>
+      <c r="AA20" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB20" s="311"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -5268,12 +6611,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:35" ht="15.75" thickBot="1">
+    <row r="21" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="D21" s="23" t="str">
         <f t="shared" si="0"/>
@@ -5281,51 +6624,51 @@
       </c>
       <c r="E21" s="60"/>
       <c r="F21" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="254"/>
-      <c r="H21" s="255"/>
-      <c r="I21" s="255"/>
-      <c r="J21" s="256"/>
+        <v>28</v>
+      </c>
+      <c r="G21" s="320"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="322"/>
       <c r="K21" s="44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="231" t="s">
-        <v>62</v>
-      </c>
-      <c r="O21" s="232"/>
-      <c r="P21" s="233"/>
+      <c r="N21" s="250" t="s">
+        <v>58</v>
+      </c>
+      <c r="O21" s="251"/>
+      <c r="P21" s="252"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
       <c r="S21" s="45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="227" t="s">
-        <v>96</v>
-      </c>
-      <c r="V21" s="228"/>
+      <c r="U21" s="310" t="s">
+        <v>88</v>
+      </c>
+      <c r="V21" s="311"/>
       <c r="W21" s="34">
+        <v>0</v>
+      </c>
+      <c r="X21" s="34">
         <v>1</v>
       </c>
-      <c r="X21" s="34">
-        <v>0</v>
-      </c>
       <c r="Y21" s="34">
         <v>0</v>
       </c>
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="227" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB21" s="228"/>
+      <c r="AA21" s="310" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB21" s="311"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -5348,51 +6691,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:35" ht="15.75" thickBot="1">
+    <row r="22" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="D22" s="23" t="str">
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="260"/>
-      <c r="F22" s="255"/>
-      <c r="G22" s="255"/>
-      <c r="H22" s="255"/>
-      <c r="I22" s="255"/>
-      <c r="J22" s="256"/>
+      <c r="E22" s="324"/>
+      <c r="F22" s="321"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="321"/>
+      <c r="I22" s="321"/>
+      <c r="J22" s="322"/>
       <c r="K22" s="40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="231" t="s">
-        <v>63</v>
-      </c>
-      <c r="O22" s="232"/>
-      <c r="P22" s="233"/>
+      <c r="N22" s="250" t="s">
+        <v>59</v>
+      </c>
+      <c r="O22" s="251"/>
+      <c r="P22" s="252"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
       <c r="S22" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V22" s="228"/>
+      <c r="U22" s="310" t="s">
+        <v>88</v>
+      </c>
+      <c r="V22" s="311"/>
       <c r="W22" s="34">
+        <v>0</v>
+      </c>
+      <c r="X22" s="34">
         <v>1</v>
-      </c>
-      <c r="X22" s="34">
-        <v>0</v>
       </c>
       <c r="Y22" s="34">
         <v>0</v>
@@ -5400,10 +6743,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="227" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB22" s="228"/>
+      <c r="AA22" s="310" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB22" s="311"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -5414,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AF22" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="34">
         <v>0</v>
@@ -5426,52 +6769,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:35" ht="15.75" thickBot="1">
+    <row r="23" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="D23" s="23" t="str">
         <f t="shared" si="0"/>
         <v>10010</v>
       </c>
       <c r="E23" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="261" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="232"/>
-      <c r="I23" s="232"/>
-      <c r="J23" s="233"/>
+      <c r="G23" s="323" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="251"/>
+      <c r="I23" s="251"/>
+      <c r="J23" s="252"/>
       <c r="K23" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="231" t="s">
-        <v>82</v>
-      </c>
-      <c r="O23" s="232"/>
-      <c r="P23" s="233"/>
+      <c r="N23" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" s="251"/>
+      <c r="P23" s="252"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
       <c r="S23" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="227" t="s">
-        <v>97</v>
-      </c>
-      <c r="V23" s="228"/>
+      <c r="U23" s="310" t="s">
+        <v>89</v>
+      </c>
+      <c r="V23" s="311"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -5484,10 +6827,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="227" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB23" s="228"/>
+      <c r="AA23" s="310" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB23" s="311"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -5510,52 +6853,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:35" ht="15.75" thickBot="1">
+    <row r="24" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="D24" s="23" t="str">
         <f t="shared" si="0"/>
         <v>10011</v>
       </c>
       <c r="E24" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" s="261" t="s">
-        <v>77</v>
-      </c>
-      <c r="H24" s="232"/>
-      <c r="I24" s="232"/>
-      <c r="J24" s="233"/>
+      <c r="G24" s="323" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="251"/>
+      <c r="I24" s="251"/>
+      <c r="J24" s="252"/>
       <c r="K24" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="231" t="s">
-        <v>81</v>
-      </c>
-      <c r="O24" s="232"/>
-      <c r="P24" s="233"/>
+      <c r="N24" s="250" t="s">
+        <v>77</v>
+      </c>
+      <c r="O24" s="251"/>
+      <c r="P24" s="252"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
       <c r="S24" s="32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V24" s="228"/>
+      <c r="U24" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V24" s="311"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -5568,10 +6911,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="227" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB24" s="228"/>
+      <c r="AA24" s="310" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB24" s="311"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -5594,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:35" ht="15.75" thickBot="1">
+    <row r="25" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>20</v>
       </c>
@@ -5604,40 +6947,40 @@
         <v>10100</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="254"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="255"/>
-      <c r="J25" s="256"/>
+        <v>27</v>
+      </c>
+      <c r="G25" s="320"/>
+      <c r="H25" s="321"/>
+      <c r="I25" s="321"/>
+      <c r="J25" s="322"/>
       <c r="K25" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L25" s="57" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="231" t="s">
-        <v>41</v>
-      </c>
-      <c r="O25" s="232"/>
-      <c r="P25" s="233"/>
+      <c r="N25" s="250" t="s">
+        <v>40</v>
+      </c>
+      <c r="O25" s="251"/>
+      <c r="P25" s="252"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
       <c r="S25" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V25" s="228"/>
+      <c r="U25" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V25" s="311"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -5650,10 +6993,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB25" s="228"/>
+      <c r="AA25" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB25" s="311"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -5676,7 +7019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:35" ht="15.75" thickBot="1">
+    <row r="26" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>21</v>
       </c>
@@ -5686,40 +7029,40 @@
         <v>10101</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="254"/>
-      <c r="H26" s="255"/>
-      <c r="I26" s="255"/>
-      <c r="J26" s="256"/>
+        <v>42</v>
+      </c>
+      <c r="G26" s="320"/>
+      <c r="H26" s="321"/>
+      <c r="I26" s="321"/>
+      <c r="J26" s="322"/>
       <c r="K26" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L26" s="57" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="231" t="s">
-        <v>42</v>
-      </c>
-      <c r="O26" s="232"/>
-      <c r="P26" s="233"/>
+      <c r="N26" s="250" t="s">
+        <v>41</v>
+      </c>
+      <c r="O26" s="251"/>
+      <c r="P26" s="252"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
       <c r="S26" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V26" s="228"/>
+      <c r="U26" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V26" s="311"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -5732,10 +7075,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB26" s="228"/>
+      <c r="AA26" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB26" s="311"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -5758,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:35" ht="15.75" thickBot="1">
+    <row r="27" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>22</v>
       </c>
@@ -5767,35 +7110,35 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="260"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="256"/>
+      <c r="E27" s="324"/>
+      <c r="F27" s="321"/>
+      <c r="G27" s="321"/>
+      <c r="H27" s="321"/>
+      <c r="I27" s="321"/>
+      <c r="J27" s="322"/>
       <c r="K27" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="231" t="s">
-        <v>46</v>
-      </c>
-      <c r="O27" s="232"/>
-      <c r="P27" s="233"/>
+      <c r="N27" s="250" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" s="251"/>
+      <c r="P27" s="252"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
       <c r="S27" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="V27" s="228"/>
+      <c r="U27" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="V27" s="311"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -5808,10 +7151,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="227" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB27" s="228"/>
+      <c r="AA27" s="310" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB27" s="311"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -5834,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:35" ht="15.75" thickBot="1">
+    <row r="28" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>23</v>
       </c>
@@ -5843,37 +7186,37 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="257"/>
-      <c r="F28" s="258"/>
-      <c r="G28" s="258"/>
-      <c r="H28" s="258"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="259"/>
+      <c r="E28" s="328"/>
+      <c r="F28" s="329"/>
+      <c r="G28" s="329"/>
+      <c r="H28" s="329"/>
+      <c r="I28" s="329"/>
+      <c r="J28" s="330"/>
       <c r="K28" s="52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L28" s="58" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="251" t="s">
-        <v>92</v>
-      </c>
-      <c r="O28" s="252"/>
-      <c r="P28" s="253"/>
+      <c r="N28" s="247" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" s="248"/>
+      <c r="P28" s="249"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
       <c r="S28" s="53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="229" t="s">
-        <v>73</v>
-      </c>
-      <c r="V28" s="230"/>
+      <c r="U28" s="357" t="s">
+        <v>69</v>
+      </c>
+      <c r="V28" s="358"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -5886,10 +7229,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="229" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB28" s="230"/>
+      <c r="AA28" s="357" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB28" s="358"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -5912,10 +7255,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:35" ht="15.75" thickBot="1"/>
-    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1">
+    <row r="29" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:35" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="66" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C30" s="6" t="str">
         <f>DEC2BIN(B5,2)</f>
@@ -5934,7 +7277,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="66" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="I30" s="73">
         <v>7</v>
@@ -5961,42 +7304,51 @@
         <v>0</v>
       </c>
       <c r="R30" s="71" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="S30" s="75" t="s">
-        <v>155</v>
-      </c>
-      <c r="T30" s="273" t="s">
-        <v>156</v>
-      </c>
-      <c r="U30" s="273"/>
-      <c r="V30" s="273"/>
-      <c r="W30" s="273"/>
-      <c r="X30" s="273"/>
-      <c r="Y30" s="273"/>
-      <c r="Z30" s="273"/>
-      <c r="AA30" s="273"/>
-      <c r="AB30" s="273"/>
-      <c r="AC30" s="242"/>
-    </row>
-    <row r="31" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
+        <v>132</v>
+      </c>
+      <c r="T30" s="293" t="s">
+        <v>133</v>
+      </c>
+      <c r="U30" s="293"/>
+      <c r="V30" s="293"/>
+      <c r="W30" s="293"/>
+      <c r="X30" s="293"/>
+      <c r="Y30" s="293"/>
+      <c r="Z30" s="293"/>
+      <c r="AA30" s="293"/>
+      <c r="AB30" s="293"/>
+      <c r="AC30" s="294"/>
+      <c r="AE30" s="242" t="s">
+        <v>422</v>
+      </c>
+      <c r="AF30" s="243"/>
+      <c r="AG30" s="242" t="s">
+        <v>423</v>
+      </c>
+      <c r="AH30" s="243"/>
+      <c r="AI30" s="244"/>
+    </row>
+    <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C31" s="62" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H31" s="77" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I31" s="78"/>
       <c r="J31" s="79"/>
@@ -6004,72 +7356,81 @@
       <c r="L31" s="79"/>
       <c r="M31" s="79"/>
       <c r="N31" s="79" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="O31" s="79" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="P31" s="80" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="R31" s="67">
         <v>0</v>
       </c>
       <c r="S31" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="T31" s="202" t="s">
-        <v>161</v>
-      </c>
-      <c r="U31" s="247"/>
-      <c r="V31" s="247"/>
-      <c r="W31" s="247"/>
-      <c r="X31" s="247"/>
-      <c r="Y31" s="247"/>
-      <c r="Z31" s="247"/>
-      <c r="AA31" s="247"/>
-      <c r="AB31" s="247"/>
-      <c r="AC31" s="203"/>
-    </row>
-    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
+        <v>134</v>
+      </c>
+      <c r="T31" s="253" t="s">
+        <v>138</v>
+      </c>
+      <c r="U31" s="254"/>
+      <c r="V31" s="254"/>
+      <c r="W31" s="254"/>
+      <c r="X31" s="254"/>
+      <c r="Y31" s="254"/>
+      <c r="Z31" s="254"/>
+      <c r="AA31" s="254"/>
+      <c r="AB31" s="254"/>
+      <c r="AC31" s="255"/>
+      <c r="AE31" s="288">
+        <v>2</v>
+      </c>
+      <c r="AF31" s="289"/>
+      <c r="AG31" s="290" t="str" cm="1">
+        <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
+        <v>No encontrado</v>
+      </c>
+      <c r="AH31" s="291"/>
+      <c r="AI31" s="292"/>
+    </row>
+    <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C32" s="65" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="N32" s="315"/>
+        <v>85</v>
+      </c>
       <c r="R32" s="2">
         <v>1</v>
       </c>
       <c r="S32" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="T32" s="231" t="s">
-        <v>162</v>
-      </c>
-      <c r="U32" s="232"/>
-      <c r="V32" s="232"/>
-      <c r="W32" s="232"/>
-      <c r="X32" s="232"/>
-      <c r="Y32" s="232"/>
-      <c r="Z32" s="232"/>
-      <c r="AA32" s="232"/>
-      <c r="AB32" s="232"/>
-      <c r="AC32" s="233"/>
-    </row>
-    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1">
+        <v>64</v>
+      </c>
+      <c r="T32" s="250" t="s">
+        <v>139</v>
+      </c>
+      <c r="U32" s="251"/>
+      <c r="V32" s="251"/>
+      <c r="W32" s="251"/>
+      <c r="X32" s="251"/>
+      <c r="Y32" s="251"/>
+      <c r="Z32" s="251"/>
+      <c r="AA32" s="251"/>
+      <c r="AB32" s="251"/>
+      <c r="AC32" s="252"/>
+    </row>
+    <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I33" s="73">
         <v>7</v>
@@ -6099,107 +7460,107 @@
         <v>2</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="T33" s="231" t="s">
-        <v>163</v>
-      </c>
-      <c r="U33" s="232"/>
-      <c r="V33" s="232"/>
-      <c r="W33" s="232"/>
-      <c r="X33" s="232"/>
-      <c r="Y33" s="232"/>
-      <c r="Z33" s="232"/>
-      <c r="AA33" s="232"/>
-      <c r="AB33" s="232"/>
-      <c r="AC33" s="233"/>
-    </row>
-    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B34" s="222" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="220" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="221"/>
-      <c r="E34" s="220" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="221"/>
+        <v>135</v>
+      </c>
+      <c r="T33" s="250" t="s">
+        <v>140</v>
+      </c>
+      <c r="U33" s="251"/>
+      <c r="V33" s="251"/>
+      <c r="W33" s="251"/>
+      <c r="X33" s="251"/>
+      <c r="Y33" s="251"/>
+      <c r="Z33" s="251"/>
+      <c r="AA33" s="251"/>
+      <c r="AB33" s="251"/>
+      <c r="AC33" s="252"/>
+    </row>
+    <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="355" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="331" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="333"/>
+      <c r="E34" s="331" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="333"/>
       <c r="H34" s="77" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I34" s="78"/>
       <c r="J34" s="79"/>
       <c r="K34" s="79"/>
       <c r="L34" s="79" t="s">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="M34" s="79" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="N34" s="79" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="O34" s="79" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="P34" s="80" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="R34" s="2">
         <v>3</v>
       </c>
       <c r="S34" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="T34" s="231" t="s">
-        <v>164</v>
-      </c>
-      <c r="U34" s="232"/>
-      <c r="V34" s="232"/>
-      <c r="W34" s="232"/>
-      <c r="X34" s="232"/>
-      <c r="Y34" s="232"/>
-      <c r="Z34" s="232"/>
-      <c r="AA34" s="232"/>
-      <c r="AB34" s="232"/>
-      <c r="AC34" s="233"/>
-    </row>
-    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B35" s="223"/>
+        <v>23</v>
+      </c>
+      <c r="T34" s="250" t="s">
+        <v>141</v>
+      </c>
+      <c r="U34" s="251"/>
+      <c r="V34" s="251"/>
+      <c r="W34" s="251"/>
+      <c r="X34" s="251"/>
+      <c r="Y34" s="251"/>
+      <c r="Z34" s="251"/>
+      <c r="AA34" s="251"/>
+      <c r="AB34" s="251"/>
+      <c r="AC34" s="252"/>
+    </row>
+    <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="356"/>
       <c r="C35" s="64" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E35" s="64" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R35" s="2">
         <v>4</v>
       </c>
       <c r="S35" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="T35" s="231" t="s">
-        <v>165</v>
-      </c>
-      <c r="U35" s="232"/>
-      <c r="V35" s="232"/>
-      <c r="W35" s="232"/>
-      <c r="X35" s="232"/>
-      <c r="Y35" s="232"/>
-      <c r="Z35" s="232"/>
-      <c r="AA35" s="232"/>
-      <c r="AB35" s="232"/>
-      <c r="AC35" s="233"/>
-    </row>
-    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1">
+        <v>21</v>
+      </c>
+      <c r="T35" s="250" t="s">
+        <v>142</v>
+      </c>
+      <c r="U35" s="251"/>
+      <c r="V35" s="251"/>
+      <c r="W35" s="251"/>
+      <c r="X35" s="251"/>
+      <c r="Y35" s="251"/>
+      <c r="Z35" s="251"/>
+      <c r="AA35" s="251"/>
+      <c r="AB35" s="251"/>
+      <c r="AC35" s="252"/>
+    </row>
+    <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>0</v>
       </c>
@@ -6207,16 +7568,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F36" s="68" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="H36" s="84" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="I36" s="73">
         <v>7</v>
@@ -6246,827 +7607,1139 @@
         <v>5</v>
       </c>
       <c r="S36" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="T36" s="231" t="s">
-        <v>166</v>
-      </c>
-      <c r="U36" s="232"/>
-      <c r="V36" s="232"/>
-      <c r="W36" s="232"/>
-      <c r="X36" s="232"/>
-      <c r="Y36" s="232"/>
-      <c r="Z36" s="232"/>
-      <c r="AA36" s="232"/>
-      <c r="AB36" s="232"/>
-      <c r="AC36" s="233"/>
-    </row>
-    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1">
+        <v>22</v>
+      </c>
+      <c r="T36" s="250" t="s">
+        <v>143</v>
+      </c>
+      <c r="U36" s="251"/>
+      <c r="V36" s="251"/>
+      <c r="W36" s="251"/>
+      <c r="X36" s="251"/>
+      <c r="Y36" s="251"/>
+      <c r="Z36" s="251"/>
+      <c r="AA36" s="251"/>
+      <c r="AB36" s="251"/>
+      <c r="AC36" s="252"/>
+    </row>
+    <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>1</v>
       </c>
       <c r="C37" s="70" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D37" s="69" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H37" s="77" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I37" s="78"/>
       <c r="J37" s="79"/>
       <c r="K37" s="79"/>
       <c r="L37" s="79"/>
-      <c r="M37" s="178" t="s">
-        <v>338</v>
+      <c r="M37" s="159" t="s">
+        <v>285</v>
       </c>
       <c r="N37" s="79" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="O37" s="79" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="P37" s="80" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="R37" s="2">
         <v>6</v>
       </c>
       <c r="S37" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="T37" s="231" t="s">
-        <v>192</v>
-      </c>
-      <c r="U37" s="232"/>
-      <c r="V37" s="232"/>
-      <c r="W37" s="232"/>
-      <c r="X37" s="232"/>
-      <c r="Y37" s="232"/>
-      <c r="Z37" s="232"/>
-      <c r="AA37" s="232"/>
-      <c r="AB37" s="232"/>
-      <c r="AC37" s="233"/>
-    </row>
-    <row r="38" spans="2:29" ht="15.75" thickBot="1">
+        <v>11</v>
+      </c>
+      <c r="T37" s="250" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="251"/>
+      <c r="V37" s="251"/>
+      <c r="W37" s="251"/>
+      <c r="X37" s="251"/>
+      <c r="Y37" s="251"/>
+      <c r="Z37" s="251"/>
+      <c r="AA37" s="251"/>
+      <c r="AB37" s="251"/>
+      <c r="AC37" s="252"/>
+    </row>
+    <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>2</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="274" t="s">
-        <v>72</v>
-      </c>
-      <c r="T38" s="276" t="s">
-        <v>167</v>
-      </c>
-      <c r="U38" s="277"/>
-      <c r="V38" s="277"/>
-      <c r="W38" s="277"/>
-      <c r="X38" s="277"/>
-      <c r="Y38" s="277"/>
-      <c r="Z38" s="277"/>
-      <c r="AA38" s="277"/>
-      <c r="AB38" s="277"/>
-      <c r="AC38" s="278"/>
-    </row>
-    <row r="39" spans="2:29" ht="15" customHeight="1">
+      <c r="S38" s="295" t="s">
+        <v>68</v>
+      </c>
+      <c r="T38" s="297" t="s">
+        <v>144</v>
+      </c>
+      <c r="U38" s="298"/>
+      <c r="V38" s="298"/>
+      <c r="W38" s="298"/>
+      <c r="X38" s="298"/>
+      <c r="Y38" s="298"/>
+      <c r="Z38" s="298"/>
+      <c r="AA38" s="298"/>
+      <c r="AB38" s="298"/>
+      <c r="AC38" s="299"/>
+    </row>
+    <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>3</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G39" s="204" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="205"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="206"/>
+        <v>97</v>
+      </c>
+      <c r="G39" s="303" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="246"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="275"/>
-      <c r="T39" s="279"/>
-      <c r="U39" s="280"/>
-      <c r="V39" s="280"/>
-      <c r="W39" s="280"/>
-      <c r="X39" s="280"/>
-      <c r="Y39" s="280"/>
-      <c r="Z39" s="280"/>
-      <c r="AA39" s="280"/>
-      <c r="AB39" s="280"/>
-      <c r="AC39" s="281"/>
-    </row>
-    <row r="40" spans="2:29" ht="37.5" customHeight="1">
+      <c r="S39" s="296"/>
+      <c r="T39" s="300"/>
+      <c r="U39" s="301"/>
+      <c r="V39" s="301"/>
+      <c r="W39" s="301"/>
+      <c r="X39" s="301"/>
+      <c r="Y39" s="301"/>
+      <c r="Z39" s="301"/>
+      <c r="AA39" s="301"/>
+      <c r="AB39" s="301"/>
+      <c r="AC39" s="302"/>
+    </row>
+    <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>4</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="D40" s="69" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G40" s="207"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="209"/>
+        <v>98</v>
+      </c>
+      <c r="G40" s="307"/>
+      <c r="H40" s="308"/>
+      <c r="I40" s="308"/>
+      <c r="J40" s="309"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="T40" s="231" t="s">
-        <v>168</v>
-      </c>
-      <c r="U40" s="232"/>
-      <c r="V40" s="232"/>
-      <c r="W40" s="232"/>
-      <c r="X40" s="232"/>
-      <c r="Y40" s="232"/>
-      <c r="Z40" s="232"/>
-      <c r="AA40" s="232"/>
-      <c r="AB40" s="232"/>
-      <c r="AC40" s="233"/>
-    </row>
-    <row r="41" spans="2:29" ht="30" customHeight="1">
+        <v>24</v>
+      </c>
+      <c r="T40" s="250" t="s">
+        <v>321</v>
+      </c>
+      <c r="U40" s="251"/>
+      <c r="V40" s="251"/>
+      <c r="W40" s="251"/>
+      <c r="X40" s="251"/>
+      <c r="Y40" s="251"/>
+      <c r="Z40" s="251"/>
+      <c r="AA40" s="251"/>
+      <c r="AB40" s="251"/>
+      <c r="AC40" s="252"/>
+    </row>
+    <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
         <v>5</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>104</v>
+        <v>322</v>
       </c>
       <c r="D41" s="69" t="s">
-        <v>135</v>
+        <v>323</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="G41" s="207"/>
-      <c r="H41" s="208"/>
-      <c r="I41" s="208"/>
-      <c r="J41" s="209"/>
+        <v>99</v>
+      </c>
+      <c r="G41" s="307"/>
+      <c r="H41" s="308"/>
+      <c r="I41" s="308"/>
+      <c r="J41" s="309"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="T41" s="231" t="s">
-        <v>169</v>
-      </c>
-      <c r="U41" s="232"/>
-      <c r="V41" s="232"/>
-      <c r="W41" s="232"/>
-      <c r="X41" s="232"/>
-      <c r="Y41" s="232"/>
-      <c r="Z41" s="232"/>
-      <c r="AA41" s="232"/>
-      <c r="AB41" s="232"/>
-      <c r="AC41" s="233"/>
-    </row>
-    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1">
+        <v>10</v>
+      </c>
+      <c r="T41" s="250" t="s">
+        <v>324</v>
+      </c>
+      <c r="U41" s="251"/>
+      <c r="V41" s="251"/>
+      <c r="W41" s="251"/>
+      <c r="X41" s="251"/>
+      <c r="Y41" s="251"/>
+      <c r="Z41" s="251"/>
+      <c r="AA41" s="251"/>
+      <c r="AB41" s="251"/>
+      <c r="AC41" s="252"/>
+    </row>
+    <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>6</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>105</v>
+        <v>325</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>174</v>
-      </c>
-      <c r="G42" s="210"/>
-      <c r="H42" s="211"/>
-      <c r="I42" s="211"/>
-      <c r="J42" s="212"/>
+        <v>148</v>
+      </c>
+      <c r="G42" s="304"/>
+      <c r="H42" s="305"/>
+      <c r="I42" s="305"/>
+      <c r="J42" s="306"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="T42" s="231" t="s">
-        <v>170</v>
-      </c>
-      <c r="U42" s="232"/>
-      <c r="V42" s="232"/>
-      <c r="W42" s="232"/>
-      <c r="X42" s="232"/>
-      <c r="Y42" s="232"/>
-      <c r="Z42" s="232"/>
-      <c r="AA42" s="232"/>
-      <c r="AB42" s="232"/>
-      <c r="AC42" s="233"/>
-    </row>
-    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1">
+        <v>136</v>
+      </c>
+      <c r="T42" s="250" t="s">
+        <v>145</v>
+      </c>
+      <c r="U42" s="251"/>
+      <c r="V42" s="251"/>
+      <c r="W42" s="251"/>
+      <c r="X42" s="251"/>
+      <c r="Y42" s="251"/>
+      <c r="Z42" s="251"/>
+      <c r="AA42" s="251"/>
+      <c r="AB42" s="251"/>
+      <c r="AC42" s="252"/>
+    </row>
+    <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>7</v>
       </c>
       <c r="C43" s="70" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D43" s="69" t="s">
-        <v>146</v>
+        <v>326</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="G43" s="179" t="s">
-        <v>189</v>
-      </c>
-      <c r="H43" s="197"/>
-      <c r="I43" s="197"/>
-      <c r="J43" s="180"/>
+        <v>327</v>
+      </c>
+      <c r="G43" s="268" t="s">
+        <v>328</v>
+      </c>
+      <c r="H43" s="269"/>
+      <c r="I43" s="269"/>
+      <c r="J43" s="270"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="T43" s="231" t="s">
-        <v>171</v>
-      </c>
-      <c r="U43" s="232"/>
-      <c r="V43" s="232"/>
-      <c r="W43" s="232"/>
-      <c r="X43" s="232"/>
-      <c r="Y43" s="232"/>
-      <c r="Z43" s="232"/>
-      <c r="AA43" s="232"/>
-      <c r="AB43" s="232"/>
-      <c r="AC43" s="233"/>
-    </row>
-    <row r="44" spans="2:29" ht="45.75" thickBot="1">
+        <v>137</v>
+      </c>
+      <c r="T43" s="250" t="s">
+        <v>146</v>
+      </c>
+      <c r="U43" s="251"/>
+      <c r="V43" s="251"/>
+      <c r="W43" s="251"/>
+      <c r="X43" s="251"/>
+      <c r="Y43" s="251"/>
+      <c r="Z43" s="251"/>
+      <c r="AA43" s="251"/>
+      <c r="AB43" s="251"/>
+      <c r="AC43" s="252"/>
+    </row>
+    <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>8</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D44" s="69" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="274" t="s">
-        <v>75</v>
-      </c>
-      <c r="T44" s="276" t="s">
-        <v>172</v>
-      </c>
-      <c r="U44" s="277"/>
-      <c r="V44" s="277"/>
-      <c r="W44" s="277"/>
-      <c r="X44" s="277"/>
-      <c r="Y44" s="277"/>
-      <c r="Z44" s="277"/>
-      <c r="AA44" s="277"/>
-      <c r="AB44" s="277"/>
-      <c r="AC44" s="278"/>
-    </row>
-    <row r="45" spans="2:29" ht="30.75" customHeight="1">
+      <c r="S44" s="295" t="s">
+        <v>71</v>
+      </c>
+      <c r="T44" s="297" t="s">
+        <v>330</v>
+      </c>
+      <c r="U44" s="298"/>
+      <c r="V44" s="298"/>
+      <c r="W44" s="298"/>
+      <c r="X44" s="298"/>
+      <c r="Y44" s="298"/>
+      <c r="Z44" s="298"/>
+      <c r="AA44" s="298"/>
+      <c r="AB44" s="298"/>
+      <c r="AC44" s="299"/>
+    </row>
+    <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
         <v>9</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D45" s="69" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G45" s="204" t="s">
-        <v>178</v>
-      </c>
-      <c r="H45" s="205"/>
-      <c r="I45" s="205"/>
-      <c r="J45" s="206"/>
+        <v>123</v>
+      </c>
+      <c r="G45" s="303" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="245"/>
+      <c r="I45" s="245"/>
+      <c r="J45" s="246"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="275"/>
-      <c r="T45" s="279"/>
-      <c r="U45" s="280"/>
-      <c r="V45" s="280"/>
-      <c r="W45" s="280"/>
-      <c r="X45" s="280"/>
-      <c r="Y45" s="280"/>
-      <c r="Z45" s="280"/>
-      <c r="AA45" s="280"/>
-      <c r="AB45" s="280"/>
-      <c r="AC45" s="281"/>
-    </row>
-    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1">
+      <c r="S45" s="296"/>
+      <c r="T45" s="300"/>
+      <c r="U45" s="301"/>
+      <c r="V45" s="301"/>
+      <c r="W45" s="301"/>
+      <c r="X45" s="301"/>
+      <c r="Y45" s="301"/>
+      <c r="Z45" s="301"/>
+      <c r="AA45" s="301"/>
+      <c r="AB45" s="301"/>
+      <c r="AC45" s="302"/>
+    </row>
+    <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>10</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D46" s="69" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E46" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="F46" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="G46" s="210"/>
-      <c r="H46" s="211"/>
-      <c r="I46" s="211"/>
-      <c r="J46" s="212"/>
+      <c r="G46" s="304"/>
+      <c r="H46" s="305"/>
+      <c r="I46" s="305"/>
+      <c r="J46" s="306"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="T46" s="251" t="s">
-        <v>173</v>
-      </c>
-      <c r="U46" s="252"/>
-      <c r="V46" s="252"/>
-      <c r="W46" s="252"/>
-      <c r="X46" s="252"/>
-      <c r="Y46" s="252"/>
-      <c r="Z46" s="252"/>
-      <c r="AA46" s="252"/>
-      <c r="AB46" s="252"/>
-      <c r="AC46" s="253"/>
-    </row>
-    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1">
+        <v>127</v>
+      </c>
+      <c r="T46" s="247" t="s">
+        <v>147</v>
+      </c>
+      <c r="U46" s="248"/>
+      <c r="V46" s="248"/>
+      <c r="W46" s="248"/>
+      <c r="X46" s="248"/>
+      <c r="Y46" s="248"/>
+      <c r="Z46" s="248"/>
+      <c r="AA46" s="248"/>
+      <c r="AB46" s="248"/>
+      <c r="AC46" s="249"/>
+    </row>
+    <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>11</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D47" s="69" t="s">
-        <v>149</v>
+        <v>331</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" s="197" t="s">
-        <v>150</v>
-      </c>
-      <c r="H47" s="197"/>
-      <c r="I47" s="197"/>
-      <c r="J47" s="180"/>
-    </row>
-    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1">
+        <v>129</v>
+      </c>
+      <c r="G47" s="269" t="s">
+        <v>332</v>
+      </c>
+      <c r="H47" s="269"/>
+      <c r="I47" s="269"/>
+      <c r="J47" s="270"/>
+    </row>
+    <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>12</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D48" s="69" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA48" s="106" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" ht="35.25" customHeight="1">
+        <v>162</v>
+      </c>
+      <c r="R48" s="84" t="s">
+        <v>298</v>
+      </c>
+      <c r="S48" s="73">
+        <v>7</v>
+      </c>
+      <c r="T48" s="74">
+        <v>6</v>
+      </c>
+      <c r="U48" s="74">
+        <v>5</v>
+      </c>
+      <c r="V48" s="74">
+        <v>4</v>
+      </c>
+      <c r="W48" s="74">
+        <v>3</v>
+      </c>
+      <c r="X48" s="74">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="74">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="368" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB48" s="369"/>
+      <c r="AC48" s="370"/>
+    </row>
+    <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>13</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>152</v>
+        <v>335</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="G49" s="204" t="s">
-        <v>153</v>
-      </c>
-      <c r="H49" s="205"/>
-      <c r="I49" s="205"/>
-      <c r="J49" s="206"/>
-    </row>
-    <row r="50" spans="2:14" ht="30" customHeight="1">
+        <v>130</v>
+      </c>
+      <c r="G49" s="303" t="s">
+        <v>336</v>
+      </c>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="246"/>
+      <c r="R49" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="S49" s="78"/>
+      <c r="T49" s="79"/>
+      <c r="U49" s="79"/>
+      <c r="V49" s="79"/>
+      <c r="W49" s="159"/>
+      <c r="X49" s="79"/>
+      <c r="Y49" s="79" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z49" s="80" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA49" s="371"/>
+      <c r="AB49" s="372"/>
+      <c r="AC49" s="373"/>
+    </row>
+    <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>14</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>152</v>
+        <v>335</v>
       </c>
       <c r="E50" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="F50" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="G50" s="207"/>
-      <c r="H50" s="208"/>
-      <c r="I50" s="208"/>
-      <c r="J50" s="209"/>
-    </row>
-    <row r="51" spans="2:14" ht="32.25" customHeight="1" thickBot="1">
+      <c r="G50" s="307"/>
+      <c r="H50" s="308"/>
+      <c r="I50" s="308"/>
+      <c r="J50" s="309"/>
+    </row>
+    <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>15</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>152</v>
+        <v>335</v>
       </c>
       <c r="E51" s="63" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G51" s="210"/>
-      <c r="H51" s="211"/>
-      <c r="I51" s="211"/>
-      <c r="J51" s="212"/>
-    </row>
-    <row r="52" spans="2:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B52" s="224" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" s="225"/>
-      <c r="D52" s="225"/>
-      <c r="E52" s="225"/>
-      <c r="F52" s="226"/>
-    </row>
-    <row r="53" spans="2:14" ht="31.5" customHeight="1" thickBot="1"/>
-    <row r="54" spans="2:14" ht="36.75" customHeight="1">
-      <c r="B54" s="218" t="s">
-        <v>180</v>
-      </c>
-      <c r="C54" s="215" t="s">
-        <v>182</v>
-      </c>
-      <c r="D54" s="198" t="s">
-        <v>181</v>
-      </c>
-      <c r="E54" s="199"/>
-      <c r="H54" s="213" t="s">
-        <v>344</v>
-      </c>
-      <c r="I54" s="215" t="s">
-        <v>182</v>
-      </c>
-      <c r="J54" s="181" t="s">
-        <v>181</v>
-      </c>
-      <c r="K54" s="182"/>
-      <c r="L54" s="183"/>
-    </row>
-    <row r="55" spans="2:14" ht="24" customHeight="1" thickBot="1">
-      <c r="B55" s="219"/>
-      <c r="C55" s="217"/>
-      <c r="D55" s="200"/>
-      <c r="E55" s="201"/>
-      <c r="H55" s="214"/>
-      <c r="I55" s="216"/>
-      <c r="J55" s="184"/>
-      <c r="K55" s="185"/>
-      <c r="L55" s="186"/>
-    </row>
-    <row r="56" spans="2:14" ht="49.5" customHeight="1" thickBot="1">
+        <v>130</v>
+      </c>
+      <c r="G51" s="304"/>
+      <c r="H51" s="305"/>
+      <c r="I51" s="305"/>
+      <c r="J51" s="306"/>
+      <c r="R51" s="365" t="s">
+        <v>299</v>
+      </c>
+      <c r="S51" s="349" t="s">
+        <v>156</v>
+      </c>
+      <c r="T51" s="361" t="s">
+        <v>155</v>
+      </c>
+      <c r="U51" s="361"/>
+      <c r="V51" s="362"/>
+    </row>
+    <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="242" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" s="243"/>
+      <c r="D52" s="243"/>
+      <c r="E52" s="243"/>
+      <c r="F52" s="244"/>
+      <c r="R52" s="385"/>
+      <c r="S52" s="350"/>
+      <c r="T52" s="363"/>
+      <c r="U52" s="363"/>
+      <c r="V52" s="364"/>
+    </row>
+    <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R53" s="164" t="s">
+        <v>195</v>
+      </c>
+      <c r="S53" s="165" t="s">
+        <v>300</v>
+      </c>
+      <c r="T53" s="380" t="s">
+        <v>338</v>
+      </c>
+      <c r="U53" s="380"/>
+      <c r="V53" s="381"/>
+    </row>
+    <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="351" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="349" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" s="361" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="362"/>
+      <c r="H54" s="365" t="s">
+        <v>290</v>
+      </c>
+      <c r="I54" s="349" t="s">
+        <v>156</v>
+      </c>
+      <c r="J54" s="374" t="s">
+        <v>155</v>
+      </c>
+      <c r="K54" s="375"/>
+      <c r="L54" s="376"/>
+      <c r="R54" s="162" t="s">
+        <v>204</v>
+      </c>
+      <c r="S54" s="160" t="s">
+        <v>301</v>
+      </c>
+      <c r="T54" s="386" t="s">
+        <v>307</v>
+      </c>
+      <c r="U54" s="386"/>
+      <c r="V54" s="354"/>
+    </row>
+    <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="352"/>
+      <c r="C55" s="350"/>
+      <c r="D55" s="363"/>
+      <c r="E55" s="364"/>
+      <c r="H55" s="366"/>
+      <c r="I55" s="367"/>
+      <c r="J55" s="340"/>
+      <c r="K55" s="377"/>
+      <c r="L55" s="378"/>
+      <c r="R55" s="162" t="s">
+        <v>190</v>
+      </c>
+      <c r="S55" s="160" t="s">
+        <v>302</v>
+      </c>
+      <c r="T55" s="386" t="s">
+        <v>339</v>
+      </c>
+      <c r="U55" s="386"/>
+      <c r="V55" s="354"/>
+    </row>
+    <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <v>0</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="202" t="s">
-        <v>200</v>
-      </c>
-      <c r="E56" s="203"/>
+        <v>9</v>
+      </c>
+      <c r="D56" s="253" t="s">
+        <v>170</v>
+      </c>
+      <c r="E56" s="255"/>
       <c r="H56" s="81" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
-        <v>342</v>
-      </c>
-      <c r="J56" s="187" t="s">
-        <v>345</v>
-      </c>
-      <c r="K56" s="188"/>
-      <c r="L56" s="189"/>
-      <c r="M56" s="179" t="s">
-        <v>348</v>
-      </c>
-      <c r="N56" s="180"/>
-    </row>
-    <row r="57" spans="2:14" ht="49.5" customHeight="1" thickBot="1">
+        <v>288</v>
+      </c>
+      <c r="J56" s="379" t="s">
+        <v>291</v>
+      </c>
+      <c r="K56" s="380"/>
+      <c r="L56" s="381"/>
+      <c r="M56" s="268" t="s">
+        <v>340</v>
+      </c>
+      <c r="N56" s="270"/>
+      <c r="R56" s="162" t="s">
+        <v>215</v>
+      </c>
+      <c r="S56" s="160" t="s">
+        <v>303</v>
+      </c>
+      <c r="T56" s="386" t="s">
+        <v>341</v>
+      </c>
+      <c r="U56" s="386"/>
+      <c r="V56" s="354"/>
+    </row>
+    <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
         <v>1</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>339</v>
-      </c>
-      <c r="D57" s="193" t="s">
-        <v>340</v>
-      </c>
-      <c r="E57" s="194"/>
-      <c r="F57" s="179" t="s">
-        <v>341</v>
-      </c>
-      <c r="G57" s="180"/>
+        <v>286</v>
+      </c>
+      <c r="D57" s="353" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57" s="354"/>
+      <c r="F57" s="268" t="s">
+        <v>342</v>
+      </c>
+      <c r="G57" s="270"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
-        <v>346</v>
-      </c>
-      <c r="J57" s="190" t="s">
-        <v>351</v>
-      </c>
-      <c r="K57" s="191"/>
-      <c r="L57" s="192"/>
-    </row>
-    <row r="58" spans="2:14" ht="30.75" customHeight="1">
+        <v>292</v>
+      </c>
+      <c r="J57" s="382" t="s">
+        <v>343</v>
+      </c>
+      <c r="K57" s="383"/>
+      <c r="L57" s="384"/>
+      <c r="R57" s="162" t="s">
+        <v>228</v>
+      </c>
+      <c r="S57" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="T57" s="386" t="s">
+        <v>344</v>
+      </c>
+      <c r="U57" s="386"/>
+      <c r="V57" s="354"/>
+    </row>
+    <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
         <v>2</v>
       </c>
       <c r="C58" s="85" t="s">
-        <v>193</v>
-      </c>
-      <c r="D58" s="193" t="s">
-        <v>194</v>
-      </c>
-      <c r="E58" s="194"/>
+        <v>164</v>
+      </c>
+      <c r="D58" s="353" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="354"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
-        <v>349</v>
-      </c>
-      <c r="J58" s="190" t="s">
-        <v>352</v>
-      </c>
-      <c r="K58" s="191"/>
-      <c r="L58" s="192"/>
-    </row>
-    <row r="59" spans="2:14" ht="33.75" customHeight="1">
+        <v>346</v>
+      </c>
+      <c r="J58" s="382" t="s">
+        <v>347</v>
+      </c>
+      <c r="K58" s="383"/>
+      <c r="L58" s="384"/>
+      <c r="R58" s="162" t="s">
+        <v>229</v>
+      </c>
+      <c r="S58" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="T58" s="386" t="s">
+        <v>348</v>
+      </c>
+      <c r="U58" s="386"/>
+      <c r="V58" s="354"/>
+    </row>
+    <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
         <v>3</v>
       </c>
       <c r="C59" s="85" t="s">
-        <v>183</v>
-      </c>
-      <c r="D59" s="193" t="s">
-        <v>186</v>
-      </c>
-      <c r="E59" s="194"/>
+        <v>349</v>
+      </c>
+      <c r="D59" s="353" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" s="354"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
-        <v>343</v>
-      </c>
-      <c r="J59" s="190" t="s">
-        <v>353</v>
-      </c>
-      <c r="K59" s="191"/>
-      <c r="L59" s="192"/>
-    </row>
-    <row r="60" spans="2:14" ht="28.5" customHeight="1">
+        <v>289</v>
+      </c>
+      <c r="J59" s="382" t="s">
+        <v>350</v>
+      </c>
+      <c r="K59" s="383"/>
+      <c r="L59" s="384"/>
+      <c r="R59" s="162" t="s">
+        <v>230</v>
+      </c>
+      <c r="S59" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="T59" s="386" t="s">
+        <v>351</v>
+      </c>
+      <c r="U59" s="386"/>
+      <c r="V59" s="354"/>
+      <c r="X59" s="166"/>
+    </row>
+    <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="82">
         <v>4</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="D60" s="193" t="s">
-        <v>187</v>
-      </c>
-      <c r="E60" s="194"/>
+        <v>157</v>
+      </c>
+      <c r="D60" s="353" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" s="354"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>350</v>
-      </c>
-      <c r="J60" s="190" t="s">
-        <v>354</v>
-      </c>
-      <c r="K60" s="191"/>
-      <c r="L60" s="192"/>
-    </row>
-    <row r="61" spans="2:14" ht="40.5" customHeight="1">
+        <v>294</v>
+      </c>
+      <c r="J60" s="382" t="s">
+        <v>309</v>
+      </c>
+      <c r="K60" s="383"/>
+      <c r="L60" s="384"/>
+      <c r="R60" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="S60" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T60" s="386" t="s">
+        <v>461</v>
+      </c>
+      <c r="U60" s="386"/>
+      <c r="V60" s="354"/>
+    </row>
+    <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
         <v>5</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" s="193" t="s">
-        <v>188</v>
-      </c>
-      <c r="E61" s="194"/>
+        <v>158</v>
+      </c>
+      <c r="D61" s="353" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="354"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="190"/>
-      <c r="K61" s="191"/>
-      <c r="L61" s="192"/>
-    </row>
-    <row r="62" spans="2:14" ht="53.25" customHeight="1">
+      <c r="J61" s="382"/>
+      <c r="K61" s="383"/>
+      <c r="L61" s="384"/>
+      <c r="R61" s="162" t="s">
+        <v>232</v>
+      </c>
+      <c r="S61" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T61" s="386"/>
+      <c r="U61" s="386"/>
+      <c r="V61" s="354"/>
+    </row>
+    <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="193"/>
-      <c r="E62" s="194"/>
+      <c r="D62" s="353"/>
+      <c r="E62" s="354"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="190"/>
-      <c r="K62" s="191"/>
-      <c r="L62" s="192"/>
-    </row>
-    <row r="63" spans="2:14" ht="36" customHeight="1">
+      <c r="J62" s="382"/>
+      <c r="K62" s="383"/>
+      <c r="L62" s="384"/>
+      <c r="R62" s="162" t="s">
+        <v>264</v>
+      </c>
+      <c r="S62" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T62" s="386"/>
+      <c r="U62" s="386"/>
+      <c r="V62" s="354"/>
+    </row>
+    <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="193"/>
-      <c r="E63" s="194"/>
+      <c r="D63" s="353"/>
+      <c r="E63" s="354"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="190"/>
-      <c r="K63" s="191"/>
-      <c r="L63" s="192"/>
-    </row>
-    <row r="64" spans="2:14" ht="40.5" customHeight="1">
+      <c r="J63" s="382"/>
+      <c r="K63" s="383"/>
+      <c r="L63" s="384"/>
+      <c r="R63" s="162" t="s">
+        <v>352</v>
+      </c>
+      <c r="S63" s="160" t="s">
+        <v>306</v>
+      </c>
+      <c r="T63" s="386"/>
+      <c r="U63" s="386"/>
+      <c r="V63" s="354"/>
+    </row>
+    <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="193"/>
-      <c r="E64" s="194"/>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="D64" s="353"/>
+      <c r="E64" s="354"/>
+      <c r="R64" s="163" t="s">
+        <v>458</v>
+      </c>
+      <c r="S64" s="161" t="s">
+        <v>459</v>
+      </c>
+      <c r="T64" s="424" t="s">
+        <v>460</v>
+      </c>
+      <c r="U64" s="424"/>
+      <c r="V64" s="360"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="193"/>
-      <c r="E65" s="194"/>
-    </row>
-    <row r="66" spans="2:5" ht="30" customHeight="1">
+      <c r="D65" s="353"/>
+      <c r="E65" s="354"/>
+      <c r="T65" s="166"/>
+    </row>
+    <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="82">
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="193"/>
-      <c r="E66" s="194"/>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="D66" s="353"/>
+      <c r="E66" s="354"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="193"/>
-      <c r="E67" s="194"/>
-    </row>
-    <row r="68" spans="2:5">
+      <c r="D67" s="353"/>
+      <c r="E67" s="354"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="193"/>
-      <c r="E68" s="194"/>
-    </row>
-    <row r="69" spans="2:5">
+      <c r="D68" s="353"/>
+      <c r="E68" s="354"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="193"/>
-      <c r="E69" s="194"/>
-    </row>
-    <row r="70" spans="2:5" ht="30" customHeight="1">
+      <c r="D69" s="353"/>
+      <c r="E69" s="354"/>
+    </row>
+    <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="193"/>
-      <c r="E70" s="194"/>
-    </row>
-    <row r="71" spans="2:5" ht="15.75" thickBot="1">
+      <c r="D70" s="353"/>
+      <c r="E70" s="354"/>
+    </row>
+    <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="195"/>
-      <c r="E71" s="196"/>
-    </row>
-    <row r="75" spans="2:5" ht="72" customHeight="1"/>
+      <c r="D71" s="359"/>
+      <c r="E71" s="360"/>
+    </row>
+    <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="171">
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
+  <mergeCells count="188">
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
     <mergeCell ref="AA20:AB20"/>
     <mergeCell ref="AA21:AB21"/>
     <mergeCell ref="AA22:AB22"/>
@@ -7091,139 +8764,36 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="AA5:AB20 U5:V20 U22:V22 V21 U24:V28 V23 AA25:AB28 AB21 AB22 AB23 AB24" numberStoredAsText="1"/>
+    <ignoredError sqref="AA5:AB20 U5:V20 V22 V21 U24:V28 V23 AA25:AB28 AB21 AB22 AB23 AB24" numberStoredAsText="1"/>
     <ignoredError sqref="D30" formula="1"/>
   </ignoredErrors>
 </worksheet>
@@ -7231,14 +8801,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CBBBEA-E421-4197-9F44-CA2E8EC0215F}">
-  <dimension ref="B1:AB30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="B1:AB33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="10" width="10.140625" customWidth="1"/>
     <col min="12" max="12" width="10.140625" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
@@ -7248,1004 +8818,1096 @@
     <col min="17" max="19" width="18.42578125" customWidth="1"/>
     <col min="20" max="20" width="28.5703125" customWidth="1"/>
     <col min="21" max="21" width="8" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" customWidth="1"/>
     <col min="24" max="24" width="27.42578125" customWidth="1"/>
     <col min="25" max="25" width="48.140625" customWidth="1"/>
     <col min="26" max="28" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:28" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B2" s="88" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="103" t="s">
-        <v>202</v>
-      </c>
-      <c r="D2" s="103" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="119" t="s">
+    <row r="1" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:28" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="185" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="180" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" s="178" t="s">
+        <v>357</v>
+      </c>
+      <c r="E2" s="178" t="s">
+        <v>416</v>
+      </c>
+      <c r="F2" s="179" t="s">
+        <v>358</v>
+      </c>
+      <c r="G2" s="245" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="246"/>
+      <c r="L2" s="259" t="s">
+        <v>274</v>
+      </c>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="262" t="s">
+        <v>237</v>
+      </c>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="256" t="s">
+        <v>260</v>
+      </c>
+      <c r="W2" s="257"/>
+      <c r="X2" s="257"/>
+      <c r="Y2" s="257"/>
+      <c r="Z2" s="257"/>
+      <c r="AA2" s="257"/>
+      <c r="AB2" s="258"/>
+    </row>
+    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="186" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="181" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="190" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="176" t="s">
+        <v>362</v>
+      </c>
+      <c r="F3" s="177" t="s">
+        <v>363</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="253" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" s="254"/>
+      <c r="J3" s="255"/>
+      <c r="L3" s="126" t="s">
+        <v>223</v>
+      </c>
+      <c r="M3" s="127" t="s">
+        <v>224</v>
+      </c>
+      <c r="N3" s="128" t="s">
+        <v>225</v>
+      </c>
+      <c r="O3" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="150" t="s">
+        <v>223</v>
+      </c>
+      <c r="R3" s="151" t="s">
+        <v>224</v>
+      </c>
+      <c r="S3" s="151" t="s">
+        <v>225</v>
+      </c>
+      <c r="T3" s="152" t="s">
+        <v>226</v>
+      </c>
+      <c r="U3" s="114"/>
+      <c r="V3" s="150" t="s">
+        <v>223</v>
+      </c>
+      <c r="W3" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="X3" s="151" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y3" s="152" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z3" s="277" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA3" s="278"/>
+      <c r="AB3" s="279"/>
+    </row>
+    <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="187" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="182" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>366</v>
+      </c>
+      <c r="E4" s="171" t="s">
+        <v>367</v>
+      </c>
+      <c r="F4" s="172" t="s">
+        <v>368</v>
+      </c>
+      <c r="G4" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="250">
+        <v>63</v>
+      </c>
+      <c r="I4" s="251"/>
+      <c r="J4" s="252"/>
+      <c r="L4" s="132" t="s">
+        <v>195</v>
+      </c>
+      <c r="M4" s="157" t="s">
+        <v>227</v>
+      </c>
+      <c r="N4" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="O4" s="116" t="s">
+        <v>269</v>
+      </c>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="R4" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="S4" s="118" t="s">
+        <v>235</v>
+      </c>
+      <c r="T4" s="119" t="s">
+        <v>238</v>
+      </c>
+      <c r="U4" s="114"/>
+      <c r="V4" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="W4" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="X4" s="118" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y4" s="119" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z4" s="280" t="s">
+        <v>421</v>
+      </c>
+      <c r="AA4" s="281"/>
+      <c r="AB4" s="282"/>
+    </row>
+    <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="188" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="182" t="s">
+        <v>360</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>370</v>
+      </c>
+      <c r="E5" s="171" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="172" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" s="250">
+        <v>31</v>
+      </c>
+      <c r="I5" s="251"/>
+      <c r="J5" s="252"/>
+      <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
-      <c r="F2" s="102" t="s">
-        <v>205</v>
-      </c>
-      <c r="G2" s="204" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206"/>
-      <c r="L2" s="298" t="s">
-        <v>325</v>
-      </c>
-      <c r="M2" s="299"/>
-      <c r="N2" s="299"/>
-      <c r="O2" s="300"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="301" t="s">
-        <v>285</v>
-      </c>
-      <c r="R2" s="302"/>
-      <c r="S2" s="302"/>
-      <c r="T2" s="303"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="291" t="s">
-        <v>308</v>
-      </c>
-      <c r="W2" s="292"/>
-      <c r="X2" s="292"/>
-      <c r="Y2" s="292"/>
-      <c r="Z2" s="292"/>
-      <c r="AA2" s="292"/>
-      <c r="AB2" s="293"/>
-    </row>
-    <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B3" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="95">
-        <v>0</v>
-      </c>
-      <c r="D3" s="96">
-        <v>0</v>
-      </c>
-      <c r="E3" s="96">
-        <v>0</v>
-      </c>
-      <c r="F3" s="97" t="str">
-        <f t="shared" ref="F3:F12" si="0">DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(C3,20)+_xlfn.BITLSHIFT(D3,15)+_xlfn.BITLSHIFT(E3,12))</f>
-        <v>E0000000</v>
-      </c>
-      <c r="G3" s="92" t="s">
-        <v>207</v>
-      </c>
-      <c r="H3" s="202" t="s">
-        <v>211</v>
-      </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="203"/>
-      <c r="L3" s="144" t="s">
+      <c r="M5" s="91" t="s">
+        <v>227</v>
+      </c>
+      <c r="N5" s="154" t="s">
+        <v>268</v>
+      </c>
+      <c r="O5" s="116" t="s">
+        <v>266</v>
+      </c>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="145" t="s">
+        <v>229</v>
+      </c>
+      <c r="R5" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="S5" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="T5" s="116" t="s">
+        <v>238</v>
+      </c>
+      <c r="U5" s="114"/>
+      <c r="V5" s="145" t="s">
+        <v>229</v>
+      </c>
+      <c r="W5" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="X5" s="115" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y5" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z5" s="280"/>
+      <c r="AA5" s="281"/>
+      <c r="AB5" s="282"/>
+    </row>
+    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="187" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="182" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="191" t="s">
+        <v>374</v>
+      </c>
+      <c r="E6" s="171" t="s">
+        <v>375</v>
+      </c>
+      <c r="F6" s="172" t="s">
+        <v>376</v>
+      </c>
+      <c r="G6" s="90" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="247">
+        <v>7</v>
+      </c>
+      <c r="I6" s="248"/>
+      <c r="J6" s="249"/>
+      <c r="L6" s="133" t="s">
+        <v>190</v>
+      </c>
+      <c r="M6" s="123" t="s">
+        <v>418</v>
+      </c>
+      <c r="N6" s="92" t="s">
+        <v>420</v>
+      </c>
+      <c r="O6" s="116" t="s">
+        <v>236</v>
+      </c>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="145" t="s">
+        <v>230</v>
+      </c>
+      <c r="R6" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="S6" s="115" t="s">
         <v>271</v>
       </c>
-      <c r="M3" s="145" t="s">
-        <v>272</v>
-      </c>
-      <c r="N3" s="146" t="s">
-        <v>273</v>
-      </c>
-      <c r="O3" s="147" t="s">
-        <v>274</v>
-      </c>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="168" t="s">
-        <v>271</v>
-      </c>
-      <c r="R3" s="169" t="s">
-        <v>272</v>
-      </c>
-      <c r="S3" s="169" t="s">
-        <v>273</v>
-      </c>
-      <c r="T3" s="170" t="s">
-        <v>274</v>
-      </c>
-      <c r="U3" s="132"/>
-      <c r="V3" s="168" t="s">
-        <v>271</v>
-      </c>
-      <c r="W3" s="171" t="s">
-        <v>272</v>
-      </c>
-      <c r="X3" s="169" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y3" s="170" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z3" s="282" t="s">
-        <v>313</v>
-      </c>
-      <c r="AA3" s="283"/>
-      <c r="AB3" s="284"/>
-    </row>
-    <row r="4" spans="2:28" ht="53.25" customHeight="1">
-      <c r="B4" s="90" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="98">
-        <v>0</v>
-      </c>
-      <c r="D4" s="99">
-        <v>1</v>
-      </c>
-      <c r="E4" s="99">
-        <v>0</v>
-      </c>
-      <c r="F4" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0008000</v>
-      </c>
-      <c r="G4" s="93" t="s">
-        <v>208</v>
-      </c>
-      <c r="H4" s="231">
-        <v>63</v>
-      </c>
-      <c r="I4" s="232"/>
-      <c r="J4" s="233"/>
-      <c r="L4" s="150" t="s">
-        <v>240</v>
-      </c>
-      <c r="M4" s="176" t="s">
-        <v>275</v>
-      </c>
-      <c r="N4" s="99" t="s">
-        <v>317</v>
-      </c>
-      <c r="O4" s="134" t="s">
-        <v>320</v>
-      </c>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="162" t="s">
-        <v>276</v>
-      </c>
-      <c r="R4" s="138" t="s">
-        <v>275</v>
-      </c>
-      <c r="S4" s="136" t="s">
-        <v>283</v>
-      </c>
-      <c r="T4" s="137" t="s">
-        <v>286</v>
-      </c>
-      <c r="U4" s="132"/>
-      <c r="V4" s="162" t="s">
-        <v>276</v>
-      </c>
-      <c r="W4" s="138" t="s">
-        <v>275</v>
-      </c>
-      <c r="X4" s="136" t="s">
-        <v>328</v>
-      </c>
-      <c r="Y4" s="137" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z4" s="285" t="s">
-        <v>314</v>
-      </c>
-      <c r="AA4" s="286"/>
-      <c r="AB4" s="287"/>
-    </row>
-    <row r="5" spans="2:28" ht="47.25" customHeight="1">
-      <c r="B5" s="90" t="s">
+      <c r="T6" s="116" t="s">
+        <v>238</v>
+      </c>
+      <c r="U6" s="114"/>
+      <c r="V6" s="146" t="s">
+        <v>230</v>
+      </c>
+      <c r="W6" s="122" t="s">
+        <v>227</v>
+      </c>
+      <c r="X6" s="117" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y6" s="125" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z6" s="283"/>
+      <c r="AA6" s="284"/>
+      <c r="AB6" s="285"/>
+    </row>
+    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="188" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="182" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="191" t="s">
+        <v>378</v>
+      </c>
+      <c r="E7" s="171" t="s">
+        <v>379</v>
+      </c>
+      <c r="F7" s="172" t="s">
+        <v>380</v>
+      </c>
+      <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="C5" s="98">
-        <v>0</v>
-      </c>
-      <c r="D5" s="99">
-        <v>2</v>
-      </c>
-      <c r="E5" s="99">
-        <v>0</v>
-      </c>
-      <c r="F5" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0010000</v>
-      </c>
-      <c r="G5" s="93" t="s">
-        <v>209</v>
-      </c>
-      <c r="H5" s="231">
-        <v>31</v>
-      </c>
-      <c r="I5" s="232"/>
-      <c r="J5" s="233"/>
-      <c r="L5" s="148" t="s">
-        <v>249</v>
-      </c>
-      <c r="M5" s="98" t="s">
-        <v>275</v>
-      </c>
-      <c r="N5" s="173" t="s">
-        <v>318</v>
-      </c>
-      <c r="O5" s="134" t="s">
-        <v>316</v>
-      </c>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="163" t="s">
-        <v>277</v>
-      </c>
-      <c r="R5" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="S5" s="133" t="s">
-        <v>321</v>
-      </c>
-      <c r="T5" s="134" t="s">
-        <v>286</v>
-      </c>
-      <c r="U5" s="132"/>
-      <c r="V5" s="163" t="s">
-        <v>277</v>
-      </c>
-      <c r="W5" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="X5" s="133" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y5" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="Z5" s="285"/>
-      <c r="AA5" s="286"/>
-      <c r="AB5" s="287"/>
-    </row>
-    <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B6" s="107" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="108">
-        <v>0</v>
-      </c>
-      <c r="D6" s="109">
-        <v>3</v>
-      </c>
-      <c r="E6" s="109">
-        <v>0</v>
-      </c>
-      <c r="F6" s="110" t="str">
-        <f t="shared" si="0"/>
-        <v>E0018000</v>
-      </c>
-      <c r="G6" s="94" t="s">
-        <v>210</v>
-      </c>
-      <c r="H6" s="251">
-        <v>7</v>
-      </c>
-      <c r="I6" s="252"/>
-      <c r="J6" s="253"/>
-      <c r="L6" s="151" t="s">
-        <v>235</v>
-      </c>
-      <c r="M6" s="141" t="s">
-        <v>275</v>
-      </c>
-      <c r="N6" s="99" t="s">
-        <v>319</v>
-      </c>
-      <c r="O6" s="134" t="s">
-        <v>284</v>
-      </c>
-      <c r="P6" s="132"/>
-      <c r="Q6" s="163" t="s">
-        <v>278</v>
-      </c>
-      <c r="R6" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="S6" s="133" t="s">
-        <v>322</v>
-      </c>
-      <c r="T6" s="134" t="s">
-        <v>286</v>
-      </c>
-      <c r="U6" s="132"/>
-      <c r="V6" s="164" t="s">
-        <v>278</v>
-      </c>
-      <c r="W6" s="140" t="s">
-        <v>275</v>
-      </c>
-      <c r="X6" s="135" t="s">
-        <v>309</v>
-      </c>
-      <c r="Y6" s="143" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z6" s="288"/>
-      <c r="AA6" s="289"/>
-      <c r="AB6" s="290"/>
-    </row>
-    <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1">
-      <c r="B7" s="89" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="95">
-        <v>1</v>
-      </c>
-      <c r="D7" s="96">
-        <v>0</v>
-      </c>
-      <c r="E7" s="96">
-        <v>0</v>
-      </c>
-      <c r="F7" s="97" t="str">
-        <f t="shared" si="0"/>
-        <v>E0100000</v>
-      </c>
-      <c r="G7" s="87" t="s">
-        <v>268</v>
-      </c>
-      <c r="H7" s="304" t="str">
+      <c r="H7" s="235" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="305"/>
-      <c r="J7" s="306"/>
-      <c r="L7" s="149" t="s">
-        <v>260</v>
-      </c>
-      <c r="M7" s="142" t="s">
+      <c r="I7" s="236"/>
+      <c r="J7" s="237"/>
+      <c r="L7" s="131" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" s="124" t="s">
+        <v>419</v>
+      </c>
+      <c r="N7" s="93" t="s">
         <v>275</v>
       </c>
-      <c r="N7" s="101" t="s">
-        <v>326</v>
-      </c>
-      <c r="O7" s="143" t="s">
-        <v>324</v>
-      </c>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="163" t="s">
-        <v>279</v>
-      </c>
-      <c r="R7" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="S7" s="133" t="s">
-        <v>323</v>
-      </c>
-      <c r="T7" s="134" t="s">
-        <v>286</v>
-      </c>
-      <c r="U7" s="132"/>
-    </row>
-    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="98">
-        <v>1</v>
-      </c>
-      <c r="D8" s="99">
-        <v>1</v>
-      </c>
-      <c r="E8" s="99">
-        <v>0</v>
-      </c>
-      <c r="F8" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0108000</v>
+      <c r="O7" s="125" t="s">
+        <v>273</v>
+      </c>
+      <c r="P7" s="114"/>
+      <c r="Q7" s="145" t="s">
+        <v>231</v>
+      </c>
+      <c r="R7" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="S7" s="115" t="s">
+        <v>272</v>
+      </c>
+      <c r="T7" s="116" t="s">
+        <v>238</v>
+      </c>
+      <c r="U7" s="114"/>
+    </row>
+    <row r="8" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="187" t="s">
+        <v>381</v>
+      </c>
+      <c r="C8" s="183" t="s">
+        <v>382</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>383</v>
+      </c>
+      <c r="E8" s="170" t="s">
+        <v>383</v>
+      </c>
+      <c r="F8" s="173" t="s">
+        <v>384</v>
       </c>
       <c r="G8" s="87" t="s">
-        <v>212</v>
-      </c>
-      <c r="H8" s="304" t="str">
+        <v>177</v>
+      </c>
+      <c r="H8" s="235" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="305"/>
-      <c r="J8" s="306"/>
-      <c r="L8" s="179" t="s">
-        <v>327</v>
-      </c>
-      <c r="M8" s="197"/>
-      <c r="N8" s="197"/>
-      <c r="O8" s="180"/>
-      <c r="P8" s="132"/>
-      <c r="Q8" s="163" t="s">
-        <v>280</v>
-      </c>
-      <c r="R8" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="S8" s="133" t="s">
-        <v>281</v>
-      </c>
-      <c r="T8" s="134" t="s">
-        <v>287</v>
-      </c>
-      <c r="U8" s="132"/>
-      <c r="X8" s="172" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1">
-      <c r="B9" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="98">
-        <v>1</v>
-      </c>
-      <c r="D9" s="99">
-        <v>2</v>
-      </c>
-      <c r="E9" s="99">
-        <v>0</v>
-      </c>
-      <c r="F9" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0110000</v>
+      <c r="I8" s="236"/>
+      <c r="J8" s="237"/>
+      <c r="L8" s="268" t="s">
+        <v>417</v>
+      </c>
+      <c r="M8" s="269"/>
+      <c r="N8" s="269"/>
+      <c r="O8" s="270"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="145" t="s">
+        <v>232</v>
+      </c>
+      <c r="R8" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="S8" s="115" t="s">
+        <v>233</v>
+      </c>
+      <c r="T8" s="116" t="s">
+        <v>239</v>
+      </c>
+      <c r="U8" s="114"/>
+      <c r="V8" s="231" t="s">
+        <v>453</v>
+      </c>
+      <c r="W8" s="271" t="s">
+        <v>454</v>
+      </c>
+      <c r="X8" s="272"/>
+      <c r="Y8" s="230"/>
+    </row>
+    <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="187" t="s">
+        <v>385</v>
+      </c>
+      <c r="C9" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D9" s="191" t="s">
+        <v>387</v>
+      </c>
+      <c r="E9" s="171" t="s">
+        <v>388</v>
+      </c>
+      <c r="F9" s="172" t="s">
+        <v>389</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="164" t="s">
-        <v>312</v>
-      </c>
-      <c r="R9" s="140" t="s">
-        <v>275</v>
-      </c>
-      <c r="S9" s="135" t="s">
-        <v>282</v>
-      </c>
-      <c r="T9" s="143" t="s">
-        <v>288</v>
-      </c>
-      <c r="U9" s="132"/>
-    </row>
-    <row r="10" spans="2:28" ht="28.5" customHeight="1" thickBot="1">
-      <c r="B10" s="90" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="98">
+      <c r="P9" s="114"/>
+      <c r="Q9" s="146" t="s">
+        <v>264</v>
+      </c>
+      <c r="R9" s="122" t="s">
+        <v>227</v>
+      </c>
+      <c r="S9" s="117" t="s">
+        <v>234</v>
+      </c>
+      <c r="T9" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="U9" s="114"/>
+      <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="D10" s="99">
-        <v>3</v>
-      </c>
-      <c r="E10" s="99">
-        <v>0</v>
-      </c>
-      <c r="F10" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0118000</v>
+      <c r="W9" s="273" t="s">
+        <v>456</v>
+      </c>
+      <c r="X9" s="274"/>
+    </row>
+    <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="187" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="191" t="s">
+        <v>391</v>
+      </c>
+      <c r="E10" s="171" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" s="172" t="s">
+        <v>393</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="132"/>
-      <c r="N10" s="132"/>
-      <c r="O10" s="132"/>
-      <c r="P10" s="132"/>
-      <c r="U10" s="132"/>
-    </row>
-    <row r="11" spans="2:28" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B11" s="90" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="98">
-        <v>1</v>
-      </c>
-      <c r="D11" s="99">
-        <v>4</v>
-      </c>
-      <c r="E11" s="99">
-        <v>0</v>
-      </c>
-      <c r="F11" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0120000</v>
+      <c r="L10" s="114"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="U10" s="114"/>
+      <c r="V10" s="2">
+        <v>2</v>
+      </c>
+      <c r="W10" s="275" t="s">
+        <v>455</v>
+      </c>
+      <c r="X10" s="276"/>
+    </row>
+    <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="187" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="191" t="s">
+        <v>395</v>
+      </c>
+      <c r="E11" s="171" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="172" t="s">
+        <v>397</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-      <c r="N11" s="132"/>
-      <c r="O11" s="132"/>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="307" t="s">
-        <v>307</v>
-      </c>
-      <c r="R11" s="308"/>
-      <c r="S11" s="308"/>
-      <c r="T11" s="309"/>
-      <c r="U11" s="132"/>
-    </row>
-    <row r="12" spans="2:28" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B12" s="90" t="s">
-        <v>219</v>
-      </c>
-      <c r="C12" s="98">
-        <v>1</v>
-      </c>
-      <c r="D12" s="99">
-        <v>5</v>
-      </c>
-      <c r="E12" s="99">
-        <v>0</v>
-      </c>
-      <c r="F12" s="104" t="str">
-        <f t="shared" si="0"/>
-        <v>E0128000</v>
-      </c>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="114"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="R11" s="266"/>
+      <c r="S11" s="266"/>
+      <c r="T11" s="267"/>
+      <c r="U11" s="114"/>
+      <c r="V11" s="1">
+        <v>3</v>
+      </c>
+      <c r="W11" s="275" t="s">
+        <v>425</v>
+      </c>
+      <c r="X11" s="276"/>
+    </row>
+    <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="187" t="s">
+        <v>398</v>
+      </c>
+      <c r="C12" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="191" t="s">
+        <v>399</v>
+      </c>
+      <c r="E12" s="171" t="s">
+        <v>400</v>
+      </c>
+      <c r="F12" s="172"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="144" t="s">
-        <v>289</v>
-      </c>
-      <c r="R12" s="174" t="s">
-        <v>272</v>
-      </c>
-      <c r="S12" s="174" t="s">
-        <v>273</v>
-      </c>
-      <c r="T12" s="175" t="s">
-        <v>274</v>
-      </c>
-      <c r="U12" s="132"/>
-    </row>
-    <row r="13" spans="2:28" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B13" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C13" s="100">
-        <v>1</v>
-      </c>
-      <c r="D13" s="101">
-        <v>7</v>
-      </c>
-      <c r="E13" s="101">
-        <v>0</v>
-      </c>
-      <c r="F13" s="105" t="str">
-        <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(C13,20)+_xlfn.BITLSHIFT(D13,15)+_xlfn.BITLSHIFT(E13,12))</f>
-        <v>E0138000</v>
-      </c>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="114"/>
+      <c r="O12" s="114"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="126" t="s">
+        <v>241</v>
+      </c>
+      <c r="R12" s="155" t="s">
+        <v>224</v>
+      </c>
+      <c r="S12" s="155" t="s">
+        <v>225</v>
+      </c>
+      <c r="T12" s="156" t="s">
+        <v>226</v>
+      </c>
+      <c r="U12" s="114"/>
+      <c r="V12" s="2">
+        <v>4</v>
+      </c>
+      <c r="W12" s="275"/>
+      <c r="X12" s="276"/>
+    </row>
+    <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="187" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D13" s="191" t="s">
+        <v>402</v>
+      </c>
+      <c r="E13" s="171" t="s">
+        <v>403</v>
+      </c>
+      <c r="F13" s="172"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="165" t="s">
-        <v>290</v>
-      </c>
-      <c r="R13" s="159" t="s">
-        <v>291</v>
-      </c>
-      <c r="S13" s="160" t="s">
-        <v>292</v>
-      </c>
-      <c r="T13" s="161" t="s">
-        <v>293</v>
-      </c>
-      <c r="U13" s="132"/>
-    </row>
-    <row r="14" spans="2:28" ht="54" customHeight="1">
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="147" t="s">
+        <v>242</v>
+      </c>
+      <c r="R13" s="141" t="s">
+        <v>243</v>
+      </c>
+      <c r="S13" s="142" t="s">
+        <v>244</v>
+      </c>
+      <c r="T13" s="143" t="s">
+        <v>245</v>
+      </c>
+      <c r="U13" s="114"/>
+      <c r="V13" s="1">
+        <v>5</v>
+      </c>
+      <c r="W13" s="275"/>
+      <c r="X13" s="276"/>
+    </row>
+    <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="187" t="s">
+        <v>404</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" s="191" t="s">
+        <v>405</v>
+      </c>
+      <c r="E14" s="171" t="s">
+        <v>406</v>
+      </c>
+      <c r="F14" s="172"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
-      <c r="L14" s="132"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="132"/>
-      <c r="P14" s="132"/>
-      <c r="Q14" s="166" t="s">
-        <v>294</v>
-      </c>
-      <c r="R14" s="157" t="s">
-        <v>291</v>
-      </c>
-      <c r="S14" s="152" t="s">
-        <v>295</v>
-      </c>
-      <c r="T14" s="153" t="s">
-        <v>296</v>
-      </c>
-      <c r="U14" s="132"/>
-    </row>
-    <row r="15" spans="2:28" ht="87.75" customHeight="1" thickBot="1">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="148" t="s">
+        <v>246</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="S14" s="134" t="s">
+        <v>247</v>
+      </c>
+      <c r="T14" s="135" t="s">
+        <v>248</v>
+      </c>
+      <c r="U14" s="114"/>
+      <c r="V14" s="2">
+        <v>6</v>
+      </c>
+      <c r="W14" s="275"/>
+      <c r="X14" s="276"/>
+    </row>
+    <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="187" t="s">
+        <v>407</v>
+      </c>
+      <c r="C15" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D15" s="191" t="s">
+        <v>408</v>
+      </c>
+      <c r="E15" s="171" t="s">
+        <v>409</v>
+      </c>
+      <c r="F15" s="172"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="166" t="s">
-        <v>297</v>
-      </c>
-      <c r="R15" s="157" t="s">
-        <v>298</v>
-      </c>
-      <c r="S15" s="152" t="s">
-        <v>299</v>
-      </c>
-      <c r="T15" s="153" t="s">
-        <v>300</v>
-      </c>
-      <c r="U15" s="132"/>
-    </row>
-    <row r="16" spans="2:28" ht="68.25" customHeight="1" thickBot="1">
-      <c r="B16" s="120" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="121" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="122" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="122" t="s">
-        <v>226</v>
-      </c>
-      <c r="F16" s="123" t="s">
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="148" t="s">
+        <v>249</v>
+      </c>
+      <c r="R15" s="139" t="s">
+        <v>250</v>
+      </c>
+      <c r="S15" s="134" t="s">
+        <v>251</v>
+      </c>
+      <c r="T15" s="135" t="s">
+        <v>252</v>
+      </c>
+      <c r="U15" s="114"/>
+      <c r="V15" s="1">
+        <v>7</v>
+      </c>
+      <c r="W15" s="275"/>
+      <c r="X15" s="276"/>
+    </row>
+    <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="187" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="191" t="s">
+        <v>411</v>
+      </c>
+      <c r="E16" s="171" t="s">
+        <v>412</v>
+      </c>
+      <c r="F16" s="172"/>
+      <c r="Q16" s="148" t="s">
+        <v>253</v>
+      </c>
+      <c r="R16" s="139" t="s">
         <v>227</v>
       </c>
-      <c r="G16" s="224" t="s">
-        <v>265</v>
-      </c>
-      <c r="H16" s="225"/>
-      <c r="I16" s="225"/>
-      <c r="J16" s="226"/>
-      <c r="Q16" s="166" t="s">
-        <v>301</v>
-      </c>
-      <c r="R16" s="157" t="s">
-        <v>275</v>
-      </c>
-      <c r="S16" s="152" t="s">
-        <v>302</v>
-      </c>
-      <c r="T16" s="154" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" ht="60.75" customHeight="1" thickBot="1">
-      <c r="B17" s="296" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="294" t="s">
-        <v>229</v>
-      </c>
-      <c r="D17" s="124" t="s">
-        <v>228</v>
-      </c>
-      <c r="E17" s="125" t="s">
-        <v>230</v>
-      </c>
-      <c r="F17" s="126" t="s">
-        <v>231</v>
-      </c>
-      <c r="G17" s="310" t="s">
-        <v>266</v>
-      </c>
-      <c r="H17" s="311"/>
-      <c r="I17" s="311"/>
-      <c r="J17" s="312"/>
-      <c r="Q17" s="167" t="s">
-        <v>304</v>
-      </c>
-      <c r="R17" s="158" t="s">
-        <v>298</v>
-      </c>
-      <c r="S17" s="155" t="s">
-        <v>305</v>
-      </c>
-      <c r="T17" s="156" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B18" s="313"/>
-      <c r="C18" s="314"/>
-      <c r="D18" s="111" t="s">
-        <v>232</v>
-      </c>
-      <c r="E18" s="112" t="s">
-        <v>233</v>
-      </c>
-      <c r="F18" s="114" t="s">
-        <v>234</v>
-      </c>
-      <c r="G18" s="304" t="s">
-        <v>267</v>
-      </c>
-      <c r="H18" s="305"/>
-      <c r="I18" s="305"/>
-      <c r="J18" s="306"/>
-    </row>
-    <row r="19" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B19" s="297"/>
-      <c r="C19" s="295"/>
-      <c r="D19" s="116" t="s">
-        <v>235</v>
-      </c>
-      <c r="E19" s="127" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="117" t="s">
-        <v>237</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B20" s="296" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="294" t="s">
-        <v>239</v>
-      </c>
-      <c r="D20" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="E20" s="125" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" s="126" t="s">
-        <v>240</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B21" s="297"/>
-      <c r="C21" s="295"/>
-      <c r="D21" s="116" t="s">
-        <v>242</v>
-      </c>
-      <c r="E21" s="115" t="s">
-        <v>243</v>
-      </c>
-      <c r="F21" s="117" t="s">
-        <v>240</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B22" s="296" t="s">
-        <v>244</v>
-      </c>
-      <c r="C22" s="294" t="s">
-        <v>245</v>
-      </c>
-      <c r="D22" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="E22" s="113" t="s">
-        <v>246</v>
-      </c>
-      <c r="F22" s="126" t="s">
-        <v>247</v>
+      <c r="S16" s="134" t="s">
+        <v>254</v>
+      </c>
+      <c r="T16" s="136" t="s">
+        <v>255</v>
+      </c>
+      <c r="V16" s="2">
+        <v>8</v>
+      </c>
+      <c r="W16" s="275"/>
+      <c r="X16" s="276"/>
+    </row>
+    <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="189" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="184" t="s">
+        <v>386</v>
+      </c>
+      <c r="D17" s="193" t="s">
+        <v>414</v>
+      </c>
+      <c r="E17" s="174" t="s">
+        <v>415</v>
+      </c>
+      <c r="F17" s="175"/>
+      <c r="Q17" s="149" t="s">
+        <v>256</v>
+      </c>
+      <c r="R17" s="140" t="s">
+        <v>250</v>
+      </c>
+      <c r="S17" s="137" t="s">
+        <v>257</v>
+      </c>
+      <c r="T17" s="138" t="s">
+        <v>258</v>
+      </c>
+      <c r="V17" s="232">
+        <v>9</v>
+      </c>
+      <c r="W17" s="286"/>
+      <c r="X17" s="287"/>
+    </row>
+    <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="102" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="D19" s="104" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="104" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="105" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="242" t="s">
+        <v>220</v>
+      </c>
+      <c r="H19" s="243"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="244"/>
+    </row>
+    <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="167" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="233" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="106" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="108" t="s">
+        <v>186</v>
+      </c>
+      <c r="G20" s="238" t="s">
+        <v>457</v>
+      </c>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="240"/>
+    </row>
+    <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="169"/>
+      <c r="C21" s="241"/>
+      <c r="D21" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="95" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="97" t="s">
+        <v>189</v>
+      </c>
+      <c r="G21" s="235" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="237"/>
+    </row>
+    <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="168"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="99" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="109" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="100" t="s">
+        <v>192</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B23" s="297"/>
-      <c r="C23" s="295"/>
-      <c r="D23" s="116" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="115" t="s">
-        <v>248</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>240</v>
+    <row r="23" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="167" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="233" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="106" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" s="107" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="108" t="s">
+        <v>195</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B24" s="296" t="s">
-        <v>249</v>
-      </c>
-      <c r="C24" s="294" t="s">
-        <v>250</v>
-      </c>
-      <c r="D24" s="124" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" s="125" t="s">
-        <v>251</v>
-      </c>
-      <c r="F24" s="126" t="s">
-        <v>240</v>
+    <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="168"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="99" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="100" t="s">
+        <v>195</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B25" s="297"/>
-      <c r="C25" s="295"/>
-      <c r="D25" s="116" t="s">
-        <v>244</v>
-      </c>
-      <c r="E25" s="115" t="s">
-        <v>252</v>
-      </c>
-      <c r="F25" s="117" t="s">
-        <v>240</v>
+    <row r="25" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="167" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="233" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="106" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" s="96" t="s">
+        <v>201</v>
+      </c>
+      <c r="F25" s="108" t="s">
+        <v>202</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B26" s="131" t="s">
-        <v>253</v>
-      </c>
-      <c r="C26" s="118" t="s">
-        <v>254</v>
-      </c>
-      <c r="D26" s="128" t="s">
-        <v>240</v>
-      </c>
-      <c r="E26" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="F26" s="130" t="s">
-        <v>240</v>
+    <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="168"/>
+      <c r="C26" s="234"/>
+      <c r="D26" s="99" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="98" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" s="100" t="s">
+        <v>195</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B27" s="296" t="s">
-        <v>232</v>
-      </c>
-      <c r="C27" s="294" t="s">
-        <v>256</v>
-      </c>
-      <c r="D27" s="124" t="s">
-        <v>240</v>
-      </c>
-      <c r="E27" s="125" t="s">
-        <v>257</v>
-      </c>
-      <c r="F27" s="126" t="s">
-        <v>240</v>
+    <row r="27" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="167" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="233" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="106" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="107" t="s">
+        <v>206</v>
+      </c>
+      <c r="F27" s="108" t="s">
+        <v>195</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B28" s="297"/>
-      <c r="C28" s="295"/>
-      <c r="D28" s="116" t="s">
-        <v>249</v>
-      </c>
-      <c r="E28" s="127" t="s">
-        <v>258</v>
-      </c>
-      <c r="F28" s="117" t="s">
-        <v>259</v>
+    <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="168"/>
+      <c r="C28" s="234"/>
+      <c r="D28" s="99" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="98" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" s="100" t="s">
+        <v>195</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="2:20" ht="51.75" customHeight="1">
-      <c r="B29" s="296" t="s">
-        <v>260</v>
-      </c>
-      <c r="C29" s="294" t="s">
-        <v>261</v>
-      </c>
-      <c r="D29" s="124" t="s">
-        <v>244</v>
-      </c>
-      <c r="E29" s="113" t="s">
-        <v>262</v>
-      </c>
-      <c r="F29" s="126" t="s">
-        <v>263</v>
+    <row r="29" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="113" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="101" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="111" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" s="112" t="s">
+        <v>195</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="2:20" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B30" s="297"/>
-      <c r="C30" s="295"/>
-      <c r="D30" s="116" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="115" t="s">
-        <v>264</v>
-      </c>
-      <c r="F30" s="117" t="s">
-        <v>240</v>
+    <row r="30" spans="2:24" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="167" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="233" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="106" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="107" t="s">
+        <v>212</v>
+      </c>
+      <c r="F30" s="108" t="s">
+        <v>195</v>
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
     </row>
+    <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="168"/>
+      <c r="C31" s="234"/>
+      <c r="D31" s="99" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="100" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="2:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="167" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="233" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="106" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="96" t="s">
+        <v>217</v>
+      </c>
+      <c r="F32" s="108" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="168"/>
+      <c r="C33" s="234"/>
+      <c r="D33" s="99" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="F33" s="100" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C17:C19"/>
+  <mergeCells count="33">
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="V2:AB2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="V2:AB2"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="G19:J19"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="H6:J6"/>
@@ -8253,8 +9915,333 @@
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B07C92-48AD-46D8-AFE8-A66BE9216D0D}">
+  <dimension ref="B1:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="391" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2" s="392"/>
+      <c r="D2" s="393"/>
+      <c r="E2" s="393"/>
+      <c r="F2" s="393"/>
+      <c r="G2" s="393"/>
+      <c r="H2" s="394"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="194" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" s="195" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="195" t="s">
+        <v>427</v>
+      </c>
+      <c r="E3" s="195" t="s">
+        <v>428</v>
+      </c>
+      <c r="F3" s="195" t="s">
+        <v>430</v>
+      </c>
+      <c r="G3" s="389" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" s="390"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="196">
+        <v>0</v>
+      </c>
+      <c r="C4" s="202"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="223" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="395" t="s">
+        <v>436</v>
+      </c>
+      <c r="H4" s="396"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="197">
+        <v>1</v>
+      </c>
+      <c r="C5" s="198" t="s">
+        <v>439</v>
+      </c>
+      <c r="D5" s="228"/>
+      <c r="E5" s="222" t="s">
+        <v>441</v>
+      </c>
+      <c r="F5" s="224" t="s">
+        <v>431</v>
+      </c>
+      <c r="G5" s="387" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" s="388"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="197">
+        <v>2</v>
+      </c>
+      <c r="C6" s="229"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="200" t="s">
+        <v>441</v>
+      </c>
+      <c r="F6" s="224" t="s">
+        <v>432</v>
+      </c>
+      <c r="G6" s="387" t="s">
+        <v>437</v>
+      </c>
+      <c r="H6" s="388"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="197">
+        <v>3</v>
+      </c>
+      <c r="C7" s="207"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="224" t="s">
+        <v>433</v>
+      </c>
+      <c r="G7" s="387" t="s">
+        <v>438</v>
+      </c>
+      <c r="H7" s="388"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="197">
+        <v>4</v>
+      </c>
+      <c r="C8" s="198" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8" s="199" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" s="206"/>
+      <c r="F8" s="224" t="s">
+        <v>434</v>
+      </c>
+      <c r="G8" s="387" t="s">
+        <v>444</v>
+      </c>
+      <c r="H8" s="388"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="197">
+        <v>5</v>
+      </c>
+      <c r="C9" s="207"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="225" t="s">
+        <v>435</v>
+      </c>
+      <c r="G9" s="406"/>
+      <c r="H9" s="407"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="197">
+        <v>6</v>
+      </c>
+      <c r="C10" s="207"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="226" t="s">
+        <v>435</v>
+      </c>
+      <c r="G10" s="406"/>
+      <c r="H10" s="407"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="201">
+        <v>7</v>
+      </c>
+      <c r="C11" s="208"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="227" t="s">
+        <v>435</v>
+      </c>
+      <c r="G11" s="408"/>
+      <c r="H11" s="409"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="212" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" s="410" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="411"/>
+      <c r="E13" s="412"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="213">
+        <v>0</v>
+      </c>
+      <c r="C14" s="397" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="398"/>
+      <c r="E14" s="399"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="214">
+        <v>1</v>
+      </c>
+      <c r="C15" s="400" t="s">
+        <v>449</v>
+      </c>
+      <c r="D15" s="401"/>
+      <c r="E15" s="402"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="214">
+        <v>2</v>
+      </c>
+      <c r="C16" s="415" t="s">
+        <v>450</v>
+      </c>
+      <c r="D16" s="416"/>
+      <c r="E16" s="417"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="214">
+        <v>3</v>
+      </c>
+      <c r="C17" s="403" t="s">
+        <v>452</v>
+      </c>
+      <c r="D17" s="404"/>
+      <c r="E17" s="405"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="214">
+        <v>4</v>
+      </c>
+      <c r="C18" s="418"/>
+      <c r="D18" s="419"/>
+      <c r="E18" s="420"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="214">
+        <v>5</v>
+      </c>
+      <c r="C19" s="418"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="420"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="214">
+        <v>6</v>
+      </c>
+      <c r="C20" s="418"/>
+      <c r="D20" s="419"/>
+      <c r="E20" s="420"/>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="215">
+        <v>7</v>
+      </c>
+      <c r="C21" s="421"/>
+      <c r="D21" s="422"/>
+      <c r="E21" s="423"/>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="413" t="s">
+        <v>445</v>
+      </c>
+      <c r="C23" s="211">
+        <v>5</v>
+      </c>
+      <c r="D23" s="218">
+        <v>4</v>
+      </c>
+      <c r="E23" s="218">
+        <v>3</v>
+      </c>
+      <c r="F23" s="218">
+        <v>2</v>
+      </c>
+      <c r="G23" s="218">
+        <v>1</v>
+      </c>
+      <c r="H23" s="219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="414"/>
+      <c r="C24" s="220"/>
+      <c r="D24" s="221"/>
+      <c r="E24" s="221"/>
+      <c r="F24" s="221"/>
+      <c r="G24" s="216" t="s">
+        <v>448</v>
+      </c>
+      <c r="H24" s="217" t="s">
+        <v>447</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787BD476-9523-4D51-AED7-9AF633FAF38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FC1EE5-D686-407E-B6CE-219046E28209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -4173,21 +4173,459 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4200,440 +4638,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4641,6 +4704,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4664,90 +4748,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5069,62 +5069,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="325" t="s">
+      <c r="B2" s="311" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="334" t="s">
+      <c r="C2" s="326" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="335"/>
-      <c r="E2" s="336" t="s">
+      <c r="D2" s="327"/>
+      <c r="E2" s="328" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="336"/>
-      <c r="G2" s="337" t="s">
+      <c r="F2" s="328"/>
+      <c r="G2" s="329" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="336"/>
-      <c r="I2" s="336" t="s">
+      <c r="H2" s="328"/>
+      <c r="I2" s="328" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="336"/>
-      <c r="K2" s="338" t="s">
+      <c r="J2" s="328"/>
+      <c r="K2" s="330" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="336"/>
-      <c r="M2" s="336"/>
-      <c r="N2" s="336"/>
-      <c r="O2" s="336"/>
-      <c r="P2" s="339"/>
-      <c r="R2" s="342" t="s">
+      <c r="L2" s="328"/>
+      <c r="M2" s="328"/>
+      <c r="N2" s="328"/>
+      <c r="O2" s="328"/>
+      <c r="P2" s="331"/>
+      <c r="R2" s="307" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="294" t="s">
+      <c r="S2" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="346" t="s">
+      <c r="T2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="347"/>
-      <c r="V2" s="347"/>
-      <c r="W2" s="347"/>
-      <c r="X2" s="347"/>
-      <c r="Y2" s="347"/>
-      <c r="Z2" s="347"/>
-      <c r="AA2" s="347"/>
-      <c r="AB2" s="347" t="s">
+      <c r="U2" s="299"/>
+      <c r="V2" s="299"/>
+      <c r="W2" s="299"/>
+      <c r="X2" s="299"/>
+      <c r="Y2" s="299"/>
+      <c r="Z2" s="299"/>
+      <c r="AA2" s="299"/>
+      <c r="AB2" s="299" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="347"/>
-      <c r="AD2" s="347"/>
-      <c r="AE2" s="347"/>
-      <c r="AF2" s="347"/>
-      <c r="AG2" s="347"/>
-      <c r="AH2" s="347"/>
-      <c r="AI2" s="348"/>
+      <c r="AC2" s="299"/>
+      <c r="AD2" s="299"/>
+      <c r="AE2" s="299"/>
+      <c r="AF2" s="299"/>
+      <c r="AG2" s="299"/>
+      <c r="AH2" s="299"/>
+      <c r="AI2" s="300"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="326"/>
+      <c r="B3" s="312"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5149,21 +5149,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="331"/>
-      <c r="L3" s="332"/>
-      <c r="M3" s="332"/>
-      <c r="N3" s="332"/>
-      <c r="O3" s="332"/>
-      <c r="P3" s="333"/>
-      <c r="R3" s="343"/>
-      <c r="S3" s="340"/>
+      <c r="K3" s="283"/>
+      <c r="L3" s="325"/>
+      <c r="M3" s="325"/>
+      <c r="N3" s="325"/>
+      <c r="O3" s="325"/>
+      <c r="P3" s="284"/>
+      <c r="R3" s="308"/>
+      <c r="S3" s="246"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="312" t="s">
+      <c r="U3" s="335" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="312"/>
+      <c r="V3" s="335"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5176,10 +5176,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="345" t="s">
+      <c r="AA3" s="297" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="345"/>
+      <c r="AB3" s="297"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5203,21 +5203,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="327"/>
+      <c r="B4" s="313"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="313" t="s">
+      <c r="E4" s="301" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
-      <c r="H4" s="243"/>
-      <c r="I4" s="243"/>
-      <c r="J4" s="244"/>
+      <c r="F4" s="288"/>
+      <c r="G4" s="288"/>
+      <c r="H4" s="288"/>
+      <c r="I4" s="288"/>
+      <c r="J4" s="289"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5227,20 +5227,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="313" t="s">
+      <c r="N4" s="301" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="243"/>
-      <c r="P4" s="244"/>
-      <c r="R4" s="344"/>
-      <c r="S4" s="341"/>
+      <c r="O4" s="288"/>
+      <c r="P4" s="289"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="306"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="313" t="s">
+      <c r="U4" s="301" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="314"/>
+      <c r="V4" s="302"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5253,10 +5253,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="313" t="s">
+      <c r="AA4" s="301" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="314"/>
+      <c r="AB4" s="302"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5288,22 +5288,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="317"/>
-      <c r="F5" s="318"/>
-      <c r="G5" s="318"/>
-      <c r="H5" s="318"/>
-      <c r="I5" s="318"/>
-      <c r="J5" s="319"/>
+      <c r="E5" s="332"/>
+      <c r="F5" s="333"/>
+      <c r="G5" s="333"/>
+      <c r="H5" s="333"/>
+      <c r="I5" s="333"/>
+      <c r="J5" s="334"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="253" t="s">
+      <c r="N5" s="268" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="254"/>
-      <c r="P5" s="255"/>
+      <c r="O5" s="310"/>
+      <c r="P5" s="269"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5313,10 +5313,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="315" t="s">
+      <c r="U5" s="303" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="316"/>
+      <c r="V5" s="304"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5329,10 +5329,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="315" t="s">
+      <c r="AA5" s="303" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="316"/>
+      <c r="AB5" s="304"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5364,12 +5364,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="324"/>
-      <c r="F6" s="321"/>
-      <c r="G6" s="321"/>
-      <c r="H6" s="321"/>
-      <c r="I6" s="321"/>
-      <c r="J6" s="322"/>
+      <c r="E6" s="323"/>
+      <c r="F6" s="318"/>
+      <c r="G6" s="318"/>
+      <c r="H6" s="318"/>
+      <c r="I6" s="318"/>
+      <c r="J6" s="319"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5377,11 +5377,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="250" t="s">
+      <c r="N6" s="294" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="251"/>
-      <c r="P6" s="252"/>
+      <c r="O6" s="295"/>
+      <c r="P6" s="296"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5391,10 +5391,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="310" t="s">
+      <c r="U6" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="311"/>
+      <c r="V6" s="291"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5407,10 +5407,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="310" t="s">
+      <c r="AA6" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="311"/>
+      <c r="AB6" s="291"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5453,9 +5453,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="320"/>
-      <c r="I7" s="321"/>
-      <c r="J7" s="322"/>
+      <c r="H7" s="317"/>
+      <c r="I7" s="318"/>
+      <c r="J7" s="319"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5463,11 +5463,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="250" t="s">
+      <c r="N7" s="294" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="251"/>
-      <c r="P7" s="252"/>
+      <c r="O7" s="295"/>
+      <c r="P7" s="296"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5477,10 +5477,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="310" t="s">
+      <c r="U7" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="311"/>
+      <c r="V7" s="291"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5493,10 +5493,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="310" t="s">
+      <c r="AA7" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="311"/>
+      <c r="AB7" s="291"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5539,9 +5539,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="320"/>
-      <c r="I8" s="321"/>
-      <c r="J8" s="322"/>
+      <c r="H8" s="317"/>
+      <c r="I8" s="318"/>
+      <c r="J8" s="319"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5549,11 +5549,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="250" t="s">
+      <c r="N8" s="294" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="251"/>
-      <c r="P8" s="252"/>
+      <c r="O8" s="295"/>
+      <c r="P8" s="296"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5563,10 +5563,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="310" t="s">
+      <c r="U8" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="311"/>
+      <c r="V8" s="291"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5579,10 +5579,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="310" t="s">
+      <c r="AA8" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="311"/>
+      <c r="AB8" s="291"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5625,9 +5625,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="320"/>
-      <c r="I9" s="321"/>
-      <c r="J9" s="322"/>
+      <c r="H9" s="317"/>
+      <c r="I9" s="318"/>
+      <c r="J9" s="319"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5635,11 +5635,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="250" t="s">
+      <c r="N9" s="294" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="251"/>
-      <c r="P9" s="252"/>
+      <c r="O9" s="295"/>
+      <c r="P9" s="296"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5649,10 +5649,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="310" t="s">
+      <c r="U9" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="311"/>
+      <c r="V9" s="291"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5665,10 +5665,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="310" t="s">
+      <c r="AA9" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="311"/>
+      <c r="AB9" s="291"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5711,9 +5711,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="320"/>
-      <c r="I10" s="321"/>
-      <c r="J10" s="322"/>
+      <c r="H10" s="317"/>
+      <c r="I10" s="318"/>
+      <c r="J10" s="319"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5721,11 +5721,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="250" t="s">
+      <c r="N10" s="294" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="251"/>
-      <c r="P10" s="252"/>
+      <c r="O10" s="295"/>
+      <c r="P10" s="296"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5735,10 +5735,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="310" t="s">
+      <c r="U10" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="311"/>
+      <c r="V10" s="291"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5751,10 +5751,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="310" t="s">
+      <c r="AA10" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="311"/>
+      <c r="AB10" s="291"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5797,9 +5797,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="320"/>
-      <c r="I11" s="321"/>
-      <c r="J11" s="322"/>
+      <c r="H11" s="317"/>
+      <c r="I11" s="318"/>
+      <c r="J11" s="319"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5807,11 +5807,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="250" t="s">
+      <c r="N11" s="294" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="251"/>
-      <c r="P11" s="252"/>
+      <c r="O11" s="295"/>
+      <c r="P11" s="296"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5821,10 +5821,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="310" t="s">
+      <c r="U11" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="311"/>
+      <c r="V11" s="291"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5837,10 +5837,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="310" t="s">
+      <c r="AA11" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="311"/>
+      <c r="AB11" s="291"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5883,9 +5883,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="320"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="322"/>
+      <c r="H12" s="317"/>
+      <c r="I12" s="318"/>
+      <c r="J12" s="319"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5893,11 +5893,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="250" t="s">
+      <c r="N12" s="294" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="251"/>
-      <c r="P12" s="252"/>
+      <c r="O12" s="295"/>
+      <c r="P12" s="296"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5907,10 +5907,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="310" t="s">
+      <c r="U12" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="311"/>
+      <c r="V12" s="291"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5923,10 +5923,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="310" t="s">
+      <c r="AA12" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="311"/>
+      <c r="AB12" s="291"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -5969,9 +5969,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="320"/>
-      <c r="I13" s="321"/>
-      <c r="J13" s="322"/>
+      <c r="H13" s="317"/>
+      <c r="I13" s="318"/>
+      <c r="J13" s="319"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -5979,11 +5979,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="250" t="s">
+      <c r="N13" s="294" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="251"/>
-      <c r="P13" s="252"/>
+      <c r="O13" s="295"/>
+      <c r="P13" s="296"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -5993,10 +5993,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="310" t="s">
+      <c r="U13" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="311"/>
+      <c r="V13" s="291"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6009,10 +6009,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="310" t="s">
+      <c r="AA13" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="311"/>
+      <c r="AB13" s="291"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6055,9 +6055,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="320"/>
-      <c r="I14" s="321"/>
-      <c r="J14" s="322"/>
+      <c r="H14" s="317"/>
+      <c r="I14" s="318"/>
+      <c r="J14" s="319"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6065,11 +6065,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="250" t="s">
+      <c r="N14" s="294" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="251"/>
-      <c r="P14" s="252"/>
+      <c r="O14" s="295"/>
+      <c r="P14" s="296"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6079,10 +6079,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="310" t="s">
+      <c r="U14" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="311"/>
+      <c r="V14" s="291"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6095,10 +6095,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="310" t="s">
+      <c r="AA14" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="311"/>
+      <c r="AB14" s="291"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6141,9 +6141,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="320"/>
-      <c r="I15" s="321"/>
-      <c r="J15" s="322"/>
+      <c r="H15" s="317"/>
+      <c r="I15" s="318"/>
+      <c r="J15" s="319"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6151,11 +6151,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="250" t="s">
+      <c r="N15" s="294" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="251"/>
-      <c r="P15" s="252"/>
+      <c r="O15" s="295"/>
+      <c r="P15" s="296"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6165,10 +6165,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="310" t="s">
+      <c r="U15" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="311"/>
+      <c r="V15" s="291"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6181,10 +6181,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="310" t="s">
+      <c r="AA15" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="311"/>
+      <c r="AB15" s="291"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6221,21 +6221,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="320"/>
-      <c r="G16" s="321"/>
-      <c r="H16" s="321"/>
-      <c r="I16" s="321"/>
-      <c r="J16" s="322"/>
+      <c r="F16" s="317"/>
+      <c r="G16" s="318"/>
+      <c r="H16" s="318"/>
+      <c r="I16" s="318"/>
+      <c r="J16" s="319"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="250" t="s">
+      <c r="N16" s="294" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="251"/>
-      <c r="P16" s="252"/>
+      <c r="O16" s="295"/>
+      <c r="P16" s="296"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6245,10 +6245,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="310" t="s">
+      <c r="U16" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="311"/>
+      <c r="V16" s="291"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6261,10 +6261,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="310" t="s">
+      <c r="AA16" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="311"/>
+      <c r="AB16" s="291"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6302,22 +6302,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="323" t="s">
+      <c r="G17" s="324" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="252"/>
+      <c r="H17" s="295"/>
+      <c r="I17" s="295"/>
+      <c r="J17" s="296"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="250" t="s">
+      <c r="N17" s="294" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="251"/>
-      <c r="P17" s="252"/>
+      <c r="O17" s="295"/>
+      <c r="P17" s="296"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6327,10 +6327,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="310" t="s">
+      <c r="U17" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="311"/>
+      <c r="V17" s="291"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6343,10 +6343,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="310" t="s">
+      <c r="AA17" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="311"/>
+      <c r="AB17" s="291"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6384,12 +6384,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="323" t="s">
+      <c r="G18" s="324" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="252"/>
+      <c r="H18" s="295"/>
+      <c r="I18" s="295"/>
+      <c r="J18" s="296"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6397,11 +6397,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="250" t="s">
+      <c r="N18" s="294" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="251"/>
-      <c r="P18" s="252"/>
+      <c r="O18" s="295"/>
+      <c r="P18" s="296"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6411,10 +6411,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="310" t="s">
+      <c r="U18" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="311"/>
+      <c r="V18" s="291"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6427,10 +6427,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="310" t="s">
+      <c r="AA18" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="311"/>
+      <c r="AB18" s="291"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6466,20 +6466,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="320"/>
-      <c r="H19" s="321"/>
-      <c r="I19" s="321"/>
-      <c r="J19" s="322"/>
+      <c r="G19" s="317"/>
+      <c r="H19" s="318"/>
+      <c r="I19" s="318"/>
+      <c r="J19" s="319"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="250" t="s">
+      <c r="N19" s="294" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="251"/>
-      <c r="P19" s="252"/>
+      <c r="O19" s="295"/>
+      <c r="P19" s="296"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6489,10 +6489,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="310" t="s">
+      <c r="U19" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="311"/>
+      <c r="V19" s="291"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6505,10 +6505,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="310" t="s">
+      <c r="AA19" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="311"/>
+      <c r="AB19" s="291"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6546,20 +6546,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="320"/>
-      <c r="H20" s="321"/>
-      <c r="I20" s="321"/>
-      <c r="J20" s="322"/>
+      <c r="G20" s="317"/>
+      <c r="H20" s="318"/>
+      <c r="I20" s="318"/>
+      <c r="J20" s="319"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="250" t="s">
+      <c r="N20" s="294" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="251"/>
-      <c r="P20" s="252"/>
+      <c r="O20" s="295"/>
+      <c r="P20" s="296"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6569,10 +6569,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="310" t="s">
+      <c r="U20" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="311"/>
+      <c r="V20" s="291"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6585,10 +6585,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="310" t="s">
+      <c r="AA20" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="311"/>
+      <c r="AB20" s="291"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6626,20 +6626,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="320"/>
-      <c r="H21" s="321"/>
-      <c r="I21" s="321"/>
-      <c r="J21" s="322"/>
+      <c r="G21" s="317"/>
+      <c r="H21" s="318"/>
+      <c r="I21" s="318"/>
+      <c r="J21" s="319"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="250" t="s">
+      <c r="N21" s="294" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="251"/>
-      <c r="P21" s="252"/>
+      <c r="O21" s="295"/>
+      <c r="P21" s="296"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6649,10 +6649,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="310" t="s">
+      <c r="U21" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="311"/>
+      <c r="V21" s="291"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6665,10 +6665,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="310" t="s">
+      <c r="AA21" s="290" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="311"/>
+      <c r="AB21" s="291"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6702,22 +6702,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="324"/>
-      <c r="F22" s="321"/>
-      <c r="G22" s="321"/>
-      <c r="H22" s="321"/>
-      <c r="I22" s="321"/>
-      <c r="J22" s="322"/>
+      <c r="E22" s="323"/>
+      <c r="F22" s="318"/>
+      <c r="G22" s="318"/>
+      <c r="H22" s="318"/>
+      <c r="I22" s="318"/>
+      <c r="J22" s="319"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="250" t="s">
+      <c r="N22" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="251"/>
-      <c r="P22" s="252"/>
+      <c r="O22" s="295"/>
+      <c r="P22" s="296"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6727,10 +6727,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="310" t="s">
+      <c r="U22" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="311"/>
+      <c r="V22" s="291"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6743,10 +6743,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="310" t="s">
+      <c r="AA22" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="311"/>
+      <c r="AB22" s="291"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6786,22 +6786,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="323" t="s">
+      <c r="G23" s="324" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="251"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="252"/>
+      <c r="H23" s="295"/>
+      <c r="I23" s="295"/>
+      <c r="J23" s="296"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="250" t="s">
+      <c r="N23" s="294" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="251"/>
-      <c r="P23" s="252"/>
+      <c r="O23" s="295"/>
+      <c r="P23" s="296"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6811,10 +6811,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="310" t="s">
+      <c r="U23" s="290" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="311"/>
+      <c r="V23" s="291"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6827,10 +6827,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="310" t="s">
+      <c r="AA23" s="290" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="311"/>
+      <c r="AB23" s="291"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6870,22 +6870,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="323" t="s">
+      <c r="G24" s="324" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="251"/>
-      <c r="I24" s="251"/>
-      <c r="J24" s="252"/>
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="296"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="250" t="s">
+      <c r="N24" s="294" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="251"/>
-      <c r="P24" s="252"/>
+      <c r="O24" s="295"/>
+      <c r="P24" s="296"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6895,10 +6895,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="310" t="s">
+      <c r="U24" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="311"/>
+      <c r="V24" s="291"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6911,10 +6911,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="310" t="s">
+      <c r="AA24" s="290" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="311"/>
+      <c r="AB24" s="291"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6952,10 +6952,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="320"/>
-      <c r="H25" s="321"/>
-      <c r="I25" s="321"/>
-      <c r="J25" s="322"/>
+      <c r="G25" s="317"/>
+      <c r="H25" s="318"/>
+      <c r="I25" s="318"/>
+      <c r="J25" s="319"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6963,11 +6963,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="250" t="s">
+      <c r="N25" s="294" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="251"/>
-      <c r="P25" s="252"/>
+      <c r="O25" s="295"/>
+      <c r="P25" s="296"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -6977,10 +6977,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="310" t="s">
+      <c r="U25" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="311"/>
+      <c r="V25" s="291"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -6993,10 +6993,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="310" t="s">
+      <c r="AA25" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="311"/>
+      <c r="AB25" s="291"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7034,10 +7034,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="320"/>
-      <c r="H26" s="321"/>
-      <c r="I26" s="321"/>
-      <c r="J26" s="322"/>
+      <c r="G26" s="317"/>
+      <c r="H26" s="318"/>
+      <c r="I26" s="318"/>
+      <c r="J26" s="319"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7045,11 +7045,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="250" t="s">
+      <c r="N26" s="294" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="251"/>
-      <c r="P26" s="252"/>
+      <c r="O26" s="295"/>
+      <c r="P26" s="296"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7059,10 +7059,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="310" t="s">
+      <c r="U26" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="311"/>
+      <c r="V26" s="291"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7075,10 +7075,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="310" t="s">
+      <c r="AA26" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="311"/>
+      <c r="AB26" s="291"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7110,22 +7110,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="324"/>
-      <c r="F27" s="321"/>
-      <c r="G27" s="321"/>
-      <c r="H27" s="321"/>
-      <c r="I27" s="321"/>
-      <c r="J27" s="322"/>
+      <c r="E27" s="323"/>
+      <c r="F27" s="318"/>
+      <c r="G27" s="318"/>
+      <c r="H27" s="318"/>
+      <c r="I27" s="318"/>
+      <c r="J27" s="319"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="250" t="s">
+      <c r="N27" s="294" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="251"/>
-      <c r="P27" s="252"/>
+      <c r="O27" s="295"/>
+      <c r="P27" s="296"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7135,10 +7135,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="310" t="s">
+      <c r="U27" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="311"/>
+      <c r="V27" s="291"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7151,10 +7151,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="310" t="s">
+      <c r="AA27" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="311"/>
+      <c r="AB27" s="291"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7186,12 +7186,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="328"/>
-      <c r="F28" s="329"/>
-      <c r="G28" s="329"/>
-      <c r="H28" s="329"/>
-      <c r="I28" s="329"/>
-      <c r="J28" s="330"/>
+      <c r="E28" s="320"/>
+      <c r="F28" s="321"/>
+      <c r="G28" s="321"/>
+      <c r="H28" s="321"/>
+      <c r="I28" s="321"/>
+      <c r="J28" s="322"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7199,11 +7199,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="247" t="s">
+      <c r="N28" s="314" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="248"/>
-      <c r="P28" s="249"/>
+      <c r="O28" s="315"/>
+      <c r="P28" s="316"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7213,10 +7213,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="357" t="s">
+      <c r="U28" s="292" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="358"/>
+      <c r="V28" s="293"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7229,10 +7229,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="357" t="s">
+      <c r="AA28" s="292" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="358"/>
+      <c r="AB28" s="293"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7309,27 +7309,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="293" t="s">
+      <c r="T30" s="349" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="293"/>
-      <c r="V30" s="293"/>
-      <c r="W30" s="293"/>
-      <c r="X30" s="293"/>
-      <c r="Y30" s="293"/>
-      <c r="Z30" s="293"/>
-      <c r="AA30" s="293"/>
-      <c r="AB30" s="293"/>
-      <c r="AC30" s="294"/>
-      <c r="AE30" s="242" t="s">
+      <c r="U30" s="349"/>
+      <c r="V30" s="349"/>
+      <c r="W30" s="349"/>
+      <c r="X30" s="349"/>
+      <c r="Y30" s="349"/>
+      <c r="Z30" s="349"/>
+      <c r="AA30" s="349"/>
+      <c r="AB30" s="349"/>
+      <c r="AC30" s="305"/>
+      <c r="AE30" s="287" t="s">
         <v>422</v>
       </c>
-      <c r="AF30" s="243"/>
-      <c r="AG30" s="242" t="s">
+      <c r="AF30" s="288"/>
+      <c r="AG30" s="287" t="s">
         <v>423</v>
       </c>
-      <c r="AH30" s="243"/>
-      <c r="AI30" s="244"/>
+      <c r="AH30" s="288"/>
+      <c r="AI30" s="289"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7370,28 +7370,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="253" t="s">
+      <c r="T31" s="268" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="254"/>
-      <c r="V31" s="254"/>
-      <c r="W31" s="254"/>
-      <c r="X31" s="254"/>
-      <c r="Y31" s="254"/>
-      <c r="Z31" s="254"/>
-      <c r="AA31" s="254"/>
-      <c r="AB31" s="254"/>
-      <c r="AC31" s="255"/>
-      <c r="AE31" s="288">
+      <c r="U31" s="310"/>
+      <c r="V31" s="310"/>
+      <c r="W31" s="310"/>
+      <c r="X31" s="310"/>
+      <c r="Y31" s="310"/>
+      <c r="Z31" s="310"/>
+      <c r="AA31" s="310"/>
+      <c r="AB31" s="310"/>
+      <c r="AC31" s="269"/>
+      <c r="AE31" s="344">
         <v>2</v>
       </c>
-      <c r="AF31" s="289"/>
-      <c r="AG31" s="290" t="str" cm="1">
+      <c r="AF31" s="345"/>
+      <c r="AG31" s="346" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="291"/>
-      <c r="AI31" s="292"/>
+      <c r="AH31" s="347"/>
+      <c r="AI31" s="348"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7415,18 +7415,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="250" t="s">
+      <c r="T32" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="251"/>
-      <c r="V32" s="251"/>
-      <c r="W32" s="251"/>
-      <c r="X32" s="251"/>
-      <c r="Y32" s="251"/>
-      <c r="Z32" s="251"/>
-      <c r="AA32" s="251"/>
-      <c r="AB32" s="251"/>
-      <c r="AC32" s="252"/>
+      <c r="U32" s="295"/>
+      <c r="V32" s="295"/>
+      <c r="W32" s="295"/>
+      <c r="X32" s="295"/>
+      <c r="Y32" s="295"/>
+      <c r="Z32" s="295"/>
+      <c r="AA32" s="295"/>
+      <c r="AB32" s="295"/>
+      <c r="AC32" s="296"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7462,31 +7462,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="250" t="s">
+      <c r="T33" s="294" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="251"/>
-      <c r="V33" s="251"/>
-      <c r="W33" s="251"/>
-      <c r="X33" s="251"/>
-      <c r="Y33" s="251"/>
-      <c r="Z33" s="251"/>
-      <c r="AA33" s="251"/>
-      <c r="AB33" s="251"/>
-      <c r="AC33" s="252"/>
+      <c r="U33" s="295"/>
+      <c r="V33" s="295"/>
+      <c r="W33" s="295"/>
+      <c r="X33" s="295"/>
+      <c r="Y33" s="295"/>
+      <c r="Z33" s="295"/>
+      <c r="AA33" s="295"/>
+      <c r="AB33" s="295"/>
+      <c r="AC33" s="296"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="355" t="s">
+      <c r="B34" s="285" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="331" t="s">
+      <c r="C34" s="283" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="333"/>
-      <c r="E34" s="331" t="s">
+      <c r="D34" s="284"/>
+      <c r="E34" s="283" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="333"/>
+      <c r="F34" s="284"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7514,21 +7514,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="250" t="s">
+      <c r="T34" s="294" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="251"/>
-      <c r="V34" s="251"/>
-      <c r="W34" s="251"/>
-      <c r="X34" s="251"/>
-      <c r="Y34" s="251"/>
-      <c r="Z34" s="251"/>
-      <c r="AA34" s="251"/>
-      <c r="AB34" s="251"/>
-      <c r="AC34" s="252"/>
+      <c r="U34" s="295"/>
+      <c r="V34" s="295"/>
+      <c r="W34" s="295"/>
+      <c r="X34" s="295"/>
+      <c r="Y34" s="295"/>
+      <c r="Z34" s="295"/>
+      <c r="AA34" s="295"/>
+      <c r="AB34" s="295"/>
+      <c r="AC34" s="296"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="356"/>
+      <c r="B35" s="286"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7547,18 +7547,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="250" t="s">
+      <c r="T35" s="294" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="251"/>
-      <c r="V35" s="251"/>
-      <c r="W35" s="251"/>
-      <c r="X35" s="251"/>
-      <c r="Y35" s="251"/>
-      <c r="Z35" s="251"/>
-      <c r="AA35" s="251"/>
-      <c r="AB35" s="251"/>
-      <c r="AC35" s="252"/>
+      <c r="U35" s="295"/>
+      <c r="V35" s="295"/>
+      <c r="W35" s="295"/>
+      <c r="X35" s="295"/>
+      <c r="Y35" s="295"/>
+      <c r="Z35" s="295"/>
+      <c r="AA35" s="295"/>
+      <c r="AB35" s="295"/>
+      <c r="AC35" s="296"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7609,18 +7609,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="250" t="s">
+      <c r="T36" s="294" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="251"/>
-      <c r="V36" s="251"/>
-      <c r="W36" s="251"/>
-      <c r="X36" s="251"/>
-      <c r="Y36" s="251"/>
-      <c r="Z36" s="251"/>
-      <c r="AA36" s="251"/>
-      <c r="AB36" s="251"/>
-      <c r="AC36" s="252"/>
+      <c r="U36" s="295"/>
+      <c r="V36" s="295"/>
+      <c r="W36" s="295"/>
+      <c r="X36" s="295"/>
+      <c r="Y36" s="295"/>
+      <c r="Z36" s="295"/>
+      <c r="AA36" s="295"/>
+      <c r="AB36" s="295"/>
+      <c r="AC36" s="296"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7663,18 +7663,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="250" t="s">
+      <c r="T37" s="294" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="251"/>
-      <c r="V37" s="251"/>
-      <c r="W37" s="251"/>
-      <c r="X37" s="251"/>
-      <c r="Y37" s="251"/>
-      <c r="Z37" s="251"/>
-      <c r="AA37" s="251"/>
-      <c r="AB37" s="251"/>
-      <c r="AC37" s="252"/>
+      <c r="U37" s="295"/>
+      <c r="V37" s="295"/>
+      <c r="W37" s="295"/>
+      <c r="X37" s="295"/>
+      <c r="Y37" s="295"/>
+      <c r="Z37" s="295"/>
+      <c r="AA37" s="295"/>
+      <c r="AB37" s="295"/>
+      <c r="AC37" s="296"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7695,21 +7695,21 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="295" t="s">
+      <c r="S38" s="336" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="297" t="s">
+      <c r="T38" s="338" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="298"/>
-      <c r="V38" s="298"/>
-      <c r="W38" s="298"/>
-      <c r="X38" s="298"/>
-      <c r="Y38" s="298"/>
-      <c r="Z38" s="298"/>
-      <c r="AA38" s="298"/>
-      <c r="AB38" s="298"/>
-      <c r="AC38" s="299"/>
+      <c r="U38" s="339"/>
+      <c r="V38" s="339"/>
+      <c r="W38" s="339"/>
+      <c r="X38" s="339"/>
+      <c r="Y38" s="339"/>
+      <c r="Z38" s="339"/>
+      <c r="AA38" s="339"/>
+      <c r="AB38" s="339"/>
+      <c r="AC38" s="340"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7727,26 +7727,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="303" t="s">
+      <c r="G39" s="270" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="246"/>
+      <c r="H39" s="271"/>
+      <c r="I39" s="271"/>
+      <c r="J39" s="272"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="296"/>
-      <c r="T39" s="300"/>
-      <c r="U39" s="301"/>
-      <c r="V39" s="301"/>
-      <c r="W39" s="301"/>
-      <c r="X39" s="301"/>
-      <c r="Y39" s="301"/>
-      <c r="Z39" s="301"/>
-      <c r="AA39" s="301"/>
-      <c r="AB39" s="301"/>
-      <c r="AC39" s="302"/>
+      <c r="S39" s="337"/>
+      <c r="T39" s="341"/>
+      <c r="U39" s="342"/>
+      <c r="V39" s="342"/>
+      <c r="W39" s="342"/>
+      <c r="X39" s="342"/>
+      <c r="Y39" s="342"/>
+      <c r="Z39" s="342"/>
+      <c r="AA39" s="342"/>
+      <c r="AB39" s="342"/>
+      <c r="AC39" s="343"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7764,28 +7764,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="307"/>
-      <c r="H40" s="308"/>
-      <c r="I40" s="308"/>
-      <c r="J40" s="309"/>
+      <c r="G40" s="273"/>
+      <c r="H40" s="274"/>
+      <c r="I40" s="274"/>
+      <c r="J40" s="275"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="250" t="s">
+      <c r="T40" s="294" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="251"/>
-      <c r="V40" s="251"/>
-      <c r="W40" s="251"/>
-      <c r="X40" s="251"/>
-      <c r="Y40" s="251"/>
-      <c r="Z40" s="251"/>
-      <c r="AA40" s="251"/>
-      <c r="AB40" s="251"/>
-      <c r="AC40" s="252"/>
+      <c r="U40" s="295"/>
+      <c r="V40" s="295"/>
+      <c r="W40" s="295"/>
+      <c r="X40" s="295"/>
+      <c r="Y40" s="295"/>
+      <c r="Z40" s="295"/>
+      <c r="AA40" s="295"/>
+      <c r="AB40" s="295"/>
+      <c r="AC40" s="296"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7803,28 +7803,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="307"/>
-      <c r="H41" s="308"/>
-      <c r="I41" s="308"/>
-      <c r="J41" s="309"/>
+      <c r="G41" s="273"/>
+      <c r="H41" s="274"/>
+      <c r="I41" s="274"/>
+      <c r="J41" s="275"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="250" t="s">
+      <c r="T41" s="294" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="251"/>
-      <c r="V41" s="251"/>
-      <c r="W41" s="251"/>
-      <c r="X41" s="251"/>
-      <c r="Y41" s="251"/>
-      <c r="Z41" s="251"/>
-      <c r="AA41" s="251"/>
-      <c r="AB41" s="251"/>
-      <c r="AC41" s="252"/>
+      <c r="U41" s="295"/>
+      <c r="V41" s="295"/>
+      <c r="W41" s="295"/>
+      <c r="X41" s="295"/>
+      <c r="Y41" s="295"/>
+      <c r="Z41" s="295"/>
+      <c r="AA41" s="295"/>
+      <c r="AB41" s="295"/>
+      <c r="AC41" s="296"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7842,28 +7842,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="304"/>
-      <c r="H42" s="305"/>
-      <c r="I42" s="305"/>
-      <c r="J42" s="306"/>
+      <c r="G42" s="276"/>
+      <c r="H42" s="277"/>
+      <c r="I42" s="277"/>
+      <c r="J42" s="278"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="250" t="s">
+      <c r="T42" s="294" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="251"/>
-      <c r="V42" s="251"/>
-      <c r="W42" s="251"/>
-      <c r="X42" s="251"/>
-      <c r="Y42" s="251"/>
-      <c r="Z42" s="251"/>
-      <c r="AA42" s="251"/>
-      <c r="AB42" s="251"/>
-      <c r="AC42" s="252"/>
+      <c r="U42" s="295"/>
+      <c r="V42" s="295"/>
+      <c r="W42" s="295"/>
+      <c r="X42" s="295"/>
+      <c r="Y42" s="295"/>
+      <c r="Z42" s="295"/>
+      <c r="AA42" s="295"/>
+      <c r="AB42" s="295"/>
+      <c r="AC42" s="296"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7881,30 +7881,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="268" t="s">
+      <c r="G43" s="241" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="269"/>
-      <c r="I43" s="269"/>
-      <c r="J43" s="270"/>
+      <c r="H43" s="267"/>
+      <c r="I43" s="267"/>
+      <c r="J43" s="242"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="250" t="s">
+      <c r="T43" s="294" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="251"/>
-      <c r="V43" s="251"/>
-      <c r="W43" s="251"/>
-      <c r="X43" s="251"/>
-      <c r="Y43" s="251"/>
-      <c r="Z43" s="251"/>
-      <c r="AA43" s="251"/>
-      <c r="AB43" s="251"/>
-      <c r="AC43" s="252"/>
+      <c r="U43" s="295"/>
+      <c r="V43" s="295"/>
+      <c r="W43" s="295"/>
+      <c r="X43" s="295"/>
+      <c r="Y43" s="295"/>
+      <c r="Z43" s="295"/>
+      <c r="AA43" s="295"/>
+      <c r="AB43" s="295"/>
+      <c r="AC43" s="296"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7925,21 +7925,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="295" t="s">
+      <c r="S44" s="336" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="297" t="s">
+      <c r="T44" s="338" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="298"/>
-      <c r="V44" s="298"/>
-      <c r="W44" s="298"/>
-      <c r="X44" s="298"/>
-      <c r="Y44" s="298"/>
-      <c r="Z44" s="298"/>
-      <c r="AA44" s="298"/>
-      <c r="AB44" s="298"/>
-      <c r="AC44" s="299"/>
+      <c r="U44" s="339"/>
+      <c r="V44" s="339"/>
+      <c r="W44" s="339"/>
+      <c r="X44" s="339"/>
+      <c r="Y44" s="339"/>
+      <c r="Z44" s="339"/>
+      <c r="AA44" s="339"/>
+      <c r="AB44" s="339"/>
+      <c r="AC44" s="340"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -7957,26 +7957,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="303" t="s">
+      <c r="G45" s="270" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="245"/>
-      <c r="I45" s="245"/>
-      <c r="J45" s="246"/>
+      <c r="H45" s="271"/>
+      <c r="I45" s="271"/>
+      <c r="J45" s="272"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="296"/>
-      <c r="T45" s="300"/>
-      <c r="U45" s="301"/>
-      <c r="V45" s="301"/>
-      <c r="W45" s="301"/>
-      <c r="X45" s="301"/>
-      <c r="Y45" s="301"/>
-      <c r="Z45" s="301"/>
-      <c r="AA45" s="301"/>
-      <c r="AB45" s="301"/>
-      <c r="AC45" s="302"/>
+      <c r="S45" s="337"/>
+      <c r="T45" s="341"/>
+      <c r="U45" s="342"/>
+      <c r="V45" s="342"/>
+      <c r="W45" s="342"/>
+      <c r="X45" s="342"/>
+      <c r="Y45" s="342"/>
+      <c r="Z45" s="342"/>
+      <c r="AA45" s="342"/>
+      <c r="AB45" s="342"/>
+      <c r="AC45" s="343"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -7994,28 +7994,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="304"/>
-      <c r="H46" s="305"/>
-      <c r="I46" s="305"/>
-      <c r="J46" s="306"/>
+      <c r="G46" s="276"/>
+      <c r="H46" s="277"/>
+      <c r="I46" s="277"/>
+      <c r="J46" s="278"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="247" t="s">
+      <c r="T46" s="314" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="248"/>
-      <c r="V46" s="248"/>
-      <c r="W46" s="248"/>
-      <c r="X46" s="248"/>
-      <c r="Y46" s="248"/>
-      <c r="Z46" s="248"/>
-      <c r="AA46" s="248"/>
-      <c r="AB46" s="248"/>
-      <c r="AC46" s="249"/>
+      <c r="U46" s="315"/>
+      <c r="V46" s="315"/>
+      <c r="W46" s="315"/>
+      <c r="X46" s="315"/>
+      <c r="Y46" s="315"/>
+      <c r="Z46" s="315"/>
+      <c r="AA46" s="315"/>
+      <c r="AB46" s="315"/>
+      <c r="AC46" s="316"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8033,12 +8033,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="269" t="s">
+      <c r="G47" s="267" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="269"/>
-      <c r="I47" s="269"/>
-      <c r="J47" s="270"/>
+      <c r="H47" s="267"/>
+      <c r="I47" s="267"/>
+      <c r="J47" s="242"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8083,11 +8083,11 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="368" t="s">
+      <c r="AA48" s="235" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="369"/>
-      <c r="AC48" s="370"/>
+      <c r="AB48" s="236"/>
+      <c r="AC48" s="237"/>
     </row>
     <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
@@ -8105,12 +8105,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="303" t="s">
+      <c r="G49" s="270" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="245"/>
-      <c r="I49" s="245"/>
-      <c r="J49" s="246"/>
+      <c r="H49" s="271"/>
+      <c r="I49" s="271"/>
+      <c r="J49" s="272"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8126,9 +8126,9 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="371"/>
-      <c r="AB49" s="372"/>
-      <c r="AC49" s="373"/>
+      <c r="AA49" s="238"/>
+      <c r="AB49" s="239"/>
+      <c r="AC49" s="240"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
@@ -8146,10 +8146,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="307"/>
-      <c r="H50" s="308"/>
-      <c r="I50" s="308"/>
-      <c r="J50" s="309"/>
+      <c r="G50" s="273"/>
+      <c r="H50" s="274"/>
+      <c r="I50" s="274"/>
+      <c r="J50" s="275"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8167,35 +8167,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="304"/>
-      <c r="H51" s="305"/>
-      <c r="I51" s="305"/>
-      <c r="J51" s="306"/>
-      <c r="R51" s="365" t="s">
+      <c r="G51" s="276"/>
+      <c r="H51" s="277"/>
+      <c r="I51" s="277"/>
+      <c r="J51" s="278"/>
+      <c r="R51" s="255" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="349" t="s">
+      <c r="S51" s="257" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="361" t="s">
+      <c r="T51" s="259" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="361"/>
-      <c r="V51" s="362"/>
+      <c r="U51" s="259"/>
+      <c r="V51" s="260"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="287" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="244"/>
-      <c r="R52" s="385"/>
-      <c r="S52" s="350"/>
-      <c r="T52" s="363"/>
-      <c r="U52" s="363"/>
-      <c r="V52" s="364"/>
+      <c r="C52" s="288"/>
+      <c r="D52" s="288"/>
+      <c r="E52" s="288"/>
+      <c r="F52" s="289"/>
+      <c r="R52" s="256"/>
+      <c r="S52" s="258"/>
+      <c r="T52" s="261"/>
+      <c r="U52" s="261"/>
+      <c r="V52" s="262"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8204,67 +8204,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="380" t="s">
+      <c r="T53" s="250" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="380"/>
-      <c r="V53" s="381"/>
+      <c r="U53" s="250"/>
+      <c r="V53" s="251"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="351" t="s">
+      <c r="B54" s="281" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="349" t="s">
+      <c r="C54" s="257" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="361" t="s">
+      <c r="D54" s="259" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="362"/>
-      <c r="H54" s="365" t="s">
+      <c r="E54" s="260"/>
+      <c r="H54" s="255" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="349" t="s">
+      <c r="I54" s="257" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="374" t="s">
+      <c r="J54" s="243" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="375"/>
-      <c r="L54" s="376"/>
+      <c r="K54" s="244"/>
+      <c r="L54" s="245"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="386" t="s">
+      <c r="T54" s="263" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="386"/>
-      <c r="V54" s="354"/>
+      <c r="U54" s="263"/>
+      <c r="V54" s="264"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="352"/>
-      <c r="C55" s="350"/>
-      <c r="D55" s="363"/>
-      <c r="E55" s="364"/>
-      <c r="H55" s="366"/>
-      <c r="I55" s="367"/>
-      <c r="J55" s="340"/>
-      <c r="K55" s="377"/>
-      <c r="L55" s="378"/>
+      <c r="B55" s="282"/>
+      <c r="C55" s="258"/>
+      <c r="D55" s="261"/>
+      <c r="E55" s="262"/>
+      <c r="H55" s="279"/>
+      <c r="I55" s="280"/>
+      <c r="J55" s="246"/>
+      <c r="K55" s="247"/>
+      <c r="L55" s="248"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="386" t="s">
+      <c r="T55" s="263" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="386"/>
-      <c r="V55" s="354"/>
+      <c r="U55" s="263"/>
+      <c r="V55" s="264"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8273,36 +8273,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="253" t="s">
+      <c r="D56" s="268" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="255"/>
+      <c r="E56" s="269"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="379" t="s">
+      <c r="J56" s="249" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="380"/>
-      <c r="L56" s="381"/>
-      <c r="M56" s="268" t="s">
+      <c r="K56" s="250"/>
+      <c r="L56" s="251"/>
+      <c r="M56" s="241" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="270"/>
+      <c r="N56" s="242"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="386" t="s">
+      <c r="T56" s="263" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="386"/>
-      <c r="V56" s="354"/>
+      <c r="U56" s="263"/>
+      <c r="V56" s="264"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8311,36 +8311,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="353" t="s">
+      <c r="D57" s="265" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="354"/>
-      <c r="F57" s="268" t="s">
+      <c r="E57" s="264"/>
+      <c r="F57" s="241" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="270"/>
+      <c r="G57" s="242"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="382" t="s">
+      <c r="J57" s="252" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="383"/>
-      <c r="L57" s="384"/>
+      <c r="K57" s="253"/>
+      <c r="L57" s="254"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="386" t="s">
+      <c r="T57" s="263" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="386"/>
-      <c r="V57" s="354"/>
+      <c r="U57" s="263"/>
+      <c r="V57" s="264"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8349,32 +8349,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="353" t="s">
+      <c r="D58" s="265" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="354"/>
+      <c r="E58" s="264"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="382" t="s">
+      <c r="J58" s="252" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="383"/>
-      <c r="L58" s="384"/>
+      <c r="K58" s="253"/>
+      <c r="L58" s="254"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="386" t="s">
+      <c r="T58" s="263" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="386"/>
-      <c r="V58" s="354"/>
+      <c r="U58" s="263"/>
+      <c r="V58" s="264"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8383,32 +8383,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="353" t="s">
+      <c r="D59" s="265" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="354"/>
+      <c r="E59" s="264"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="382" t="s">
+      <c r="J59" s="252" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="383"/>
-      <c r="L59" s="384"/>
+      <c r="K59" s="253"/>
+      <c r="L59" s="254"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="386" t="s">
+      <c r="T59" s="263" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="386"/>
-      <c r="V59" s="354"/>
+      <c r="U59" s="263"/>
+      <c r="V59" s="264"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8418,32 +8418,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="353" t="s">
+      <c r="D60" s="265" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="354"/>
+      <c r="E60" s="264"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="382" t="s">
+      <c r="J60" s="252" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="383"/>
-      <c r="L60" s="384"/>
+      <c r="K60" s="253"/>
+      <c r="L60" s="254"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="386" t="s">
+      <c r="T60" s="263" t="s">
         <v>461</v>
       </c>
-      <c r="U60" s="386"/>
-      <c r="V60" s="354"/>
+      <c r="U60" s="263"/>
+      <c r="V60" s="264"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8452,101 +8452,101 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="353" t="s">
+      <c r="D61" s="265" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="354"/>
+      <c r="E61" s="264"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="382"/>
-      <c r="K61" s="383"/>
-      <c r="L61" s="384"/>
+      <c r="J61" s="252"/>
+      <c r="K61" s="253"/>
+      <c r="L61" s="254"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="386"/>
-      <c r="U61" s="386"/>
-      <c r="V61" s="354"/>
+      <c r="T61" s="263"/>
+      <c r="U61" s="263"/>
+      <c r="V61" s="264"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="353"/>
-      <c r="E62" s="354"/>
+      <c r="D62" s="265"/>
+      <c r="E62" s="264"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="382"/>
-      <c r="K62" s="383"/>
-      <c r="L62" s="384"/>
+      <c r="J62" s="252"/>
+      <c r="K62" s="253"/>
+      <c r="L62" s="254"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="386"/>
-      <c r="U62" s="386"/>
-      <c r="V62" s="354"/>
+      <c r="T62" s="263"/>
+      <c r="U62" s="263"/>
+      <c r="V62" s="264"/>
     </row>
     <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="353"/>
-      <c r="E63" s="354"/>
+      <c r="D63" s="265"/>
+      <c r="E63" s="264"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="382"/>
-      <c r="K63" s="383"/>
-      <c r="L63" s="384"/>
+      <c r="J63" s="252"/>
+      <c r="K63" s="253"/>
+      <c r="L63" s="254"/>
       <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
       <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="386"/>
-      <c r="U63" s="386"/>
-      <c r="V63" s="354"/>
+      <c r="T63" s="263"/>
+      <c r="U63" s="263"/>
+      <c r="V63" s="264"/>
     </row>
     <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="353"/>
-      <c r="E64" s="354"/>
+      <c r="D64" s="265"/>
+      <c r="E64" s="264"/>
       <c r="R64" s="163" t="s">
         <v>458</v>
       </c>
       <c r="S64" s="161" t="s">
         <v>459</v>
       </c>
-      <c r="T64" s="424" t="s">
+      <c r="T64" s="233" t="s">
         <v>460</v>
       </c>
-      <c r="U64" s="424"/>
-      <c r="V64" s="360"/>
+      <c r="U64" s="233"/>
+      <c r="V64" s="234"/>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="353"/>
-      <c r="E65" s="354"/>
+      <c r="D65" s="265"/>
+      <c r="E65" s="264"/>
       <c r="T65" s="166"/>
     </row>
     <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8554,96 +8554,172 @@
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="353"/>
-      <c r="E66" s="354"/>
+      <c r="D66" s="265"/>
+      <c r="E66" s="264"/>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="353"/>
-      <c r="E67" s="354"/>
+      <c r="D67" s="265"/>
+      <c r="E67" s="264"/>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="353"/>
-      <c r="E68" s="354"/>
+      <c r="D68" s="265"/>
+      <c r="E68" s="264"/>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="353"/>
-      <c r="E69" s="354"/>
+      <c r="D69" s="265"/>
+      <c r="E69" s="264"/>
     </row>
     <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="353"/>
-      <c r="E70" s="354"/>
+      <c r="D70" s="265"/>
+      <c r="E70" s="264"/>
     </row>
     <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="359"/>
-      <c r="E71" s="360"/>
+      <c r="D71" s="266"/>
+      <c r="E71" s="234"/>
     </row>
     <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="T64:V64"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="D57:E57"/>
@@ -8668,126 +8744,50 @@
     <mergeCell ref="N20:P20"/>
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8805,7 +8805,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
@@ -8842,35 +8842,35 @@
       <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="G2" s="245" t="s">
+      <c r="G2" s="271" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="245"/>
-      <c r="I2" s="245"/>
-      <c r="J2" s="246"/>
-      <c r="L2" s="259" t="s">
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="L2" s="357" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="261"/>
+      <c r="M2" s="358"/>
+      <c r="N2" s="358"/>
+      <c r="O2" s="359"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="262" t="s">
+      <c r="Q2" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
+      <c r="R2" s="361"/>
+      <c r="S2" s="361"/>
+      <c r="T2" s="362"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="256" t="s">
+      <c r="V2" s="354" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="257"/>
-      <c r="X2" s="257"/>
-      <c r="Y2" s="257"/>
-      <c r="Z2" s="257"/>
-      <c r="AA2" s="257"/>
-      <c r="AB2" s="258"/>
+      <c r="W2" s="355"/>
+      <c r="X2" s="355"/>
+      <c r="Y2" s="355"/>
+      <c r="Z2" s="355"/>
+      <c r="AA2" s="355"/>
+      <c r="AB2" s="356"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
@@ -8891,11 +8891,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="253" t="s">
+      <c r="H3" s="268" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="255"/>
+      <c r="I3" s="310"/>
+      <c r="J3" s="269"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8934,11 +8934,11 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="277" t="s">
+      <c r="Z3" s="370" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="278"/>
-      <c r="AB3" s="279"/>
+      <c r="AA3" s="371"/>
+      <c r="AB3" s="372"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
@@ -8959,11 +8959,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="250">
+      <c r="H4" s="294">
         <v>63</v>
       </c>
-      <c r="I4" s="251"/>
-      <c r="J4" s="252"/>
+      <c r="I4" s="295"/>
+      <c r="J4" s="296"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9002,11 +9002,11 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="280" t="s">
+      <c r="Z4" s="373" t="s">
         <v>421</v>
       </c>
-      <c r="AA4" s="281"/>
-      <c r="AB4" s="282"/>
+      <c r="AA4" s="374"/>
+      <c r="AB4" s="375"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
@@ -9027,11 +9027,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="250">
+      <c r="H5" s="294">
         <v>31</v>
       </c>
-      <c r="I5" s="251"/>
-      <c r="J5" s="252"/>
+      <c r="I5" s="295"/>
+      <c r="J5" s="296"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9070,9 +9070,9 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="280"/>
-      <c r="AA5" s="281"/>
-      <c r="AB5" s="282"/>
+      <c r="Z5" s="373"/>
+      <c r="AA5" s="374"/>
+      <c r="AB5" s="375"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
@@ -9093,11 +9093,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="247">
+      <c r="H6" s="314">
         <v>7</v>
       </c>
-      <c r="I6" s="248"/>
-      <c r="J6" s="249"/>
+      <c r="I6" s="315"/>
+      <c r="J6" s="316"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -9136,9 +9136,9 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="283"/>
-      <c r="AA6" s="284"/>
-      <c r="AB6" s="285"/>
+      <c r="Z6" s="376"/>
+      <c r="AA6" s="377"/>
+      <c r="AB6" s="378"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
@@ -9159,12 +9159,12 @@
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="235" t="str">
+      <c r="H7" s="379" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="236"/>
-      <c r="J7" s="237"/>
+      <c r="I7" s="380"/>
+      <c r="J7" s="381"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -9211,18 +9211,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="235" t="str">
+      <c r="H8" s="379" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="236"/>
-      <c r="J8" s="237"/>
-      <c r="L8" s="268" t="s">
+      <c r="I8" s="380"/>
+      <c r="J8" s="381"/>
+      <c r="L8" s="241" t="s">
         <v>417</v>
       </c>
-      <c r="M8" s="269"/>
-      <c r="N8" s="269"/>
-      <c r="O8" s="270"/>
+      <c r="M8" s="267"/>
+      <c r="N8" s="267"/>
+      <c r="O8" s="242"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9240,10 +9240,10 @@
       <c r="V8" s="231" t="s">
         <v>453</v>
       </c>
-      <c r="W8" s="271" t="s">
+      <c r="W8" s="366" t="s">
         <v>454</v>
       </c>
-      <c r="X8" s="272"/>
+      <c r="X8" s="367"/>
       <c r="Y8" s="230"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9283,10 +9283,10 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="273" t="s">
+      <c r="W9" s="368" t="s">
         <v>456</v>
       </c>
-      <c r="X9" s="274"/>
+      <c r="X9" s="369"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
@@ -9317,10 +9317,10 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="275" t="s">
+      <c r="W10" s="352" t="s">
         <v>455</v>
       </c>
-      <c r="X10" s="276"/>
+      <c r="X10" s="353"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
@@ -9347,20 +9347,20 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="265" t="s">
+      <c r="Q11" s="363" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="266"/>
-      <c r="S11" s="266"/>
-      <c r="T11" s="267"/>
+      <c r="R11" s="364"/>
+      <c r="S11" s="364"/>
+      <c r="T11" s="365"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="275" t="s">
+      <c r="W11" s="352" t="s">
         <v>425</v>
       </c>
-      <c r="X11" s="276"/>
+      <c r="X11" s="353"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
@@ -9401,8 +9401,8 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="275"/>
-      <c r="X12" s="276"/>
+      <c r="W12" s="352"/>
+      <c r="X12" s="353"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
@@ -9443,8 +9443,8 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="275"/>
-      <c r="X13" s="276"/>
+      <c r="W13" s="352"/>
+      <c r="X13" s="353"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
@@ -9485,8 +9485,8 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="275"/>
-      <c r="X14" s="276"/>
+      <c r="W14" s="352"/>
+      <c r="X14" s="353"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
@@ -9527,8 +9527,8 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="275"/>
-      <c r="X15" s="276"/>
+      <c r="W15" s="352"/>
+      <c r="X15" s="353"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
@@ -9559,8 +9559,8 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="275"/>
-      <c r="X16" s="276"/>
+      <c r="W16" s="352"/>
+      <c r="X16" s="353"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
@@ -9591,8 +9591,8 @@
       <c r="V17" s="232">
         <v>9</v>
       </c>
-      <c r="W17" s="286"/>
-      <c r="X17" s="287"/>
+      <c r="W17" s="350"/>
+      <c r="X17" s="351"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9611,18 +9611,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="242" t="s">
+      <c r="G19" s="287" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="243"/>
-      <c r="I19" s="243"/>
-      <c r="J19" s="244"/>
+      <c r="H19" s="288"/>
+      <c r="I19" s="288"/>
+      <c r="J19" s="289"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="233" t="s">
+      <c r="C20" s="382" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9634,16 +9634,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="238" t="s">
+      <c r="G20" s="384" t="s">
         <v>457</v>
       </c>
-      <c r="H20" s="239"/>
-      <c r="I20" s="239"/>
-      <c r="J20" s="240"/>
+      <c r="H20" s="385"/>
+      <c r="I20" s="385"/>
+      <c r="J20" s="386"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="241"/>
+      <c r="C21" s="387"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9653,16 +9653,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="235" t="s">
+      <c r="G21" s="379" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="237"/>
+      <c r="H21" s="380"/>
+      <c r="I21" s="380"/>
+      <c r="J21" s="381"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="234"/>
+      <c r="C22" s="383"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9681,7 +9681,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="233" t="s">
+      <c r="C23" s="382" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9700,7 +9700,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="234"/>
+      <c r="C24" s="383"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9719,7 +9719,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="233" t="s">
+      <c r="C25" s="382" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9738,7 +9738,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="234"/>
+      <c r="C26" s="383"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9757,7 +9757,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="382" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9776,7 +9776,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="234"/>
+      <c r="C28" s="383"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9816,7 +9816,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="233" t="s">
+      <c r="C30" s="382" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9835,7 +9835,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="234"/>
+      <c r="C31" s="383"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9854,7 +9854,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="233" t="s">
+      <c r="C32" s="382" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9873,7 +9873,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="234"/>
+      <c r="C33" s="383"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9890,12 +9890,22 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9907,22 +9917,12 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9945,15 +9945,15 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="391" t="s">
+      <c r="B2" s="419" t="s">
         <v>425</v>
       </c>
-      <c r="C2" s="392"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="394"/>
+      <c r="C2" s="420"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
+      <c r="G2" s="421"/>
+      <c r="H2" s="422"/>
     </row>
     <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="194" t="s">
@@ -9971,10 +9971,10 @@
       <c r="F3" s="195" t="s">
         <v>430</v>
       </c>
-      <c r="G3" s="389" t="s">
+      <c r="G3" s="417" t="s">
         <v>429</v>
       </c>
-      <c r="H3" s="390"/>
+      <c r="H3" s="418"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="196">
@@ -9986,10 +9986,10 @@
       <c r="F4" s="223" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="395" t="s">
+      <c r="G4" s="423" t="s">
         <v>436</v>
       </c>
-      <c r="H4" s="396"/>
+      <c r="H4" s="424"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="197">
@@ -10005,10 +10005,10 @@
       <c r="F5" s="224" t="s">
         <v>431</v>
       </c>
-      <c r="G5" s="387" t="s">
+      <c r="G5" s="408" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="388"/>
+      <c r="H5" s="409"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="197">
@@ -10022,10 +10022,10 @@
       <c r="F6" s="224" t="s">
         <v>432</v>
       </c>
-      <c r="G6" s="387" t="s">
+      <c r="G6" s="408" t="s">
         <v>437</v>
       </c>
-      <c r="H6" s="388"/>
+      <c r="H6" s="409"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="197">
@@ -10037,10 +10037,10 @@
       <c r="F7" s="224" t="s">
         <v>433</v>
       </c>
-      <c r="G7" s="387" t="s">
+      <c r="G7" s="408" t="s">
         <v>438</v>
       </c>
-      <c r="H7" s="388"/>
+      <c r="H7" s="409"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="197">
@@ -10056,10 +10056,10 @@
       <c r="F8" s="224" t="s">
         <v>434</v>
       </c>
-      <c r="G8" s="387" t="s">
+      <c r="G8" s="408" t="s">
         <v>444</v>
       </c>
-      <c r="H8" s="388"/>
+      <c r="H8" s="409"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="197">
@@ -10071,8 +10071,8 @@
       <c r="F9" s="225" t="s">
         <v>435</v>
       </c>
-      <c r="G9" s="406"/>
-      <c r="H9" s="407"/>
+      <c r="G9" s="410"/>
+      <c r="H9" s="411"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="197">
@@ -10084,8 +10084,8 @@
       <c r="F10" s="226" t="s">
         <v>435</v>
       </c>
-      <c r="G10" s="406"/>
-      <c r="H10" s="407"/>
+      <c r="G10" s="410"/>
+      <c r="H10" s="411"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="201">
@@ -10097,95 +10097,95 @@
       <c r="F11" s="227" t="s">
         <v>435</v>
       </c>
-      <c r="G11" s="408"/>
-      <c r="H11" s="409"/>
+      <c r="G11" s="412"/>
+      <c r="H11" s="413"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="212" t="s">
         <v>446</v>
       </c>
-      <c r="C13" s="410" t="s">
+      <c r="C13" s="414" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="411"/>
-      <c r="E13" s="412"/>
+      <c r="D13" s="415"/>
+      <c r="E13" s="416"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="213">
         <v>0</v>
       </c>
-      <c r="C14" s="397" t="s">
+      <c r="C14" s="399" t="s">
         <v>451</v>
       </c>
-      <c r="D14" s="398"/>
-      <c r="E14" s="399"/>
+      <c r="D14" s="400"/>
+      <c r="E14" s="401"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="214">
         <v>1</v>
       </c>
-      <c r="C15" s="400" t="s">
+      <c r="C15" s="402" t="s">
         <v>449</v>
       </c>
-      <c r="D15" s="401"/>
-      <c r="E15" s="402"/>
+      <c r="D15" s="403"/>
+      <c r="E15" s="404"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="214">
         <v>2</v>
       </c>
-      <c r="C16" s="415" t="s">
+      <c r="C16" s="390" t="s">
         <v>450</v>
       </c>
-      <c r="D16" s="416"/>
-      <c r="E16" s="417"/>
+      <c r="D16" s="391"/>
+      <c r="E16" s="392"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="214">
         <v>3</v>
       </c>
-      <c r="C17" s="403" t="s">
+      <c r="C17" s="405" t="s">
         <v>452</v>
       </c>
-      <c r="D17" s="404"/>
-      <c r="E17" s="405"/>
+      <c r="D17" s="406"/>
+      <c r="E17" s="407"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="214">
         <v>4</v>
       </c>
-      <c r="C18" s="418"/>
-      <c r="D18" s="419"/>
-      <c r="E18" s="420"/>
+      <c r="C18" s="393"/>
+      <c r="D18" s="394"/>
+      <c r="E18" s="395"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="214">
         <v>5</v>
       </c>
-      <c r="C19" s="418"/>
-      <c r="D19" s="419"/>
-      <c r="E19" s="420"/>
+      <c r="C19" s="393"/>
+      <c r="D19" s="394"/>
+      <c r="E19" s="395"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="214">
         <v>6</v>
       </c>
-      <c r="C20" s="418"/>
-      <c r="D20" s="419"/>
-      <c r="E20" s="420"/>
+      <c r="C20" s="393"/>
+      <c r="D20" s="394"/>
+      <c r="E20" s="395"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="215">
         <v>7</v>
       </c>
-      <c r="C21" s="421"/>
-      <c r="D21" s="422"/>
-      <c r="E21" s="423"/>
+      <c r="C21" s="396"/>
+      <c r="D21" s="397"/>
+      <c r="E21" s="398"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="413" t="s">
+      <c r="B23" s="388" t="s">
         <v>445</v>
       </c>
       <c r="C23" s="211">
@@ -10208,7 +10208,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="414"/>
+      <c r="B24" s="389"/>
       <c r="C24" s="220"/>
       <c r="D24" s="221"/>
       <c r="E24" s="221"/>
@@ -10222,12 +10222,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C17:E17"/>
@@ -10236,12 +10236,12 @@
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FC1EE5-D686-407E-B6CE-219046E28209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2733A860-57C0-4CE3-A1F2-A60B3736D5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="468">
   <si>
     <t>OpCode</t>
   </si>
@@ -2388,6 +2388,24 @@
   </si>
   <si>
     <t xml:space="preserve">Valores que guardan las interrupciones en cola (mapa de bits). </t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Keyboard Controller</t>
+  </si>
+  <si>
+    <t>Cls</t>
+  </si>
+  <si>
+    <t>Limpia el buffer</t>
+  </si>
+  <si>
+    <t>Limpia el estado IRQ</t>
+  </si>
+  <si>
+    <t>Enable Keyboard</t>
   </si>
 </sst>
 </file>
@@ -3495,7 +3513,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="425">
+  <cellXfs count="444">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4147,9 +4165,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4173,12 +4188,414 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4197,12 +4614,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4210,9 +4621,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4239,404 +4647,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4671,84 +4764,46 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -5069,62 +5124,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="311" t="s">
+      <c r="B2" s="324" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="326" t="s">
+      <c r="C2" s="333" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328" t="s">
+      <c r="D2" s="334"/>
+      <c r="E2" s="335" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="328"/>
-      <c r="G2" s="329" t="s">
+      <c r="F2" s="335"/>
+      <c r="G2" s="336" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="328"/>
-      <c r="I2" s="328" t="s">
+      <c r="H2" s="335"/>
+      <c r="I2" s="335" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="328"/>
-      <c r="K2" s="330" t="s">
+      <c r="J2" s="335"/>
+      <c r="K2" s="337" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="328"/>
-      <c r="M2" s="328"/>
-      <c r="N2" s="328"/>
-      <c r="O2" s="328"/>
-      <c r="P2" s="331"/>
-      <c r="R2" s="307" t="s">
+      <c r="L2" s="335"/>
+      <c r="M2" s="335"/>
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="338"/>
+      <c r="R2" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="305" t="s">
+      <c r="S2" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="298" t="s">
+      <c r="T2" s="345" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="299"/>
-      <c r="V2" s="299"/>
-      <c r="W2" s="299"/>
-      <c r="X2" s="299"/>
-      <c r="Y2" s="299"/>
-      <c r="Z2" s="299"/>
-      <c r="AA2" s="299"/>
-      <c r="AB2" s="299" t="s">
+      <c r="U2" s="346"/>
+      <c r="V2" s="346"/>
+      <c r="W2" s="346"/>
+      <c r="X2" s="346"/>
+      <c r="Y2" s="346"/>
+      <c r="Z2" s="346"/>
+      <c r="AA2" s="346"/>
+      <c r="AB2" s="346" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="299"/>
-      <c r="AD2" s="299"/>
-      <c r="AE2" s="299"/>
-      <c r="AF2" s="299"/>
-      <c r="AG2" s="299"/>
-      <c r="AH2" s="299"/>
-      <c r="AI2" s="300"/>
+      <c r="AC2" s="346"/>
+      <c r="AD2" s="346"/>
+      <c r="AE2" s="346"/>
+      <c r="AF2" s="346"/>
+      <c r="AG2" s="346"/>
+      <c r="AH2" s="346"/>
+      <c r="AI2" s="347"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="312"/>
+      <c r="B3" s="325"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5149,21 +5204,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="283"/>
-      <c r="L3" s="325"/>
-      <c r="M3" s="325"/>
-      <c r="N3" s="325"/>
-      <c r="O3" s="325"/>
-      <c r="P3" s="284"/>
-      <c r="R3" s="308"/>
-      <c r="S3" s="246"/>
+      <c r="K3" s="330"/>
+      <c r="L3" s="331"/>
+      <c r="M3" s="331"/>
+      <c r="N3" s="331"/>
+      <c r="O3" s="331"/>
+      <c r="P3" s="332"/>
+      <c r="R3" s="342"/>
+      <c r="S3" s="339"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="335" t="s">
+      <c r="U3" s="311" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="335"/>
+      <c r="V3" s="311"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5176,10 +5231,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="297" t="s">
+      <c r="AA3" s="344" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="297"/>
+      <c r="AB3" s="344"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5203,21 +5258,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="313"/>
+      <c r="B4" s="326"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="301" t="s">
+      <c r="E4" s="312" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="288"/>
-      <c r="G4" s="288"/>
-      <c r="H4" s="288"/>
-      <c r="I4" s="288"/>
-      <c r="J4" s="289"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="243"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5227,20 +5282,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="301" t="s">
+      <c r="N4" s="312" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="288"/>
-      <c r="P4" s="289"/>
-      <c r="R4" s="309"/>
-      <c r="S4" s="306"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="243"/>
+      <c r="R4" s="343"/>
+      <c r="S4" s="340"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="301" t="s">
+      <c r="U4" s="312" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="302"/>
+      <c r="V4" s="313"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5253,10 +5308,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="301" t="s">
+      <c r="AA4" s="312" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="302"/>
+      <c r="AB4" s="313"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5288,22 +5343,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="332"/>
-      <c r="F5" s="333"/>
-      <c r="G5" s="333"/>
-      <c r="H5" s="333"/>
-      <c r="I5" s="333"/>
-      <c r="J5" s="334"/>
+      <c r="E5" s="316"/>
+      <c r="F5" s="317"/>
+      <c r="G5" s="317"/>
+      <c r="H5" s="317"/>
+      <c r="I5" s="317"/>
+      <c r="J5" s="318"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="268" t="s">
+      <c r="N5" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="310"/>
-      <c r="P5" s="269"/>
+      <c r="O5" s="253"/>
+      <c r="P5" s="254"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5313,10 +5368,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="303" t="s">
+      <c r="U5" s="314" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="304"/>
+      <c r="V5" s="315"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5329,10 +5384,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="303" t="s">
+      <c r="AA5" s="314" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="304"/>
+      <c r="AB5" s="315"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5365,11 +5420,11 @@
         <v>00001</v>
       </c>
       <c r="E6" s="323"/>
-      <c r="F6" s="318"/>
-      <c r="G6" s="318"/>
-      <c r="H6" s="318"/>
-      <c r="I6" s="318"/>
-      <c r="J6" s="319"/>
+      <c r="F6" s="320"/>
+      <c r="G6" s="320"/>
+      <c r="H6" s="320"/>
+      <c r="I6" s="320"/>
+      <c r="J6" s="321"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5377,11 +5432,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="294" t="s">
+      <c r="N6" s="249" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="295"/>
-      <c r="P6" s="296"/>
+      <c r="O6" s="250"/>
+      <c r="P6" s="251"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5391,10 +5446,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="290" t="s">
+      <c r="U6" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="291"/>
+      <c r="V6" s="310"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5407,10 +5462,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="290" t="s">
+      <c r="AA6" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="291"/>
+      <c r="AB6" s="310"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5453,9 +5508,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="317"/>
-      <c r="I7" s="318"/>
-      <c r="J7" s="319"/>
+      <c r="H7" s="319"/>
+      <c r="I7" s="320"/>
+      <c r="J7" s="321"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5463,11 +5518,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="294" t="s">
+      <c r="N7" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="295"/>
-      <c r="P7" s="296"/>
+      <c r="O7" s="250"/>
+      <c r="P7" s="251"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5477,10 +5532,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="290" t="s">
+      <c r="U7" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="291"/>
+      <c r="V7" s="310"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5493,10 +5548,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="290" t="s">
+      <c r="AA7" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="291"/>
+      <c r="AB7" s="310"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5539,9 +5594,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="317"/>
-      <c r="I8" s="318"/>
-      <c r="J8" s="319"/>
+      <c r="H8" s="319"/>
+      <c r="I8" s="320"/>
+      <c r="J8" s="321"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5549,11 +5604,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="294" t="s">
+      <c r="N8" s="249" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="295"/>
-      <c r="P8" s="296"/>
+      <c r="O8" s="250"/>
+      <c r="P8" s="251"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5563,10 +5618,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="290" t="s">
+      <c r="U8" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="291"/>
+      <c r="V8" s="310"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5579,10 +5634,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="290" t="s">
+      <c r="AA8" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="291"/>
+      <c r="AB8" s="310"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5625,9 +5680,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="317"/>
-      <c r="I9" s="318"/>
-      <c r="J9" s="319"/>
+      <c r="H9" s="319"/>
+      <c r="I9" s="320"/>
+      <c r="J9" s="321"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5635,11 +5690,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="294" t="s">
+      <c r="N9" s="249" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="295"/>
-      <c r="P9" s="296"/>
+      <c r="O9" s="250"/>
+      <c r="P9" s="251"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5649,10 +5704,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="290" t="s">
+      <c r="U9" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="291"/>
+      <c r="V9" s="310"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5665,10 +5720,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="290" t="s">
+      <c r="AA9" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="291"/>
+      <c r="AB9" s="310"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5711,9 +5766,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="317"/>
-      <c r="I10" s="318"/>
-      <c r="J10" s="319"/>
+      <c r="H10" s="319"/>
+      <c r="I10" s="320"/>
+      <c r="J10" s="321"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5721,11 +5776,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="294" t="s">
+      <c r="N10" s="249" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="295"/>
-      <c r="P10" s="296"/>
+      <c r="O10" s="250"/>
+      <c r="P10" s="251"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5735,10 +5790,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="290" t="s">
+      <c r="U10" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="291"/>
+      <c r="V10" s="310"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5751,10 +5806,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="290" t="s">
+      <c r="AA10" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="291"/>
+      <c r="AB10" s="310"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5797,9 +5852,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="317"/>
-      <c r="I11" s="318"/>
-      <c r="J11" s="319"/>
+      <c r="H11" s="319"/>
+      <c r="I11" s="320"/>
+      <c r="J11" s="321"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5807,11 +5862,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="294" t="s">
+      <c r="N11" s="249" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="295"/>
-      <c r="P11" s="296"/>
+      <c r="O11" s="250"/>
+      <c r="P11" s="251"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5821,10 +5876,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="290" t="s">
+      <c r="U11" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="291"/>
+      <c r="V11" s="310"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5837,10 +5892,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="290" t="s">
+      <c r="AA11" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="291"/>
+      <c r="AB11" s="310"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5883,9 +5938,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="317"/>
-      <c r="I12" s="318"/>
-      <c r="J12" s="319"/>
+      <c r="H12" s="319"/>
+      <c r="I12" s="320"/>
+      <c r="J12" s="321"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5893,11 +5948,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="294" t="s">
+      <c r="N12" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="295"/>
-      <c r="P12" s="296"/>
+      <c r="O12" s="250"/>
+      <c r="P12" s="251"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5907,10 +5962,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="290" t="s">
+      <c r="U12" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="291"/>
+      <c r="V12" s="310"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5923,10 +5978,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="290" t="s">
+      <c r="AA12" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="291"/>
+      <c r="AB12" s="310"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -5969,9 +6024,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="317"/>
-      <c r="I13" s="318"/>
-      <c r="J13" s="319"/>
+      <c r="H13" s="319"/>
+      <c r="I13" s="320"/>
+      <c r="J13" s="321"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -5979,11 +6034,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="294" t="s">
+      <c r="N13" s="249" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="295"/>
-      <c r="P13" s="296"/>
+      <c r="O13" s="250"/>
+      <c r="P13" s="251"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -5993,10 +6048,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="290" t="s">
+      <c r="U13" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="291"/>
+      <c r="V13" s="310"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6009,10 +6064,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="290" t="s">
+      <c r="AA13" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="291"/>
+      <c r="AB13" s="310"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6055,9 +6110,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="317"/>
-      <c r="I14" s="318"/>
-      <c r="J14" s="319"/>
+      <c r="H14" s="319"/>
+      <c r="I14" s="320"/>
+      <c r="J14" s="321"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6065,11 +6120,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="294" t="s">
+      <c r="N14" s="249" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="295"/>
-      <c r="P14" s="296"/>
+      <c r="O14" s="250"/>
+      <c r="P14" s="251"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6079,10 +6134,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="290" t="s">
+      <c r="U14" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="291"/>
+      <c r="V14" s="310"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6095,10 +6150,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="290" t="s">
+      <c r="AA14" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="291"/>
+      <c r="AB14" s="310"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6141,9 +6196,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="317"/>
-      <c r="I15" s="318"/>
-      <c r="J15" s="319"/>
+      <c r="H15" s="319"/>
+      <c r="I15" s="320"/>
+      <c r="J15" s="321"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6151,11 +6206,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="294" t="s">
+      <c r="N15" s="249" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="295"/>
-      <c r="P15" s="296"/>
+      <c r="O15" s="250"/>
+      <c r="P15" s="251"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6165,10 +6220,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="290" t="s">
+      <c r="U15" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="291"/>
+      <c r="V15" s="310"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6181,10 +6236,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="290" t="s">
+      <c r="AA15" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="291"/>
+      <c r="AB15" s="310"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6221,21 +6276,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="317"/>
-      <c r="G16" s="318"/>
-      <c r="H16" s="318"/>
-      <c r="I16" s="318"/>
-      <c r="J16" s="319"/>
+      <c r="F16" s="319"/>
+      <c r="G16" s="320"/>
+      <c r="H16" s="320"/>
+      <c r="I16" s="320"/>
+      <c r="J16" s="321"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="294" t="s">
+      <c r="N16" s="249" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="295"/>
-      <c r="P16" s="296"/>
+      <c r="O16" s="250"/>
+      <c r="P16" s="251"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6245,10 +6300,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="290" t="s">
+      <c r="U16" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="291"/>
+      <c r="V16" s="310"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6261,10 +6316,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="290" t="s">
+      <c r="AA16" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="291"/>
+      <c r="AB16" s="310"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6302,22 +6357,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="324" t="s">
+      <c r="G17" s="322" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="295"/>
-      <c r="I17" s="295"/>
-      <c r="J17" s="296"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
+      <c r="J17" s="251"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="294" t="s">
+      <c r="N17" s="249" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="295"/>
-      <c r="P17" s="296"/>
+      <c r="O17" s="250"/>
+      <c r="P17" s="251"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6327,10 +6382,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="290" t="s">
+      <c r="U17" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="291"/>
+      <c r="V17" s="310"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6343,10 +6398,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="290" t="s">
+      <c r="AA17" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="291"/>
+      <c r="AB17" s="310"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6384,12 +6439,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="324" t="s">
+      <c r="G18" s="322" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="295"/>
-      <c r="I18" s="295"/>
-      <c r="J18" s="296"/>
+      <c r="H18" s="250"/>
+      <c r="I18" s="250"/>
+      <c r="J18" s="251"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6397,11 +6452,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="294" t="s">
+      <c r="N18" s="249" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="295"/>
-      <c r="P18" s="296"/>
+      <c r="O18" s="250"/>
+      <c r="P18" s="251"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6411,10 +6466,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="290" t="s">
+      <c r="U18" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="291"/>
+      <c r="V18" s="310"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6427,10 +6482,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="290" t="s">
+      <c r="AA18" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="291"/>
+      <c r="AB18" s="310"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6466,20 +6521,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="317"/>
-      <c r="H19" s="318"/>
-      <c r="I19" s="318"/>
-      <c r="J19" s="319"/>
+      <c r="G19" s="319"/>
+      <c r="H19" s="320"/>
+      <c r="I19" s="320"/>
+      <c r="J19" s="321"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="294" t="s">
+      <c r="N19" s="249" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="295"/>
-      <c r="P19" s="296"/>
+      <c r="O19" s="250"/>
+      <c r="P19" s="251"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6489,10 +6544,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="290" t="s">
+      <c r="U19" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="291"/>
+      <c r="V19" s="310"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6505,10 +6560,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="290" t="s">
+      <c r="AA19" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="291"/>
+      <c r="AB19" s="310"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6546,20 +6601,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="317"/>
-      <c r="H20" s="318"/>
-      <c r="I20" s="318"/>
-      <c r="J20" s="319"/>
+      <c r="G20" s="319"/>
+      <c r="H20" s="320"/>
+      <c r="I20" s="320"/>
+      <c r="J20" s="321"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="294" t="s">
+      <c r="N20" s="249" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="295"/>
-      <c r="P20" s="296"/>
+      <c r="O20" s="250"/>
+      <c r="P20" s="251"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6569,10 +6624,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="290" t="s">
+      <c r="U20" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="291"/>
+      <c r="V20" s="310"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6585,10 +6640,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="290" t="s">
+      <c r="AA20" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="291"/>
+      <c r="AB20" s="310"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6626,20 +6681,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="317"/>
-      <c r="H21" s="318"/>
-      <c r="I21" s="318"/>
-      <c r="J21" s="319"/>
+      <c r="G21" s="319"/>
+      <c r="H21" s="320"/>
+      <c r="I21" s="320"/>
+      <c r="J21" s="321"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="294" t="s">
+      <c r="N21" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="295"/>
-      <c r="P21" s="296"/>
+      <c r="O21" s="250"/>
+      <c r="P21" s="251"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6649,10 +6704,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="290" t="s">
+      <c r="U21" s="309" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="291"/>
+      <c r="V21" s="310"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6665,10 +6720,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="290" t="s">
+      <c r="AA21" s="309" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="291"/>
+      <c r="AB21" s="310"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6703,21 +6758,21 @@
         <v>10001</v>
       </c>
       <c r="E22" s="323"/>
-      <c r="F22" s="318"/>
-      <c r="G22" s="318"/>
-      <c r="H22" s="318"/>
-      <c r="I22" s="318"/>
-      <c r="J22" s="319"/>
+      <c r="F22" s="320"/>
+      <c r="G22" s="320"/>
+      <c r="H22" s="320"/>
+      <c r="I22" s="320"/>
+      <c r="J22" s="321"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="294" t="s">
+      <c r="N22" s="249" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="295"/>
-      <c r="P22" s="296"/>
+      <c r="O22" s="250"/>
+      <c r="P22" s="251"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6727,10 +6782,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="290" t="s">
+      <c r="U22" s="309" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="291"/>
+      <c r="V22" s="310"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6743,10 +6798,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="290" t="s">
+      <c r="AA22" s="309" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="291"/>
+      <c r="AB22" s="310"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6786,22 +6841,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="324" t="s">
+      <c r="G23" s="322" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="295"/>
-      <c r="I23" s="295"/>
-      <c r="J23" s="296"/>
+      <c r="H23" s="250"/>
+      <c r="I23" s="250"/>
+      <c r="J23" s="251"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="294" t="s">
+      <c r="N23" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="295"/>
-      <c r="P23" s="296"/>
+      <c r="O23" s="250"/>
+      <c r="P23" s="251"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6811,10 +6866,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="290" t="s">
+      <c r="U23" s="309" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="291"/>
+      <c r="V23" s="310"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6827,10 +6882,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="290" t="s">
+      <c r="AA23" s="309" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="291"/>
+      <c r="AB23" s="310"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6870,22 +6925,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="324" t="s">
+      <c r="G24" s="322" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="295"/>
-      <c r="I24" s="295"/>
-      <c r="J24" s="296"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="250"/>
+      <c r="J24" s="251"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="294" t="s">
+      <c r="N24" s="249" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="295"/>
-      <c r="P24" s="296"/>
+      <c r="O24" s="250"/>
+      <c r="P24" s="251"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6895,10 +6950,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="290" t="s">
+      <c r="U24" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="291"/>
+      <c r="V24" s="310"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6911,10 +6966,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="290" t="s">
+      <c r="AA24" s="309" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="291"/>
+      <c r="AB24" s="310"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6952,10 +7007,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="317"/>
-      <c r="H25" s="318"/>
-      <c r="I25" s="318"/>
-      <c r="J25" s="319"/>
+      <c r="G25" s="319"/>
+      <c r="H25" s="320"/>
+      <c r="I25" s="320"/>
+      <c r="J25" s="321"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6963,11 +7018,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="294" t="s">
+      <c r="N25" s="249" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="295"/>
-      <c r="P25" s="296"/>
+      <c r="O25" s="250"/>
+      <c r="P25" s="251"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -6977,10 +7032,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="290" t="s">
+      <c r="U25" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="291"/>
+      <c r="V25" s="310"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -6993,10 +7048,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="290" t="s">
+      <c r="AA25" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="291"/>
+      <c r="AB25" s="310"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7034,10 +7089,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="317"/>
-      <c r="H26" s="318"/>
-      <c r="I26" s="318"/>
-      <c r="J26" s="319"/>
+      <c r="G26" s="319"/>
+      <c r="H26" s="320"/>
+      <c r="I26" s="320"/>
+      <c r="J26" s="321"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7045,11 +7100,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="294" t="s">
+      <c r="N26" s="249" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="295"/>
-      <c r="P26" s="296"/>
+      <c r="O26" s="250"/>
+      <c r="P26" s="251"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7059,10 +7114,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="290" t="s">
+      <c r="U26" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="291"/>
+      <c r="V26" s="310"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7075,10 +7130,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="290" t="s">
+      <c r="AA26" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="291"/>
+      <c r="AB26" s="310"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7111,21 +7166,21 @@
         <v>10110</v>
       </c>
       <c r="E27" s="323"/>
-      <c r="F27" s="318"/>
-      <c r="G27" s="318"/>
-      <c r="H27" s="318"/>
-      <c r="I27" s="318"/>
-      <c r="J27" s="319"/>
+      <c r="F27" s="320"/>
+      <c r="G27" s="320"/>
+      <c r="H27" s="320"/>
+      <c r="I27" s="320"/>
+      <c r="J27" s="321"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="294" t="s">
+      <c r="N27" s="249" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="295"/>
-      <c r="P27" s="296"/>
+      <c r="O27" s="250"/>
+      <c r="P27" s="251"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7135,10 +7190,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="290" t="s">
+      <c r="U27" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="291"/>
+      <c r="V27" s="310"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7151,10 +7206,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="290" t="s">
+      <c r="AA27" s="309" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="291"/>
+      <c r="AB27" s="310"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7186,12 +7241,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="320"/>
-      <c r="F28" s="321"/>
-      <c r="G28" s="321"/>
-      <c r="H28" s="321"/>
-      <c r="I28" s="321"/>
-      <c r="J28" s="322"/>
+      <c r="E28" s="327"/>
+      <c r="F28" s="328"/>
+      <c r="G28" s="328"/>
+      <c r="H28" s="328"/>
+      <c r="I28" s="328"/>
+      <c r="J28" s="329"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7199,11 +7254,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="314" t="s">
+      <c r="N28" s="246" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="315"/>
-      <c r="P28" s="316"/>
+      <c r="O28" s="247"/>
+      <c r="P28" s="248"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7213,10 +7268,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="292" t="s">
+      <c r="U28" s="356" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="293"/>
+      <c r="V28" s="357"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7229,10 +7284,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="292" t="s">
+      <c r="AA28" s="356" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="293"/>
+      <c r="AB28" s="357"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7309,27 +7364,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="349" t="s">
+      <c r="T30" s="292" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="349"/>
-      <c r="V30" s="349"/>
-      <c r="W30" s="349"/>
-      <c r="X30" s="349"/>
-      <c r="Y30" s="349"/>
-      <c r="Z30" s="349"/>
-      <c r="AA30" s="349"/>
-      <c r="AB30" s="349"/>
-      <c r="AC30" s="305"/>
-      <c r="AE30" s="287" t="s">
+      <c r="U30" s="292"/>
+      <c r="V30" s="292"/>
+      <c r="W30" s="292"/>
+      <c r="X30" s="292"/>
+      <c r="Y30" s="292"/>
+      <c r="Z30" s="292"/>
+      <c r="AA30" s="292"/>
+      <c r="AB30" s="292"/>
+      <c r="AC30" s="293"/>
+      <c r="AE30" s="241" t="s">
         <v>422</v>
       </c>
-      <c r="AF30" s="288"/>
-      <c r="AG30" s="287" t="s">
+      <c r="AF30" s="242"/>
+      <c r="AG30" s="241" t="s">
         <v>423</v>
       </c>
-      <c r="AH30" s="288"/>
-      <c r="AI30" s="289"/>
+      <c r="AH30" s="242"/>
+      <c r="AI30" s="243"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7370,28 +7425,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="268" t="s">
+      <c r="T31" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="310"/>
-      <c r="V31" s="310"/>
-      <c r="W31" s="310"/>
-      <c r="X31" s="310"/>
-      <c r="Y31" s="310"/>
-      <c r="Z31" s="310"/>
-      <c r="AA31" s="310"/>
-      <c r="AB31" s="310"/>
-      <c r="AC31" s="269"/>
-      <c r="AE31" s="344">
+      <c r="U31" s="253"/>
+      <c r="V31" s="253"/>
+      <c r="W31" s="253"/>
+      <c r="X31" s="253"/>
+      <c r="Y31" s="253"/>
+      <c r="Z31" s="253"/>
+      <c r="AA31" s="253"/>
+      <c r="AB31" s="253"/>
+      <c r="AC31" s="254"/>
+      <c r="AE31" s="287">
         <v>2</v>
       </c>
-      <c r="AF31" s="345"/>
-      <c r="AG31" s="346" t="str" cm="1">
+      <c r="AF31" s="288"/>
+      <c r="AG31" s="289" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="347"/>
-      <c r="AI31" s="348"/>
+      <c r="AH31" s="290"/>
+      <c r="AI31" s="291"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7415,18 +7470,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="294" t="s">
+      <c r="T32" s="249" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="295"/>
-      <c r="V32" s="295"/>
-      <c r="W32" s="295"/>
-      <c r="X32" s="295"/>
-      <c r="Y32" s="295"/>
-      <c r="Z32" s="295"/>
-      <c r="AA32" s="295"/>
-      <c r="AB32" s="295"/>
-      <c r="AC32" s="296"/>
+      <c r="U32" s="250"/>
+      <c r="V32" s="250"/>
+      <c r="W32" s="250"/>
+      <c r="X32" s="250"/>
+      <c r="Y32" s="250"/>
+      <c r="Z32" s="250"/>
+      <c r="AA32" s="250"/>
+      <c r="AB32" s="250"/>
+      <c r="AC32" s="251"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7462,31 +7517,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="294" t="s">
+      <c r="T33" s="249" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="295"/>
-      <c r="V33" s="295"/>
-      <c r="W33" s="295"/>
-      <c r="X33" s="295"/>
-      <c r="Y33" s="295"/>
-      <c r="Z33" s="295"/>
-      <c r="AA33" s="295"/>
-      <c r="AB33" s="295"/>
-      <c r="AC33" s="296"/>
+      <c r="U33" s="250"/>
+      <c r="V33" s="250"/>
+      <c r="W33" s="250"/>
+      <c r="X33" s="250"/>
+      <c r="Y33" s="250"/>
+      <c r="Z33" s="250"/>
+      <c r="AA33" s="250"/>
+      <c r="AB33" s="250"/>
+      <c r="AC33" s="251"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="285" t="s">
+      <c r="B34" s="354" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="283" t="s">
+      <c r="C34" s="330" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="284"/>
-      <c r="E34" s="283" t="s">
+      <c r="D34" s="332"/>
+      <c r="E34" s="330" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="284"/>
+      <c r="F34" s="332"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7514,21 +7569,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="294" t="s">
+      <c r="T34" s="249" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="295"/>
-      <c r="V34" s="295"/>
-      <c r="W34" s="295"/>
-      <c r="X34" s="295"/>
-      <c r="Y34" s="295"/>
-      <c r="Z34" s="295"/>
-      <c r="AA34" s="295"/>
-      <c r="AB34" s="295"/>
-      <c r="AC34" s="296"/>
+      <c r="U34" s="250"/>
+      <c r="V34" s="250"/>
+      <c r="W34" s="250"/>
+      <c r="X34" s="250"/>
+      <c r="Y34" s="250"/>
+      <c r="Z34" s="250"/>
+      <c r="AA34" s="250"/>
+      <c r="AB34" s="250"/>
+      <c r="AC34" s="251"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="286"/>
+      <c r="B35" s="355"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7547,18 +7602,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="294" t="s">
+      <c r="T35" s="249" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="295"/>
-      <c r="V35" s="295"/>
-      <c r="W35" s="295"/>
-      <c r="X35" s="295"/>
-      <c r="Y35" s="295"/>
-      <c r="Z35" s="295"/>
-      <c r="AA35" s="295"/>
-      <c r="AB35" s="295"/>
-      <c r="AC35" s="296"/>
+      <c r="U35" s="250"/>
+      <c r="V35" s="250"/>
+      <c r="W35" s="250"/>
+      <c r="X35" s="250"/>
+      <c r="Y35" s="250"/>
+      <c r="Z35" s="250"/>
+      <c r="AA35" s="250"/>
+      <c r="AB35" s="250"/>
+      <c r="AC35" s="251"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7609,18 +7664,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="294" t="s">
+      <c r="T36" s="249" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="295"/>
-      <c r="V36" s="295"/>
-      <c r="W36" s="295"/>
-      <c r="X36" s="295"/>
-      <c r="Y36" s="295"/>
-      <c r="Z36" s="295"/>
-      <c r="AA36" s="295"/>
-      <c r="AB36" s="295"/>
-      <c r="AC36" s="296"/>
+      <c r="U36" s="250"/>
+      <c r="V36" s="250"/>
+      <c r="W36" s="250"/>
+      <c r="X36" s="250"/>
+      <c r="Y36" s="250"/>
+      <c r="Z36" s="250"/>
+      <c r="AA36" s="250"/>
+      <c r="AB36" s="250"/>
+      <c r="AC36" s="251"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7663,18 +7718,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="294" t="s">
+      <c r="T37" s="249" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="295"/>
-      <c r="V37" s="295"/>
-      <c r="W37" s="295"/>
-      <c r="X37" s="295"/>
-      <c r="Y37" s="295"/>
-      <c r="Z37" s="295"/>
-      <c r="AA37" s="295"/>
-      <c r="AB37" s="295"/>
-      <c r="AC37" s="296"/>
+      <c r="U37" s="250"/>
+      <c r="V37" s="250"/>
+      <c r="W37" s="250"/>
+      <c r="X37" s="250"/>
+      <c r="Y37" s="250"/>
+      <c r="Z37" s="250"/>
+      <c r="AA37" s="250"/>
+      <c r="AB37" s="250"/>
+      <c r="AC37" s="251"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7695,21 +7750,21 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="336" t="s">
+      <c r="S38" s="294" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="338" t="s">
+      <c r="T38" s="296" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="339"/>
-      <c r="V38" s="339"/>
-      <c r="W38" s="339"/>
-      <c r="X38" s="339"/>
-      <c r="Y38" s="339"/>
-      <c r="Z38" s="339"/>
-      <c r="AA38" s="339"/>
-      <c r="AB38" s="339"/>
-      <c r="AC38" s="340"/>
+      <c r="U38" s="297"/>
+      <c r="V38" s="297"/>
+      <c r="W38" s="297"/>
+      <c r="X38" s="297"/>
+      <c r="Y38" s="297"/>
+      <c r="Z38" s="297"/>
+      <c r="AA38" s="297"/>
+      <c r="AB38" s="297"/>
+      <c r="AC38" s="298"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7727,26 +7782,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="270" t="s">
+      <c r="G39" s="302" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="271"/>
-      <c r="I39" s="271"/>
-      <c r="J39" s="272"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="245"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="337"/>
-      <c r="T39" s="341"/>
-      <c r="U39" s="342"/>
-      <c r="V39" s="342"/>
-      <c r="W39" s="342"/>
-      <c r="X39" s="342"/>
-      <c r="Y39" s="342"/>
-      <c r="Z39" s="342"/>
-      <c r="AA39" s="342"/>
-      <c r="AB39" s="342"/>
-      <c r="AC39" s="343"/>
+      <c r="S39" s="295"/>
+      <c r="T39" s="299"/>
+      <c r="U39" s="300"/>
+      <c r="V39" s="300"/>
+      <c r="W39" s="300"/>
+      <c r="X39" s="300"/>
+      <c r="Y39" s="300"/>
+      <c r="Z39" s="300"/>
+      <c r="AA39" s="300"/>
+      <c r="AB39" s="300"/>
+      <c r="AC39" s="301"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7764,28 +7819,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="273"/>
-      <c r="H40" s="274"/>
-      <c r="I40" s="274"/>
-      <c r="J40" s="275"/>
+      <c r="G40" s="306"/>
+      <c r="H40" s="307"/>
+      <c r="I40" s="307"/>
+      <c r="J40" s="308"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="294" t="s">
+      <c r="T40" s="249" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="295"/>
-      <c r="V40" s="295"/>
-      <c r="W40" s="295"/>
-      <c r="X40" s="295"/>
-      <c r="Y40" s="295"/>
-      <c r="Z40" s="295"/>
-      <c r="AA40" s="295"/>
-      <c r="AB40" s="295"/>
-      <c r="AC40" s="296"/>
+      <c r="U40" s="250"/>
+      <c r="V40" s="250"/>
+      <c r="W40" s="250"/>
+      <c r="X40" s="250"/>
+      <c r="Y40" s="250"/>
+      <c r="Z40" s="250"/>
+      <c r="AA40" s="250"/>
+      <c r="AB40" s="250"/>
+      <c r="AC40" s="251"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7803,28 +7858,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="273"/>
-      <c r="H41" s="274"/>
-      <c r="I41" s="274"/>
-      <c r="J41" s="275"/>
+      <c r="G41" s="306"/>
+      <c r="H41" s="307"/>
+      <c r="I41" s="307"/>
+      <c r="J41" s="308"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="294" t="s">
+      <c r="T41" s="249" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="295"/>
-      <c r="V41" s="295"/>
-      <c r="W41" s="295"/>
-      <c r="X41" s="295"/>
-      <c r="Y41" s="295"/>
-      <c r="Z41" s="295"/>
-      <c r="AA41" s="295"/>
-      <c r="AB41" s="295"/>
-      <c r="AC41" s="296"/>
+      <c r="U41" s="250"/>
+      <c r="V41" s="250"/>
+      <c r="W41" s="250"/>
+      <c r="X41" s="250"/>
+      <c r="Y41" s="250"/>
+      <c r="Z41" s="250"/>
+      <c r="AA41" s="250"/>
+      <c r="AB41" s="250"/>
+      <c r="AC41" s="251"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7842,28 +7897,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="276"/>
-      <c r="H42" s="277"/>
-      <c r="I42" s="277"/>
-      <c r="J42" s="278"/>
+      <c r="G42" s="303"/>
+      <c r="H42" s="304"/>
+      <c r="I42" s="304"/>
+      <c r="J42" s="305"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="294" t="s">
+      <c r="T42" s="249" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="295"/>
-      <c r="V42" s="295"/>
-      <c r="W42" s="295"/>
-      <c r="X42" s="295"/>
-      <c r="Y42" s="295"/>
-      <c r="Z42" s="295"/>
-      <c r="AA42" s="295"/>
-      <c r="AB42" s="295"/>
-      <c r="AC42" s="296"/>
+      <c r="U42" s="250"/>
+      <c r="V42" s="250"/>
+      <c r="W42" s="250"/>
+      <c r="X42" s="250"/>
+      <c r="Y42" s="250"/>
+      <c r="Z42" s="250"/>
+      <c r="AA42" s="250"/>
+      <c r="AB42" s="250"/>
+      <c r="AC42" s="251"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7881,30 +7936,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="241" t="s">
+      <c r="G43" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="267"/>
-      <c r="I43" s="267"/>
-      <c r="J43" s="242"/>
+      <c r="H43" s="268"/>
+      <c r="I43" s="268"/>
+      <c r="J43" s="269"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="294" t="s">
+      <c r="T43" s="249" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="295"/>
-      <c r="V43" s="295"/>
-      <c r="W43" s="295"/>
-      <c r="X43" s="295"/>
-      <c r="Y43" s="295"/>
-      <c r="Z43" s="295"/>
-      <c r="AA43" s="295"/>
-      <c r="AB43" s="295"/>
-      <c r="AC43" s="296"/>
+      <c r="U43" s="250"/>
+      <c r="V43" s="250"/>
+      <c r="W43" s="250"/>
+      <c r="X43" s="250"/>
+      <c r="Y43" s="250"/>
+      <c r="Z43" s="250"/>
+      <c r="AA43" s="250"/>
+      <c r="AB43" s="250"/>
+      <c r="AC43" s="251"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7925,21 +7980,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="336" t="s">
+      <c r="S44" s="294" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="338" t="s">
+      <c r="T44" s="296" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="339"/>
-      <c r="V44" s="339"/>
-      <c r="W44" s="339"/>
-      <c r="X44" s="339"/>
-      <c r="Y44" s="339"/>
-      <c r="Z44" s="339"/>
-      <c r="AA44" s="339"/>
-      <c r="AB44" s="339"/>
-      <c r="AC44" s="340"/>
+      <c r="U44" s="297"/>
+      <c r="V44" s="297"/>
+      <c r="W44" s="297"/>
+      <c r="X44" s="297"/>
+      <c r="Y44" s="297"/>
+      <c r="Z44" s="297"/>
+      <c r="AA44" s="297"/>
+      <c r="AB44" s="297"/>
+      <c r="AC44" s="298"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -7957,26 +8012,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="270" t="s">
+      <c r="G45" s="302" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="271"/>
-      <c r="I45" s="271"/>
-      <c r="J45" s="272"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="244"/>
+      <c r="J45" s="245"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="337"/>
-      <c r="T45" s="341"/>
-      <c r="U45" s="342"/>
-      <c r="V45" s="342"/>
-      <c r="W45" s="342"/>
-      <c r="X45" s="342"/>
-      <c r="Y45" s="342"/>
-      <c r="Z45" s="342"/>
-      <c r="AA45" s="342"/>
-      <c r="AB45" s="342"/>
-      <c r="AC45" s="343"/>
+      <c r="S45" s="295"/>
+      <c r="T45" s="299"/>
+      <c r="U45" s="300"/>
+      <c r="V45" s="300"/>
+      <c r="W45" s="300"/>
+      <c r="X45" s="300"/>
+      <c r="Y45" s="300"/>
+      <c r="Z45" s="300"/>
+      <c r="AA45" s="300"/>
+      <c r="AB45" s="300"/>
+      <c r="AC45" s="301"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -7994,28 +8049,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="276"/>
-      <c r="H46" s="277"/>
-      <c r="I46" s="277"/>
-      <c r="J46" s="278"/>
+      <c r="G46" s="303"/>
+      <c r="H46" s="304"/>
+      <c r="I46" s="304"/>
+      <c r="J46" s="305"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="314" t="s">
+      <c r="T46" s="246" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="315"/>
-      <c r="V46" s="315"/>
-      <c r="W46" s="315"/>
-      <c r="X46" s="315"/>
-      <c r="Y46" s="315"/>
-      <c r="Z46" s="315"/>
-      <c r="AA46" s="315"/>
-      <c r="AB46" s="315"/>
-      <c r="AC46" s="316"/>
+      <c r="U46" s="247"/>
+      <c r="V46" s="247"/>
+      <c r="W46" s="247"/>
+      <c r="X46" s="247"/>
+      <c r="Y46" s="247"/>
+      <c r="Z46" s="247"/>
+      <c r="AA46" s="247"/>
+      <c r="AB46" s="247"/>
+      <c r="AC46" s="248"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8033,12 +8088,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="267" t="s">
+      <c r="G47" s="268" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="267"/>
-      <c r="I47" s="267"/>
-      <c r="J47" s="242"/>
+      <c r="H47" s="268"/>
+      <c r="I47" s="268"/>
+      <c r="J47" s="269"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8083,11 +8138,11 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="235" t="s">
+      <c r="AA48" s="368" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="236"/>
-      <c r="AC48" s="237"/>
+      <c r="AB48" s="369"/>
+      <c r="AC48" s="370"/>
     </row>
     <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
@@ -8105,12 +8160,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="270" t="s">
+      <c r="G49" s="302" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
-      <c r="J49" s="272"/>
+      <c r="H49" s="244"/>
+      <c r="I49" s="244"/>
+      <c r="J49" s="245"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8126,9 +8181,9 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="238"/>
-      <c r="AB49" s="239"/>
-      <c r="AC49" s="240"/>
+      <c r="AA49" s="371"/>
+      <c r="AB49" s="372"/>
+      <c r="AC49" s="373"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
@@ -8146,10 +8201,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="273"/>
-      <c r="H50" s="274"/>
-      <c r="I50" s="274"/>
-      <c r="J50" s="275"/>
+      <c r="G50" s="306"/>
+      <c r="H50" s="307"/>
+      <c r="I50" s="307"/>
+      <c r="J50" s="308"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8167,35 +8222,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="276"/>
-      <c r="H51" s="277"/>
-      <c r="I51" s="277"/>
-      <c r="J51" s="278"/>
-      <c r="R51" s="255" t="s">
+      <c r="G51" s="303"/>
+      <c r="H51" s="304"/>
+      <c r="I51" s="304"/>
+      <c r="J51" s="305"/>
+      <c r="R51" s="364" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="257" t="s">
+      <c r="S51" s="348" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="259" t="s">
+      <c r="T51" s="360" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="259"/>
-      <c r="V51" s="260"/>
+      <c r="U51" s="360"/>
+      <c r="V51" s="361"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="287" t="s">
+      <c r="B52" s="241" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="288"/>
-      <c r="D52" s="288"/>
-      <c r="E52" s="288"/>
-      <c r="F52" s="289"/>
-      <c r="R52" s="256"/>
-      <c r="S52" s="258"/>
-      <c r="T52" s="261"/>
-      <c r="U52" s="261"/>
-      <c r="V52" s="262"/>
+      <c r="C52" s="242"/>
+      <c r="D52" s="242"/>
+      <c r="E52" s="242"/>
+      <c r="F52" s="243"/>
+      <c r="R52" s="385"/>
+      <c r="S52" s="349"/>
+      <c r="T52" s="362"/>
+      <c r="U52" s="362"/>
+      <c r="V52" s="363"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8204,67 +8259,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="250" t="s">
+      <c r="T53" s="380" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="250"/>
-      <c r="V53" s="251"/>
+      <c r="U53" s="380"/>
+      <c r="V53" s="381"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="281" t="s">
+      <c r="B54" s="350" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="257" t="s">
+      <c r="C54" s="348" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="259" t="s">
+      <c r="D54" s="360" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="260"/>
-      <c r="H54" s="255" t="s">
+      <c r="E54" s="361"/>
+      <c r="H54" s="364" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="257" t="s">
+      <c r="I54" s="348" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="243" t="s">
+      <c r="J54" s="374" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="244"/>
-      <c r="L54" s="245"/>
+      <c r="K54" s="375"/>
+      <c r="L54" s="376"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="263" t="s">
+      <c r="T54" s="386" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="263"/>
-      <c r="V54" s="264"/>
+      <c r="U54" s="386"/>
+      <c r="V54" s="353"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="282"/>
-      <c r="C55" s="258"/>
-      <c r="D55" s="261"/>
-      <c r="E55" s="262"/>
-      <c r="H55" s="279"/>
-      <c r="I55" s="280"/>
-      <c r="J55" s="246"/>
-      <c r="K55" s="247"/>
-      <c r="L55" s="248"/>
+      <c r="B55" s="351"/>
+      <c r="C55" s="349"/>
+      <c r="D55" s="362"/>
+      <c r="E55" s="363"/>
+      <c r="H55" s="365"/>
+      <c r="I55" s="366"/>
+      <c r="J55" s="339"/>
+      <c r="K55" s="377"/>
+      <c r="L55" s="378"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="263" t="s">
+      <c r="T55" s="386" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="263"/>
-      <c r="V55" s="264"/>
+      <c r="U55" s="386"/>
+      <c r="V55" s="353"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8273,36 +8328,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="268" t="s">
+      <c r="D56" s="252" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="269"/>
+      <c r="E56" s="254"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="249" t="s">
+      <c r="J56" s="379" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="250"/>
-      <c r="L56" s="251"/>
-      <c r="M56" s="241" t="s">
+      <c r="K56" s="380"/>
+      <c r="L56" s="381"/>
+      <c r="M56" s="267" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="242"/>
+      <c r="N56" s="269"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="263" t="s">
+      <c r="T56" s="386" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="263"/>
-      <c r="V56" s="264"/>
+      <c r="U56" s="386"/>
+      <c r="V56" s="353"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8311,36 +8366,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="265" t="s">
+      <c r="D57" s="352" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="264"/>
-      <c r="F57" s="241" t="s">
+      <c r="E57" s="353"/>
+      <c r="F57" s="267" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="242"/>
+      <c r="G57" s="269"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="252" t="s">
+      <c r="J57" s="382" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="253"/>
-      <c r="L57" s="254"/>
+      <c r="K57" s="383"/>
+      <c r="L57" s="384"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="263" t="s">
+      <c r="T57" s="386" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="263"/>
-      <c r="V57" s="264"/>
+      <c r="U57" s="386"/>
+      <c r="V57" s="353"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8349,32 +8404,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="265" t="s">
+      <c r="D58" s="352" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="264"/>
+      <c r="E58" s="353"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="252" t="s">
+      <c r="J58" s="382" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="253"/>
-      <c r="L58" s="254"/>
+      <c r="K58" s="383"/>
+      <c r="L58" s="384"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="263" t="s">
+      <c r="T58" s="386" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="263"/>
-      <c r="V58" s="264"/>
+      <c r="U58" s="386"/>
+      <c r="V58" s="353"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8383,32 +8438,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="265" t="s">
+      <c r="D59" s="352" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="264"/>
+      <c r="E59" s="353"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="252" t="s">
+      <c r="J59" s="382" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="253"/>
-      <c r="L59" s="254"/>
+      <c r="K59" s="383"/>
+      <c r="L59" s="384"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="263" t="s">
+      <c r="T59" s="386" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="263"/>
-      <c r="V59" s="264"/>
+      <c r="U59" s="386"/>
+      <c r="V59" s="353"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8418,32 +8473,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="265" t="s">
+      <c r="D60" s="352" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="264"/>
+      <c r="E60" s="353"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="252" t="s">
+      <c r="J60" s="382" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="253"/>
-      <c r="L60" s="254"/>
+      <c r="K60" s="383"/>
+      <c r="L60" s="384"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="263" t="s">
+      <c r="T60" s="386" t="s">
         <v>461</v>
       </c>
-      <c r="U60" s="263"/>
-      <c r="V60" s="264"/>
+      <c r="U60" s="386"/>
+      <c r="V60" s="353"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8452,101 +8507,101 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="265" t="s">
+      <c r="D61" s="352" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="264"/>
+      <c r="E61" s="353"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="252"/>
-      <c r="K61" s="253"/>
-      <c r="L61" s="254"/>
+      <c r="J61" s="382"/>
+      <c r="K61" s="383"/>
+      <c r="L61" s="384"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="263"/>
-      <c r="U61" s="263"/>
-      <c r="V61" s="264"/>
+      <c r="T61" s="386"/>
+      <c r="U61" s="386"/>
+      <c r="V61" s="353"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="265"/>
-      <c r="E62" s="264"/>
+      <c r="D62" s="352"/>
+      <c r="E62" s="353"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="252"/>
-      <c r="K62" s="253"/>
-      <c r="L62" s="254"/>
+      <c r="J62" s="382"/>
+      <c r="K62" s="383"/>
+      <c r="L62" s="384"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="263"/>
-      <c r="U62" s="263"/>
-      <c r="V62" s="264"/>
+      <c r="T62" s="386"/>
+      <c r="U62" s="386"/>
+      <c r="V62" s="353"/>
     </row>
     <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="265"/>
-      <c r="E63" s="264"/>
+      <c r="D63" s="352"/>
+      <c r="E63" s="353"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="252"/>
-      <c r="K63" s="253"/>
-      <c r="L63" s="254"/>
+      <c r="J63" s="382"/>
+      <c r="K63" s="383"/>
+      <c r="L63" s="384"/>
       <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
       <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="263"/>
-      <c r="U63" s="263"/>
-      <c r="V63" s="264"/>
+      <c r="T63" s="386"/>
+      <c r="U63" s="386"/>
+      <c r="V63" s="353"/>
     </row>
     <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="265"/>
-      <c r="E64" s="264"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="353"/>
       <c r="R64" s="163" t="s">
         <v>458</v>
       </c>
       <c r="S64" s="161" t="s">
         <v>459</v>
       </c>
-      <c r="T64" s="233" t="s">
+      <c r="T64" s="367" t="s">
         <v>460</v>
       </c>
-      <c r="U64" s="233"/>
-      <c r="V64" s="234"/>
+      <c r="U64" s="367"/>
+      <c r="V64" s="359"/>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="265"/>
-      <c r="E65" s="264"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="353"/>
       <c r="T65" s="166"/>
     </row>
     <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8554,76 +8609,192 @@
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="265"/>
-      <c r="E66" s="264"/>
+      <c r="D66" s="352"/>
+      <c r="E66" s="353"/>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="265"/>
-      <c r="E67" s="264"/>
+      <c r="D67" s="352"/>
+      <c r="E67" s="353"/>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="265"/>
-      <c r="E68" s="264"/>
+      <c r="D68" s="352"/>
+      <c r="E68" s="353"/>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="265"/>
-      <c r="E69" s="264"/>
+      <c r="D69" s="352"/>
+      <c r="E69" s="353"/>
     </row>
     <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="265"/>
-      <c r="E70" s="264"/>
+      <c r="D70" s="352"/>
+      <c r="E70" s="353"/>
     </row>
     <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="266"/>
-      <c r="E71" s="234"/>
+      <c r="D71" s="358"/>
+      <c r="E71" s="359"/>
     </row>
     <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
     <mergeCell ref="AA20:AB20"/>
     <mergeCell ref="AA21:AB21"/>
     <mergeCell ref="AA22:AB22"/>
@@ -8648,146 +8819,30 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="T64:V64"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8842,35 +8897,35 @@
       <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="G2" s="271" t="s">
+      <c r="G2" s="244" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="L2" s="357" t="s">
+      <c r="H2" s="244"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="245"/>
+      <c r="L2" s="258" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="358"/>
-      <c r="N2" s="358"/>
-      <c r="O2" s="359"/>
+      <c r="M2" s="259"/>
+      <c r="N2" s="259"/>
+      <c r="O2" s="260"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="360" t="s">
+      <c r="Q2" s="261" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="361"/>
-      <c r="S2" s="361"/>
-      <c r="T2" s="362"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="354" t="s">
+      <c r="V2" s="255" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="355"/>
-      <c r="X2" s="355"/>
-      <c r="Y2" s="355"/>
-      <c r="Z2" s="355"/>
-      <c r="AA2" s="355"/>
-      <c r="AB2" s="356"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="257"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
@@ -8891,11 +8946,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="268" t="s">
+      <c r="H3" s="252" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="310"/>
-      <c r="J3" s="269"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="254"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8934,11 +8989,11 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="370" t="s">
+      <c r="Z3" s="276" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="371"/>
-      <c r="AB3" s="372"/>
+      <c r="AA3" s="277"/>
+      <c r="AB3" s="278"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
@@ -8959,11 +9014,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="249">
         <v>63</v>
       </c>
-      <c r="I4" s="295"/>
-      <c r="J4" s="296"/>
+      <c r="I4" s="250"/>
+      <c r="J4" s="251"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9002,11 +9057,11 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="373" t="s">
+      <c r="Z4" s="279" t="s">
         <v>421</v>
       </c>
-      <c r="AA4" s="374"/>
-      <c r="AB4" s="375"/>
+      <c r="AA4" s="280"/>
+      <c r="AB4" s="281"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
@@ -9027,11 +9082,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="249">
         <v>31</v>
       </c>
-      <c r="I5" s="295"/>
-      <c r="J5" s="296"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="251"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9070,9 +9125,9 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="373"/>
-      <c r="AA5" s="374"/>
-      <c r="AB5" s="375"/>
+      <c r="Z5" s="279"/>
+      <c r="AA5" s="280"/>
+      <c r="AB5" s="281"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
@@ -9093,11 +9148,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="314">
+      <c r="H6" s="246">
         <v>7</v>
       </c>
-      <c r="I6" s="315"/>
-      <c r="J6" s="316"/>
+      <c r="I6" s="247"/>
+      <c r="J6" s="248"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -9136,9 +9191,9 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="376"/>
-      <c r="AA6" s="377"/>
-      <c r="AB6" s="378"/>
+      <c r="Z6" s="282"/>
+      <c r="AA6" s="283"/>
+      <c r="AB6" s="284"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
@@ -9159,12 +9214,12 @@
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="379" t="str">
+      <c r="H7" s="234" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="380"/>
-      <c r="J7" s="381"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="236"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -9211,18 +9266,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="379" t="str">
+      <c r="H8" s="234" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="380"/>
-      <c r="J8" s="381"/>
-      <c r="L8" s="241" t="s">
+      <c r="I8" s="235"/>
+      <c r="J8" s="236"/>
+      <c r="L8" s="267" t="s">
         <v>417</v>
       </c>
-      <c r="M8" s="267"/>
-      <c r="N8" s="267"/>
-      <c r="O8" s="242"/>
+      <c r="M8" s="268"/>
+      <c r="N8" s="268"/>
+      <c r="O8" s="269"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9237,14 +9292,14 @@
         <v>239</v>
       </c>
       <c r="U8" s="114"/>
-      <c r="V8" s="231" t="s">
+      <c r="V8" s="230" t="s">
         <v>453</v>
       </c>
-      <c r="W8" s="366" t="s">
+      <c r="W8" s="270" t="s">
         <v>454</v>
       </c>
-      <c r="X8" s="367"/>
-      <c r="Y8" s="230"/>
+      <c r="X8" s="271"/>
+      <c r="Y8" s="229"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="187" t="s">
@@ -9283,10 +9338,10 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="368" t="s">
+      <c r="W9" s="272" t="s">
         <v>456</v>
       </c>
-      <c r="X9" s="369"/>
+      <c r="X9" s="273"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
@@ -9317,10 +9372,10 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="352" t="s">
+      <c r="W10" s="274" t="s">
         <v>455</v>
       </c>
-      <c r="X10" s="353"/>
+      <c r="X10" s="275"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
@@ -9347,20 +9402,20 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="363" t="s">
+      <c r="Q11" s="264" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="364"/>
-      <c r="S11" s="364"/>
-      <c r="T11" s="365"/>
+      <c r="R11" s="265"/>
+      <c r="S11" s="265"/>
+      <c r="T11" s="266"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="352" t="s">
+      <c r="W11" s="274" t="s">
         <v>425</v>
       </c>
-      <c r="X11" s="353"/>
+      <c r="X11" s="275"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
@@ -9401,8 +9456,10 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="352"/>
-      <c r="X12" s="353"/>
+      <c r="W12" s="274" t="s">
+        <v>462</v>
+      </c>
+      <c r="X12" s="275"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
@@ -9443,8 +9500,8 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="352"/>
-      <c r="X13" s="353"/>
+      <c r="W13" s="274"/>
+      <c r="X13" s="275"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
@@ -9485,8 +9542,8 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="352"/>
-      <c r="X14" s="353"/>
+      <c r="W14" s="274"/>
+      <c r="X14" s="275"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
@@ -9527,8 +9584,8 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="352"/>
-      <c r="X15" s="353"/>
+      <c r="W15" s="274"/>
+      <c r="X15" s="275"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
@@ -9559,8 +9616,8 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="352"/>
-      <c r="X16" s="353"/>
+      <c r="W16" s="274"/>
+      <c r="X16" s="275"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
@@ -9588,11 +9645,11 @@
       <c r="T17" s="138" t="s">
         <v>258</v>
       </c>
-      <c r="V17" s="232">
+      <c r="V17" s="231">
         <v>9</v>
       </c>
-      <c r="W17" s="350"/>
-      <c r="X17" s="351"/>
+      <c r="W17" s="285"/>
+      <c r="X17" s="286"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9611,18 +9668,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="287" t="s">
+      <c r="G19" s="241" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="288"/>
-      <c r="I19" s="288"/>
-      <c r="J19" s="289"/>
+      <c r="H19" s="242"/>
+      <c r="I19" s="242"/>
+      <c r="J19" s="243"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="382" t="s">
+      <c r="C20" s="232" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9634,16 +9691,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="384" t="s">
+      <c r="G20" s="237" t="s">
         <v>457</v>
       </c>
-      <c r="H20" s="385"/>
-      <c r="I20" s="385"/>
-      <c r="J20" s="386"/>
+      <c r="H20" s="238"/>
+      <c r="I20" s="238"/>
+      <c r="J20" s="239"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="387"/>
+      <c r="C21" s="240"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9653,16 +9710,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="379" t="s">
+      <c r="G21" s="234" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="380"/>
-      <c r="I21" s="380"/>
-      <c r="J21" s="381"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="236"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="383"/>
+      <c r="C22" s="233"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9681,7 +9738,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="382" t="s">
+      <c r="C23" s="232" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9700,7 +9757,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="383"/>
+      <c r="C24" s="233"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9719,7 +9776,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="382" t="s">
+      <c r="C25" s="232" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9738,7 +9795,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="383"/>
+      <c r="C26" s="233"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9757,7 +9814,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="382" t="s">
+      <c r="C27" s="232" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9776,7 +9833,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="383"/>
+      <c r="C28" s="233"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9816,7 +9873,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="382" t="s">
+      <c r="C30" s="232" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9835,7 +9892,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="383"/>
+      <c r="C31" s="233"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9854,7 +9911,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="382" t="s">
+      <c r="C32" s="232" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9873,7 +9930,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="383"/>
+      <c r="C33" s="233"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9890,22 +9947,12 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9917,12 +9964,22 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9932,7 +9989,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B07C92-48AD-46D8-AFE8-A66BE9216D0D}">
-  <dimension ref="B1:H24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="8.28515625" customWidth="1"/>
@@ -9943,19 +10000,46 @@
     <col min="8" max="8" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="419" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="424"/>
+      <c r="B1" s="425"/>
+      <c r="C1" s="425"/>
+      <c r="D1" s="425"/>
+      <c r="E1" s="425"/>
+      <c r="F1" s="425"/>
+      <c r="G1" s="425"/>
+      <c r="H1" s="425"/>
+      <c r="I1" s="426"/>
+      <c r="J1" s="424"/>
+      <c r="K1" s="425"/>
+      <c r="L1" s="425"/>
+      <c r="M1" s="425"/>
+      <c r="N1" s="425"/>
+      <c r="O1" s="426"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="427"/>
+      <c r="B2" s="391" t="s">
         <v>425</v>
       </c>
-      <c r="C2" s="420"/>
-      <c r="D2" s="421"/>
-      <c r="E2" s="421"/>
-      <c r="F2" s="421"/>
-      <c r="G2" s="421"/>
-      <c r="H2" s="422"/>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="392"/>
+      <c r="D2" s="393"/>
+      <c r="E2" s="393"/>
+      <c r="F2" s="393"/>
+      <c r="G2" s="393"/>
+      <c r="H2" s="394"/>
+      <c r="I2" s="428"/>
+      <c r="J2" s="427"/>
+      <c r="K2" s="435" t="s">
+        <v>463</v>
+      </c>
+      <c r="L2" s="436"/>
+      <c r="M2" s="436"/>
+      <c r="N2" s="437"/>
+      <c r="O2" s="428"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="427"/>
       <c r="B3" s="194" t="s">
         <v>424</v>
       </c>
@@ -9971,78 +10055,142 @@
       <c r="F3" s="195" t="s">
         <v>430</v>
       </c>
-      <c r="G3" s="417" t="s">
+      <c r="G3" s="389" t="s">
         <v>429</v>
       </c>
-      <c r="H3" s="418"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="390"/>
+      <c r="I3" s="428"/>
+      <c r="J3" s="427"/>
+      <c r="K3" s="194" t="s">
+        <v>424</v>
+      </c>
+      <c r="L3" s="195" t="s">
+        <v>430</v>
+      </c>
+      <c r="M3" s="389" t="s">
+        <v>429</v>
+      </c>
+      <c r="N3" s="390"/>
+      <c r="O3" s="428"/>
+    </row>
+    <row r="4" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="427"/>
       <c r="B4" s="196">
         <v>0</v>
       </c>
       <c r="C4" s="202"/>
       <c r="D4" s="203"/>
       <c r="E4" s="204"/>
-      <c r="F4" s="223" t="s">
+      <c r="F4" s="442" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="423" t="s">
+      <c r="G4" s="395" t="s">
         <v>436</v>
       </c>
-      <c r="H4" s="424"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H4" s="396"/>
+      <c r="I4" s="428"/>
+      <c r="J4" s="427"/>
+      <c r="K4" s="196">
+        <v>0</v>
+      </c>
+      <c r="L4" s="439" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="395" t="s">
+        <v>436</v>
+      </c>
+      <c r="N4" s="396"/>
+      <c r="O4" s="428"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="427"/>
       <c r="B5" s="197">
         <v>1</v>
       </c>
       <c r="C5" s="198" t="s">
         <v>439</v>
       </c>
-      <c r="D5" s="228"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="222" t="s">
         <v>441</v>
       </c>
-      <c r="F5" s="224" t="s">
+      <c r="F5" s="223" t="s">
         <v>431</v>
       </c>
-      <c r="G5" s="408" t="s">
+      <c r="G5" s="387" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="409"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="388"/>
+      <c r="I5" s="428"/>
+      <c r="J5" s="427"/>
+      <c r="K5" s="197">
+        <v>1</v>
+      </c>
+      <c r="L5" s="440" t="s">
+        <v>464</v>
+      </c>
+      <c r="M5" s="387" t="s">
+        <v>465</v>
+      </c>
+      <c r="N5" s="388"/>
+      <c r="O5" s="428"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="427"/>
       <c r="B6" s="197">
         <v>2</v>
       </c>
-      <c r="C6" s="229"/>
+      <c r="C6" s="228"/>
       <c r="D6" s="205"/>
       <c r="E6" s="200" t="s">
         <v>441</v>
       </c>
-      <c r="F6" s="224" t="s">
+      <c r="F6" s="223" t="s">
         <v>432</v>
       </c>
-      <c r="G6" s="408" t="s">
+      <c r="G6" s="387" t="s">
         <v>437</v>
       </c>
-      <c r="H6" s="409"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H6" s="388"/>
+      <c r="I6" s="428"/>
+      <c r="J6" s="427"/>
+      <c r="K6" s="201">
+        <v>2</v>
+      </c>
+      <c r="L6" s="441" t="s">
+        <v>308</v>
+      </c>
+      <c r="M6" s="433" t="s">
+        <v>466</v>
+      </c>
+      <c r="N6" s="434"/>
+      <c r="O6" s="428"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="427"/>
       <c r="B7" s="197">
         <v>3</v>
       </c>
       <c r="C7" s="207"/>
       <c r="D7" s="205"/>
       <c r="E7" s="206"/>
-      <c r="F7" s="224" t="s">
+      <c r="F7" s="223" t="s">
         <v>433</v>
       </c>
-      <c r="G7" s="408" t="s">
+      <c r="G7" s="387" t="s">
         <v>438</v>
       </c>
-      <c r="H7" s="409"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="388"/>
+      <c r="I7" s="428"/>
+      <c r="J7" s="427"/>
+      <c r="K7" s="429"/>
+      <c r="L7" s="429"/>
+      <c r="M7" s="429"/>
+      <c r="N7" s="429"/>
+      <c r="O7" s="428"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="427"/>
       <c r="B8" s="197">
         <v>4</v>
       </c>
@@ -10053,139 +10201,247 @@
         <v>443</v>
       </c>
       <c r="E8" s="206"/>
-      <c r="F8" s="224" t="s">
+      <c r="F8" s="223" t="s">
         <v>434</v>
       </c>
-      <c r="G8" s="408" t="s">
+      <c r="G8" s="387" t="s">
         <v>444</v>
       </c>
-      <c r="H8" s="409"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H8" s="388"/>
+      <c r="I8" s="428"/>
+      <c r="J8" s="427"/>
+      <c r="K8" s="413" t="s">
+        <v>445</v>
+      </c>
+      <c r="L8" s="218">
+        <v>2</v>
+      </c>
+      <c r="M8" s="218">
+        <v>1</v>
+      </c>
+      <c r="N8" s="219">
+        <v>0</v>
+      </c>
+      <c r="O8" s="428"/>
+    </row>
+    <row r="9" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="427"/>
       <c r="B9" s="197">
         <v>5</v>
       </c>
       <c r="C9" s="207"/>
       <c r="D9" s="205"/>
       <c r="E9" s="206"/>
-      <c r="F9" s="225" t="s">
+      <c r="F9" s="224" t="s">
         <v>435</v>
       </c>
-      <c r="G9" s="410"/>
-      <c r="H9" s="411"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="406"/>
+      <c r="H9" s="407"/>
+      <c r="I9" s="428"/>
+      <c r="J9" s="427"/>
+      <c r="K9" s="414"/>
+      <c r="L9" s="221"/>
+      <c r="M9" s="221"/>
+      <c r="N9" s="438" t="s">
+        <v>467</v>
+      </c>
+      <c r="O9" s="428"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="427"/>
       <c r="B10" s="197">
         <v>6</v>
       </c>
       <c r="C10" s="207"/>
       <c r="D10" s="205"/>
       <c r="E10" s="206"/>
-      <c r="F10" s="226" t="s">
+      <c r="F10" s="225" t="s">
         <v>435</v>
       </c>
-      <c r="G10" s="410"/>
-      <c r="H10" s="411"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="406"/>
+      <c r="H10" s="407"/>
+      <c r="I10" s="428"/>
+      <c r="J10" s="427"/>
+      <c r="K10" s="429"/>
+      <c r="L10" s="429"/>
+      <c r="M10" s="429"/>
+      <c r="N10" s="429"/>
+      <c r="O10" s="428"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="427"/>
       <c r="B11" s="201">
         <v>7</v>
       </c>
       <c r="C11" s="208"/>
       <c r="D11" s="209"/>
       <c r="E11" s="210"/>
-      <c r="F11" s="227" t="s">
+      <c r="F11" s="226" t="s">
         <v>435</v>
       </c>
-      <c r="G11" s="412"/>
-      <c r="H11" s="413"/>
-    </row>
-    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="408"/>
+      <c r="H11" s="409"/>
+      <c r="I11" s="428"/>
+      <c r="J11" s="430"/>
+      <c r="K11" s="431"/>
+      <c r="L11" s="431"/>
+      <c r="M11" s="431"/>
+      <c r="N11" s="431"/>
+      <c r="O11" s="432"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="427"/>
+      <c r="B12" s="429"/>
+      <c r="C12" s="429"/>
+      <c r="D12" s="429"/>
+      <c r="E12" s="429"/>
+      <c r="F12" s="429"/>
+      <c r="G12" s="429"/>
+      <c r="H12" s="429"/>
+      <c r="I12" s="428"/>
+      <c r="O12" s="443"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="427"/>
       <c r="B13" s="212" t="s">
         <v>446</v>
       </c>
-      <c r="C13" s="414" t="s">
+      <c r="C13" s="410" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="415"/>
-      <c r="E13" s="416"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D13" s="411"/>
+      <c r="E13" s="412"/>
+      <c r="F13" s="429"/>
+      <c r="G13" s="429"/>
+      <c r="H13" s="429"/>
+      <c r="I13" s="428"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="427"/>
       <c r="B14" s="213">
         <v>0</v>
       </c>
-      <c r="C14" s="399" t="s">
+      <c r="C14" s="397" t="s">
         <v>451</v>
       </c>
-      <c r="D14" s="400"/>
-      <c r="E14" s="401"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="398"/>
+      <c r="E14" s="399"/>
+      <c r="F14" s="429"/>
+      <c r="G14" s="429"/>
+      <c r="H14" s="429"/>
+      <c r="I14" s="428"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="427"/>
       <c r="B15" s="214">
         <v>1</v>
       </c>
-      <c r="C15" s="402" t="s">
+      <c r="C15" s="400" t="s">
         <v>449</v>
       </c>
-      <c r="D15" s="403"/>
-      <c r="E15" s="404"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D15" s="401"/>
+      <c r="E15" s="402"/>
+      <c r="F15" s="429"/>
+      <c r="G15" s="429"/>
+      <c r="H15" s="429"/>
+      <c r="I15" s="428"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="427"/>
       <c r="B16" s="214">
         <v>2</v>
       </c>
-      <c r="C16" s="390" t="s">
+      <c r="C16" s="415" t="s">
         <v>450</v>
       </c>
-      <c r="D16" s="391"/>
-      <c r="E16" s="392"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D16" s="416"/>
+      <c r="E16" s="417"/>
+      <c r="F16" s="429"/>
+      <c r="G16" s="429"/>
+      <c r="H16" s="429"/>
+      <c r="I16" s="428"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="427"/>
       <c r="B17" s="214">
         <v>3</v>
       </c>
-      <c r="C17" s="405" t="s">
+      <c r="C17" s="403" t="s">
         <v>452</v>
       </c>
-      <c r="D17" s="406"/>
-      <c r="E17" s="407"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="404"/>
+      <c r="E17" s="405"/>
+      <c r="F17" s="429"/>
+      <c r="G17" s="429"/>
+      <c r="H17" s="429"/>
+      <c r="I17" s="428"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="427"/>
       <c r="B18" s="214">
         <v>4</v>
       </c>
-      <c r="C18" s="393"/>
-      <c r="D18" s="394"/>
-      <c r="E18" s="395"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C18" s="418"/>
+      <c r="D18" s="419"/>
+      <c r="E18" s="420"/>
+      <c r="F18" s="429"/>
+      <c r="G18" s="429"/>
+      <c r="H18" s="429"/>
+      <c r="I18" s="428"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="427"/>
       <c r="B19" s="214">
         <v>5</v>
       </c>
-      <c r="C19" s="393"/>
-      <c r="D19" s="394"/>
-      <c r="E19" s="395"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C19" s="418"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="420"/>
+      <c r="F19" s="429"/>
+      <c r="G19" s="429"/>
+      <c r="H19" s="429"/>
+      <c r="I19" s="428"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="427"/>
       <c r="B20" s="214">
         <v>6</v>
       </c>
-      <c r="C20" s="393"/>
-      <c r="D20" s="394"/>
-      <c r="E20" s="395"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="418"/>
+      <c r="D20" s="419"/>
+      <c r="E20" s="420"/>
+      <c r="F20" s="429"/>
+      <c r="G20" s="429"/>
+      <c r="H20" s="429"/>
+      <c r="I20" s="428"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="427"/>
       <c r="B21" s="215">
         <v>7</v>
       </c>
-      <c r="C21" s="396"/>
-      <c r="D21" s="397"/>
-      <c r="E21" s="398"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="388" t="s">
+      <c r="C21" s="421"/>
+      <c r="D21" s="422"/>
+      <c r="E21" s="423"/>
+      <c r="F21" s="429"/>
+      <c r="G21" s="429"/>
+      <c r="H21" s="429"/>
+      <c r="I21" s="428"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="427"/>
+      <c r="B22" s="429"/>
+      <c r="C22" s="429"/>
+      <c r="D22" s="429"/>
+      <c r="E22" s="429"/>
+      <c r="F22" s="429"/>
+      <c r="G22" s="429"/>
+      <c r="H22" s="429"/>
+      <c r="I22" s="428"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="427"/>
+      <c r="B23" s="413" t="s">
         <v>445</v>
       </c>
       <c r="C23" s="211">
@@ -10206,9 +10462,11 @@
       <c r="H23" s="219">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="389"/>
+      <c r="I23" s="428"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="427"/>
+      <c r="B24" s="414"/>
       <c r="C24" s="220"/>
       <c r="D24" s="221"/>
       <c r="E24" s="221"/>
@@ -10219,15 +10477,33 @@
       <c r="H24" s="217" t="s">
         <v>447</v>
       </c>
+      <c r="I24" s="428"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="430"/>
+      <c r="B25" s="431"/>
+      <c r="C25" s="431"/>
+      <c r="D25" s="431"/>
+      <c r="E25" s="431"/>
+      <c r="F25" s="431"/>
+      <c r="G25" s="431"/>
+      <c r="H25" s="431"/>
+      <c r="I25" s="432"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+  <mergeCells count="26">
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C17:E17"/>
@@ -10236,12 +10512,12 @@
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2733A860-57C0-4CE3-A1F2-A60B3736D5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E1875F-F608-4B78-A33B-6FABBF1EC8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="597" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="466">
   <si>
     <t>OpCode</t>
   </si>
@@ -2288,9 +2288,6 @@
     <t>Dato 2</t>
   </si>
   <si>
-    <t>Dato 3</t>
-  </si>
-  <si>
     <t>Descrip</t>
   </si>
   <si>
@@ -2331,9 +2328,6 @@
   </si>
   <si>
     <t>Addr</t>
-  </si>
-  <si>
-    <t>Length</t>
   </si>
   <si>
     <t xml:space="preserve">Escribe los bytes de la direccion dicha </t>
@@ -3513,7 +3507,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="444">
+  <cellXfs count="440">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4109,9 +4103,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4121,15 +4112,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4137,9 +4122,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4177,7 +4159,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -4187,592 +4168,520 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4788,22 +4697,99 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -5124,62 +5110,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="324" t="s">
+      <c r="B2" s="360" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="333" t="s">
+      <c r="C2" s="372" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="334"/>
-      <c r="E2" s="335" t="s">
+      <c r="D2" s="373"/>
+      <c r="E2" s="374" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="335"/>
-      <c r="G2" s="336" t="s">
+      <c r="F2" s="374"/>
+      <c r="G2" s="375" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="335"/>
-      <c r="I2" s="335" t="s">
+      <c r="H2" s="374"/>
+      <c r="I2" s="374" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="335"/>
-      <c r="K2" s="337" t="s">
+      <c r="J2" s="374"/>
+      <c r="K2" s="376" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="335"/>
-      <c r="M2" s="335"/>
-      <c r="N2" s="335"/>
-      <c r="O2" s="335"/>
-      <c r="P2" s="338"/>
-      <c r="R2" s="341" t="s">
+      <c r="L2" s="374"/>
+      <c r="M2" s="374"/>
+      <c r="N2" s="374"/>
+      <c r="O2" s="374"/>
+      <c r="P2" s="377"/>
+      <c r="R2" s="357" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="293" t="s">
+      <c r="S2" s="355" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="345" t="s">
+      <c r="T2" s="348" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="346"/>
-      <c r="V2" s="346"/>
-      <c r="W2" s="346"/>
-      <c r="X2" s="346"/>
-      <c r="Y2" s="346"/>
-      <c r="Z2" s="346"/>
-      <c r="AA2" s="346"/>
-      <c r="AB2" s="346" t="s">
+      <c r="U2" s="349"/>
+      <c r="V2" s="349"/>
+      <c r="W2" s="349"/>
+      <c r="X2" s="349"/>
+      <c r="Y2" s="349"/>
+      <c r="Z2" s="349"/>
+      <c r="AA2" s="349"/>
+      <c r="AB2" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="346"/>
-      <c r="AD2" s="346"/>
-      <c r="AE2" s="346"/>
-      <c r="AF2" s="346"/>
-      <c r="AG2" s="346"/>
-      <c r="AH2" s="346"/>
-      <c r="AI2" s="347"/>
+      <c r="AC2" s="349"/>
+      <c r="AD2" s="349"/>
+      <c r="AE2" s="349"/>
+      <c r="AF2" s="349"/>
+      <c r="AG2" s="349"/>
+      <c r="AH2" s="349"/>
+      <c r="AI2" s="350"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="325"/>
+      <c r="B3" s="361"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5204,21 +5190,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="330"/>
-      <c r="L3" s="331"/>
-      <c r="M3" s="331"/>
-      <c r="N3" s="331"/>
-      <c r="O3" s="331"/>
-      <c r="P3" s="332"/>
-      <c r="R3" s="342"/>
-      <c r="S3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="371"/>
+      <c r="M3" s="371"/>
+      <c r="N3" s="371"/>
+      <c r="O3" s="371"/>
+      <c r="P3" s="340"/>
+      <c r="R3" s="358"/>
+      <c r="S3" s="307"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="311" t="s">
+      <c r="U3" s="381" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="311"/>
+      <c r="V3" s="381"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5231,10 +5217,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="344" t="s">
+      <c r="AA3" s="347" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="344"/>
+      <c r="AB3" s="347"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5258,21 +5244,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="326"/>
+      <c r="B4" s="362"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="312" t="s">
+      <c r="E4" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="243"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="275"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5282,20 +5268,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="312" t="s">
+      <c r="N4" s="351" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="242"/>
-      <c r="P4" s="243"/>
-      <c r="R4" s="343"/>
-      <c r="S4" s="340"/>
+      <c r="O4" s="274"/>
+      <c r="P4" s="275"/>
+      <c r="R4" s="359"/>
+      <c r="S4" s="356"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="312" t="s">
+      <c r="U4" s="351" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="313"/>
+      <c r="V4" s="352"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5308,10 +5294,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="312" t="s">
+      <c r="AA4" s="351" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="313"/>
+      <c r="AB4" s="352"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5343,22 +5329,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="316"/>
-      <c r="F5" s="317"/>
-      <c r="G5" s="317"/>
-      <c r="H5" s="317"/>
-      <c r="I5" s="317"/>
-      <c r="J5" s="318"/>
+      <c r="E5" s="378"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="379"/>
+      <c r="J5" s="380"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="252" t="s">
+      <c r="N5" s="287" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="253"/>
-      <c r="P5" s="254"/>
+      <c r="O5" s="288"/>
+      <c r="P5" s="289"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5368,10 +5354,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="314" t="s">
+      <c r="U5" s="353" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="315"/>
+      <c r="V5" s="354"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5384,10 +5370,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="314" t="s">
+      <c r="AA5" s="353" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="315"/>
+      <c r="AB5" s="354"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5419,12 +5405,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="323"/>
-      <c r="F6" s="320"/>
-      <c r="G6" s="320"/>
-      <c r="H6" s="320"/>
-      <c r="I6" s="320"/>
-      <c r="J6" s="321"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="365"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5432,11 +5418,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="249" t="s">
+      <c r="N6" s="284" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="250"/>
-      <c r="P6" s="251"/>
+      <c r="O6" s="285"/>
+      <c r="P6" s="286"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5446,10 +5432,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="309" t="s">
+      <c r="U6" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="310"/>
+      <c r="V6" s="344"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5462,10 +5448,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="309" t="s">
+      <c r="AA6" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="310"/>
+      <c r="AB6" s="344"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5508,9 +5494,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="319"/>
-      <c r="I7" s="320"/>
-      <c r="J7" s="321"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="364"/>
+      <c r="J7" s="365"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5518,11 +5504,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="249" t="s">
+      <c r="N7" s="284" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="250"/>
-      <c r="P7" s="251"/>
+      <c r="O7" s="285"/>
+      <c r="P7" s="286"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5532,10 +5518,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="309" t="s">
+      <c r="U7" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="310"/>
+      <c r="V7" s="344"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5548,10 +5534,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="309" t="s">
+      <c r="AA7" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="310"/>
+      <c r="AB7" s="344"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5594,9 +5580,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="319"/>
-      <c r="I8" s="320"/>
-      <c r="J8" s="321"/>
+      <c r="H8" s="363"/>
+      <c r="I8" s="364"/>
+      <c r="J8" s="365"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5604,11 +5590,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="249" t="s">
+      <c r="N8" s="284" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="250"/>
-      <c r="P8" s="251"/>
+      <c r="O8" s="285"/>
+      <c r="P8" s="286"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5618,10 +5604,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="309" t="s">
+      <c r="U8" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="310"/>
+      <c r="V8" s="344"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5634,10 +5620,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="309" t="s">
+      <c r="AA8" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="310"/>
+      <c r="AB8" s="344"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5680,9 +5666,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="319"/>
-      <c r="I9" s="320"/>
-      <c r="J9" s="321"/>
+      <c r="H9" s="363"/>
+      <c r="I9" s="364"/>
+      <c r="J9" s="365"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5690,11 +5676,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="249" t="s">
+      <c r="N9" s="284" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="250"/>
-      <c r="P9" s="251"/>
+      <c r="O9" s="285"/>
+      <c r="P9" s="286"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5704,10 +5690,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="309" t="s">
+      <c r="U9" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="310"/>
+      <c r="V9" s="344"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5720,10 +5706,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="309" t="s">
+      <c r="AA9" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="310"/>
+      <c r="AB9" s="344"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5766,9 +5752,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="319"/>
-      <c r="I10" s="320"/>
-      <c r="J10" s="321"/>
+      <c r="H10" s="363"/>
+      <c r="I10" s="364"/>
+      <c r="J10" s="365"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5776,11 +5762,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="249" t="s">
+      <c r="N10" s="284" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="250"/>
-      <c r="P10" s="251"/>
+      <c r="O10" s="285"/>
+      <c r="P10" s="286"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5790,10 +5776,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="309" t="s">
+      <c r="U10" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="310"/>
+      <c r="V10" s="344"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5806,10 +5792,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="309" t="s">
+      <c r="AA10" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="310"/>
+      <c r="AB10" s="344"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5852,9 +5838,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="319"/>
-      <c r="I11" s="320"/>
-      <c r="J11" s="321"/>
+      <c r="H11" s="363"/>
+      <c r="I11" s="364"/>
+      <c r="J11" s="365"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5862,11 +5848,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="249" t="s">
+      <c r="N11" s="284" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="250"/>
-      <c r="P11" s="251"/>
+      <c r="O11" s="285"/>
+      <c r="P11" s="286"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5876,10 +5862,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="309" t="s">
+      <c r="U11" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="310"/>
+      <c r="V11" s="344"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5892,10 +5878,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="309" t="s">
+      <c r="AA11" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="310"/>
+      <c r="AB11" s="344"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5938,9 +5924,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="319"/>
-      <c r="I12" s="320"/>
-      <c r="J12" s="321"/>
+      <c r="H12" s="363"/>
+      <c r="I12" s="364"/>
+      <c r="J12" s="365"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5948,11 +5934,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="249" t="s">
+      <c r="N12" s="284" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="250"/>
-      <c r="P12" s="251"/>
+      <c r="O12" s="285"/>
+      <c r="P12" s="286"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5962,10 +5948,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="309" t="s">
+      <c r="U12" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="310"/>
+      <c r="V12" s="344"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5978,10 +5964,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="309" t="s">
+      <c r="AA12" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="310"/>
+      <c r="AB12" s="344"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -6024,9 +6010,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="319"/>
-      <c r="I13" s="320"/>
-      <c r="J13" s="321"/>
+      <c r="H13" s="363"/>
+      <c r="I13" s="364"/>
+      <c r="J13" s="365"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -6034,11 +6020,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="249" t="s">
+      <c r="N13" s="284" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="250"/>
-      <c r="P13" s="251"/>
+      <c r="O13" s="285"/>
+      <c r="P13" s="286"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -6048,10 +6034,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="309" t="s">
+      <c r="U13" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="310"/>
+      <c r="V13" s="344"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6064,10 +6050,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="309" t="s">
+      <c r="AA13" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="310"/>
+      <c r="AB13" s="344"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6110,9 +6096,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="319"/>
-      <c r="I14" s="320"/>
-      <c r="J14" s="321"/>
+      <c r="H14" s="363"/>
+      <c r="I14" s="364"/>
+      <c r="J14" s="365"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6120,11 +6106,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="249" t="s">
+      <c r="N14" s="284" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="250"/>
-      <c r="P14" s="251"/>
+      <c r="O14" s="285"/>
+      <c r="P14" s="286"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6134,10 +6120,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="309" t="s">
+      <c r="U14" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="310"/>
+      <c r="V14" s="344"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6150,10 +6136,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="309" t="s">
+      <c r="AA14" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="310"/>
+      <c r="AB14" s="344"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6196,9 +6182,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="319"/>
-      <c r="I15" s="320"/>
-      <c r="J15" s="321"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="364"/>
+      <c r="J15" s="365"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6206,11 +6192,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="249" t="s">
+      <c r="N15" s="284" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="250"/>
-      <c r="P15" s="251"/>
+      <c r="O15" s="285"/>
+      <c r="P15" s="286"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6220,10 +6206,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="309" t="s">
+      <c r="U15" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="310"/>
+      <c r="V15" s="344"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6236,10 +6222,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="309" t="s">
+      <c r="AA15" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="310"/>
+      <c r="AB15" s="344"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6276,21 +6262,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="319"/>
-      <c r="G16" s="320"/>
-      <c r="H16" s="320"/>
-      <c r="I16" s="320"/>
-      <c r="J16" s="321"/>
+      <c r="F16" s="363"/>
+      <c r="G16" s="364"/>
+      <c r="H16" s="364"/>
+      <c r="I16" s="364"/>
+      <c r="J16" s="365"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="249" t="s">
+      <c r="N16" s="284" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="250"/>
-      <c r="P16" s="251"/>
+      <c r="O16" s="285"/>
+      <c r="P16" s="286"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6300,10 +6286,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="309" t="s">
+      <c r="U16" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="310"/>
+      <c r="V16" s="344"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6316,10 +6302,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="309" t="s">
+      <c r="AA16" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="310"/>
+      <c r="AB16" s="344"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6357,22 +6343,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="322" t="s">
+      <c r="G17" s="370" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
-      <c r="J17" s="251"/>
+      <c r="H17" s="285"/>
+      <c r="I17" s="285"/>
+      <c r="J17" s="286"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="249" t="s">
+      <c r="N17" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="250"/>
-      <c r="P17" s="251"/>
+      <c r="O17" s="285"/>
+      <c r="P17" s="286"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6382,10 +6368,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="309" t="s">
+      <c r="U17" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="310"/>
+      <c r="V17" s="344"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6398,10 +6384,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="309" t="s">
+      <c r="AA17" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="310"/>
+      <c r="AB17" s="344"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6439,12 +6425,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="322" t="s">
+      <c r="G18" s="370" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="250"/>
-      <c r="I18" s="250"/>
-      <c r="J18" s="251"/>
+      <c r="H18" s="285"/>
+      <c r="I18" s="285"/>
+      <c r="J18" s="286"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6452,11 +6438,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="249" t="s">
+      <c r="N18" s="284" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="250"/>
-      <c r="P18" s="251"/>
+      <c r="O18" s="285"/>
+      <c r="P18" s="286"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6466,10 +6452,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="309" t="s">
+      <c r="U18" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="310"/>
+      <c r="V18" s="344"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6482,10 +6468,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="309" t="s">
+      <c r="AA18" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="310"/>
+      <c r="AB18" s="344"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6521,20 +6507,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="319"/>
-      <c r="H19" s="320"/>
-      <c r="I19" s="320"/>
-      <c r="J19" s="321"/>
+      <c r="G19" s="363"/>
+      <c r="H19" s="364"/>
+      <c r="I19" s="364"/>
+      <c r="J19" s="365"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="249" t="s">
+      <c r="N19" s="284" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="250"/>
-      <c r="P19" s="251"/>
+      <c r="O19" s="285"/>
+      <c r="P19" s="286"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6544,10 +6530,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="309" t="s">
+      <c r="U19" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="310"/>
+      <c r="V19" s="344"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6560,10 +6546,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="309" t="s">
+      <c r="AA19" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="310"/>
+      <c r="AB19" s="344"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6601,20 +6587,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="319"/>
-      <c r="H20" s="320"/>
-      <c r="I20" s="320"/>
-      <c r="J20" s="321"/>
+      <c r="G20" s="363"/>
+      <c r="H20" s="364"/>
+      <c r="I20" s="364"/>
+      <c r="J20" s="365"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="249" t="s">
+      <c r="N20" s="284" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="250"/>
-      <c r="P20" s="251"/>
+      <c r="O20" s="285"/>
+      <c r="P20" s="286"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6624,10 +6610,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="309" t="s">
+      <c r="U20" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="310"/>
+      <c r="V20" s="344"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6640,10 +6626,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="309" t="s">
+      <c r="AA20" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="310"/>
+      <c r="AB20" s="344"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6681,20 +6667,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="319"/>
-      <c r="H21" s="320"/>
-      <c r="I21" s="320"/>
-      <c r="J21" s="321"/>
+      <c r="G21" s="363"/>
+      <c r="H21" s="364"/>
+      <c r="I21" s="364"/>
+      <c r="J21" s="365"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="249" t="s">
+      <c r="N21" s="284" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="250"/>
-      <c r="P21" s="251"/>
+      <c r="O21" s="285"/>
+      <c r="P21" s="286"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6704,10 +6690,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="309" t="s">
+      <c r="U21" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="310"/>
+      <c r="V21" s="344"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6720,10 +6706,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="309" t="s">
+      <c r="AA21" s="343" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="310"/>
+      <c r="AB21" s="344"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6757,22 +6743,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="323"/>
-      <c r="F22" s="320"/>
-      <c r="G22" s="320"/>
-      <c r="H22" s="320"/>
-      <c r="I22" s="320"/>
-      <c r="J22" s="321"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="364"/>
+      <c r="G22" s="364"/>
+      <c r="H22" s="364"/>
+      <c r="I22" s="364"/>
+      <c r="J22" s="365"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="249" t="s">
+      <c r="N22" s="284" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="250"/>
-      <c r="P22" s="251"/>
+      <c r="O22" s="285"/>
+      <c r="P22" s="286"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6782,10 +6768,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="309" t="s">
+      <c r="U22" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="310"/>
+      <c r="V22" s="344"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6798,10 +6784,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="309" t="s">
+      <c r="AA22" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="310"/>
+      <c r="AB22" s="344"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6841,22 +6827,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="322" t="s">
+      <c r="G23" s="370" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="250"/>
-      <c r="I23" s="250"/>
-      <c r="J23" s="251"/>
+      <c r="H23" s="285"/>
+      <c r="I23" s="285"/>
+      <c r="J23" s="286"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="249" t="s">
+      <c r="N23" s="284" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="250"/>
-      <c r="P23" s="251"/>
+      <c r="O23" s="285"/>
+      <c r="P23" s="286"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6866,10 +6852,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="309" t="s">
+      <c r="U23" s="343" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="310"/>
+      <c r="V23" s="344"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6882,10 +6868,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="309" t="s">
+      <c r="AA23" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="310"/>
+      <c r="AB23" s="344"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6925,22 +6911,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="322" t="s">
+      <c r="G24" s="370" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="250"/>
-      <c r="I24" s="250"/>
-      <c r="J24" s="251"/>
+      <c r="H24" s="285"/>
+      <c r="I24" s="285"/>
+      <c r="J24" s="286"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="249" t="s">
+      <c r="N24" s="284" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="250"/>
-      <c r="P24" s="251"/>
+      <c r="O24" s="285"/>
+      <c r="P24" s="286"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6950,10 +6936,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="309" t="s">
+      <c r="U24" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="310"/>
+      <c r="V24" s="344"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6966,10 +6952,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="309" t="s">
+      <c r="AA24" s="343" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="310"/>
+      <c r="AB24" s="344"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -7007,10 +6993,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="319"/>
-      <c r="H25" s="320"/>
-      <c r="I25" s="320"/>
-      <c r="J25" s="321"/>
+      <c r="G25" s="363"/>
+      <c r="H25" s="364"/>
+      <c r="I25" s="364"/>
+      <c r="J25" s="365"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -7018,11 +7004,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="249" t="s">
+      <c r="N25" s="284" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="250"/>
-      <c r="P25" s="251"/>
+      <c r="O25" s="285"/>
+      <c r="P25" s="286"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -7032,10 +7018,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="309" t="s">
+      <c r="U25" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="310"/>
+      <c r="V25" s="344"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -7048,10 +7034,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="309" t="s">
+      <c r="AA25" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="310"/>
+      <c r="AB25" s="344"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7089,10 +7075,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="319"/>
-      <c r="H26" s="320"/>
-      <c r="I26" s="320"/>
-      <c r="J26" s="321"/>
+      <c r="G26" s="363"/>
+      <c r="H26" s="364"/>
+      <c r="I26" s="364"/>
+      <c r="J26" s="365"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7100,11 +7086,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="249" t="s">
+      <c r="N26" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="250"/>
-      <c r="P26" s="251"/>
+      <c r="O26" s="285"/>
+      <c r="P26" s="286"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7114,10 +7100,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="309" t="s">
+      <c r="U26" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="310"/>
+      <c r="V26" s="344"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7130,10 +7116,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="309" t="s">
+      <c r="AA26" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="310"/>
+      <c r="AB26" s="344"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7165,22 +7151,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="323"/>
-      <c r="F27" s="320"/>
-      <c r="G27" s="320"/>
-      <c r="H27" s="320"/>
-      <c r="I27" s="320"/>
-      <c r="J27" s="321"/>
+      <c r="E27" s="369"/>
+      <c r="F27" s="364"/>
+      <c r="G27" s="364"/>
+      <c r="H27" s="364"/>
+      <c r="I27" s="364"/>
+      <c r="J27" s="365"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="249" t="s">
+      <c r="N27" s="284" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="250"/>
-      <c r="P27" s="251"/>
+      <c r="O27" s="285"/>
+      <c r="P27" s="286"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7190,10 +7176,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="309" t="s">
+      <c r="U27" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="310"/>
+      <c r="V27" s="344"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7206,10 +7192,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="309" t="s">
+      <c r="AA27" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="310"/>
+      <c r="AB27" s="344"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7241,12 +7227,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="327"/>
-      <c r="F28" s="328"/>
-      <c r="G28" s="328"/>
-      <c r="H28" s="328"/>
-      <c r="I28" s="328"/>
-      <c r="J28" s="329"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="367"/>
+      <c r="G28" s="367"/>
+      <c r="H28" s="367"/>
+      <c r="I28" s="367"/>
+      <c r="J28" s="368"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7254,11 +7240,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="246" t="s">
+      <c r="N28" s="281" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="247"/>
-      <c r="P28" s="248"/>
+      <c r="O28" s="282"/>
+      <c r="P28" s="283"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7268,10 +7254,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="356" t="s">
+      <c r="U28" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="357"/>
+      <c r="V28" s="346"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7284,10 +7270,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="356" t="s">
+      <c r="AA28" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="357"/>
+      <c r="AB28" s="346"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7364,27 +7350,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="292" t="s">
+      <c r="T30" s="395" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="292"/>
-      <c r="V30" s="292"/>
-      <c r="W30" s="292"/>
-      <c r="X30" s="292"/>
-      <c r="Y30" s="292"/>
-      <c r="Z30" s="292"/>
-      <c r="AA30" s="292"/>
-      <c r="AB30" s="292"/>
-      <c r="AC30" s="293"/>
-      <c r="AE30" s="241" t="s">
+      <c r="U30" s="395"/>
+      <c r="V30" s="395"/>
+      <c r="W30" s="395"/>
+      <c r="X30" s="395"/>
+      <c r="Y30" s="395"/>
+      <c r="Z30" s="395"/>
+      <c r="AA30" s="395"/>
+      <c r="AB30" s="395"/>
+      <c r="AC30" s="355"/>
+      <c r="AE30" s="273" t="s">
         <v>422</v>
       </c>
-      <c r="AF30" s="242"/>
-      <c r="AG30" s="241" t="s">
+      <c r="AF30" s="274"/>
+      <c r="AG30" s="273" t="s">
         <v>423</v>
       </c>
-      <c r="AH30" s="242"/>
-      <c r="AI30" s="243"/>
+      <c r="AH30" s="274"/>
+      <c r="AI30" s="275"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7425,28 +7411,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="252" t="s">
+      <c r="T31" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="253"/>
-      <c r="V31" s="253"/>
-      <c r="W31" s="253"/>
-      <c r="X31" s="253"/>
-      <c r="Y31" s="253"/>
-      <c r="Z31" s="253"/>
-      <c r="AA31" s="253"/>
-      <c r="AB31" s="253"/>
-      <c r="AC31" s="254"/>
-      <c r="AE31" s="287">
+      <c r="U31" s="288"/>
+      <c r="V31" s="288"/>
+      <c r="W31" s="288"/>
+      <c r="X31" s="288"/>
+      <c r="Y31" s="288"/>
+      <c r="Z31" s="288"/>
+      <c r="AA31" s="288"/>
+      <c r="AB31" s="288"/>
+      <c r="AC31" s="289"/>
+      <c r="AE31" s="390">
         <v>2</v>
       </c>
-      <c r="AF31" s="288"/>
-      <c r="AG31" s="289" t="str" cm="1">
+      <c r="AF31" s="391"/>
+      <c r="AG31" s="392" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="290"/>
-      <c r="AI31" s="291"/>
+      <c r="AH31" s="393"/>
+      <c r="AI31" s="394"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7470,18 +7456,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="249" t="s">
+      <c r="T32" s="284" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="250"/>
-      <c r="V32" s="250"/>
-      <c r="W32" s="250"/>
-      <c r="X32" s="250"/>
-      <c r="Y32" s="250"/>
-      <c r="Z32" s="250"/>
-      <c r="AA32" s="250"/>
-      <c r="AB32" s="250"/>
-      <c r="AC32" s="251"/>
+      <c r="U32" s="285"/>
+      <c r="V32" s="285"/>
+      <c r="W32" s="285"/>
+      <c r="X32" s="285"/>
+      <c r="Y32" s="285"/>
+      <c r="Z32" s="285"/>
+      <c r="AA32" s="285"/>
+      <c r="AB32" s="285"/>
+      <c r="AC32" s="286"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7517,31 +7503,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="249" t="s">
+      <c r="T33" s="284" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="250"/>
-      <c r="V33" s="250"/>
-      <c r="W33" s="250"/>
-      <c r="X33" s="250"/>
-      <c r="Y33" s="250"/>
-      <c r="Z33" s="250"/>
-      <c r="AA33" s="250"/>
-      <c r="AB33" s="250"/>
-      <c r="AC33" s="251"/>
+      <c r="U33" s="285"/>
+      <c r="V33" s="285"/>
+      <c r="W33" s="285"/>
+      <c r="X33" s="285"/>
+      <c r="Y33" s="285"/>
+      <c r="Z33" s="285"/>
+      <c r="AA33" s="285"/>
+      <c r="AB33" s="285"/>
+      <c r="AC33" s="286"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="354" t="s">
+      <c r="B34" s="341" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="330" t="s">
+      <c r="C34" s="339" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="332"/>
-      <c r="E34" s="330" t="s">
+      <c r="D34" s="340"/>
+      <c r="E34" s="339" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="332"/>
+      <c r="F34" s="340"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7569,21 +7555,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="249" t="s">
+      <c r="T34" s="284" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="250"/>
-      <c r="V34" s="250"/>
-      <c r="W34" s="250"/>
-      <c r="X34" s="250"/>
-      <c r="Y34" s="250"/>
-      <c r="Z34" s="250"/>
-      <c r="AA34" s="250"/>
-      <c r="AB34" s="250"/>
-      <c r="AC34" s="251"/>
+      <c r="U34" s="285"/>
+      <c r="V34" s="285"/>
+      <c r="W34" s="285"/>
+      <c r="X34" s="285"/>
+      <c r="Y34" s="285"/>
+      <c r="Z34" s="285"/>
+      <c r="AA34" s="285"/>
+      <c r="AB34" s="285"/>
+      <c r="AC34" s="286"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="355"/>
+      <c r="B35" s="342"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7602,18 +7588,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="249" t="s">
+      <c r="T35" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="250"/>
-      <c r="V35" s="250"/>
-      <c r="W35" s="250"/>
-      <c r="X35" s="250"/>
-      <c r="Y35" s="250"/>
-      <c r="Z35" s="250"/>
-      <c r="AA35" s="250"/>
-      <c r="AB35" s="250"/>
-      <c r="AC35" s="251"/>
+      <c r="U35" s="285"/>
+      <c r="V35" s="285"/>
+      <c r="W35" s="285"/>
+      <c r="X35" s="285"/>
+      <c r="Y35" s="285"/>
+      <c r="Z35" s="285"/>
+      <c r="AA35" s="285"/>
+      <c r="AB35" s="285"/>
+      <c r="AC35" s="286"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7664,18 +7650,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="249" t="s">
+      <c r="T36" s="284" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="250"/>
-      <c r="V36" s="250"/>
-      <c r="W36" s="250"/>
-      <c r="X36" s="250"/>
-      <c r="Y36" s="250"/>
-      <c r="Z36" s="250"/>
-      <c r="AA36" s="250"/>
-      <c r="AB36" s="250"/>
-      <c r="AC36" s="251"/>
+      <c r="U36" s="285"/>
+      <c r="V36" s="285"/>
+      <c r="W36" s="285"/>
+      <c r="X36" s="285"/>
+      <c r="Y36" s="285"/>
+      <c r="Z36" s="285"/>
+      <c r="AA36" s="285"/>
+      <c r="AB36" s="285"/>
+      <c r="AC36" s="286"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7718,18 +7704,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="249" t="s">
+      <c r="T37" s="284" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="250"/>
-      <c r="V37" s="250"/>
-      <c r="W37" s="250"/>
-      <c r="X37" s="250"/>
-      <c r="Y37" s="250"/>
-      <c r="Z37" s="250"/>
-      <c r="AA37" s="250"/>
-      <c r="AB37" s="250"/>
-      <c r="AC37" s="251"/>
+      <c r="U37" s="285"/>
+      <c r="V37" s="285"/>
+      <c r="W37" s="285"/>
+      <c r="X37" s="285"/>
+      <c r="Y37" s="285"/>
+      <c r="Z37" s="285"/>
+      <c r="AA37" s="285"/>
+      <c r="AB37" s="285"/>
+      <c r="AC37" s="286"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7750,21 +7736,21 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="294" t="s">
+      <c r="S38" s="382" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="296" t="s">
+      <c r="T38" s="384" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="297"/>
-      <c r="V38" s="297"/>
-      <c r="W38" s="297"/>
-      <c r="X38" s="297"/>
-      <c r="Y38" s="297"/>
-      <c r="Z38" s="297"/>
-      <c r="AA38" s="297"/>
-      <c r="AB38" s="297"/>
-      <c r="AC38" s="298"/>
+      <c r="U38" s="385"/>
+      <c r="V38" s="385"/>
+      <c r="W38" s="385"/>
+      <c r="X38" s="385"/>
+      <c r="Y38" s="385"/>
+      <c r="Z38" s="385"/>
+      <c r="AA38" s="385"/>
+      <c r="AB38" s="385"/>
+      <c r="AC38" s="386"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7782,26 +7768,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="302" t="s">
+      <c r="G39" s="328" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="244"/>
-      <c r="I39" s="244"/>
-      <c r="J39" s="245"/>
+      <c r="H39" s="279"/>
+      <c r="I39" s="279"/>
+      <c r="J39" s="280"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="295"/>
-      <c r="T39" s="299"/>
-      <c r="U39" s="300"/>
-      <c r="V39" s="300"/>
-      <c r="W39" s="300"/>
-      <c r="X39" s="300"/>
-      <c r="Y39" s="300"/>
-      <c r="Z39" s="300"/>
-      <c r="AA39" s="300"/>
-      <c r="AB39" s="300"/>
-      <c r="AC39" s="301"/>
+      <c r="S39" s="383"/>
+      <c r="T39" s="387"/>
+      <c r="U39" s="388"/>
+      <c r="V39" s="388"/>
+      <c r="W39" s="388"/>
+      <c r="X39" s="388"/>
+      <c r="Y39" s="388"/>
+      <c r="Z39" s="388"/>
+      <c r="AA39" s="388"/>
+      <c r="AB39" s="388"/>
+      <c r="AC39" s="389"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7819,28 +7805,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="306"/>
-      <c r="H40" s="307"/>
-      <c r="I40" s="307"/>
-      <c r="J40" s="308"/>
+      <c r="G40" s="329"/>
+      <c r="H40" s="330"/>
+      <c r="I40" s="330"/>
+      <c r="J40" s="331"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="249" t="s">
+      <c r="T40" s="284" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="250"/>
-      <c r="V40" s="250"/>
-      <c r="W40" s="250"/>
-      <c r="X40" s="250"/>
-      <c r="Y40" s="250"/>
-      <c r="Z40" s="250"/>
-      <c r="AA40" s="250"/>
-      <c r="AB40" s="250"/>
-      <c r="AC40" s="251"/>
+      <c r="U40" s="285"/>
+      <c r="V40" s="285"/>
+      <c r="W40" s="285"/>
+      <c r="X40" s="285"/>
+      <c r="Y40" s="285"/>
+      <c r="Z40" s="285"/>
+      <c r="AA40" s="285"/>
+      <c r="AB40" s="285"/>
+      <c r="AC40" s="286"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7858,28 +7844,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="306"/>
-      <c r="H41" s="307"/>
-      <c r="I41" s="307"/>
-      <c r="J41" s="308"/>
+      <c r="G41" s="329"/>
+      <c r="H41" s="330"/>
+      <c r="I41" s="330"/>
+      <c r="J41" s="331"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="249" t="s">
+      <c r="T41" s="284" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="250"/>
-      <c r="V41" s="250"/>
-      <c r="W41" s="250"/>
-      <c r="X41" s="250"/>
-      <c r="Y41" s="250"/>
-      <c r="Z41" s="250"/>
-      <c r="AA41" s="250"/>
-      <c r="AB41" s="250"/>
-      <c r="AC41" s="251"/>
+      <c r="U41" s="285"/>
+      <c r="V41" s="285"/>
+      <c r="W41" s="285"/>
+      <c r="X41" s="285"/>
+      <c r="Y41" s="285"/>
+      <c r="Z41" s="285"/>
+      <c r="AA41" s="285"/>
+      <c r="AB41" s="285"/>
+      <c r="AC41" s="286"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7897,28 +7883,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="303"/>
-      <c r="H42" s="304"/>
-      <c r="I42" s="304"/>
-      <c r="J42" s="305"/>
+      <c r="G42" s="332"/>
+      <c r="H42" s="333"/>
+      <c r="I42" s="333"/>
+      <c r="J42" s="334"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="249" t="s">
+      <c r="T42" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="250"/>
-      <c r="V42" s="250"/>
-      <c r="W42" s="250"/>
-      <c r="X42" s="250"/>
-      <c r="Y42" s="250"/>
-      <c r="Z42" s="250"/>
-      <c r="AA42" s="250"/>
-      <c r="AB42" s="250"/>
-      <c r="AC42" s="251"/>
+      <c r="U42" s="285"/>
+      <c r="V42" s="285"/>
+      <c r="W42" s="285"/>
+      <c r="X42" s="285"/>
+      <c r="Y42" s="285"/>
+      <c r="Z42" s="285"/>
+      <c r="AA42" s="285"/>
+      <c r="AB42" s="285"/>
+      <c r="AC42" s="286"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7936,30 +7922,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="267" t="s">
+      <c r="G43" s="257" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="268"/>
-      <c r="I43" s="268"/>
-      <c r="J43" s="269"/>
+      <c r="H43" s="258"/>
+      <c r="I43" s="258"/>
+      <c r="J43" s="259"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="249" t="s">
+      <c r="T43" s="284" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="250"/>
-      <c r="V43" s="250"/>
-      <c r="W43" s="250"/>
-      <c r="X43" s="250"/>
-      <c r="Y43" s="250"/>
-      <c r="Z43" s="250"/>
-      <c r="AA43" s="250"/>
-      <c r="AB43" s="250"/>
-      <c r="AC43" s="251"/>
+      <c r="U43" s="285"/>
+      <c r="V43" s="285"/>
+      <c r="W43" s="285"/>
+      <c r="X43" s="285"/>
+      <c r="Y43" s="285"/>
+      <c r="Z43" s="285"/>
+      <c r="AA43" s="285"/>
+      <c r="AB43" s="285"/>
+      <c r="AC43" s="286"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7980,21 +7966,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="294" t="s">
+      <c r="S44" s="382" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="296" t="s">
+      <c r="T44" s="384" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="297"/>
-      <c r="V44" s="297"/>
-      <c r="W44" s="297"/>
-      <c r="X44" s="297"/>
-      <c r="Y44" s="297"/>
-      <c r="Z44" s="297"/>
-      <c r="AA44" s="297"/>
-      <c r="AB44" s="297"/>
-      <c r="AC44" s="298"/>
+      <c r="U44" s="385"/>
+      <c r="V44" s="385"/>
+      <c r="W44" s="385"/>
+      <c r="X44" s="385"/>
+      <c r="Y44" s="385"/>
+      <c r="Z44" s="385"/>
+      <c r="AA44" s="385"/>
+      <c r="AB44" s="385"/>
+      <c r="AC44" s="386"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -8012,26 +7998,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="302" t="s">
+      <c r="G45" s="328" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="244"/>
-      <c r="I45" s="244"/>
-      <c r="J45" s="245"/>
+      <c r="H45" s="279"/>
+      <c r="I45" s="279"/>
+      <c r="J45" s="280"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="295"/>
-      <c r="T45" s="299"/>
-      <c r="U45" s="300"/>
-      <c r="V45" s="300"/>
-      <c r="W45" s="300"/>
-      <c r="X45" s="300"/>
-      <c r="Y45" s="300"/>
-      <c r="Z45" s="300"/>
-      <c r="AA45" s="300"/>
-      <c r="AB45" s="300"/>
-      <c r="AC45" s="301"/>
+      <c r="S45" s="383"/>
+      <c r="T45" s="387"/>
+      <c r="U45" s="388"/>
+      <c r="V45" s="388"/>
+      <c r="W45" s="388"/>
+      <c r="X45" s="388"/>
+      <c r="Y45" s="388"/>
+      <c r="Z45" s="388"/>
+      <c r="AA45" s="388"/>
+      <c r="AB45" s="388"/>
+      <c r="AC45" s="389"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -8049,28 +8035,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="303"/>
-      <c r="H46" s="304"/>
-      <c r="I46" s="304"/>
-      <c r="J46" s="305"/>
+      <c r="G46" s="332"/>
+      <c r="H46" s="333"/>
+      <c r="I46" s="333"/>
+      <c r="J46" s="334"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="246" t="s">
+      <c r="T46" s="281" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="247"/>
-      <c r="V46" s="247"/>
-      <c r="W46" s="247"/>
-      <c r="X46" s="247"/>
-      <c r="Y46" s="247"/>
-      <c r="Z46" s="247"/>
-      <c r="AA46" s="247"/>
-      <c r="AB46" s="247"/>
-      <c r="AC46" s="248"/>
+      <c r="U46" s="282"/>
+      <c r="V46" s="282"/>
+      <c r="W46" s="282"/>
+      <c r="X46" s="282"/>
+      <c r="Y46" s="282"/>
+      <c r="Z46" s="282"/>
+      <c r="AA46" s="282"/>
+      <c r="AB46" s="282"/>
+      <c r="AC46" s="283"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8088,12 +8074,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="268" t="s">
+      <c r="G47" s="258" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="268"/>
-      <c r="I47" s="268"/>
-      <c r="J47" s="269"/>
+      <c r="H47" s="258"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="259"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8138,11 +8124,11 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="368" t="s">
+      <c r="AA48" s="298" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="369"/>
-      <c r="AC48" s="370"/>
+      <c r="AB48" s="299"/>
+      <c r="AC48" s="300"/>
     </row>
     <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
@@ -8160,12 +8146,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="302" t="s">
+      <c r="G49" s="328" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="244"/>
-      <c r="I49" s="244"/>
-      <c r="J49" s="245"/>
+      <c r="H49" s="279"/>
+      <c r="I49" s="279"/>
+      <c r="J49" s="280"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8181,9 +8167,9 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="371"/>
-      <c r="AB49" s="372"/>
-      <c r="AC49" s="373"/>
+      <c r="AA49" s="301"/>
+      <c r="AB49" s="302"/>
+      <c r="AC49" s="303"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
@@ -8201,10 +8187,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="306"/>
-      <c r="H50" s="307"/>
-      <c r="I50" s="307"/>
-      <c r="J50" s="308"/>
+      <c r="G50" s="329"/>
+      <c r="H50" s="330"/>
+      <c r="I50" s="330"/>
+      <c r="J50" s="331"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8222,35 +8208,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="303"/>
-      <c r="H51" s="304"/>
-      <c r="I51" s="304"/>
-      <c r="J51" s="305"/>
-      <c r="R51" s="364" t="s">
+      <c r="G51" s="332"/>
+      <c r="H51" s="333"/>
+      <c r="I51" s="333"/>
+      <c r="J51" s="334"/>
+      <c r="R51" s="316" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="348" t="s">
+      <c r="S51" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="360" t="s">
+      <c r="T51" s="320" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="360"/>
-      <c r="V51" s="361"/>
+      <c r="U51" s="320"/>
+      <c r="V51" s="321"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="241" t="s">
+      <c r="B52" s="273" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="242"/>
-      <c r="D52" s="242"/>
-      <c r="E52" s="242"/>
-      <c r="F52" s="243"/>
-      <c r="R52" s="385"/>
-      <c r="S52" s="349"/>
-      <c r="T52" s="362"/>
-      <c r="U52" s="362"/>
-      <c r="V52" s="363"/>
+      <c r="C52" s="274"/>
+      <c r="D52" s="274"/>
+      <c r="E52" s="274"/>
+      <c r="F52" s="275"/>
+      <c r="R52" s="317"/>
+      <c r="S52" s="319"/>
+      <c r="T52" s="322"/>
+      <c r="U52" s="322"/>
+      <c r="V52" s="323"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8259,67 +8245,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="380" t="s">
+      <c r="T53" s="311" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="380"/>
-      <c r="V53" s="381"/>
+      <c r="U53" s="311"/>
+      <c r="V53" s="312"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="350" t="s">
+      <c r="B54" s="337" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="348" t="s">
+      <c r="C54" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="360" t="s">
+      <c r="D54" s="320" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="361"/>
-      <c r="H54" s="364" t="s">
+      <c r="E54" s="321"/>
+      <c r="H54" s="316" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="348" t="s">
+      <c r="I54" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="374" t="s">
+      <c r="J54" s="304" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="375"/>
-      <c r="L54" s="376"/>
+      <c r="K54" s="305"/>
+      <c r="L54" s="306"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="386" t="s">
+      <c r="T54" s="324" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="386"/>
-      <c r="V54" s="353"/>
+      <c r="U54" s="324"/>
+      <c r="V54" s="325"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="351"/>
-      <c r="C55" s="349"/>
-      <c r="D55" s="362"/>
-      <c r="E55" s="363"/>
-      <c r="H55" s="365"/>
-      <c r="I55" s="366"/>
-      <c r="J55" s="339"/>
-      <c r="K55" s="377"/>
-      <c r="L55" s="378"/>
+      <c r="B55" s="338"/>
+      <c r="C55" s="319"/>
+      <c r="D55" s="322"/>
+      <c r="E55" s="323"/>
+      <c r="H55" s="335"/>
+      <c r="I55" s="336"/>
+      <c r="J55" s="307"/>
+      <c r="K55" s="308"/>
+      <c r="L55" s="309"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="386" t="s">
+      <c r="T55" s="324" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="386"/>
-      <c r="V55" s="353"/>
+      <c r="U55" s="324"/>
+      <c r="V55" s="325"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8328,36 +8314,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="252" t="s">
+      <c r="D56" s="287" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="254"/>
+      <c r="E56" s="289"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="379" t="s">
+      <c r="J56" s="310" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="380"/>
-      <c r="L56" s="381"/>
-      <c r="M56" s="267" t="s">
+      <c r="K56" s="311"/>
+      <c r="L56" s="312"/>
+      <c r="M56" s="257" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="269"/>
+      <c r="N56" s="259"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="386" t="s">
+      <c r="T56" s="324" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="386"/>
-      <c r="V56" s="353"/>
+      <c r="U56" s="324"/>
+      <c r="V56" s="325"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8366,36 +8352,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="352" t="s">
+      <c r="D57" s="326" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="353"/>
-      <c r="F57" s="267" t="s">
+      <c r="E57" s="325"/>
+      <c r="F57" s="257" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="269"/>
+      <c r="G57" s="259"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="382" t="s">
+      <c r="J57" s="313" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="383"/>
-      <c r="L57" s="384"/>
+      <c r="K57" s="314"/>
+      <c r="L57" s="315"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="386" t="s">
+      <c r="T57" s="324" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="386"/>
-      <c r="V57" s="353"/>
+      <c r="U57" s="324"/>
+      <c r="V57" s="325"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8404,32 +8390,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="352" t="s">
+      <c r="D58" s="326" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="353"/>
+      <c r="E58" s="325"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="382" t="s">
+      <c r="J58" s="313" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="383"/>
-      <c r="L58" s="384"/>
+      <c r="K58" s="314"/>
+      <c r="L58" s="315"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="386" t="s">
+      <c r="T58" s="324" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="386"/>
-      <c r="V58" s="353"/>
+      <c r="U58" s="324"/>
+      <c r="V58" s="325"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8438,32 +8424,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="352" t="s">
+      <c r="D59" s="326" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="353"/>
+      <c r="E59" s="325"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="382" t="s">
+      <c r="J59" s="313" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="383"/>
-      <c r="L59" s="384"/>
+      <c r="K59" s="314"/>
+      <c r="L59" s="315"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="386" t="s">
+      <c r="T59" s="324" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="386"/>
-      <c r="V59" s="353"/>
+      <c r="U59" s="324"/>
+      <c r="V59" s="325"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8473,32 +8459,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="352" t="s">
+      <c r="D60" s="326" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="353"/>
+      <c r="E60" s="325"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="382" t="s">
+      <c r="J60" s="313" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="383"/>
-      <c r="L60" s="384"/>
+      <c r="K60" s="314"/>
+      <c r="L60" s="315"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="386" t="s">
-        <v>461</v>
-      </c>
-      <c r="U60" s="386"/>
-      <c r="V60" s="353"/>
+      <c r="T60" s="324" t="s">
+        <v>459</v>
+      </c>
+      <c r="U60" s="324"/>
+      <c r="V60" s="325"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8507,101 +8493,101 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="352" t="s">
+      <c r="D61" s="326" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="353"/>
+      <c r="E61" s="325"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="382"/>
-      <c r="K61" s="383"/>
-      <c r="L61" s="384"/>
+      <c r="J61" s="313"/>
+      <c r="K61" s="314"/>
+      <c r="L61" s="315"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="386"/>
-      <c r="U61" s="386"/>
-      <c r="V61" s="353"/>
+      <c r="T61" s="324"/>
+      <c r="U61" s="324"/>
+      <c r="V61" s="325"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="352"/>
-      <c r="E62" s="353"/>
+      <c r="D62" s="326"/>
+      <c r="E62" s="325"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="382"/>
-      <c r="K62" s="383"/>
-      <c r="L62" s="384"/>
+      <c r="J62" s="313"/>
+      <c r="K62" s="314"/>
+      <c r="L62" s="315"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="386"/>
-      <c r="U62" s="386"/>
-      <c r="V62" s="353"/>
+      <c r="T62" s="324"/>
+      <c r="U62" s="324"/>
+      <c r="V62" s="325"/>
     </row>
     <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="352"/>
-      <c r="E63" s="353"/>
+      <c r="D63" s="326"/>
+      <c r="E63" s="325"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="382"/>
-      <c r="K63" s="383"/>
-      <c r="L63" s="384"/>
+      <c r="J63" s="313"/>
+      <c r="K63" s="314"/>
+      <c r="L63" s="315"/>
       <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
       <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="386"/>
-      <c r="U63" s="386"/>
-      <c r="V63" s="353"/>
+      <c r="T63" s="324"/>
+      <c r="U63" s="324"/>
+      <c r="V63" s="325"/>
     </row>
     <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="352"/>
-      <c r="E64" s="353"/>
+      <c r="D64" s="326"/>
+      <c r="E64" s="325"/>
       <c r="R64" s="163" t="s">
+        <v>456</v>
+      </c>
+      <c r="S64" s="161" t="s">
+        <v>457</v>
+      </c>
+      <c r="T64" s="296" t="s">
         <v>458</v>
       </c>
-      <c r="S64" s="161" t="s">
-        <v>459</v>
-      </c>
-      <c r="T64" s="367" t="s">
-        <v>460</v>
-      </c>
-      <c r="U64" s="367"/>
-      <c r="V64" s="359"/>
+      <c r="U64" s="296"/>
+      <c r="V64" s="297"/>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="352"/>
-      <c r="E65" s="353"/>
+      <c r="D65" s="326"/>
+      <c r="E65" s="325"/>
       <c r="T65" s="166"/>
     </row>
     <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8609,96 +8595,172 @@
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="352"/>
-      <c r="E66" s="353"/>
+      <c r="D66" s="326"/>
+      <c r="E66" s="325"/>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="352"/>
-      <c r="E67" s="353"/>
+      <c r="D67" s="326"/>
+      <c r="E67" s="325"/>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="352"/>
-      <c r="E68" s="353"/>
+      <c r="D68" s="326"/>
+      <c r="E68" s="325"/>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="352"/>
-      <c r="E69" s="353"/>
+      <c r="D69" s="326"/>
+      <c r="E69" s="325"/>
     </row>
     <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="352"/>
-      <c r="E70" s="353"/>
+      <c r="D70" s="326"/>
+      <c r="E70" s="325"/>
     </row>
     <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="358"/>
-      <c r="E71" s="359"/>
+      <c r="D71" s="327"/>
+      <c r="E71" s="297"/>
     </row>
     <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="T64:V64"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="D57:E57"/>
@@ -8723,126 +8785,50 @@
     <mergeCell ref="N20:P20"/>
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8897,35 +8883,35 @@
       <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="G2" s="244" t="s">
+      <c r="G2" s="279" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="244"/>
-      <c r="I2" s="244"/>
-      <c r="J2" s="245"/>
-      <c r="L2" s="258" t="s">
+      <c r="H2" s="279"/>
+      <c r="I2" s="279"/>
+      <c r="J2" s="280"/>
+      <c r="L2" s="248" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="259"/>
-      <c r="N2" s="259"/>
-      <c r="O2" s="260"/>
+      <c r="M2" s="249"/>
+      <c r="N2" s="249"/>
+      <c r="O2" s="250"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="261" t="s">
+      <c r="Q2" s="251" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="253"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="255" t="s">
+      <c r="V2" s="245" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256"/>
-      <c r="AB2" s="257"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="247"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
@@ -8946,11 +8932,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="252" t="s">
+      <c r="H3" s="287" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="253"/>
-      <c r="J3" s="254"/>
+      <c r="I3" s="288"/>
+      <c r="J3" s="289"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8989,11 +8975,11 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="276" t="s">
+      <c r="Z3" s="264" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="277"/>
-      <c r="AB3" s="278"/>
+      <c r="AA3" s="265"/>
+      <c r="AB3" s="266"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
@@ -9014,11 +9000,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="249">
+      <c r="H4" s="284">
         <v>63</v>
       </c>
-      <c r="I4" s="250"/>
-      <c r="J4" s="251"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="286"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9057,11 +9043,11 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="279" t="s">
+      <c r="Z4" s="267" t="s">
         <v>421</v>
       </c>
-      <c r="AA4" s="280"/>
-      <c r="AB4" s="281"/>
+      <c r="AA4" s="268"/>
+      <c r="AB4" s="269"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
@@ -9082,11 +9068,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="249">
+      <c r="H5" s="284">
         <v>31</v>
       </c>
-      <c r="I5" s="250"/>
-      <c r="J5" s="251"/>
+      <c r="I5" s="285"/>
+      <c r="J5" s="286"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9125,9 +9111,9 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="279"/>
-      <c r="AA5" s="280"/>
-      <c r="AB5" s="281"/>
+      <c r="Z5" s="267"/>
+      <c r="AA5" s="268"/>
+      <c r="AB5" s="269"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
@@ -9148,11 +9134,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="246">
+      <c r="H6" s="281">
         <v>7</v>
       </c>
-      <c r="I6" s="247"/>
-      <c r="J6" s="248"/>
+      <c r="I6" s="282"/>
+      <c r="J6" s="283"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -9191,9 +9177,9 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="282"/>
-      <c r="AA6" s="283"/>
-      <c r="AB6" s="284"/>
+      <c r="Z6" s="270"/>
+      <c r="AA6" s="271"/>
+      <c r="AB6" s="272"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
@@ -9214,12 +9200,12 @@
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="234" t="str">
+      <c r="H7" s="276" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="235"/>
-      <c r="J7" s="236"/>
+      <c r="I7" s="277"/>
+      <c r="J7" s="278"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -9266,18 +9252,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="234" t="str">
+      <c r="H8" s="276" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="235"/>
-      <c r="J8" s="236"/>
-      <c r="L8" s="267" t="s">
+      <c r="I8" s="277"/>
+      <c r="J8" s="278"/>
+      <c r="L8" s="257" t="s">
         <v>417</v>
       </c>
-      <c r="M8" s="268"/>
-      <c r="N8" s="268"/>
-      <c r="O8" s="269"/>
+      <c r="M8" s="258"/>
+      <c r="N8" s="258"/>
+      <c r="O8" s="259"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9292,14 +9278,14 @@
         <v>239</v>
       </c>
       <c r="U8" s="114"/>
-      <c r="V8" s="230" t="s">
-        <v>453</v>
-      </c>
-      <c r="W8" s="270" t="s">
-        <v>454</v>
-      </c>
-      <c r="X8" s="271"/>
-      <c r="Y8" s="229"/>
+      <c r="V8" s="225" t="s">
+        <v>451</v>
+      </c>
+      <c r="W8" s="260" t="s">
+        <v>452</v>
+      </c>
+      <c r="X8" s="261"/>
+      <c r="Y8" s="224"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="187" t="s">
@@ -9338,10 +9324,10 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="272" t="s">
-        <v>456</v>
-      </c>
-      <c r="X9" s="273"/>
+      <c r="W9" s="262" t="s">
+        <v>454</v>
+      </c>
+      <c r="X9" s="263"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
@@ -9372,10 +9358,10 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="274" t="s">
-        <v>455</v>
-      </c>
-      <c r="X10" s="275"/>
+      <c r="W10" s="243" t="s">
+        <v>453</v>
+      </c>
+      <c r="X10" s="244"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
@@ -9402,20 +9388,20 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="264" t="s">
+      <c r="Q11" s="254" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="265"/>
-      <c r="S11" s="265"/>
-      <c r="T11" s="266"/>
+      <c r="R11" s="255"/>
+      <c r="S11" s="255"/>
+      <c r="T11" s="256"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="274" t="s">
+      <c r="W11" s="243" t="s">
         <v>425</v>
       </c>
-      <c r="X11" s="275"/>
+      <c r="X11" s="244"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
@@ -9456,10 +9442,10 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="274" t="s">
-        <v>462</v>
-      </c>
-      <c r="X12" s="275"/>
+      <c r="W12" s="243" t="s">
+        <v>460</v>
+      </c>
+      <c r="X12" s="244"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
@@ -9500,8 +9486,8 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="274"/>
-      <c r="X13" s="275"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="244"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
@@ -9542,8 +9528,8 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="274"/>
-      <c r="X14" s="275"/>
+      <c r="W14" s="243"/>
+      <c r="X14" s="244"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
@@ -9584,8 +9570,8 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="274"/>
-      <c r="X15" s="275"/>
+      <c r="W15" s="243"/>
+      <c r="X15" s="244"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
@@ -9616,8 +9602,8 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="274"/>
-      <c r="X16" s="275"/>
+      <c r="W16" s="243"/>
+      <c r="X16" s="244"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
@@ -9645,11 +9631,11 @@
       <c r="T17" s="138" t="s">
         <v>258</v>
       </c>
-      <c r="V17" s="231">
+      <c r="V17" s="226">
         <v>9</v>
       </c>
-      <c r="W17" s="285"/>
-      <c r="X17" s="286"/>
+      <c r="W17" s="241"/>
+      <c r="X17" s="242"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9668,18 +9654,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="241" t="s">
+      <c r="G19" s="273" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="242"/>
-      <c r="I19" s="242"/>
-      <c r="J19" s="243"/>
+      <c r="H19" s="274"/>
+      <c r="I19" s="274"/>
+      <c r="J19" s="275"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="232" t="s">
+      <c r="C20" s="290" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9691,16 +9677,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="237" t="s">
-        <v>457</v>
-      </c>
-      <c r="H20" s="238"/>
-      <c r="I20" s="238"/>
-      <c r="J20" s="239"/>
+      <c r="G20" s="292" t="s">
+        <v>455</v>
+      </c>
+      <c r="H20" s="293"/>
+      <c r="I20" s="293"/>
+      <c r="J20" s="294"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="240"/>
+      <c r="C21" s="295"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9710,16 +9696,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="234" t="s">
+      <c r="G21" s="276" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="235"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="236"/>
+      <c r="H21" s="277"/>
+      <c r="I21" s="277"/>
+      <c r="J21" s="278"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="233"/>
+      <c r="C22" s="291"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9738,7 +9724,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="232" t="s">
+      <c r="C23" s="290" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9757,7 +9743,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="233"/>
+      <c r="C24" s="291"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9776,7 +9762,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="232" t="s">
+      <c r="C25" s="290" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9795,7 +9781,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="233"/>
+      <c r="C26" s="291"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9814,7 +9800,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="232" t="s">
+      <c r="C27" s="290" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9833,7 +9819,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="233"/>
+      <c r="C28" s="291"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9873,7 +9859,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="232" t="s">
+      <c r="C30" s="290" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9892,7 +9878,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="233"/>
+      <c r="C31" s="291"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9911,7 +9897,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="232" t="s">
+      <c r="C32" s="290" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9930,7 +9916,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="233"/>
+      <c r="C33" s="291"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9947,12 +9933,22 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9964,22 +9960,12 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9994,52 +9980,51 @@
   <cols>
     <col min="2" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="424"/>
-      <c r="B1" s="425"/>
-      <c r="C1" s="425"/>
-      <c r="D1" s="425"/>
-      <c r="E1" s="425"/>
-      <c r="F1" s="425"/>
-      <c r="G1" s="425"/>
-      <c r="H1" s="425"/>
-      <c r="I1" s="426"/>
-      <c r="J1" s="424"/>
-      <c r="K1" s="425"/>
-      <c r="L1" s="425"/>
-      <c r="M1" s="425"/>
-      <c r="N1" s="425"/>
-      <c r="O1" s="426"/>
+      <c r="A1" s="227"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="229"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="427"/>
-      <c r="B2" s="391" t="s">
+      <c r="A2" s="230"/>
+      <c r="B2" s="406" t="s">
         <v>425</v>
       </c>
-      <c r="C2" s="392"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="394"/>
-      <c r="I2" s="428"/>
-      <c r="J2" s="427"/>
-      <c r="K2" s="435" t="s">
-        <v>463</v>
-      </c>
-      <c r="L2" s="436"/>
-      <c r="M2" s="436"/>
-      <c r="N2" s="437"/>
-      <c r="O2" s="428"/>
+      <c r="C2" s="407"/>
+      <c r="D2" s="407"/>
+      <c r="E2" s="407"/>
+      <c r="F2" s="407"/>
+      <c r="G2" s="408"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="406" t="s">
+        <v>461</v>
+      </c>
+      <c r="L2" s="407"/>
+      <c r="M2" s="407"/>
+      <c r="N2" s="408"/>
+      <c r="O2" s="231"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="427"/>
+      <c r="A3" s="230"/>
       <c r="B3" s="194" t="s">
         <v>424</v>
       </c>
@@ -10050,453 +10035,396 @@
         <v>427</v>
       </c>
       <c r="E3" s="195" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="430" t="s">
         <v>428</v>
       </c>
-      <c r="F3" s="195" t="s">
-        <v>430</v>
-      </c>
-      <c r="G3" s="389" t="s">
-        <v>429</v>
-      </c>
-      <c r="H3" s="390"/>
-      <c r="I3" s="428"/>
-      <c r="J3" s="427"/>
+      <c r="G3" s="431"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="230"/>
       <c r="K3" s="194" t="s">
         <v>424</v>
       </c>
       <c r="L3" s="195" t="s">
-        <v>430</v>
-      </c>
-      <c r="M3" s="389" t="s">
         <v>429</v>
       </c>
-      <c r="N3" s="390"/>
-      <c r="O3" s="428"/>
+      <c r="M3" s="398" t="s">
+        <v>428</v>
+      </c>
+      <c r="N3" s="399"/>
+      <c r="O3" s="231"/>
     </row>
     <row r="4" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="427"/>
+      <c r="A4" s="230"/>
       <c r="B4" s="196">
         <v>0</v>
       </c>
-      <c r="C4" s="202"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="442" t="s">
+      <c r="C4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="395" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4" s="396"/>
-      <c r="I4" s="428"/>
-      <c r="J4" s="427"/>
+      <c r="F4" s="436" t="s">
+        <v>435</v>
+      </c>
+      <c r="G4" s="437"/>
+      <c r="I4" s="231"/>
+      <c r="J4" s="230"/>
       <c r="K4" s="196">
         <v>0</v>
       </c>
-      <c r="L4" s="439" t="s">
+      <c r="L4" s="236" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="395" t="s">
-        <v>436</v>
-      </c>
-      <c r="N4" s="396"/>
-      <c r="O4" s="428"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="427"/>
+      <c r="M4" s="400" t="s">
+        <v>435</v>
+      </c>
+      <c r="N4" s="401"/>
+      <c r="O4" s="231"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="230"/>
       <c r="B5" s="197">
         <v>1</v>
       </c>
       <c r="C5" s="198" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="218" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" s="219" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" s="438" t="s">
         <v>439</v>
       </c>
-      <c r="D5" s="227"/>
-      <c r="E5" s="222" t="s">
-        <v>441</v>
-      </c>
-      <c r="F5" s="223" t="s">
-        <v>431</v>
-      </c>
-      <c r="G5" s="387" t="s">
-        <v>440</v>
-      </c>
-      <c r="H5" s="388"/>
-      <c r="I5" s="428"/>
-      <c r="J5" s="427"/>
+      <c r="G5" s="439"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="230"/>
       <c r="K5" s="197">
         <v>1</v>
       </c>
-      <c r="L5" s="440" t="s">
-        <v>464</v>
-      </c>
-      <c r="M5" s="387" t="s">
-        <v>465</v>
-      </c>
-      <c r="N5" s="388"/>
-      <c r="O5" s="428"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="427"/>
+      <c r="L5" s="237" t="s">
+        <v>462</v>
+      </c>
+      <c r="M5" s="402" t="s">
+        <v>463</v>
+      </c>
+      <c r="N5" s="403"/>
+      <c r="O5" s="231"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="230"/>
       <c r="B6" s="197">
         <v>2</v>
       </c>
-      <c r="C6" s="228"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="200" t="s">
-        <v>441</v>
-      </c>
-      <c r="F6" s="223" t="s">
-        <v>432</v>
-      </c>
-      <c r="G6" s="387" t="s">
-        <v>437</v>
-      </c>
-      <c r="H6" s="388"/>
-      <c r="I6" s="428"/>
-      <c r="J6" s="427"/>
-      <c r="K6" s="201">
+      <c r="C6" s="223"/>
+      <c r="D6" s="199" t="s">
+        <v>440</v>
+      </c>
+      <c r="E6" s="219" t="s">
+        <v>431</v>
+      </c>
+      <c r="F6" s="438" t="s">
+        <v>436</v>
+      </c>
+      <c r="G6" s="439"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="200">
         <v>2</v>
       </c>
-      <c r="L6" s="441" t="s">
+      <c r="L6" s="238" t="s">
         <v>308</v>
       </c>
-      <c r="M6" s="433" t="s">
-        <v>466</v>
-      </c>
-      <c r="N6" s="434"/>
-      <c r="O6" s="428"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="427"/>
+      <c r="M6" s="404" t="s">
+        <v>464</v>
+      </c>
+      <c r="N6" s="405"/>
+      <c r="O6" s="231"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="230"/>
       <c r="B7" s="197">
         <v>3</v>
       </c>
-      <c r="C7" s="207"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="223" t="s">
-        <v>433</v>
-      </c>
-      <c r="G7" s="387" t="s">
-        <v>438</v>
-      </c>
-      <c r="H7" s="388"/>
-      <c r="I7" s="428"/>
-      <c r="J7" s="427"/>
-      <c r="K7" s="429"/>
-      <c r="L7" s="429"/>
-      <c r="M7" s="429"/>
-      <c r="N7" s="429"/>
-      <c r="O7" s="428"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="427"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="219" t="s">
+        <v>432</v>
+      </c>
+      <c r="F7" s="438" t="s">
+        <v>437</v>
+      </c>
+      <c r="G7" s="439"/>
+      <c r="I7" s="231"/>
+      <c r="J7" s="230"/>
+      <c r="O7" s="231"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="230"/>
       <c r="B8" s="197">
         <v>4</v>
       </c>
       <c r="C8" s="198" t="s">
+        <v>441</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="219" t="s">
+        <v>433</v>
+      </c>
+      <c r="F8" s="438" t="s">
         <v>442</v>
       </c>
-      <c r="D8" s="199" t="s">
+      <c r="G8" s="439"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="396" t="s">
         <v>443</v>
       </c>
-      <c r="E8" s="206"/>
-      <c r="F8" s="223" t="s">
-        <v>434</v>
-      </c>
-      <c r="G8" s="387" t="s">
-        <v>444</v>
-      </c>
-      <c r="H8" s="388"/>
-      <c r="I8" s="428"/>
-      <c r="J8" s="427"/>
-      <c r="K8" s="413" t="s">
-        <v>445</v>
-      </c>
-      <c r="L8" s="218">
+      <c r="L8" s="214">
         <v>2</v>
       </c>
-      <c r="M8" s="218">
+      <c r="M8" s="214">
         <v>1</v>
       </c>
-      <c r="N8" s="219">
-        <v>0</v>
-      </c>
-      <c r="O8" s="428"/>
+      <c r="N8" s="215">
+        <v>0</v>
+      </c>
+      <c r="O8" s="231"/>
     </row>
     <row r="9" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="427"/>
+      <c r="A9" s="230"/>
       <c r="B9" s="197">
         <v>5</v>
       </c>
-      <c r="C9" s="207"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="224" t="s">
-        <v>435</v>
-      </c>
-      <c r="G9" s="406"/>
-      <c r="H9" s="407"/>
-      <c r="I9" s="428"/>
-      <c r="J9" s="427"/>
-      <c r="K9" s="414"/>
-      <c r="L9" s="221"/>
-      <c r="M9" s="221"/>
-      <c r="N9" s="438" t="s">
-        <v>467</v>
-      </c>
-      <c r="O9" s="428"/>
+      <c r="C9" s="204"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="220" t="s">
+        <v>434</v>
+      </c>
+      <c r="F9" s="432"/>
+      <c r="G9" s="433"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="397"/>
+      <c r="L9" s="217"/>
+      <c r="M9" s="217"/>
+      <c r="N9" s="235" t="s">
+        <v>465</v>
+      </c>
+      <c r="O9" s="231"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="427"/>
+      <c r="A10" s="230"/>
       <c r="B10" s="197">
         <v>6</v>
       </c>
-      <c r="C10" s="207"/>
-      <c r="D10" s="205"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="225" t="s">
-        <v>435</v>
-      </c>
-      <c r="G10" s="406"/>
-      <c r="H10" s="407"/>
-      <c r="I10" s="428"/>
-      <c r="J10" s="427"/>
-      <c r="K10" s="429"/>
-      <c r="L10" s="429"/>
-      <c r="M10" s="429"/>
-      <c r="N10" s="429"/>
-      <c r="O10" s="428"/>
+      <c r="C10" s="204"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="221" t="s">
+        <v>434</v>
+      </c>
+      <c r="F10" s="432"/>
+      <c r="G10" s="433"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="230"/>
+      <c r="O10" s="231"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="427"/>
-      <c r="B11" s="201">
+      <c r="A11" s="230"/>
+      <c r="B11" s="200">
         <v>7</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="209"/>
-      <c r="E11" s="210"/>
-      <c r="F11" s="226" t="s">
-        <v>435</v>
-      </c>
-      <c r="G11" s="408"/>
-      <c r="H11" s="409"/>
-      <c r="I11" s="428"/>
-      <c r="J11" s="430"/>
-      <c r="K11" s="431"/>
-      <c r="L11" s="431"/>
-      <c r="M11" s="431"/>
-      <c r="N11" s="431"/>
-      <c r="O11" s="432"/>
+      <c r="C11" s="205"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="222" t="s">
+        <v>434</v>
+      </c>
+      <c r="F11" s="434"/>
+      <c r="G11" s="435"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="233"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="234"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="427"/>
-      <c r="B12" s="429"/>
-      <c r="C12" s="429"/>
-      <c r="D12" s="429"/>
-      <c r="E12" s="429"/>
-      <c r="F12" s="429"/>
-      <c r="G12" s="429"/>
-      <c r="H12" s="429"/>
-      <c r="I12" s="428"/>
-      <c r="O12" s="443"/>
+      <c r="A12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="O12" s="240"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="427"/>
-      <c r="B13" s="212" t="s">
+      <c r="A13" s="230"/>
+      <c r="B13" s="208" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" s="427" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="428"/>
+      <c r="E13" s="429"/>
+      <c r="I13" s="231"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="230"/>
+      <c r="B14" s="209">
+        <v>0</v>
+      </c>
+      <c r="C14" s="418" t="s">
+        <v>449</v>
+      </c>
+      <c r="D14" s="419"/>
+      <c r="E14" s="420"/>
+      <c r="I14" s="231"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="230"/>
+      <c r="B15" s="210">
+        <v>1</v>
+      </c>
+      <c r="C15" s="421" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="422"/>
+      <c r="E15" s="423"/>
+      <c r="I15" s="231"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="230"/>
+      <c r="B16" s="210">
+        <v>2</v>
+      </c>
+      <c r="C16" s="409" t="s">
+        <v>448</v>
+      </c>
+      <c r="D16" s="410"/>
+      <c r="E16" s="411"/>
+      <c r="I16" s="231"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="230"/>
+      <c r="B17" s="210">
+        <v>3</v>
+      </c>
+      <c r="C17" s="424" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="425"/>
+      <c r="E17" s="426"/>
+      <c r="I17" s="231"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="230"/>
+      <c r="B18" s="210">
+        <v>4</v>
+      </c>
+      <c r="C18" s="412"/>
+      <c r="D18" s="413"/>
+      <c r="E18" s="414"/>
+      <c r="I18" s="231"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="230"/>
+      <c r="B19" s="210">
+        <v>5</v>
+      </c>
+      <c r="C19" s="412"/>
+      <c r="D19" s="413"/>
+      <c r="E19" s="414"/>
+      <c r="I19" s="231"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="230"/>
+      <c r="B20" s="210">
+        <v>6</v>
+      </c>
+      <c r="C20" s="412"/>
+      <c r="D20" s="413"/>
+      <c r="E20" s="414"/>
+      <c r="I20" s="231"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="230"/>
+      <c r="B21" s="211">
+        <v>7</v>
+      </c>
+      <c r="C21" s="415"/>
+      <c r="D21" s="416"/>
+      <c r="E21" s="417"/>
+      <c r="I21" s="231"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="230"/>
+      <c r="I22" s="231"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="230"/>
+      <c r="B23" s="396" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="207">
+        <v>5</v>
+      </c>
+      <c r="D23" s="214">
+        <v>4</v>
+      </c>
+      <c r="E23" s="214">
+        <v>3</v>
+      </c>
+      <c r="F23" s="214">
+        <v>2</v>
+      </c>
+      <c r="G23" s="214">
+        <v>1</v>
+      </c>
+      <c r="H23" s="215">
+        <v>0</v>
+      </c>
+      <c r="I23" s="231"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="230"/>
+      <c r="B24" s="397"/>
+      <c r="C24" s="216"/>
+      <c r="D24" s="217"/>
+      <c r="E24" s="217"/>
+      <c r="F24" s="217"/>
+      <c r="G24" s="212" t="s">
         <v>446</v>
       </c>
-      <c r="C13" s="410" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="411"/>
-      <c r="E13" s="412"/>
-      <c r="F13" s="429"/>
-      <c r="G13" s="429"/>
-      <c r="H13" s="429"/>
-      <c r="I13" s="428"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="427"/>
-      <c r="B14" s="213">
-        <v>0</v>
-      </c>
-      <c r="C14" s="397" t="s">
-        <v>451</v>
-      </c>
-      <c r="D14" s="398"/>
-      <c r="E14" s="399"/>
-      <c r="F14" s="429"/>
-      <c r="G14" s="429"/>
-      <c r="H14" s="429"/>
-      <c r="I14" s="428"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="427"/>
-      <c r="B15" s="214">
-        <v>1</v>
-      </c>
-      <c r="C15" s="400" t="s">
-        <v>449</v>
-      </c>
-      <c r="D15" s="401"/>
-      <c r="E15" s="402"/>
-      <c r="F15" s="429"/>
-      <c r="G15" s="429"/>
-      <c r="H15" s="429"/>
-      <c r="I15" s="428"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="427"/>
-      <c r="B16" s="214">
-        <v>2</v>
-      </c>
-      <c r="C16" s="415" t="s">
-        <v>450</v>
-      </c>
-      <c r="D16" s="416"/>
-      <c r="E16" s="417"/>
-      <c r="F16" s="429"/>
-      <c r="G16" s="429"/>
-      <c r="H16" s="429"/>
-      <c r="I16" s="428"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="427"/>
-      <c r="B17" s="214">
-        <v>3</v>
-      </c>
-      <c r="C17" s="403" t="s">
-        <v>452</v>
-      </c>
-      <c r="D17" s="404"/>
-      <c r="E17" s="405"/>
-      <c r="F17" s="429"/>
-      <c r="G17" s="429"/>
-      <c r="H17" s="429"/>
-      <c r="I17" s="428"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="427"/>
-      <c r="B18" s="214">
-        <v>4</v>
-      </c>
-      <c r="C18" s="418"/>
-      <c r="D18" s="419"/>
-      <c r="E18" s="420"/>
-      <c r="F18" s="429"/>
-      <c r="G18" s="429"/>
-      <c r="H18" s="429"/>
-      <c r="I18" s="428"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="427"/>
-      <c r="B19" s="214">
-        <v>5</v>
-      </c>
-      <c r="C19" s="418"/>
-      <c r="D19" s="419"/>
-      <c r="E19" s="420"/>
-      <c r="F19" s="429"/>
-      <c r="G19" s="429"/>
-      <c r="H19" s="429"/>
-      <c r="I19" s="428"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="427"/>
-      <c r="B20" s="214">
-        <v>6</v>
-      </c>
-      <c r="C20" s="418"/>
-      <c r="D20" s="419"/>
-      <c r="E20" s="420"/>
-      <c r="F20" s="429"/>
-      <c r="G20" s="429"/>
-      <c r="H20" s="429"/>
-      <c r="I20" s="428"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="427"/>
-      <c r="B21" s="215">
-        <v>7</v>
-      </c>
-      <c r="C21" s="421"/>
-      <c r="D21" s="422"/>
-      <c r="E21" s="423"/>
-      <c r="F21" s="429"/>
-      <c r="G21" s="429"/>
-      <c r="H21" s="429"/>
-      <c r="I21" s="428"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="427"/>
-      <c r="B22" s="429"/>
-      <c r="C22" s="429"/>
-      <c r="D22" s="429"/>
-      <c r="E22" s="429"/>
-      <c r="F22" s="429"/>
-      <c r="G22" s="429"/>
-      <c r="H22" s="429"/>
-      <c r="I22" s="428"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="427"/>
-      <c r="B23" s="413" t="s">
+      <c r="H24" s="213" t="s">
         <v>445</v>
       </c>
-      <c r="C23" s="211">
-        <v>5</v>
-      </c>
-      <c r="D23" s="218">
-        <v>4</v>
-      </c>
-      <c r="E23" s="218">
-        <v>3</v>
-      </c>
-      <c r="F23" s="218">
-        <v>2</v>
-      </c>
-      <c r="G23" s="218">
-        <v>1</v>
-      </c>
-      <c r="H23" s="219">
-        <v>0</v>
-      </c>
-      <c r="I23" s="428"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="427"/>
-      <c r="B24" s="414"/>
-      <c r="C24" s="220"/>
-      <c r="D24" s="221"/>
-      <c r="E24" s="221"/>
-      <c r="F24" s="221"/>
-      <c r="G24" s="216" t="s">
-        <v>448</v>
-      </c>
-      <c r="H24" s="217" t="s">
-        <v>447</v>
-      </c>
-      <c r="I24" s="428"/>
+      <c r="I24" s="231"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="430"/>
-      <c r="B25" s="431"/>
-      <c r="C25" s="431"/>
-      <c r="D25" s="431"/>
-      <c r="E25" s="431"/>
-      <c r="F25" s="431"/>
-      <c r="G25" s="431"/>
-      <c r="H25" s="431"/>
-      <c r="I25" s="432"/>
+      <c r="A25" s="232"/>
+      <c r="B25" s="233"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="233"/>
+      <c r="E25" s="233"/>
+      <c r="F25" s="233"/>
+      <c r="G25" s="233"/>
+      <c r="H25" s="233"/>
+      <c r="I25" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C16:E16"/>
@@ -10507,17 +10435,12 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787BD476-9523-4D51-AED7-9AF633FAF38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E1875F-F608-4B78-A33B-6FABBF1EC8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="597" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="466">
   <si>
     <t>OpCode</t>
   </si>
@@ -2288,9 +2288,6 @@
     <t>Dato 2</t>
   </si>
   <si>
-    <t>Dato 3</t>
-  </si>
-  <si>
     <t>Descrip</t>
   </si>
   <si>
@@ -2333,9 +2330,6 @@
     <t>Addr</t>
   </si>
   <si>
-    <t>Length</t>
-  </si>
-  <si>
     <t xml:space="preserve">Escribe los bytes de la direccion dicha </t>
   </si>
   <si>
@@ -2388,6 +2382,24 @@
   </si>
   <si>
     <t xml:space="preserve">Valores que guardan las interrupciones en cola (mapa de bits). </t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Keyboard Controller</t>
+  </si>
+  <si>
+    <t>Cls</t>
+  </si>
+  <si>
+    <t>Limpia el buffer</t>
+  </si>
+  <si>
+    <t>Limpia el estado IRQ</t>
+  </si>
+  <si>
+    <t>Enable Keyboard</t>
   </si>
 </sst>
 </file>
@@ -3495,7 +3507,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="425">
+  <cellXfs count="440">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4091,9 +4103,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4103,15 +4112,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4119,9 +4122,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4147,9 +4147,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4162,7 +4159,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -4173,21 +4169,183 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4200,143 +4358,287 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4356,284 +4658,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4641,29 +4682,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4692,18 +4751,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4713,41 +4760,35 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5069,62 +5110,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="325" t="s">
+      <c r="B2" s="360" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="334" t="s">
+      <c r="C2" s="372" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="335"/>
-      <c r="E2" s="336" t="s">
+      <c r="D2" s="373"/>
+      <c r="E2" s="374" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="336"/>
-      <c r="G2" s="337" t="s">
+      <c r="F2" s="374"/>
+      <c r="G2" s="375" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="336"/>
-      <c r="I2" s="336" t="s">
+      <c r="H2" s="374"/>
+      <c r="I2" s="374" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="336"/>
-      <c r="K2" s="338" t="s">
+      <c r="J2" s="374"/>
+      <c r="K2" s="376" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="336"/>
-      <c r="M2" s="336"/>
-      <c r="N2" s="336"/>
-      <c r="O2" s="336"/>
-      <c r="P2" s="339"/>
-      <c r="R2" s="342" t="s">
+      <c r="L2" s="374"/>
+      <c r="M2" s="374"/>
+      <c r="N2" s="374"/>
+      <c r="O2" s="374"/>
+      <c r="P2" s="377"/>
+      <c r="R2" s="357" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="294" t="s">
+      <c r="S2" s="355" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="346" t="s">
+      <c r="T2" s="348" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="347"/>
-      <c r="V2" s="347"/>
-      <c r="W2" s="347"/>
-      <c r="X2" s="347"/>
-      <c r="Y2" s="347"/>
-      <c r="Z2" s="347"/>
-      <c r="AA2" s="347"/>
-      <c r="AB2" s="347" t="s">
+      <c r="U2" s="349"/>
+      <c r="V2" s="349"/>
+      <c r="W2" s="349"/>
+      <c r="X2" s="349"/>
+      <c r="Y2" s="349"/>
+      <c r="Z2" s="349"/>
+      <c r="AA2" s="349"/>
+      <c r="AB2" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="347"/>
-      <c r="AD2" s="347"/>
-      <c r="AE2" s="347"/>
-      <c r="AF2" s="347"/>
-      <c r="AG2" s="347"/>
-      <c r="AH2" s="347"/>
-      <c r="AI2" s="348"/>
+      <c r="AC2" s="349"/>
+      <c r="AD2" s="349"/>
+      <c r="AE2" s="349"/>
+      <c r="AF2" s="349"/>
+      <c r="AG2" s="349"/>
+      <c r="AH2" s="349"/>
+      <c r="AI2" s="350"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="326"/>
+      <c r="B3" s="361"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5149,21 +5190,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="331"/>
-      <c r="L3" s="332"/>
-      <c r="M3" s="332"/>
-      <c r="N3" s="332"/>
-      <c r="O3" s="332"/>
-      <c r="P3" s="333"/>
-      <c r="R3" s="343"/>
-      <c r="S3" s="340"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="371"/>
+      <c r="M3" s="371"/>
+      <c r="N3" s="371"/>
+      <c r="O3" s="371"/>
+      <c r="P3" s="340"/>
+      <c r="R3" s="358"/>
+      <c r="S3" s="307"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="312" t="s">
+      <c r="U3" s="381" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="312"/>
+      <c r="V3" s="381"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5176,10 +5217,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="345" t="s">
+      <c r="AA3" s="347" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="345"/>
+      <c r="AB3" s="347"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5203,21 +5244,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="327"/>
+      <c r="B4" s="362"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="313" t="s">
+      <c r="E4" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
-      <c r="H4" s="243"/>
-      <c r="I4" s="243"/>
-      <c r="J4" s="244"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="275"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5227,20 +5268,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="313" t="s">
+      <c r="N4" s="351" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="243"/>
-      <c r="P4" s="244"/>
-      <c r="R4" s="344"/>
-      <c r="S4" s="341"/>
+      <c r="O4" s="274"/>
+      <c r="P4" s="275"/>
+      <c r="R4" s="359"/>
+      <c r="S4" s="356"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="313" t="s">
+      <c r="U4" s="351" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="314"/>
+      <c r="V4" s="352"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5253,10 +5294,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="313" t="s">
+      <c r="AA4" s="351" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="314"/>
+      <c r="AB4" s="352"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5288,22 +5329,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="317"/>
-      <c r="F5" s="318"/>
-      <c r="G5" s="318"/>
-      <c r="H5" s="318"/>
-      <c r="I5" s="318"/>
-      <c r="J5" s="319"/>
+      <c r="E5" s="378"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="379"/>
+      <c r="J5" s="380"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="253" t="s">
+      <c r="N5" s="287" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="254"/>
-      <c r="P5" s="255"/>
+      <c r="O5" s="288"/>
+      <c r="P5" s="289"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5313,10 +5354,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="315" t="s">
+      <c r="U5" s="353" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="316"/>
+      <c r="V5" s="354"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5329,10 +5370,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="315" t="s">
+      <c r="AA5" s="353" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="316"/>
+      <c r="AB5" s="354"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5364,12 +5405,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="324"/>
-      <c r="F6" s="321"/>
-      <c r="G6" s="321"/>
-      <c r="H6" s="321"/>
-      <c r="I6" s="321"/>
-      <c r="J6" s="322"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="365"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5377,11 +5418,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="250" t="s">
+      <c r="N6" s="284" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="251"/>
-      <c r="P6" s="252"/>
+      <c r="O6" s="285"/>
+      <c r="P6" s="286"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5391,10 +5432,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="310" t="s">
+      <c r="U6" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="311"/>
+      <c r="V6" s="344"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5407,10 +5448,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="310" t="s">
+      <c r="AA6" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="311"/>
+      <c r="AB6" s="344"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5453,9 +5494,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="320"/>
-      <c r="I7" s="321"/>
-      <c r="J7" s="322"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="364"/>
+      <c r="J7" s="365"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5463,11 +5504,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="250" t="s">
+      <c r="N7" s="284" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="251"/>
-      <c r="P7" s="252"/>
+      <c r="O7" s="285"/>
+      <c r="P7" s="286"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5477,10 +5518,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="310" t="s">
+      <c r="U7" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="311"/>
+      <c r="V7" s="344"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5493,10 +5534,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="310" t="s">
+      <c r="AA7" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="311"/>
+      <c r="AB7" s="344"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5539,9 +5580,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="320"/>
-      <c r="I8" s="321"/>
-      <c r="J8" s="322"/>
+      <c r="H8" s="363"/>
+      <c r="I8" s="364"/>
+      <c r="J8" s="365"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5549,11 +5590,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="250" t="s">
+      <c r="N8" s="284" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="251"/>
-      <c r="P8" s="252"/>
+      <c r="O8" s="285"/>
+      <c r="P8" s="286"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5563,10 +5604,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="310" t="s">
+      <c r="U8" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="311"/>
+      <c r="V8" s="344"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5579,10 +5620,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="310" t="s">
+      <c r="AA8" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="311"/>
+      <c r="AB8" s="344"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5625,9 +5666,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="320"/>
-      <c r="I9" s="321"/>
-      <c r="J9" s="322"/>
+      <c r="H9" s="363"/>
+      <c r="I9" s="364"/>
+      <c r="J9" s="365"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5635,11 +5676,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="250" t="s">
+      <c r="N9" s="284" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="251"/>
-      <c r="P9" s="252"/>
+      <c r="O9" s="285"/>
+      <c r="P9" s="286"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5649,10 +5690,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="310" t="s">
+      <c r="U9" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="311"/>
+      <c r="V9" s="344"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5665,10 +5706,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="310" t="s">
+      <c r="AA9" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="311"/>
+      <c r="AB9" s="344"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5711,9 +5752,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="320"/>
-      <c r="I10" s="321"/>
-      <c r="J10" s="322"/>
+      <c r="H10" s="363"/>
+      <c r="I10" s="364"/>
+      <c r="J10" s="365"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5721,11 +5762,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="250" t="s">
+      <c r="N10" s="284" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="251"/>
-      <c r="P10" s="252"/>
+      <c r="O10" s="285"/>
+      <c r="P10" s="286"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5735,10 +5776,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="310" t="s">
+      <c r="U10" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="311"/>
+      <c r="V10" s="344"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5751,10 +5792,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="310" t="s">
+      <c r="AA10" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="311"/>
+      <c r="AB10" s="344"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5797,9 +5838,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="320"/>
-      <c r="I11" s="321"/>
-      <c r="J11" s="322"/>
+      <c r="H11" s="363"/>
+      <c r="I11" s="364"/>
+      <c r="J11" s="365"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5807,11 +5848,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="250" t="s">
+      <c r="N11" s="284" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="251"/>
-      <c r="P11" s="252"/>
+      <c r="O11" s="285"/>
+      <c r="P11" s="286"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5821,10 +5862,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="310" t="s">
+      <c r="U11" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="311"/>
+      <c r="V11" s="344"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5837,10 +5878,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="310" t="s">
+      <c r="AA11" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="311"/>
+      <c r="AB11" s="344"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5883,9 +5924,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="320"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="322"/>
+      <c r="H12" s="363"/>
+      <c r="I12" s="364"/>
+      <c r="J12" s="365"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5893,11 +5934,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="250" t="s">
+      <c r="N12" s="284" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="251"/>
-      <c r="P12" s="252"/>
+      <c r="O12" s="285"/>
+      <c r="P12" s="286"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5907,10 +5948,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="310" t="s">
+      <c r="U12" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="311"/>
+      <c r="V12" s="344"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5923,10 +5964,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="310" t="s">
+      <c r="AA12" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="311"/>
+      <c r="AB12" s="344"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -5969,9 +6010,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="320"/>
-      <c r="I13" s="321"/>
-      <c r="J13" s="322"/>
+      <c r="H13" s="363"/>
+      <c r="I13" s="364"/>
+      <c r="J13" s="365"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -5979,11 +6020,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="250" t="s">
+      <c r="N13" s="284" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="251"/>
-      <c r="P13" s="252"/>
+      <c r="O13" s="285"/>
+      <c r="P13" s="286"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -5993,10 +6034,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="310" t="s">
+      <c r="U13" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="311"/>
+      <c r="V13" s="344"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6009,10 +6050,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="310" t="s">
+      <c r="AA13" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="311"/>
+      <c r="AB13" s="344"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6055,9 +6096,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="320"/>
-      <c r="I14" s="321"/>
-      <c r="J14" s="322"/>
+      <c r="H14" s="363"/>
+      <c r="I14" s="364"/>
+      <c r="J14" s="365"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6065,11 +6106,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="250" t="s">
+      <c r="N14" s="284" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="251"/>
-      <c r="P14" s="252"/>
+      <c r="O14" s="285"/>
+      <c r="P14" s="286"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6079,10 +6120,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="310" t="s">
+      <c r="U14" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="311"/>
+      <c r="V14" s="344"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6095,10 +6136,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="310" t="s">
+      <c r="AA14" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="311"/>
+      <c r="AB14" s="344"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6141,9 +6182,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="320"/>
-      <c r="I15" s="321"/>
-      <c r="J15" s="322"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="364"/>
+      <c r="J15" s="365"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6151,11 +6192,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="250" t="s">
+      <c r="N15" s="284" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="251"/>
-      <c r="P15" s="252"/>
+      <c r="O15" s="285"/>
+      <c r="P15" s="286"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6165,10 +6206,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="310" t="s">
+      <c r="U15" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="311"/>
+      <c r="V15" s="344"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6181,10 +6222,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="310" t="s">
+      <c r="AA15" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="311"/>
+      <c r="AB15" s="344"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6221,21 +6262,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="320"/>
-      <c r="G16" s="321"/>
-      <c r="H16" s="321"/>
-      <c r="I16" s="321"/>
-      <c r="J16" s="322"/>
+      <c r="F16" s="363"/>
+      <c r="G16" s="364"/>
+      <c r="H16" s="364"/>
+      <c r="I16" s="364"/>
+      <c r="J16" s="365"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="250" t="s">
+      <c r="N16" s="284" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="251"/>
-      <c r="P16" s="252"/>
+      <c r="O16" s="285"/>
+      <c r="P16" s="286"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6245,10 +6286,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="310" t="s">
+      <c r="U16" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="311"/>
+      <c r="V16" s="344"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6261,10 +6302,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="310" t="s">
+      <c r="AA16" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="311"/>
+      <c r="AB16" s="344"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6302,22 +6343,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="323" t="s">
+      <c r="G17" s="370" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="252"/>
+      <c r="H17" s="285"/>
+      <c r="I17" s="285"/>
+      <c r="J17" s="286"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="250" t="s">
+      <c r="N17" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="251"/>
-      <c r="P17" s="252"/>
+      <c r="O17" s="285"/>
+      <c r="P17" s="286"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6327,10 +6368,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="310" t="s">
+      <c r="U17" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="311"/>
+      <c r="V17" s="344"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6343,10 +6384,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="310" t="s">
+      <c r="AA17" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="311"/>
+      <c r="AB17" s="344"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6384,12 +6425,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="323" t="s">
+      <c r="G18" s="370" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="252"/>
+      <c r="H18" s="285"/>
+      <c r="I18" s="285"/>
+      <c r="J18" s="286"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6397,11 +6438,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="250" t="s">
+      <c r="N18" s="284" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="251"/>
-      <c r="P18" s="252"/>
+      <c r="O18" s="285"/>
+      <c r="P18" s="286"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6411,10 +6452,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="310" t="s">
+      <c r="U18" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="311"/>
+      <c r="V18" s="344"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6427,10 +6468,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="310" t="s">
+      <c r="AA18" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="311"/>
+      <c r="AB18" s="344"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6466,20 +6507,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="320"/>
-      <c r="H19" s="321"/>
-      <c r="I19" s="321"/>
-      <c r="J19" s="322"/>
+      <c r="G19" s="363"/>
+      <c r="H19" s="364"/>
+      <c r="I19" s="364"/>
+      <c r="J19" s="365"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="250" t="s">
+      <c r="N19" s="284" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="251"/>
-      <c r="P19" s="252"/>
+      <c r="O19" s="285"/>
+      <c r="P19" s="286"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6489,10 +6530,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="310" t="s">
+      <c r="U19" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="311"/>
+      <c r="V19" s="344"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6505,10 +6546,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="310" t="s">
+      <c r="AA19" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="311"/>
+      <c r="AB19" s="344"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6546,20 +6587,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="320"/>
-      <c r="H20" s="321"/>
-      <c r="I20" s="321"/>
-      <c r="J20" s="322"/>
+      <c r="G20" s="363"/>
+      <c r="H20" s="364"/>
+      <c r="I20" s="364"/>
+      <c r="J20" s="365"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="250" t="s">
+      <c r="N20" s="284" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="251"/>
-      <c r="P20" s="252"/>
+      <c r="O20" s="285"/>
+      <c r="P20" s="286"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6569,10 +6610,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="310" t="s">
+      <c r="U20" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="311"/>
+      <c r="V20" s="344"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6585,10 +6626,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="310" t="s">
+      <c r="AA20" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="311"/>
+      <c r="AB20" s="344"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6626,20 +6667,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="320"/>
-      <c r="H21" s="321"/>
-      <c r="I21" s="321"/>
-      <c r="J21" s="322"/>
+      <c r="G21" s="363"/>
+      <c r="H21" s="364"/>
+      <c r="I21" s="364"/>
+      <c r="J21" s="365"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="250" t="s">
+      <c r="N21" s="284" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="251"/>
-      <c r="P21" s="252"/>
+      <c r="O21" s="285"/>
+      <c r="P21" s="286"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6649,10 +6690,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="310" t="s">
+      <c r="U21" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="311"/>
+      <c r="V21" s="344"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6665,10 +6706,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="310" t="s">
+      <c r="AA21" s="343" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="311"/>
+      <c r="AB21" s="344"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6702,22 +6743,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="324"/>
-      <c r="F22" s="321"/>
-      <c r="G22" s="321"/>
-      <c r="H22" s="321"/>
-      <c r="I22" s="321"/>
-      <c r="J22" s="322"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="364"/>
+      <c r="G22" s="364"/>
+      <c r="H22" s="364"/>
+      <c r="I22" s="364"/>
+      <c r="J22" s="365"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="250" t="s">
+      <c r="N22" s="284" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="251"/>
-      <c r="P22" s="252"/>
+      <c r="O22" s="285"/>
+      <c r="P22" s="286"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6727,10 +6768,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="310" t="s">
+      <c r="U22" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="311"/>
+      <c r="V22" s="344"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6743,10 +6784,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="310" t="s">
+      <c r="AA22" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="311"/>
+      <c r="AB22" s="344"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6786,22 +6827,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="323" t="s">
+      <c r="G23" s="370" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="251"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="252"/>
+      <c r="H23" s="285"/>
+      <c r="I23" s="285"/>
+      <c r="J23" s="286"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="250" t="s">
+      <c r="N23" s="284" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="251"/>
-      <c r="P23" s="252"/>
+      <c r="O23" s="285"/>
+      <c r="P23" s="286"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6811,10 +6852,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="310" t="s">
+      <c r="U23" s="343" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="311"/>
+      <c r="V23" s="344"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6827,10 +6868,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="310" t="s">
+      <c r="AA23" s="343" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="311"/>
+      <c r="AB23" s="344"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6870,22 +6911,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="323" t="s">
+      <c r="G24" s="370" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="251"/>
-      <c r="I24" s="251"/>
-      <c r="J24" s="252"/>
+      <c r="H24" s="285"/>
+      <c r="I24" s="285"/>
+      <c r="J24" s="286"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="250" t="s">
+      <c r="N24" s="284" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="251"/>
-      <c r="P24" s="252"/>
+      <c r="O24" s="285"/>
+      <c r="P24" s="286"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6895,10 +6936,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="310" t="s">
+      <c r="U24" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="311"/>
+      <c r="V24" s="344"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6911,10 +6952,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="310" t="s">
+      <c r="AA24" s="343" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="311"/>
+      <c r="AB24" s="344"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6952,10 +6993,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="320"/>
-      <c r="H25" s="321"/>
-      <c r="I25" s="321"/>
-      <c r="J25" s="322"/>
+      <c r="G25" s="363"/>
+      <c r="H25" s="364"/>
+      <c r="I25" s="364"/>
+      <c r="J25" s="365"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -6963,11 +7004,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="250" t="s">
+      <c r="N25" s="284" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="251"/>
-      <c r="P25" s="252"/>
+      <c r="O25" s="285"/>
+      <c r="P25" s="286"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -6977,10 +7018,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="310" t="s">
+      <c r="U25" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="311"/>
+      <c r="V25" s="344"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -6993,10 +7034,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="310" t="s">
+      <c r="AA25" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="311"/>
+      <c r="AB25" s="344"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7034,10 +7075,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="320"/>
-      <c r="H26" s="321"/>
-      <c r="I26" s="321"/>
-      <c r="J26" s="322"/>
+      <c r="G26" s="363"/>
+      <c r="H26" s="364"/>
+      <c r="I26" s="364"/>
+      <c r="J26" s="365"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7045,11 +7086,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="250" t="s">
+      <c r="N26" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="251"/>
-      <c r="P26" s="252"/>
+      <c r="O26" s="285"/>
+      <c r="P26" s="286"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7059,10 +7100,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="310" t="s">
+      <c r="U26" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="311"/>
+      <c r="V26" s="344"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7075,10 +7116,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="310" t="s">
+      <c r="AA26" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="311"/>
+      <c r="AB26" s="344"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7110,22 +7151,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="324"/>
-      <c r="F27" s="321"/>
-      <c r="G27" s="321"/>
-      <c r="H27" s="321"/>
-      <c r="I27" s="321"/>
-      <c r="J27" s="322"/>
+      <c r="E27" s="369"/>
+      <c r="F27" s="364"/>
+      <c r="G27" s="364"/>
+      <c r="H27" s="364"/>
+      <c r="I27" s="364"/>
+      <c r="J27" s="365"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="250" t="s">
+      <c r="N27" s="284" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="251"/>
-      <c r="P27" s="252"/>
+      <c r="O27" s="285"/>
+      <c r="P27" s="286"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7135,10 +7176,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="310" t="s">
+      <c r="U27" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="311"/>
+      <c r="V27" s="344"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7151,10 +7192,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="310" t="s">
+      <c r="AA27" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="311"/>
+      <c r="AB27" s="344"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7186,12 +7227,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="328"/>
-      <c r="F28" s="329"/>
-      <c r="G28" s="329"/>
-      <c r="H28" s="329"/>
-      <c r="I28" s="329"/>
-      <c r="J28" s="330"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="367"/>
+      <c r="G28" s="367"/>
+      <c r="H28" s="367"/>
+      <c r="I28" s="367"/>
+      <c r="J28" s="368"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7199,11 +7240,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="247" t="s">
+      <c r="N28" s="281" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="248"/>
-      <c r="P28" s="249"/>
+      <c r="O28" s="282"/>
+      <c r="P28" s="283"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7213,10 +7254,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="357" t="s">
+      <c r="U28" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="358"/>
+      <c r="V28" s="346"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7229,10 +7270,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="357" t="s">
+      <c r="AA28" s="345" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="358"/>
+      <c r="AB28" s="346"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7309,27 +7350,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="293" t="s">
+      <c r="T30" s="395" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="293"/>
-      <c r="V30" s="293"/>
-      <c r="W30" s="293"/>
-      <c r="X30" s="293"/>
-      <c r="Y30" s="293"/>
-      <c r="Z30" s="293"/>
-      <c r="AA30" s="293"/>
-      <c r="AB30" s="293"/>
-      <c r="AC30" s="294"/>
-      <c r="AE30" s="242" t="s">
+      <c r="U30" s="395"/>
+      <c r="V30" s="395"/>
+      <c r="W30" s="395"/>
+      <c r="X30" s="395"/>
+      <c r="Y30" s="395"/>
+      <c r="Z30" s="395"/>
+      <c r="AA30" s="395"/>
+      <c r="AB30" s="395"/>
+      <c r="AC30" s="355"/>
+      <c r="AE30" s="273" t="s">
         <v>422</v>
       </c>
-      <c r="AF30" s="243"/>
-      <c r="AG30" s="242" t="s">
+      <c r="AF30" s="274"/>
+      <c r="AG30" s="273" t="s">
         <v>423</v>
       </c>
-      <c r="AH30" s="243"/>
-      <c r="AI30" s="244"/>
+      <c r="AH30" s="274"/>
+      <c r="AI30" s="275"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7370,28 +7411,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="253" t="s">
+      <c r="T31" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="254"/>
-      <c r="V31" s="254"/>
-      <c r="W31" s="254"/>
-      <c r="X31" s="254"/>
-      <c r="Y31" s="254"/>
-      <c r="Z31" s="254"/>
-      <c r="AA31" s="254"/>
-      <c r="AB31" s="254"/>
-      <c r="AC31" s="255"/>
-      <c r="AE31" s="288">
+      <c r="U31" s="288"/>
+      <c r="V31" s="288"/>
+      <c r="W31" s="288"/>
+      <c r="X31" s="288"/>
+      <c r="Y31" s="288"/>
+      <c r="Z31" s="288"/>
+      <c r="AA31" s="288"/>
+      <c r="AB31" s="288"/>
+      <c r="AC31" s="289"/>
+      <c r="AE31" s="390">
         <v>2</v>
       </c>
-      <c r="AF31" s="289"/>
-      <c r="AG31" s="290" t="str" cm="1">
+      <c r="AF31" s="391"/>
+      <c r="AG31" s="392" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="291"/>
-      <c r="AI31" s="292"/>
+      <c r="AH31" s="393"/>
+      <c r="AI31" s="394"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7415,18 +7456,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="250" t="s">
+      <c r="T32" s="284" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="251"/>
-      <c r="V32" s="251"/>
-      <c r="W32" s="251"/>
-      <c r="X32" s="251"/>
-      <c r="Y32" s="251"/>
-      <c r="Z32" s="251"/>
-      <c r="AA32" s="251"/>
-      <c r="AB32" s="251"/>
-      <c r="AC32" s="252"/>
+      <c r="U32" s="285"/>
+      <c r="V32" s="285"/>
+      <c r="W32" s="285"/>
+      <c r="X32" s="285"/>
+      <c r="Y32" s="285"/>
+      <c r="Z32" s="285"/>
+      <c r="AA32" s="285"/>
+      <c r="AB32" s="285"/>
+      <c r="AC32" s="286"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7462,31 +7503,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="250" t="s">
+      <c r="T33" s="284" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="251"/>
-      <c r="V33" s="251"/>
-      <c r="W33" s="251"/>
-      <c r="X33" s="251"/>
-      <c r="Y33" s="251"/>
-      <c r="Z33" s="251"/>
-      <c r="AA33" s="251"/>
-      <c r="AB33" s="251"/>
-      <c r="AC33" s="252"/>
+      <c r="U33" s="285"/>
+      <c r="V33" s="285"/>
+      <c r="W33" s="285"/>
+      <c r="X33" s="285"/>
+      <c r="Y33" s="285"/>
+      <c r="Z33" s="285"/>
+      <c r="AA33" s="285"/>
+      <c r="AB33" s="285"/>
+      <c r="AC33" s="286"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="355" t="s">
+      <c r="B34" s="341" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="331" t="s">
+      <c r="C34" s="339" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="333"/>
-      <c r="E34" s="331" t="s">
+      <c r="D34" s="340"/>
+      <c r="E34" s="339" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="333"/>
+      <c r="F34" s="340"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7514,21 +7555,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="250" t="s">
+      <c r="T34" s="284" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="251"/>
-      <c r="V34" s="251"/>
-      <c r="W34" s="251"/>
-      <c r="X34" s="251"/>
-      <c r="Y34" s="251"/>
-      <c r="Z34" s="251"/>
-      <c r="AA34" s="251"/>
-      <c r="AB34" s="251"/>
-      <c r="AC34" s="252"/>
+      <c r="U34" s="285"/>
+      <c r="V34" s="285"/>
+      <c r="W34" s="285"/>
+      <c r="X34" s="285"/>
+      <c r="Y34" s="285"/>
+      <c r="Z34" s="285"/>
+      <c r="AA34" s="285"/>
+      <c r="AB34" s="285"/>
+      <c r="AC34" s="286"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="356"/>
+      <c r="B35" s="342"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7547,18 +7588,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="250" t="s">
+      <c r="T35" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="251"/>
-      <c r="V35" s="251"/>
-      <c r="W35" s="251"/>
-      <c r="X35" s="251"/>
-      <c r="Y35" s="251"/>
-      <c r="Z35" s="251"/>
-      <c r="AA35" s="251"/>
-      <c r="AB35" s="251"/>
-      <c r="AC35" s="252"/>
+      <c r="U35" s="285"/>
+      <c r="V35" s="285"/>
+      <c r="W35" s="285"/>
+      <c r="X35" s="285"/>
+      <c r="Y35" s="285"/>
+      <c r="Z35" s="285"/>
+      <c r="AA35" s="285"/>
+      <c r="AB35" s="285"/>
+      <c r="AC35" s="286"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7609,18 +7650,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="250" t="s">
+      <c r="T36" s="284" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="251"/>
-      <c r="V36" s="251"/>
-      <c r="W36" s="251"/>
-      <c r="X36" s="251"/>
-      <c r="Y36" s="251"/>
-      <c r="Z36" s="251"/>
-      <c r="AA36" s="251"/>
-      <c r="AB36" s="251"/>
-      <c r="AC36" s="252"/>
+      <c r="U36" s="285"/>
+      <c r="V36" s="285"/>
+      <c r="W36" s="285"/>
+      <c r="X36" s="285"/>
+      <c r="Y36" s="285"/>
+      <c r="Z36" s="285"/>
+      <c r="AA36" s="285"/>
+      <c r="AB36" s="285"/>
+      <c r="AC36" s="286"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7663,18 +7704,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="250" t="s">
+      <c r="T37" s="284" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="251"/>
-      <c r="V37" s="251"/>
-      <c r="W37" s="251"/>
-      <c r="X37" s="251"/>
-      <c r="Y37" s="251"/>
-      <c r="Z37" s="251"/>
-      <c r="AA37" s="251"/>
-      <c r="AB37" s="251"/>
-      <c r="AC37" s="252"/>
+      <c r="U37" s="285"/>
+      <c r="V37" s="285"/>
+      <c r="W37" s="285"/>
+      <c r="X37" s="285"/>
+      <c r="Y37" s="285"/>
+      <c r="Z37" s="285"/>
+      <c r="AA37" s="285"/>
+      <c r="AB37" s="285"/>
+      <c r="AC37" s="286"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7695,21 +7736,21 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="295" t="s">
+      <c r="S38" s="382" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="297" t="s">
+      <c r="T38" s="384" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="298"/>
-      <c r="V38" s="298"/>
-      <c r="W38" s="298"/>
-      <c r="X38" s="298"/>
-      <c r="Y38" s="298"/>
-      <c r="Z38" s="298"/>
-      <c r="AA38" s="298"/>
-      <c r="AB38" s="298"/>
-      <c r="AC38" s="299"/>
+      <c r="U38" s="385"/>
+      <c r="V38" s="385"/>
+      <c r="W38" s="385"/>
+      <c r="X38" s="385"/>
+      <c r="Y38" s="385"/>
+      <c r="Z38" s="385"/>
+      <c r="AA38" s="385"/>
+      <c r="AB38" s="385"/>
+      <c r="AC38" s="386"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7727,26 +7768,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="303" t="s">
+      <c r="G39" s="328" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="246"/>
+      <c r="H39" s="279"/>
+      <c r="I39" s="279"/>
+      <c r="J39" s="280"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="296"/>
-      <c r="T39" s="300"/>
-      <c r="U39" s="301"/>
-      <c r="V39" s="301"/>
-      <c r="W39" s="301"/>
-      <c r="X39" s="301"/>
-      <c r="Y39" s="301"/>
-      <c r="Z39" s="301"/>
-      <c r="AA39" s="301"/>
-      <c r="AB39" s="301"/>
-      <c r="AC39" s="302"/>
+      <c r="S39" s="383"/>
+      <c r="T39" s="387"/>
+      <c r="U39" s="388"/>
+      <c r="V39" s="388"/>
+      <c r="W39" s="388"/>
+      <c r="X39" s="388"/>
+      <c r="Y39" s="388"/>
+      <c r="Z39" s="388"/>
+      <c r="AA39" s="388"/>
+      <c r="AB39" s="388"/>
+      <c r="AC39" s="389"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7764,28 +7805,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="307"/>
-      <c r="H40" s="308"/>
-      <c r="I40" s="308"/>
-      <c r="J40" s="309"/>
+      <c r="G40" s="329"/>
+      <c r="H40" s="330"/>
+      <c r="I40" s="330"/>
+      <c r="J40" s="331"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="250" t="s">
+      <c r="T40" s="284" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="251"/>
-      <c r="V40" s="251"/>
-      <c r="W40" s="251"/>
-      <c r="X40" s="251"/>
-      <c r="Y40" s="251"/>
-      <c r="Z40" s="251"/>
-      <c r="AA40" s="251"/>
-      <c r="AB40" s="251"/>
-      <c r="AC40" s="252"/>
+      <c r="U40" s="285"/>
+      <c r="V40" s="285"/>
+      <c r="W40" s="285"/>
+      <c r="X40" s="285"/>
+      <c r="Y40" s="285"/>
+      <c r="Z40" s="285"/>
+      <c r="AA40" s="285"/>
+      <c r="AB40" s="285"/>
+      <c r="AC40" s="286"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7803,28 +7844,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="307"/>
-      <c r="H41" s="308"/>
-      <c r="I41" s="308"/>
-      <c r="J41" s="309"/>
+      <c r="G41" s="329"/>
+      <c r="H41" s="330"/>
+      <c r="I41" s="330"/>
+      <c r="J41" s="331"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="250" t="s">
+      <c r="T41" s="284" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="251"/>
-      <c r="V41" s="251"/>
-      <c r="W41" s="251"/>
-      <c r="X41" s="251"/>
-      <c r="Y41" s="251"/>
-      <c r="Z41" s="251"/>
-      <c r="AA41" s="251"/>
-      <c r="AB41" s="251"/>
-      <c r="AC41" s="252"/>
+      <c r="U41" s="285"/>
+      <c r="V41" s="285"/>
+      <c r="W41" s="285"/>
+      <c r="X41" s="285"/>
+      <c r="Y41" s="285"/>
+      <c r="Z41" s="285"/>
+      <c r="AA41" s="285"/>
+      <c r="AB41" s="285"/>
+      <c r="AC41" s="286"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7842,28 +7883,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="304"/>
-      <c r="H42" s="305"/>
-      <c r="I42" s="305"/>
-      <c r="J42" s="306"/>
+      <c r="G42" s="332"/>
+      <c r="H42" s="333"/>
+      <c r="I42" s="333"/>
+      <c r="J42" s="334"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="250" t="s">
+      <c r="T42" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="251"/>
-      <c r="V42" s="251"/>
-      <c r="W42" s="251"/>
-      <c r="X42" s="251"/>
-      <c r="Y42" s="251"/>
-      <c r="Z42" s="251"/>
-      <c r="AA42" s="251"/>
-      <c r="AB42" s="251"/>
-      <c r="AC42" s="252"/>
+      <c r="U42" s="285"/>
+      <c r="V42" s="285"/>
+      <c r="W42" s="285"/>
+      <c r="X42" s="285"/>
+      <c r="Y42" s="285"/>
+      <c r="Z42" s="285"/>
+      <c r="AA42" s="285"/>
+      <c r="AB42" s="285"/>
+      <c r="AC42" s="286"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7881,30 +7922,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="268" t="s">
+      <c r="G43" s="257" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="269"/>
-      <c r="I43" s="269"/>
-      <c r="J43" s="270"/>
+      <c r="H43" s="258"/>
+      <c r="I43" s="258"/>
+      <c r="J43" s="259"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="250" t="s">
+      <c r="T43" s="284" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="251"/>
-      <c r="V43" s="251"/>
-      <c r="W43" s="251"/>
-      <c r="X43" s="251"/>
-      <c r="Y43" s="251"/>
-      <c r="Z43" s="251"/>
-      <c r="AA43" s="251"/>
-      <c r="AB43" s="251"/>
-      <c r="AC43" s="252"/>
+      <c r="U43" s="285"/>
+      <c r="V43" s="285"/>
+      <c r="W43" s="285"/>
+      <c r="X43" s="285"/>
+      <c r="Y43" s="285"/>
+      <c r="Z43" s="285"/>
+      <c r="AA43" s="285"/>
+      <c r="AB43" s="285"/>
+      <c r="AC43" s="286"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7925,21 +7966,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="295" t="s">
+      <c r="S44" s="382" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="297" t="s">
+      <c r="T44" s="384" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="298"/>
-      <c r="V44" s="298"/>
-      <c r="W44" s="298"/>
-      <c r="X44" s="298"/>
-      <c r="Y44" s="298"/>
-      <c r="Z44" s="298"/>
-      <c r="AA44" s="298"/>
-      <c r="AB44" s="298"/>
-      <c r="AC44" s="299"/>
+      <c r="U44" s="385"/>
+      <c r="V44" s="385"/>
+      <c r="W44" s="385"/>
+      <c r="X44" s="385"/>
+      <c r="Y44" s="385"/>
+      <c r="Z44" s="385"/>
+      <c r="AA44" s="385"/>
+      <c r="AB44" s="385"/>
+      <c r="AC44" s="386"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -7957,26 +7998,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="303" t="s">
+      <c r="G45" s="328" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="245"/>
-      <c r="I45" s="245"/>
-      <c r="J45" s="246"/>
+      <c r="H45" s="279"/>
+      <c r="I45" s="279"/>
+      <c r="J45" s="280"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="296"/>
-      <c r="T45" s="300"/>
-      <c r="U45" s="301"/>
-      <c r="V45" s="301"/>
-      <c r="W45" s="301"/>
-      <c r="X45" s="301"/>
-      <c r="Y45" s="301"/>
-      <c r="Z45" s="301"/>
-      <c r="AA45" s="301"/>
-      <c r="AB45" s="301"/>
-      <c r="AC45" s="302"/>
+      <c r="S45" s="383"/>
+      <c r="T45" s="387"/>
+      <c r="U45" s="388"/>
+      <c r="V45" s="388"/>
+      <c r="W45" s="388"/>
+      <c r="X45" s="388"/>
+      <c r="Y45" s="388"/>
+      <c r="Z45" s="388"/>
+      <c r="AA45" s="388"/>
+      <c r="AB45" s="388"/>
+      <c r="AC45" s="389"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -7994,28 +8035,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="304"/>
-      <c r="H46" s="305"/>
-      <c r="I46" s="305"/>
-      <c r="J46" s="306"/>
+      <c r="G46" s="332"/>
+      <c r="H46" s="333"/>
+      <c r="I46" s="333"/>
+      <c r="J46" s="334"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="247" t="s">
+      <c r="T46" s="281" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="248"/>
-      <c r="V46" s="248"/>
-      <c r="W46" s="248"/>
-      <c r="X46" s="248"/>
-      <c r="Y46" s="248"/>
-      <c r="Z46" s="248"/>
-      <c r="AA46" s="248"/>
-      <c r="AB46" s="248"/>
-      <c r="AC46" s="249"/>
+      <c r="U46" s="282"/>
+      <c r="V46" s="282"/>
+      <c r="W46" s="282"/>
+      <c r="X46" s="282"/>
+      <c r="Y46" s="282"/>
+      <c r="Z46" s="282"/>
+      <c r="AA46" s="282"/>
+      <c r="AB46" s="282"/>
+      <c r="AC46" s="283"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8033,12 +8074,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="269" t="s">
+      <c r="G47" s="258" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="269"/>
-      <c r="I47" s="269"/>
-      <c r="J47" s="270"/>
+      <c r="H47" s="258"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="259"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8083,11 +8124,11 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="368" t="s">
+      <c r="AA48" s="298" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="369"/>
-      <c r="AC48" s="370"/>
+      <c r="AB48" s="299"/>
+      <c r="AC48" s="300"/>
     </row>
     <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
@@ -8105,12 +8146,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="303" t="s">
+      <c r="G49" s="328" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="245"/>
-      <c r="I49" s="245"/>
-      <c r="J49" s="246"/>
+      <c r="H49" s="279"/>
+      <c r="I49" s="279"/>
+      <c r="J49" s="280"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8126,9 +8167,9 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="371"/>
-      <c r="AB49" s="372"/>
-      <c r="AC49" s="373"/>
+      <c r="AA49" s="301"/>
+      <c r="AB49" s="302"/>
+      <c r="AC49" s="303"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
@@ -8146,10 +8187,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="307"/>
-      <c r="H50" s="308"/>
-      <c r="I50" s="308"/>
-      <c r="J50" s="309"/>
+      <c r="G50" s="329"/>
+      <c r="H50" s="330"/>
+      <c r="I50" s="330"/>
+      <c r="J50" s="331"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8167,35 +8208,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="304"/>
-      <c r="H51" s="305"/>
-      <c r="I51" s="305"/>
-      <c r="J51" s="306"/>
-      <c r="R51" s="365" t="s">
+      <c r="G51" s="332"/>
+      <c r="H51" s="333"/>
+      <c r="I51" s="333"/>
+      <c r="J51" s="334"/>
+      <c r="R51" s="316" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="349" t="s">
+      <c r="S51" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="361" t="s">
+      <c r="T51" s="320" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="361"/>
-      <c r="V51" s="362"/>
+      <c r="U51" s="320"/>
+      <c r="V51" s="321"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="273" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="244"/>
-      <c r="R52" s="385"/>
-      <c r="S52" s="350"/>
-      <c r="T52" s="363"/>
-      <c r="U52" s="363"/>
-      <c r="V52" s="364"/>
+      <c r="C52" s="274"/>
+      <c r="D52" s="274"/>
+      <c r="E52" s="274"/>
+      <c r="F52" s="275"/>
+      <c r="R52" s="317"/>
+      <c r="S52" s="319"/>
+      <c r="T52" s="322"/>
+      <c r="U52" s="322"/>
+      <c r="V52" s="323"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8204,67 +8245,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="380" t="s">
+      <c r="T53" s="311" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="380"/>
-      <c r="V53" s="381"/>
+      <c r="U53" s="311"/>
+      <c r="V53" s="312"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="351" t="s">
+      <c r="B54" s="337" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="349" t="s">
+      <c r="C54" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="361" t="s">
+      <c r="D54" s="320" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="362"/>
-      <c r="H54" s="365" t="s">
+      <c r="E54" s="321"/>
+      <c r="H54" s="316" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="349" t="s">
+      <c r="I54" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="374" t="s">
+      <c r="J54" s="304" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="375"/>
-      <c r="L54" s="376"/>
+      <c r="K54" s="305"/>
+      <c r="L54" s="306"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="386" t="s">
+      <c r="T54" s="324" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="386"/>
-      <c r="V54" s="354"/>
+      <c r="U54" s="324"/>
+      <c r="V54" s="325"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="352"/>
-      <c r="C55" s="350"/>
-      <c r="D55" s="363"/>
-      <c r="E55" s="364"/>
-      <c r="H55" s="366"/>
-      <c r="I55" s="367"/>
-      <c r="J55" s="340"/>
-      <c r="K55" s="377"/>
-      <c r="L55" s="378"/>
+      <c r="B55" s="338"/>
+      <c r="C55" s="319"/>
+      <c r="D55" s="322"/>
+      <c r="E55" s="323"/>
+      <c r="H55" s="335"/>
+      <c r="I55" s="336"/>
+      <c r="J55" s="307"/>
+      <c r="K55" s="308"/>
+      <c r="L55" s="309"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="386" t="s">
+      <c r="T55" s="324" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="386"/>
-      <c r="V55" s="354"/>
+      <c r="U55" s="324"/>
+      <c r="V55" s="325"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8273,36 +8314,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="253" t="s">
+      <c r="D56" s="287" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="255"/>
+      <c r="E56" s="289"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="379" t="s">
+      <c r="J56" s="310" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="380"/>
-      <c r="L56" s="381"/>
-      <c r="M56" s="268" t="s">
+      <c r="K56" s="311"/>
+      <c r="L56" s="312"/>
+      <c r="M56" s="257" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="270"/>
+      <c r="N56" s="259"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="386" t="s">
+      <c r="T56" s="324" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="386"/>
-      <c r="V56" s="354"/>
+      <c r="U56" s="324"/>
+      <c r="V56" s="325"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8311,36 +8352,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="353" t="s">
+      <c r="D57" s="326" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="354"/>
-      <c r="F57" s="268" t="s">
+      <c r="E57" s="325"/>
+      <c r="F57" s="257" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="270"/>
+      <c r="G57" s="259"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="382" t="s">
+      <c r="J57" s="313" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="383"/>
-      <c r="L57" s="384"/>
+      <c r="K57" s="314"/>
+      <c r="L57" s="315"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="386" t="s">
+      <c r="T57" s="324" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="386"/>
-      <c r="V57" s="354"/>
+      <c r="U57" s="324"/>
+      <c r="V57" s="325"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8349,32 +8390,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="353" t="s">
+      <c r="D58" s="326" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="354"/>
+      <c r="E58" s="325"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="382" t="s">
+      <c r="J58" s="313" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="383"/>
-      <c r="L58" s="384"/>
+      <c r="K58" s="314"/>
+      <c r="L58" s="315"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="386" t="s">
+      <c r="T58" s="324" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="386"/>
-      <c r="V58" s="354"/>
+      <c r="U58" s="324"/>
+      <c r="V58" s="325"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8383,32 +8424,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="353" t="s">
+      <c r="D59" s="326" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="354"/>
+      <c r="E59" s="325"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="382" t="s">
+      <c r="J59" s="313" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="383"/>
-      <c r="L59" s="384"/>
+      <c r="K59" s="314"/>
+      <c r="L59" s="315"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="386" t="s">
+      <c r="T59" s="324" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="386"/>
-      <c r="V59" s="354"/>
+      <c r="U59" s="324"/>
+      <c r="V59" s="325"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8418,32 +8459,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="353" t="s">
+      <c r="D60" s="326" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="354"/>
+      <c r="E60" s="325"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="382" t="s">
+      <c r="J60" s="313" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="383"/>
-      <c r="L60" s="384"/>
+      <c r="K60" s="314"/>
+      <c r="L60" s="315"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="386" t="s">
-        <v>461</v>
-      </c>
-      <c r="U60" s="386"/>
-      <c r="V60" s="354"/>
+      <c r="T60" s="324" t="s">
+        <v>459</v>
+      </c>
+      <c r="U60" s="324"/>
+      <c r="V60" s="325"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8452,101 +8493,101 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="353" t="s">
+      <c r="D61" s="326" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="354"/>
+      <c r="E61" s="325"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="382"/>
-      <c r="K61" s="383"/>
-      <c r="L61" s="384"/>
+      <c r="J61" s="313"/>
+      <c r="K61" s="314"/>
+      <c r="L61" s="315"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="386"/>
-      <c r="U61" s="386"/>
-      <c r="V61" s="354"/>
+      <c r="T61" s="324"/>
+      <c r="U61" s="324"/>
+      <c r="V61" s="325"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="353"/>
-      <c r="E62" s="354"/>
+      <c r="D62" s="326"/>
+      <c r="E62" s="325"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="382"/>
-      <c r="K62" s="383"/>
-      <c r="L62" s="384"/>
+      <c r="J62" s="313"/>
+      <c r="K62" s="314"/>
+      <c r="L62" s="315"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="386"/>
-      <c r="U62" s="386"/>
-      <c r="V62" s="354"/>
+      <c r="T62" s="324"/>
+      <c r="U62" s="324"/>
+      <c r="V62" s="325"/>
     </row>
     <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="353"/>
-      <c r="E63" s="354"/>
+      <c r="D63" s="326"/>
+      <c r="E63" s="325"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="382"/>
-      <c r="K63" s="383"/>
-      <c r="L63" s="384"/>
+      <c r="J63" s="313"/>
+      <c r="K63" s="314"/>
+      <c r="L63" s="315"/>
       <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
       <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="386"/>
-      <c r="U63" s="386"/>
-      <c r="V63" s="354"/>
+      <c r="T63" s="324"/>
+      <c r="U63" s="324"/>
+      <c r="V63" s="325"/>
     </row>
     <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="353"/>
-      <c r="E64" s="354"/>
+      <c r="D64" s="326"/>
+      <c r="E64" s="325"/>
       <c r="R64" s="163" t="s">
+        <v>456</v>
+      </c>
+      <c r="S64" s="161" t="s">
+        <v>457</v>
+      </c>
+      <c r="T64" s="296" t="s">
         <v>458</v>
       </c>
-      <c r="S64" s="161" t="s">
-        <v>459</v>
-      </c>
-      <c r="T64" s="424" t="s">
-        <v>460</v>
-      </c>
-      <c r="U64" s="424"/>
-      <c r="V64" s="360"/>
+      <c r="U64" s="296"/>
+      <c r="V64" s="297"/>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="353"/>
-      <c r="E65" s="354"/>
+      <c r="D65" s="326"/>
+      <c r="E65" s="325"/>
       <c r="T65" s="166"/>
     </row>
     <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8554,96 +8595,172 @@
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="353"/>
-      <c r="E66" s="354"/>
+      <c r="D66" s="326"/>
+      <c r="E66" s="325"/>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="353"/>
-      <c r="E67" s="354"/>
+      <c r="D67" s="326"/>
+      <c r="E67" s="325"/>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="353"/>
-      <c r="E68" s="354"/>
+      <c r="D68" s="326"/>
+      <c r="E68" s="325"/>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="353"/>
-      <c r="E69" s="354"/>
+      <c r="D69" s="326"/>
+      <c r="E69" s="325"/>
     </row>
     <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="353"/>
-      <c r="E70" s="354"/>
+      <c r="D70" s="326"/>
+      <c r="E70" s="325"/>
     </row>
     <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="359"/>
-      <c r="E71" s="360"/>
+      <c r="D71" s="327"/>
+      <c r="E71" s="297"/>
     </row>
     <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="T64:V64"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="D57:E57"/>
@@ -8668,126 +8785,50 @@
     <mergeCell ref="N20:P20"/>
     <mergeCell ref="N21:P21"/>
     <mergeCell ref="N23:P23"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8805,7 +8846,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
@@ -8842,35 +8883,35 @@
       <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="G2" s="245" t="s">
+      <c r="G2" s="279" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="245"/>
-      <c r="I2" s="245"/>
-      <c r="J2" s="246"/>
-      <c r="L2" s="259" t="s">
+      <c r="H2" s="279"/>
+      <c r="I2" s="279"/>
+      <c r="J2" s="280"/>
+      <c r="L2" s="248" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="261"/>
+      <c r="M2" s="249"/>
+      <c r="N2" s="249"/>
+      <c r="O2" s="250"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="262" t="s">
+      <c r="Q2" s="251" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="253"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="256" t="s">
+      <c r="V2" s="245" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="257"/>
-      <c r="X2" s="257"/>
-      <c r="Y2" s="257"/>
-      <c r="Z2" s="257"/>
-      <c r="AA2" s="257"/>
-      <c r="AB2" s="258"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="247"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
@@ -8891,11 +8932,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="253" t="s">
+      <c r="H3" s="287" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="255"/>
+      <c r="I3" s="288"/>
+      <c r="J3" s="289"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8934,11 +8975,11 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="277" t="s">
+      <c r="Z3" s="264" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="278"/>
-      <c r="AB3" s="279"/>
+      <c r="AA3" s="265"/>
+      <c r="AB3" s="266"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
@@ -8959,11 +9000,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="250">
+      <c r="H4" s="284">
         <v>63</v>
       </c>
-      <c r="I4" s="251"/>
-      <c r="J4" s="252"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="286"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9002,11 +9043,11 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="280" t="s">
+      <c r="Z4" s="267" t="s">
         <v>421</v>
       </c>
-      <c r="AA4" s="281"/>
-      <c r="AB4" s="282"/>
+      <c r="AA4" s="268"/>
+      <c r="AB4" s="269"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
@@ -9027,11 +9068,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="250">
+      <c r="H5" s="284">
         <v>31</v>
       </c>
-      <c r="I5" s="251"/>
-      <c r="J5" s="252"/>
+      <c r="I5" s="285"/>
+      <c r="J5" s="286"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9070,9 +9111,9 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="280"/>
-      <c r="AA5" s="281"/>
-      <c r="AB5" s="282"/>
+      <c r="Z5" s="267"/>
+      <c r="AA5" s="268"/>
+      <c r="AB5" s="269"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
@@ -9093,11 +9134,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="247">
+      <c r="H6" s="281">
         <v>7</v>
       </c>
-      <c r="I6" s="248"/>
-      <c r="J6" s="249"/>
+      <c r="I6" s="282"/>
+      <c r="J6" s="283"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -9136,9 +9177,9 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="283"/>
-      <c r="AA6" s="284"/>
-      <c r="AB6" s="285"/>
+      <c r="Z6" s="270"/>
+      <c r="AA6" s="271"/>
+      <c r="AB6" s="272"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
@@ -9159,12 +9200,12 @@
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="235" t="str">
+      <c r="H7" s="276" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="236"/>
-      <c r="J7" s="237"/>
+      <c r="I7" s="277"/>
+      <c r="J7" s="278"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -9211,18 +9252,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="235" t="str">
+      <c r="H8" s="276" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="236"/>
-      <c r="J8" s="237"/>
-      <c r="L8" s="268" t="s">
+      <c r="I8" s="277"/>
+      <c r="J8" s="278"/>
+      <c r="L8" s="257" t="s">
         <v>417</v>
       </c>
-      <c r="M8" s="269"/>
-      <c r="N8" s="269"/>
-      <c r="O8" s="270"/>
+      <c r="M8" s="258"/>
+      <c r="N8" s="258"/>
+      <c r="O8" s="259"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9237,14 +9278,14 @@
         <v>239</v>
       </c>
       <c r="U8" s="114"/>
-      <c r="V8" s="231" t="s">
-        <v>453</v>
-      </c>
-      <c r="W8" s="271" t="s">
-        <v>454</v>
-      </c>
-      <c r="X8" s="272"/>
-      <c r="Y8" s="230"/>
+      <c r="V8" s="225" t="s">
+        <v>451</v>
+      </c>
+      <c r="W8" s="260" t="s">
+        <v>452</v>
+      </c>
+      <c r="X8" s="261"/>
+      <c r="Y8" s="224"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="187" t="s">
@@ -9283,10 +9324,10 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="273" t="s">
-        <v>456</v>
-      </c>
-      <c r="X9" s="274"/>
+      <c r="W9" s="262" t="s">
+        <v>454</v>
+      </c>
+      <c r="X9" s="263"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
@@ -9317,10 +9358,10 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="275" t="s">
-        <v>455</v>
-      </c>
-      <c r="X10" s="276"/>
+      <c r="W10" s="243" t="s">
+        <v>453</v>
+      </c>
+      <c r="X10" s="244"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
@@ -9347,20 +9388,20 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="265" t="s">
+      <c r="Q11" s="254" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="266"/>
-      <c r="S11" s="266"/>
-      <c r="T11" s="267"/>
+      <c r="R11" s="255"/>
+      <c r="S11" s="255"/>
+      <c r="T11" s="256"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="275" t="s">
+      <c r="W11" s="243" t="s">
         <v>425</v>
       </c>
-      <c r="X11" s="276"/>
+      <c r="X11" s="244"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
@@ -9401,8 +9442,10 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="275"/>
-      <c r="X12" s="276"/>
+      <c r="W12" s="243" t="s">
+        <v>460</v>
+      </c>
+      <c r="X12" s="244"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
@@ -9443,8 +9486,8 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="275"/>
-      <c r="X13" s="276"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="244"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
@@ -9485,8 +9528,8 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="275"/>
-      <c r="X14" s="276"/>
+      <c r="W14" s="243"/>
+      <c r="X14" s="244"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
@@ -9527,8 +9570,8 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="275"/>
-      <c r="X15" s="276"/>
+      <c r="W15" s="243"/>
+      <c r="X15" s="244"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
@@ -9559,8 +9602,8 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="275"/>
-      <c r="X16" s="276"/>
+      <c r="W16" s="243"/>
+      <c r="X16" s="244"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
@@ -9588,11 +9631,11 @@
       <c r="T17" s="138" t="s">
         <v>258</v>
       </c>
-      <c r="V17" s="232">
+      <c r="V17" s="226">
         <v>9</v>
       </c>
-      <c r="W17" s="286"/>
-      <c r="X17" s="287"/>
+      <c r="W17" s="241"/>
+      <c r="X17" s="242"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9611,18 +9654,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="242" t="s">
+      <c r="G19" s="273" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="243"/>
-      <c r="I19" s="243"/>
-      <c r="J19" s="244"/>
+      <c r="H19" s="274"/>
+      <c r="I19" s="274"/>
+      <c r="J19" s="275"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="233" t="s">
+      <c r="C20" s="290" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9634,16 +9677,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="238" t="s">
-        <v>457</v>
-      </c>
-      <c r="H20" s="239"/>
-      <c r="I20" s="239"/>
-      <c r="J20" s="240"/>
+      <c r="G20" s="292" t="s">
+        <v>455</v>
+      </c>
+      <c r="H20" s="293"/>
+      <c r="I20" s="293"/>
+      <c r="J20" s="294"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="241"/>
+      <c r="C21" s="295"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9653,16 +9696,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="235" t="s">
+      <c r="G21" s="276" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="237"/>
+      <c r="H21" s="277"/>
+      <c r="I21" s="277"/>
+      <c r="J21" s="278"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="234"/>
+      <c r="C22" s="291"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9681,7 +9724,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="233" t="s">
+      <c r="C23" s="290" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9700,7 +9743,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="234"/>
+      <c r="C24" s="291"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9719,7 +9762,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="233" t="s">
+      <c r="C25" s="290" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9738,7 +9781,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="234"/>
+      <c r="C26" s="291"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9757,7 +9800,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="290" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9776,7 +9819,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="234"/>
+      <c r="C28" s="291"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9816,7 +9859,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="233" t="s">
+      <c r="C30" s="290" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9835,7 +9878,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="234"/>
+      <c r="C31" s="291"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9854,7 +9897,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="233" t="s">
+      <c r="C32" s="290" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9873,7 +9916,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="234"/>
+      <c r="C33" s="291"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9890,12 +9933,22 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9907,22 +9960,12 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9932,30 +9975,56 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B07C92-48AD-46D8-AFE8-A66BE9216D0D}">
-  <dimension ref="B1:H24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="391" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="227"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="229"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="230"/>
+      <c r="B2" s="406" t="s">
         <v>425</v>
       </c>
-      <c r="C2" s="392"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="394"/>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="407"/>
+      <c r="D2" s="407"/>
+      <c r="E2" s="407"/>
+      <c r="F2" s="407"/>
+      <c r="G2" s="408"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="406" t="s">
+        <v>461</v>
+      </c>
+      <c r="L2" s="407"/>
+      <c r="M2" s="407"/>
+      <c r="N2" s="408"/>
+      <c r="O2" s="231"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="230"/>
       <c r="B3" s="194" t="s">
         <v>424</v>
       </c>
@@ -9966,262 +10035,397 @@
         <v>427</v>
       </c>
       <c r="E3" s="195" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="430" t="s">
         <v>428</v>
       </c>
-      <c r="F3" s="195" t="s">
-        <v>430</v>
-      </c>
-      <c r="G3" s="389" t="s">
+      <c r="G3" s="431"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="194" t="s">
+        <v>424</v>
+      </c>
+      <c r="L3" s="195" t="s">
         <v>429</v>
       </c>
-      <c r="H3" s="390"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="M3" s="398" t="s">
+        <v>428</v>
+      </c>
+      <c r="N3" s="399"/>
+      <c r="O3" s="231"/>
+    </row>
+    <row r="4" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="230"/>
       <c r="B4" s="196">
         <v>0</v>
       </c>
-      <c r="C4" s="202"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="223" t="s">
+      <c r="C4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="395" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4" s="396"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="436" t="s">
+        <v>435</v>
+      </c>
+      <c r="G4" s="437"/>
+      <c r="I4" s="231"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="196">
+        <v>0</v>
+      </c>
+      <c r="L4" s="236" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="400" t="s">
+        <v>435</v>
+      </c>
+      <c r="N4" s="401"/>
+      <c r="O4" s="231"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="230"/>
       <c r="B5" s="197">
         <v>1</v>
       </c>
       <c r="C5" s="198" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="218" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" s="219" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" s="438" t="s">
         <v>439</v>
       </c>
-      <c r="D5" s="228"/>
-      <c r="E5" s="222" t="s">
-        <v>441</v>
-      </c>
-      <c r="F5" s="224" t="s">
-        <v>431</v>
-      </c>
-      <c r="G5" s="387" t="s">
-        <v>440</v>
-      </c>
-      <c r="H5" s="388"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G5" s="439"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="197">
+        <v>1</v>
+      </c>
+      <c r="L5" s="237" t="s">
+        <v>462</v>
+      </c>
+      <c r="M5" s="402" t="s">
+        <v>463</v>
+      </c>
+      <c r="N5" s="403"/>
+      <c r="O5" s="231"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="230"/>
       <c r="B6" s="197">
         <v>2</v>
       </c>
-      <c r="C6" s="229"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="200" t="s">
-        <v>441</v>
-      </c>
-      <c r="F6" s="224" t="s">
-        <v>432</v>
-      </c>
-      <c r="G6" s="387" t="s">
-        <v>437</v>
-      </c>
-      <c r="H6" s="388"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="223"/>
+      <c r="D6" s="199" t="s">
+        <v>440</v>
+      </c>
+      <c r="E6" s="219" t="s">
+        <v>431</v>
+      </c>
+      <c r="F6" s="438" t="s">
+        <v>436</v>
+      </c>
+      <c r="G6" s="439"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="200">
+        <v>2</v>
+      </c>
+      <c r="L6" s="238" t="s">
+        <v>308</v>
+      </c>
+      <c r="M6" s="404" t="s">
+        <v>464</v>
+      </c>
+      <c r="N6" s="405"/>
+      <c r="O6" s="231"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="230"/>
       <c r="B7" s="197">
         <v>3</v>
       </c>
-      <c r="C7" s="207"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="224" t="s">
-        <v>433</v>
-      </c>
-      <c r="G7" s="387" t="s">
-        <v>438</v>
-      </c>
-      <c r="H7" s="388"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="204"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="219" t="s">
+        <v>432</v>
+      </c>
+      <c r="F7" s="438" t="s">
+        <v>437</v>
+      </c>
+      <c r="G7" s="439"/>
+      <c r="I7" s="231"/>
+      <c r="J7" s="230"/>
+      <c r="O7" s="231"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="230"/>
       <c r="B8" s="197">
         <v>4</v>
       </c>
       <c r="C8" s="198" t="s">
+        <v>441</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="219" t="s">
+        <v>433</v>
+      </c>
+      <c r="F8" s="438" t="s">
         <v>442</v>
       </c>
-      <c r="D8" s="199" t="s">
+      <c r="G8" s="439"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="396" t="s">
         <v>443</v>
       </c>
-      <c r="E8" s="206"/>
-      <c r="F8" s="224" t="s">
-        <v>434</v>
-      </c>
-      <c r="G8" s="387" t="s">
-        <v>444</v>
-      </c>
-      <c r="H8" s="388"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="L8" s="214">
+        <v>2</v>
+      </c>
+      <c r="M8" s="214">
+        <v>1</v>
+      </c>
+      <c r="N8" s="215">
+        <v>0</v>
+      </c>
+      <c r="O8" s="231"/>
+    </row>
+    <row r="9" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="230"/>
       <c r="B9" s="197">
         <v>5</v>
       </c>
-      <c r="C9" s="207"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="225" t="s">
-        <v>435</v>
-      </c>
-      <c r="G9" s="406"/>
-      <c r="H9" s="407"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="204"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="220" t="s">
+        <v>434</v>
+      </c>
+      <c r="F9" s="432"/>
+      <c r="G9" s="433"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="397"/>
+      <c r="L9" s="217"/>
+      <c r="M9" s="217"/>
+      <c r="N9" s="235" t="s">
+        <v>465</v>
+      </c>
+      <c r="O9" s="231"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="230"/>
       <c r="B10" s="197">
         <v>6</v>
       </c>
-      <c r="C10" s="207"/>
-      <c r="D10" s="205"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="226" t="s">
-        <v>435</v>
-      </c>
-      <c r="G10" s="406"/>
-      <c r="H10" s="407"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="201">
+      <c r="C10" s="204"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="221" t="s">
+        <v>434</v>
+      </c>
+      <c r="F10" s="432"/>
+      <c r="G10" s="433"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="230"/>
+      <c r="O10" s="231"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="230"/>
+      <c r="B11" s="200">
         <v>7</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="209"/>
-      <c r="E11" s="210"/>
-      <c r="F11" s="227" t="s">
-        <v>435</v>
-      </c>
-      <c r="G11" s="408"/>
-      <c r="H11" s="409"/>
-    </row>
-    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="212" t="s">
+      <c r="C11" s="205"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="222" t="s">
+        <v>434</v>
+      </c>
+      <c r="F11" s="434"/>
+      <c r="G11" s="435"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="233"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="234"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="O12" s="240"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="230"/>
+      <c r="B13" s="208" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" s="427" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="428"/>
+      <c r="E13" s="429"/>
+      <c r="I13" s="231"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="230"/>
+      <c r="B14" s="209">
+        <v>0</v>
+      </c>
+      <c r="C14" s="418" t="s">
+        <v>449</v>
+      </c>
+      <c r="D14" s="419"/>
+      <c r="E14" s="420"/>
+      <c r="I14" s="231"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="230"/>
+      <c r="B15" s="210">
+        <v>1</v>
+      </c>
+      <c r="C15" s="421" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="422"/>
+      <c r="E15" s="423"/>
+      <c r="I15" s="231"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="230"/>
+      <c r="B16" s="210">
+        <v>2</v>
+      </c>
+      <c r="C16" s="409" t="s">
+        <v>448</v>
+      </c>
+      <c r="D16" s="410"/>
+      <c r="E16" s="411"/>
+      <c r="I16" s="231"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="230"/>
+      <c r="B17" s="210">
+        <v>3</v>
+      </c>
+      <c r="C17" s="424" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="425"/>
+      <c r="E17" s="426"/>
+      <c r="I17" s="231"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="230"/>
+      <c r="B18" s="210">
+        <v>4</v>
+      </c>
+      <c r="C18" s="412"/>
+      <c r="D18" s="413"/>
+      <c r="E18" s="414"/>
+      <c r="I18" s="231"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="230"/>
+      <c r="B19" s="210">
+        <v>5</v>
+      </c>
+      <c r="C19" s="412"/>
+      <c r="D19" s="413"/>
+      <c r="E19" s="414"/>
+      <c r="I19" s="231"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="230"/>
+      <c r="B20" s="210">
+        <v>6</v>
+      </c>
+      <c r="C20" s="412"/>
+      <c r="D20" s="413"/>
+      <c r="E20" s="414"/>
+      <c r="I20" s="231"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="230"/>
+      <c r="B21" s="211">
+        <v>7</v>
+      </c>
+      <c r="C21" s="415"/>
+      <c r="D21" s="416"/>
+      <c r="E21" s="417"/>
+      <c r="I21" s="231"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="230"/>
+      <c r="I22" s="231"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="230"/>
+      <c r="B23" s="396" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="207">
+        <v>5</v>
+      </c>
+      <c r="D23" s="214">
+        <v>4</v>
+      </c>
+      <c r="E23" s="214">
+        <v>3</v>
+      </c>
+      <c r="F23" s="214">
+        <v>2</v>
+      </c>
+      <c r="G23" s="214">
+        <v>1</v>
+      </c>
+      <c r="H23" s="215">
+        <v>0</v>
+      </c>
+      <c r="I23" s="231"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="230"/>
+      <c r="B24" s="397"/>
+      <c r="C24" s="216"/>
+      <c r="D24" s="217"/>
+      <c r="E24" s="217"/>
+      <c r="F24" s="217"/>
+      <c r="G24" s="212" t="s">
         <v>446</v>
       </c>
-      <c r="C13" s="410" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="411"/>
-      <c r="E13" s="412"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="213">
-        <v>0</v>
-      </c>
-      <c r="C14" s="397" t="s">
-        <v>451</v>
-      </c>
-      <c r="D14" s="398"/>
-      <c r="E14" s="399"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="214">
-        <v>1</v>
-      </c>
-      <c r="C15" s="400" t="s">
-        <v>449</v>
-      </c>
-      <c r="D15" s="401"/>
-      <c r="E15" s="402"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="214">
-        <v>2</v>
-      </c>
-      <c r="C16" s="415" t="s">
-        <v>450</v>
-      </c>
-      <c r="D16" s="416"/>
-      <c r="E16" s="417"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="214">
-        <v>3</v>
-      </c>
-      <c r="C17" s="403" t="s">
-        <v>452</v>
-      </c>
-      <c r="D17" s="404"/>
-      <c r="E17" s="405"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="214">
-        <v>4</v>
-      </c>
-      <c r="C18" s="418"/>
-      <c r="D18" s="419"/>
-      <c r="E18" s="420"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="214">
-        <v>5</v>
-      </c>
-      <c r="C19" s="418"/>
-      <c r="D19" s="419"/>
-      <c r="E19" s="420"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="214">
-        <v>6</v>
-      </c>
-      <c r="C20" s="418"/>
-      <c r="D20" s="419"/>
-      <c r="E20" s="420"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="215">
-        <v>7</v>
-      </c>
-      <c r="C21" s="421"/>
-      <c r="D21" s="422"/>
-      <c r="E21" s="423"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="413" t="s">
+      <c r="H24" s="213" t="s">
         <v>445</v>
       </c>
-      <c r="C23" s="211">
-        <v>5</v>
-      </c>
-      <c r="D23" s="218">
-        <v>4</v>
-      </c>
-      <c r="E23" s="218">
-        <v>3</v>
-      </c>
-      <c r="F23" s="218">
-        <v>2</v>
-      </c>
-      <c r="G23" s="218">
-        <v>1</v>
-      </c>
-      <c r="H23" s="219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="414"/>
-      <c r="C24" s="220"/>
-      <c r="D24" s="221"/>
-      <c r="E24" s="221"/>
-      <c r="F24" s="221"/>
-      <c r="G24" s="216" t="s">
-        <v>448</v>
-      </c>
-      <c r="H24" s="217" t="s">
-        <v>447</v>
-      </c>
+      <c r="I24" s="231"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="232"/>
+      <c r="B25" s="233"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="233"/>
+      <c r="E25" s="233"/>
+      <c r="F25" s="233"/>
+      <c r="G25" s="233"/>
+      <c r="H25" s="233"/>
+      <c r="I25" s="234"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="26">
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="K2:N2"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C19:E19"/>
@@ -10231,17 +10435,12 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Inst.xlsx
+++ b/Inst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yo\Escritorio\Procesador-32-bits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E1875F-F608-4B78-A33B-6FABBF1EC8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4494EB60-3A2F-423C-9681-EBC5DE0E12B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="597" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="597" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="467">
   <si>
     <t>OpCode</t>
   </si>
@@ -2400,6 +2400,9 @@
   </si>
   <si>
     <t>Enable Keyboard</t>
+  </si>
+  <si>
+    <t>NVMe</t>
   </si>
 </sst>
 </file>
@@ -4193,602 +4196,602 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5110,62 +5113,62 @@
   <sheetData>
     <row r="1" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="360" t="s">
+      <c r="B2" s="338" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="372" t="s">
+      <c r="C2" s="347" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="373"/>
-      <c r="E2" s="374" t="s">
+      <c r="D2" s="348"/>
+      <c r="E2" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="374"/>
-      <c r="G2" s="375" t="s">
+      <c r="F2" s="349"/>
+      <c r="G2" s="350" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="374"/>
-      <c r="I2" s="374" t="s">
+      <c r="H2" s="349"/>
+      <c r="I2" s="349" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="374"/>
-      <c r="K2" s="376" t="s">
+      <c r="J2" s="349"/>
+      <c r="K2" s="351" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="374"/>
-      <c r="M2" s="374"/>
-      <c r="N2" s="374"/>
-      <c r="O2" s="374"/>
-      <c r="P2" s="377"/>
-      <c r="R2" s="357" t="s">
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
+      <c r="N2" s="349"/>
+      <c r="O2" s="349"/>
+      <c r="P2" s="352"/>
+      <c r="R2" s="355" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="355" t="s">
+      <c r="S2" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="348" t="s">
+      <c r="T2" s="359" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="349"/>
-      <c r="V2" s="349"/>
-      <c r="W2" s="349"/>
-      <c r="X2" s="349"/>
-      <c r="Y2" s="349"/>
-      <c r="Z2" s="349"/>
-      <c r="AA2" s="349"/>
-      <c r="AB2" s="349" t="s">
+      <c r="U2" s="360"/>
+      <c r="V2" s="360"/>
+      <c r="W2" s="360"/>
+      <c r="X2" s="360"/>
+      <c r="Y2" s="360"/>
+      <c r="Z2" s="360"/>
+      <c r="AA2" s="360"/>
+      <c r="AB2" s="360" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="349"/>
-      <c r="AD2" s="349"/>
-      <c r="AE2" s="349"/>
-      <c r="AF2" s="349"/>
-      <c r="AG2" s="349"/>
-      <c r="AH2" s="349"/>
-      <c r="AI2" s="350"/>
+      <c r="AC2" s="360"/>
+      <c r="AD2" s="360"/>
+      <c r="AE2" s="360"/>
+      <c r="AF2" s="360"/>
+      <c r="AG2" s="360"/>
+      <c r="AH2" s="360"/>
+      <c r="AI2" s="361"/>
     </row>
     <row r="3" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="361"/>
+      <c r="B3" s="339"/>
       <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
@@ -5190,21 +5193,21 @@
       <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="339"/>
-      <c r="L3" s="371"/>
-      <c r="M3" s="371"/>
-      <c r="N3" s="371"/>
-      <c r="O3" s="371"/>
-      <c r="P3" s="340"/>
-      <c r="R3" s="358"/>
-      <c r="S3" s="307"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="345"/>
+      <c r="M3" s="345"/>
+      <c r="N3" s="345"/>
+      <c r="O3" s="345"/>
+      <c r="P3" s="346"/>
+      <c r="R3" s="356"/>
+      <c r="S3" s="353"/>
       <c r="T3" s="18">
         <v>15</v>
       </c>
-      <c r="U3" s="381" t="s">
+      <c r="U3" s="325" t="s">
         <v>79</v>
       </c>
-      <c r="V3" s="381"/>
+      <c r="V3" s="325"/>
       <c r="W3" s="19">
         <v>12</v>
       </c>
@@ -5217,10 +5220,10 @@
       <c r="Z3" s="19">
         <v>9</v>
       </c>
-      <c r="AA3" s="347" t="s">
+      <c r="AA3" s="358" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="347"/>
+      <c r="AB3" s="358"/>
       <c r="AC3" s="19">
         <v>6</v>
       </c>
@@ -5244,21 +5247,21 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="362"/>
+      <c r="B4" s="340"/>
       <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="351" t="s">
+      <c r="E4" s="326" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="275"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="289"/>
       <c r="K4" s="5" t="s">
         <v>7</v>
       </c>
@@ -5268,20 +5271,20 @@
       <c r="M4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="351" t="s">
+      <c r="N4" s="326" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="274"/>
-      <c r="P4" s="275"/>
-      <c r="R4" s="359"/>
-      <c r="S4" s="356"/>
+      <c r="O4" s="286"/>
+      <c r="P4" s="289"/>
+      <c r="R4" s="357"/>
+      <c r="S4" s="354"/>
       <c r="T4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="351" t="s">
+      <c r="U4" s="326" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="352"/>
+      <c r="V4" s="327"/>
       <c r="W4" s="7" t="s">
         <v>67</v>
       </c>
@@ -5294,10 +5297,10 @@
       <c r="Z4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="351" t="s">
+      <c r="AA4" s="326" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="352"/>
+      <c r="AB4" s="327"/>
       <c r="AC4" s="7" t="s">
         <v>11</v>
       </c>
@@ -5329,22 +5332,22 @@
         <f t="shared" ref="D5:D28" si="0">DEC2BIN(B5,5)</f>
         <v>00000</v>
       </c>
-      <c r="E5" s="378"/>
-      <c r="F5" s="379"/>
-      <c r="G5" s="379"/>
-      <c r="H5" s="379"/>
-      <c r="I5" s="379"/>
-      <c r="J5" s="380"/>
+      <c r="E5" s="330"/>
+      <c r="F5" s="331"/>
+      <c r="G5" s="331"/>
+      <c r="H5" s="331"/>
+      <c r="I5" s="331"/>
+      <c r="J5" s="332"/>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="29"/>
-      <c r="N5" s="287" t="s">
+      <c r="N5" s="295" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="288"/>
-      <c r="P5" s="289"/>
+      <c r="O5" s="296"/>
+      <c r="P5" s="297"/>
       <c r="R5" s="1">
         <v>0</v>
       </c>
@@ -5354,10 +5357,10 @@
       <c r="T5" s="27">
         <v>0</v>
       </c>
-      <c r="U5" s="353" t="s">
+      <c r="U5" s="328" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="354"/>
+      <c r="V5" s="329"/>
       <c r="W5" s="28">
         <v>0</v>
       </c>
@@ -5370,10 +5373,10 @@
       <c r="Z5" s="28">
         <v>0</v>
       </c>
-      <c r="AA5" s="353" t="s">
+      <c r="AA5" s="328" t="s">
         <v>69</v>
       </c>
-      <c r="AB5" s="354"/>
+      <c r="AB5" s="329"/>
       <c r="AC5" s="28">
         <v>0</v>
       </c>
@@ -5405,12 +5408,12 @@
         <f t="shared" si="0"/>
         <v>00001</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="364"/>
-      <c r="J6" s="365"/>
+      <c r="E6" s="337"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="334"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="335"/>
       <c r="K6" s="31" t="s">
         <v>10</v>
       </c>
@@ -5418,11 +5421,11 @@
         <v>131</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="284" t="s">
+      <c r="N6" s="298" t="s">
         <v>311</v>
       </c>
-      <c r="O6" s="285"/>
-      <c r="P6" s="286"/>
+      <c r="O6" s="299"/>
+      <c r="P6" s="300"/>
       <c r="R6" s="2">
         <v>1</v>
       </c>
@@ -5432,10 +5435,10 @@
       <c r="T6" s="33">
         <v>0</v>
       </c>
-      <c r="U6" s="343" t="s">
+      <c r="U6" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="344"/>
+      <c r="V6" s="324"/>
       <c r="W6" s="34">
         <v>0</v>
       </c>
@@ -5448,10 +5451,10 @@
       <c r="Z6" s="34">
         <v>0</v>
       </c>
-      <c r="AA6" s="343" t="s">
+      <c r="AA6" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB6" s="344"/>
+      <c r="AB6" s="324"/>
       <c r="AC6" s="34">
         <v>0</v>
       </c>
@@ -5494,9 +5497,9 @@
       <c r="G7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="363"/>
-      <c r="I7" s="364"/>
-      <c r="J7" s="365"/>
+      <c r="H7" s="333"/>
+      <c r="I7" s="334"/>
+      <c r="J7" s="335"/>
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
@@ -5504,11 +5507,11 @@
       <c r="M7" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N7" s="284" t="s">
+      <c r="N7" s="298" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="285"/>
-      <c r="P7" s="286"/>
+      <c r="O7" s="299"/>
+      <c r="P7" s="300"/>
       <c r="R7" s="2">
         <v>2</v>
       </c>
@@ -5518,10 +5521,10 @@
       <c r="T7" s="33">
         <v>0</v>
       </c>
-      <c r="U7" s="343" t="s">
+      <c r="U7" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="344"/>
+      <c r="V7" s="324"/>
       <c r="W7" s="34">
         <v>0</v>
       </c>
@@ -5534,10 +5537,10 @@
       <c r="Z7" s="34">
         <v>0</v>
       </c>
-      <c r="AA7" s="343" t="s">
+      <c r="AA7" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="344"/>
+      <c r="AB7" s="324"/>
       <c r="AC7" s="34">
         <v>0</v>
       </c>
@@ -5580,9 +5583,9 @@
       <c r="G8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="363"/>
-      <c r="I8" s="364"/>
-      <c r="J8" s="365"/>
+      <c r="H8" s="333"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="335"/>
       <c r="K8" s="37" t="s">
         <v>13</v>
       </c>
@@ -5590,11 +5593,11 @@
       <c r="M8" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N8" s="284" t="s">
+      <c r="N8" s="298" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="285"/>
-      <c r="P8" s="286"/>
+      <c r="O8" s="299"/>
+      <c r="P8" s="300"/>
       <c r="R8" s="2">
         <v>3</v>
       </c>
@@ -5604,10 +5607,10 @@
       <c r="T8" s="33">
         <v>0</v>
       </c>
-      <c r="U8" s="343" t="s">
+      <c r="U8" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="344"/>
+      <c r="V8" s="324"/>
       <c r="W8" s="34">
         <v>0</v>
       </c>
@@ -5620,10 +5623,10 @@
       <c r="Z8" s="34">
         <v>0</v>
       </c>
-      <c r="AA8" s="343" t="s">
+      <c r="AA8" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB8" s="344"/>
+      <c r="AB8" s="324"/>
       <c r="AC8" s="34">
         <v>0</v>
       </c>
@@ -5666,9 +5669,9 @@
       <c r="G9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="363"/>
-      <c r="I9" s="364"/>
-      <c r="J9" s="365"/>
+      <c r="H9" s="333"/>
+      <c r="I9" s="334"/>
+      <c r="J9" s="335"/>
       <c r="K9" s="37" t="s">
         <v>46</v>
       </c>
@@ -5676,11 +5679,11 @@
       <c r="M9" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="N9" s="298" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="285"/>
-      <c r="P9" s="286"/>
+      <c r="O9" s="299"/>
+      <c r="P9" s="300"/>
       <c r="R9" s="1">
         <v>4</v>
       </c>
@@ -5690,10 +5693,10 @@
       <c r="T9" s="33">
         <v>0</v>
       </c>
-      <c r="U9" s="343" t="s">
+      <c r="U9" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="344"/>
+      <c r="V9" s="324"/>
       <c r="W9" s="34">
         <v>0</v>
       </c>
@@ -5706,10 +5709,10 @@
       <c r="Z9" s="34">
         <v>0</v>
       </c>
-      <c r="AA9" s="343" t="s">
+      <c r="AA9" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" s="344"/>
+      <c r="AB9" s="324"/>
       <c r="AC9" s="34">
         <v>0</v>
       </c>
@@ -5752,9 +5755,9 @@
       <c r="G10" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="363"/>
-      <c r="I10" s="364"/>
-      <c r="J10" s="365"/>
+      <c r="H10" s="333"/>
+      <c r="I10" s="334"/>
+      <c r="J10" s="335"/>
       <c r="K10" s="37" t="s">
         <v>47</v>
       </c>
@@ -5762,11 +5765,11 @@
       <c r="M10" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="284" t="s">
+      <c r="N10" s="298" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="285"/>
-      <c r="P10" s="286"/>
+      <c r="O10" s="299"/>
+      <c r="P10" s="300"/>
       <c r="R10" s="2">
         <v>5</v>
       </c>
@@ -5776,10 +5779,10 @@
       <c r="T10" s="33">
         <v>0</v>
       </c>
-      <c r="U10" s="343" t="s">
+      <c r="U10" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V10" s="344"/>
+      <c r="V10" s="324"/>
       <c r="W10" s="34">
         <v>0</v>
       </c>
@@ -5792,10 +5795,10 @@
       <c r="Z10" s="34">
         <v>0</v>
       </c>
-      <c r="AA10" s="343" t="s">
+      <c r="AA10" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB10" s="344"/>
+      <c r="AB10" s="324"/>
       <c r="AC10" s="34">
         <v>0</v>
       </c>
@@ -5838,9 +5841,9 @@
       <c r="G11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="363"/>
-      <c r="I11" s="364"/>
-      <c r="J11" s="365"/>
+      <c r="H11" s="333"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="335"/>
       <c r="K11" s="37" t="s">
         <v>14</v>
       </c>
@@ -5848,11 +5851,11 @@
       <c r="M11" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="284" t="s">
+      <c r="N11" s="298" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="285"/>
-      <c r="P11" s="286"/>
+      <c r="O11" s="299"/>
+      <c r="P11" s="300"/>
       <c r="R11" s="2">
         <v>6</v>
       </c>
@@ -5862,10 +5865,10 @@
       <c r="T11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="343" t="s">
+      <c r="U11" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V11" s="344"/>
+      <c r="V11" s="324"/>
       <c r="W11" s="34">
         <v>0</v>
       </c>
@@ -5878,10 +5881,10 @@
       <c r="Z11" s="34">
         <v>0</v>
       </c>
-      <c r="AA11" s="343" t="s">
+      <c r="AA11" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB11" s="344"/>
+      <c r="AB11" s="324"/>
       <c r="AC11" s="34">
         <v>0</v>
       </c>
@@ -5924,9 +5927,9 @@
       <c r="G12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="363"/>
-      <c r="I12" s="364"/>
-      <c r="J12" s="365"/>
+      <c r="H12" s="333"/>
+      <c r="I12" s="334"/>
+      <c r="J12" s="335"/>
       <c r="K12" s="37" t="s">
         <v>15</v>
       </c>
@@ -5934,11 +5937,11 @@
       <c r="M12" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="284" t="s">
+      <c r="N12" s="298" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="285"/>
-      <c r="P12" s="286"/>
+      <c r="O12" s="299"/>
+      <c r="P12" s="300"/>
       <c r="R12" s="2">
         <v>7</v>
       </c>
@@ -5948,10 +5951,10 @@
       <c r="T12" s="33">
         <v>0</v>
       </c>
-      <c r="U12" s="343" t="s">
+      <c r="U12" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="344"/>
+      <c r="V12" s="324"/>
       <c r="W12" s="34">
         <v>0</v>
       </c>
@@ -5964,10 +5967,10 @@
       <c r="Z12" s="34">
         <v>0</v>
       </c>
-      <c r="AA12" s="343" t="s">
+      <c r="AA12" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="344"/>
+      <c r="AB12" s="324"/>
       <c r="AC12" s="34">
         <v>0</v>
       </c>
@@ -6010,9 +6013,9 @@
       <c r="G13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="363"/>
-      <c r="I13" s="364"/>
-      <c r="J13" s="365"/>
+      <c r="H13" s="333"/>
+      <c r="I13" s="334"/>
+      <c r="J13" s="335"/>
       <c r="K13" s="37" t="s">
         <v>16</v>
       </c>
@@ -6020,11 +6023,11 @@
       <c r="M13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="284" t="s">
+      <c r="N13" s="298" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="285"/>
-      <c r="P13" s="286"/>
+      <c r="O13" s="299"/>
+      <c r="P13" s="300"/>
       <c r="R13" s="1">
         <v>8</v>
       </c>
@@ -6034,10 +6037,10 @@
       <c r="T13" s="33">
         <v>0</v>
       </c>
-      <c r="U13" s="343" t="s">
+      <c r="U13" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V13" s="344"/>
+      <c r="V13" s="324"/>
       <c r="W13" s="34">
         <v>0</v>
       </c>
@@ -6050,10 +6053,10 @@
       <c r="Z13" s="34">
         <v>0</v>
       </c>
-      <c r="AA13" s="343" t="s">
+      <c r="AA13" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="344"/>
+      <c r="AB13" s="324"/>
       <c r="AC13" s="34">
         <v>0</v>
       </c>
@@ -6096,9 +6099,9 @@
       <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="363"/>
-      <c r="I14" s="364"/>
-      <c r="J14" s="365"/>
+      <c r="H14" s="333"/>
+      <c r="I14" s="334"/>
+      <c r="J14" s="335"/>
       <c r="K14" s="37" t="s">
         <v>17</v>
       </c>
@@ -6106,11 +6109,11 @@
       <c r="M14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N14" s="284" t="s">
+      <c r="N14" s="298" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="285"/>
-      <c r="P14" s="286"/>
+      <c r="O14" s="299"/>
+      <c r="P14" s="300"/>
       <c r="R14" s="2">
         <v>9</v>
       </c>
@@ -6120,10 +6123,10 @@
       <c r="T14" s="33">
         <v>0</v>
       </c>
-      <c r="U14" s="343" t="s">
+      <c r="U14" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="344"/>
+      <c r="V14" s="324"/>
       <c r="W14" s="34">
         <v>0</v>
       </c>
@@ -6136,10 +6139,10 @@
       <c r="Z14" s="34">
         <v>0</v>
       </c>
-      <c r="AA14" s="343" t="s">
+      <c r="AA14" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB14" s="344"/>
+      <c r="AB14" s="324"/>
       <c r="AC14" s="34">
         <v>0</v>
       </c>
@@ -6182,9 +6185,9 @@
       <c r="G15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="363"/>
-      <c r="I15" s="364"/>
-      <c r="J15" s="365"/>
+      <c r="H15" s="333"/>
+      <c r="I15" s="334"/>
+      <c r="J15" s="335"/>
       <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
@@ -6192,11 +6195,11 @@
       <c r="M15" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="284" t="s">
+      <c r="N15" s="298" t="s">
         <v>313</v>
       </c>
-      <c r="O15" s="285"/>
-      <c r="P15" s="286"/>
+      <c r="O15" s="299"/>
+      <c r="P15" s="300"/>
       <c r="R15" s="2">
         <v>10</v>
       </c>
@@ -6206,10 +6209,10 @@
       <c r="T15" s="33">
         <v>0</v>
       </c>
-      <c r="U15" s="343" t="s">
+      <c r="U15" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V15" s="344"/>
+      <c r="V15" s="324"/>
       <c r="W15" s="34">
         <v>0</v>
       </c>
@@ -6222,10 +6225,10 @@
       <c r="Z15" s="34">
         <v>0</v>
       </c>
-      <c r="AA15" s="343" t="s">
+      <c r="AA15" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB15" s="344"/>
+      <c r="AB15" s="324"/>
       <c r="AC15" s="34">
         <v>0</v>
       </c>
@@ -6262,21 +6265,21 @@
       <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="363"/>
-      <c r="G16" s="364"/>
-      <c r="H16" s="364"/>
-      <c r="I16" s="364"/>
-      <c r="J16" s="365"/>
+      <c r="F16" s="333"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="334"/>
+      <c r="I16" s="334"/>
+      <c r="J16" s="335"/>
       <c r="K16" s="40" t="s">
         <v>48</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="35"/>
-      <c r="N16" s="284" t="s">
+      <c r="N16" s="298" t="s">
         <v>314</v>
       </c>
-      <c r="O16" s="285"/>
-      <c r="P16" s="286"/>
+      <c r="O16" s="299"/>
+      <c r="P16" s="300"/>
       <c r="R16" s="2">
         <v>11</v>
       </c>
@@ -6286,10 +6289,10 @@
       <c r="T16" s="33">
         <v>0</v>
       </c>
-      <c r="U16" s="343" t="s">
+      <c r="U16" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V16" s="344"/>
+      <c r="V16" s="324"/>
       <c r="W16" s="34">
         <v>0</v>
       </c>
@@ -6302,10 +6305,10 @@
       <c r="Z16" s="34">
         <v>0</v>
       </c>
-      <c r="AA16" s="343" t="s">
+      <c r="AA16" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB16" s="344"/>
+      <c r="AB16" s="324"/>
       <c r="AC16" s="34">
         <v>0</v>
       </c>
@@ -6343,22 +6346,22 @@
         <v>27</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="370" t="s">
+      <c r="G17" s="336" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="285"/>
-      <c r="I17" s="285"/>
-      <c r="J17" s="286"/>
+      <c r="H17" s="299"/>
+      <c r="I17" s="299"/>
+      <c r="J17" s="300"/>
       <c r="K17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="35"/>
-      <c r="N17" s="284" t="s">
+      <c r="N17" s="298" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="285"/>
-      <c r="P17" s="286"/>
+      <c r="O17" s="299"/>
+      <c r="P17" s="300"/>
       <c r="R17" s="2">
         <v>12</v>
       </c>
@@ -6368,10 +6371,10 @@
       <c r="T17" s="33">
         <v>0</v>
       </c>
-      <c r="U17" s="343" t="s">
+      <c r="U17" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V17" s="344"/>
+      <c r="V17" s="324"/>
       <c r="W17" s="34">
         <v>0</v>
       </c>
@@ -6384,10 +6387,10 @@
       <c r="Z17" s="34">
         <v>0</v>
       </c>
-      <c r="AA17" s="343" t="s">
+      <c r="AA17" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="344"/>
+      <c r="AB17" s="324"/>
       <c r="AC17" s="34">
         <v>0</v>
       </c>
@@ -6425,12 +6428,12 @@
         <v>27</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="370" t="s">
+      <c r="G18" s="336" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="285"/>
-      <c r="I18" s="285"/>
-      <c r="J18" s="286"/>
+      <c r="H18" s="299"/>
+      <c r="I18" s="299"/>
+      <c r="J18" s="300"/>
       <c r="K18" s="40" t="s">
         <v>20</v>
       </c>
@@ -6438,11 +6441,11 @@
       <c r="M18" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="284" t="s">
+      <c r="N18" s="298" t="s">
         <v>57</v>
       </c>
-      <c r="O18" s="285"/>
-      <c r="P18" s="286"/>
+      <c r="O18" s="299"/>
+      <c r="P18" s="300"/>
       <c r="R18" s="2">
         <v>13</v>
       </c>
@@ -6452,10 +6455,10 @@
       <c r="T18" s="33">
         <v>0</v>
       </c>
-      <c r="U18" s="343" t="s">
+      <c r="U18" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="344"/>
+      <c r="V18" s="324"/>
       <c r="W18" s="34">
         <v>0</v>
       </c>
@@ -6468,10 +6471,10 @@
       <c r="Z18" s="34">
         <v>0</v>
       </c>
-      <c r="AA18" s="343" t="s">
+      <c r="AA18" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB18" s="344"/>
+      <c r="AB18" s="324"/>
       <c r="AC18" s="34">
         <v>0</v>
       </c>
@@ -6507,20 +6510,20 @@
       <c r="F19" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="363"/>
-      <c r="H19" s="364"/>
-      <c r="I19" s="364"/>
-      <c r="J19" s="365"/>
+      <c r="G19" s="333"/>
+      <c r="H19" s="334"/>
+      <c r="I19" s="334"/>
+      <c r="J19" s="335"/>
       <c r="K19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="35"/>
-      <c r="N19" s="284" t="s">
+      <c r="N19" s="298" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="285"/>
-      <c r="P19" s="286"/>
+      <c r="O19" s="299"/>
+      <c r="P19" s="300"/>
       <c r="R19" s="2">
         <v>14</v>
       </c>
@@ -6530,10 +6533,10 @@
       <c r="T19" s="33">
         <v>0</v>
       </c>
-      <c r="U19" s="343" t="s">
+      <c r="U19" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="344"/>
+      <c r="V19" s="324"/>
       <c r="W19" s="34">
         <v>0</v>
       </c>
@@ -6546,10 +6549,10 @@
       <c r="Z19" s="34">
         <v>0</v>
       </c>
-      <c r="AA19" s="343" t="s">
+      <c r="AA19" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB19" s="344"/>
+      <c r="AB19" s="324"/>
       <c r="AC19" s="34">
         <v>0</v>
       </c>
@@ -6587,20 +6590,20 @@
       <c r="F20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="363"/>
-      <c r="H20" s="364"/>
-      <c r="I20" s="364"/>
-      <c r="J20" s="365"/>
+      <c r="G20" s="333"/>
+      <c r="H20" s="334"/>
+      <c r="I20" s="334"/>
+      <c r="J20" s="335"/>
       <c r="K20" s="37" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="35"/>
-      <c r="N20" s="284" t="s">
+      <c r="N20" s="298" t="s">
         <v>316</v>
       </c>
-      <c r="O20" s="285"/>
-      <c r="P20" s="286"/>
+      <c r="O20" s="299"/>
+      <c r="P20" s="300"/>
       <c r="R20" s="2">
         <v>15</v>
       </c>
@@ -6610,10 +6613,10 @@
       <c r="T20" s="33">
         <v>0</v>
       </c>
-      <c r="U20" s="343" t="s">
+      <c r="U20" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V20" s="344"/>
+      <c r="V20" s="324"/>
       <c r="W20" s="34">
         <v>0</v>
       </c>
@@ -6626,10 +6629,10 @@
       <c r="Z20" s="34">
         <v>0</v>
       </c>
-      <c r="AA20" s="343" t="s">
+      <c r="AA20" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB20" s="344"/>
+      <c r="AB20" s="324"/>
       <c r="AC20" s="34">
         <v>0</v>
       </c>
@@ -6667,20 +6670,20 @@
       <c r="F21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="363"/>
-      <c r="H21" s="364"/>
-      <c r="I21" s="364"/>
-      <c r="J21" s="365"/>
+      <c r="G21" s="333"/>
+      <c r="H21" s="334"/>
+      <c r="I21" s="334"/>
+      <c r="J21" s="335"/>
       <c r="K21" s="44" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="38"/>
       <c r="M21" s="35"/>
-      <c r="N21" s="284" t="s">
+      <c r="N21" s="298" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="285"/>
-      <c r="P21" s="286"/>
+      <c r="O21" s="299"/>
+      <c r="P21" s="300"/>
       <c r="R21" s="2">
         <v>16</v>
       </c>
@@ -6690,10 +6693,10 @@
       <c r="T21" s="33">
         <v>0</v>
       </c>
-      <c r="U21" s="343" t="s">
+      <c r="U21" s="323" t="s">
         <v>88</v>
       </c>
-      <c r="V21" s="344"/>
+      <c r="V21" s="324"/>
       <c r="W21" s="34">
         <v>0</v>
       </c>
@@ -6706,10 +6709,10 @@
       <c r="Z21" s="34">
         <v>0</v>
       </c>
-      <c r="AA21" s="343" t="s">
+      <c r="AA21" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="AB21" s="344"/>
+      <c r="AB21" s="324"/>
       <c r="AC21" s="34">
         <v>0</v>
       </c>
@@ -6743,22 +6746,22 @@
         <f t="shared" si="0"/>
         <v>10001</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="364"/>
-      <c r="G22" s="364"/>
-      <c r="H22" s="364"/>
-      <c r="I22" s="364"/>
-      <c r="J22" s="365"/>
+      <c r="E22" s="337"/>
+      <c r="F22" s="334"/>
+      <c r="G22" s="334"/>
+      <c r="H22" s="334"/>
+      <c r="I22" s="334"/>
+      <c r="J22" s="335"/>
       <c r="K22" s="40" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="35"/>
-      <c r="N22" s="284" t="s">
+      <c r="N22" s="298" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="285"/>
-      <c r="P22" s="286"/>
+      <c r="O22" s="299"/>
+      <c r="P22" s="300"/>
       <c r="R22" s="2">
         <v>17</v>
       </c>
@@ -6768,10 +6771,10 @@
       <c r="T22" s="33">
         <v>0</v>
       </c>
-      <c r="U22" s="343" t="s">
+      <c r="U22" s="323" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="344"/>
+      <c r="V22" s="324"/>
       <c r="W22" s="34">
         <v>0</v>
       </c>
@@ -6784,10 +6787,10 @@
       <c r="Z22" s="34">
         <v>1</v>
       </c>
-      <c r="AA22" s="343" t="s">
+      <c r="AA22" s="323" t="s">
         <v>88</v>
       </c>
-      <c r="AB22" s="344"/>
+      <c r="AB22" s="324"/>
       <c r="AC22" s="34">
         <v>0</v>
       </c>
@@ -6827,22 +6830,22 @@
       <c r="F23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="370" t="s">
+      <c r="G23" s="336" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="285"/>
-      <c r="I23" s="285"/>
-      <c r="J23" s="286"/>
+      <c r="H23" s="299"/>
+      <c r="I23" s="299"/>
+      <c r="J23" s="300"/>
       <c r="K23" s="44" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="35"/>
-      <c r="N23" s="284" t="s">
+      <c r="N23" s="298" t="s">
         <v>78</v>
       </c>
-      <c r="O23" s="285"/>
-      <c r="P23" s="286"/>
+      <c r="O23" s="299"/>
+      <c r="P23" s="300"/>
       <c r="R23" s="2">
         <v>18</v>
       </c>
@@ -6852,10 +6855,10 @@
       <c r="T23" s="33">
         <v>0</v>
       </c>
-      <c r="U23" s="343" t="s">
+      <c r="U23" s="323" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="344"/>
+      <c r="V23" s="324"/>
       <c r="W23" s="34">
         <v>0</v>
       </c>
@@ -6868,10 +6871,10 @@
       <c r="Z23" s="34">
         <v>0</v>
       </c>
-      <c r="AA23" s="343" t="s">
+      <c r="AA23" s="323" t="s">
         <v>88</v>
       </c>
-      <c r="AB23" s="344"/>
+      <c r="AB23" s="324"/>
       <c r="AC23" s="34">
         <v>0</v>
       </c>
@@ -6911,22 +6914,22 @@
       <c r="F24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="370" t="s">
+      <c r="G24" s="336" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="285"/>
-      <c r="I24" s="285"/>
-      <c r="J24" s="286"/>
+      <c r="H24" s="299"/>
+      <c r="I24" s="299"/>
+      <c r="J24" s="300"/>
       <c r="K24" s="31" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="56"/>
-      <c r="N24" s="284" t="s">
+      <c r="N24" s="298" t="s">
         <v>77</v>
       </c>
-      <c r="O24" s="285"/>
-      <c r="P24" s="286"/>
+      <c r="O24" s="299"/>
+      <c r="P24" s="300"/>
       <c r="R24" s="2">
         <v>19</v>
       </c>
@@ -6936,10 +6939,10 @@
       <c r="T24" s="33">
         <v>0</v>
       </c>
-      <c r="U24" s="343" t="s">
+      <c r="U24" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V24" s="344"/>
+      <c r="V24" s="324"/>
       <c r="W24" s="34">
         <v>0</v>
       </c>
@@ -6952,10 +6955,10 @@
       <c r="Z24" s="34">
         <v>0</v>
       </c>
-      <c r="AA24" s="343" t="s">
+      <c r="AA24" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="AB24" s="344"/>
+      <c r="AB24" s="324"/>
       <c r="AC24" s="34">
         <v>0</v>
       </c>
@@ -6993,10 +6996,10 @@
       <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="363"/>
-      <c r="H25" s="364"/>
-      <c r="I25" s="364"/>
-      <c r="J25" s="365"/>
+      <c r="G25" s="333"/>
+      <c r="H25" s="334"/>
+      <c r="I25" s="334"/>
+      <c r="J25" s="335"/>
       <c r="K25" s="49" t="s">
         <v>38</v>
       </c>
@@ -7004,11 +7007,11 @@
         <v>131</v>
       </c>
       <c r="M25" s="56"/>
-      <c r="N25" s="284" t="s">
+      <c r="N25" s="298" t="s">
         <v>40</v>
       </c>
-      <c r="O25" s="285"/>
-      <c r="P25" s="286"/>
+      <c r="O25" s="299"/>
+      <c r="P25" s="300"/>
       <c r="R25" s="2">
         <v>20</v>
       </c>
@@ -7018,10 +7021,10 @@
       <c r="T25" s="33">
         <v>1</v>
       </c>
-      <c r="U25" s="343" t="s">
+      <c r="U25" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V25" s="344"/>
+      <c r="V25" s="324"/>
       <c r="W25" s="34">
         <v>0</v>
       </c>
@@ -7034,10 +7037,10 @@
       <c r="Z25" s="34">
         <v>0</v>
       </c>
-      <c r="AA25" s="343" t="s">
+      <c r="AA25" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB25" s="344"/>
+      <c r="AB25" s="324"/>
       <c r="AC25" s="34">
         <v>0</v>
       </c>
@@ -7075,10 +7078,10 @@
       <c r="F26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="363"/>
-      <c r="H26" s="364"/>
-      <c r="I26" s="364"/>
-      <c r="J26" s="365"/>
+      <c r="G26" s="333"/>
+      <c r="H26" s="334"/>
+      <c r="I26" s="334"/>
+      <c r="J26" s="335"/>
       <c r="K26" s="31" t="s">
         <v>39</v>
       </c>
@@ -7086,11 +7089,11 @@
         <v>131</v>
       </c>
       <c r="M26" s="56"/>
-      <c r="N26" s="284" t="s">
+      <c r="N26" s="298" t="s">
         <v>41</v>
       </c>
-      <c r="O26" s="285"/>
-      <c r="P26" s="286"/>
+      <c r="O26" s="299"/>
+      <c r="P26" s="300"/>
       <c r="R26" s="2">
         <v>21</v>
       </c>
@@ -7100,10 +7103,10 @@
       <c r="T26" s="33">
         <v>0</v>
       </c>
-      <c r="U26" s="343" t="s">
+      <c r="U26" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V26" s="344"/>
+      <c r="V26" s="324"/>
       <c r="W26" s="34">
         <v>1</v>
       </c>
@@ -7116,10 +7119,10 @@
       <c r="Z26" s="34">
         <v>0</v>
       </c>
-      <c r="AA26" s="343" t="s">
+      <c r="AA26" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB26" s="344"/>
+      <c r="AB26" s="324"/>
       <c r="AC26" s="34">
         <v>0</v>
       </c>
@@ -7151,22 +7154,22 @@
         <f t="shared" si="0"/>
         <v>10110</v>
       </c>
-      <c r="E27" s="369"/>
-      <c r="F27" s="364"/>
-      <c r="G27" s="364"/>
-      <c r="H27" s="364"/>
-      <c r="I27" s="364"/>
-      <c r="J27" s="365"/>
+      <c r="E27" s="337"/>
+      <c r="F27" s="334"/>
+      <c r="G27" s="334"/>
+      <c r="H27" s="334"/>
+      <c r="I27" s="334"/>
+      <c r="J27" s="335"/>
       <c r="K27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="56"/>
-      <c r="N27" s="284" t="s">
+      <c r="N27" s="298" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="285"/>
-      <c r="P27" s="286"/>
+      <c r="O27" s="299"/>
+      <c r="P27" s="300"/>
       <c r="R27" s="3">
         <v>22</v>
       </c>
@@ -7176,10 +7179,10 @@
       <c r="T27" s="33">
         <v>0</v>
       </c>
-      <c r="U27" s="343" t="s">
+      <c r="U27" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="V27" s="344"/>
+      <c r="V27" s="324"/>
       <c r="W27" s="34">
         <v>0</v>
       </c>
@@ -7192,10 +7195,10 @@
       <c r="Z27" s="34">
         <v>0</v>
       </c>
-      <c r="AA27" s="343" t="s">
+      <c r="AA27" s="323" t="s">
         <v>69</v>
       </c>
-      <c r="AB27" s="344"/>
+      <c r="AB27" s="324"/>
       <c r="AC27" s="34">
         <v>1</v>
       </c>
@@ -7227,12 +7230,12 @@
         <f t="shared" si="0"/>
         <v>10111</v>
       </c>
-      <c r="E28" s="366"/>
-      <c r="F28" s="367"/>
-      <c r="G28" s="367"/>
-      <c r="H28" s="367"/>
-      <c r="I28" s="367"/>
-      <c r="J28" s="368"/>
+      <c r="E28" s="341"/>
+      <c r="F28" s="342"/>
+      <c r="G28" s="342"/>
+      <c r="H28" s="342"/>
+      <c r="I28" s="342"/>
+      <c r="J28" s="343"/>
       <c r="K28" s="52" t="s">
         <v>44</v>
       </c>
@@ -7240,11 +7243,11 @@
         <v>131</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="281" t="s">
+      <c r="N28" s="311" t="s">
         <v>317</v>
       </c>
-      <c r="O28" s="282"/>
-      <c r="P28" s="283"/>
+      <c r="O28" s="312"/>
+      <c r="P28" s="313"/>
       <c r="R28" s="4">
         <v>23</v>
       </c>
@@ -7254,10 +7257,10 @@
       <c r="T28" s="12">
         <v>0</v>
       </c>
-      <c r="U28" s="345" t="s">
+      <c r="U28" s="370" t="s">
         <v>69</v>
       </c>
-      <c r="V28" s="346"/>
+      <c r="V28" s="371"/>
       <c r="W28" s="54">
         <v>0</v>
       </c>
@@ -7270,10 +7273,10 @@
       <c r="Z28" s="54">
         <v>0</v>
       </c>
-      <c r="AA28" s="345" t="s">
+      <c r="AA28" s="370" t="s">
         <v>69</v>
       </c>
-      <c r="AB28" s="346"/>
+      <c r="AB28" s="371"/>
       <c r="AC28" s="13">
         <v>1</v>
       </c>
@@ -7350,27 +7353,27 @@
       <c r="S30" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="T30" s="395" t="s">
+      <c r="T30" s="293" t="s">
         <v>133</v>
       </c>
-      <c r="U30" s="395"/>
-      <c r="V30" s="395"/>
-      <c r="W30" s="395"/>
-      <c r="X30" s="395"/>
-      <c r="Y30" s="395"/>
-      <c r="Z30" s="395"/>
-      <c r="AA30" s="395"/>
-      <c r="AB30" s="395"/>
-      <c r="AC30" s="355"/>
-      <c r="AE30" s="273" t="s">
+      <c r="U30" s="293"/>
+      <c r="V30" s="293"/>
+      <c r="W30" s="293"/>
+      <c r="X30" s="293"/>
+      <c r="Y30" s="293"/>
+      <c r="Z30" s="293"/>
+      <c r="AA30" s="293"/>
+      <c r="AB30" s="293"/>
+      <c r="AC30" s="294"/>
+      <c r="AE30" s="285" t="s">
         <v>422</v>
       </c>
-      <c r="AF30" s="274"/>
-      <c r="AG30" s="273" t="s">
+      <c r="AF30" s="286"/>
+      <c r="AG30" s="285" t="s">
         <v>423</v>
       </c>
-      <c r="AH30" s="274"/>
-      <c r="AI30" s="275"/>
+      <c r="AH30" s="286"/>
+      <c r="AI30" s="289"/>
     </row>
     <row r="31" spans="2:35" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="67" t="s">
@@ -7411,28 +7414,28 @@
       <c r="S31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="T31" s="287" t="s">
+      <c r="T31" s="295" t="s">
         <v>138</v>
       </c>
-      <c r="U31" s="288"/>
-      <c r="V31" s="288"/>
-      <c r="W31" s="288"/>
-      <c r="X31" s="288"/>
-      <c r="Y31" s="288"/>
-      <c r="Z31" s="288"/>
-      <c r="AA31" s="288"/>
-      <c r="AB31" s="288"/>
-      <c r="AC31" s="289"/>
-      <c r="AE31" s="390">
+      <c r="U31" s="296"/>
+      <c r="V31" s="296"/>
+      <c r="W31" s="296"/>
+      <c r="X31" s="296"/>
+      <c r="Y31" s="296"/>
+      <c r="Z31" s="296"/>
+      <c r="AA31" s="296"/>
+      <c r="AB31" s="296"/>
+      <c r="AC31" s="297"/>
+      <c r="AE31" s="287">
         <v>2</v>
       </c>
-      <c r="AF31" s="391"/>
-      <c r="AG31" s="392" t="str" cm="1">
+      <c r="AF31" s="288"/>
+      <c r="AG31" s="290" t="str" cm="1">
         <f t="array" ref="AG31">_xlfn.TEXTJOIN(", ", TRUE, _xlfn._xlws.FILTER(S5:S28, (T5:T28 &amp; TEXT(U5:U28, "00") &amp; W5:W28 &amp; X5:X28 &amp; Y5:Y28 &amp; Z5:Z28 &amp; TEXT(AA5:AA28, "00") &amp; AC5:AC28 &amp; AD5:AD28 &amp; AE5:AE28 &amp; AF5:AF28 &amp; AG5:AG28 &amp; AH5:AH28 &amp; AI5:AI28) = _xlfn.BASE(HEX2DEC(AE31), 2, 16), "No encontrado"))</f>
         <v>No encontrado</v>
       </c>
-      <c r="AH31" s="393"/>
-      <c r="AI31" s="394"/>
+      <c r="AH31" s="291"/>
+      <c r="AI31" s="292"/>
     </row>
     <row r="32" spans="2:35" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
@@ -7456,18 +7459,18 @@
       <c r="S32" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="T32" s="284" t="s">
+      <c r="T32" s="298" t="s">
         <v>139</v>
       </c>
-      <c r="U32" s="285"/>
-      <c r="V32" s="285"/>
-      <c r="W32" s="285"/>
-      <c r="X32" s="285"/>
-      <c r="Y32" s="285"/>
-      <c r="Z32" s="285"/>
-      <c r="AA32" s="285"/>
-      <c r="AB32" s="285"/>
-      <c r="AC32" s="286"/>
+      <c r="U32" s="299"/>
+      <c r="V32" s="299"/>
+      <c r="W32" s="299"/>
+      <c r="X32" s="299"/>
+      <c r="Y32" s="299"/>
+      <c r="Z32" s="299"/>
+      <c r="AA32" s="299"/>
+      <c r="AB32" s="299"/>
+      <c r="AC32" s="300"/>
     </row>
     <row r="33" spans="2:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H33" s="84" t="s">
@@ -7503,31 +7506,31 @@
       <c r="S33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="T33" s="284" t="s">
+      <c r="T33" s="298" t="s">
         <v>140</v>
       </c>
-      <c r="U33" s="285"/>
-      <c r="V33" s="285"/>
-      <c r="W33" s="285"/>
-      <c r="X33" s="285"/>
-      <c r="Y33" s="285"/>
-      <c r="Z33" s="285"/>
-      <c r="AA33" s="285"/>
-      <c r="AB33" s="285"/>
-      <c r="AC33" s="286"/>
+      <c r="U33" s="299"/>
+      <c r="V33" s="299"/>
+      <c r="W33" s="299"/>
+      <c r="X33" s="299"/>
+      <c r="Y33" s="299"/>
+      <c r="Z33" s="299"/>
+      <c r="AA33" s="299"/>
+      <c r="AB33" s="299"/>
+      <c r="AC33" s="300"/>
     </row>
     <row r="34" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="341" t="s">
+      <c r="B34" s="368" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="339" t="s">
+      <c r="C34" s="344" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="340"/>
-      <c r="E34" s="339" t="s">
+      <c r="D34" s="346"/>
+      <c r="E34" s="344" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="340"/>
+      <c r="F34" s="346"/>
       <c r="H34" s="77" t="s">
         <v>61</v>
       </c>
@@ -7555,21 +7558,21 @@
       <c r="S34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="284" t="s">
+      <c r="T34" s="298" t="s">
         <v>141</v>
       </c>
-      <c r="U34" s="285"/>
-      <c r="V34" s="285"/>
-      <c r="W34" s="285"/>
-      <c r="X34" s="285"/>
-      <c r="Y34" s="285"/>
-      <c r="Z34" s="285"/>
-      <c r="AA34" s="285"/>
-      <c r="AB34" s="285"/>
-      <c r="AC34" s="286"/>
+      <c r="U34" s="299"/>
+      <c r="V34" s="299"/>
+      <c r="W34" s="299"/>
+      <c r="X34" s="299"/>
+      <c r="Y34" s="299"/>
+      <c r="Z34" s="299"/>
+      <c r="AA34" s="299"/>
+      <c r="AB34" s="299"/>
+      <c r="AC34" s="300"/>
     </row>
     <row r="35" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="342"/>
+      <c r="B35" s="369"/>
       <c r="C35" s="64" t="s">
         <v>91</v>
       </c>
@@ -7588,18 +7591,18 @@
       <c r="S35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T35" s="284" t="s">
+      <c r="T35" s="298" t="s">
         <v>142</v>
       </c>
-      <c r="U35" s="285"/>
-      <c r="V35" s="285"/>
-      <c r="W35" s="285"/>
-      <c r="X35" s="285"/>
-      <c r="Y35" s="285"/>
-      <c r="Z35" s="285"/>
-      <c r="AA35" s="285"/>
-      <c r="AB35" s="285"/>
-      <c r="AC35" s="286"/>
+      <c r="U35" s="299"/>
+      <c r="V35" s="299"/>
+      <c r="W35" s="299"/>
+      <c r="X35" s="299"/>
+      <c r="Y35" s="299"/>
+      <c r="Z35" s="299"/>
+      <c r="AA35" s="299"/>
+      <c r="AB35" s="299"/>
+      <c r="AC35" s="300"/>
     </row>
     <row r="36" spans="2:29" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
@@ -7650,18 +7653,18 @@
       <c r="S36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T36" s="284" t="s">
+      <c r="T36" s="298" t="s">
         <v>143</v>
       </c>
-      <c r="U36" s="285"/>
-      <c r="V36" s="285"/>
-      <c r="W36" s="285"/>
-      <c r="X36" s="285"/>
-      <c r="Y36" s="285"/>
-      <c r="Z36" s="285"/>
-      <c r="AA36" s="285"/>
-      <c r="AB36" s="285"/>
-      <c r="AC36" s="286"/>
+      <c r="U36" s="299"/>
+      <c r="V36" s="299"/>
+      <c r="W36" s="299"/>
+      <c r="X36" s="299"/>
+      <c r="Y36" s="299"/>
+      <c r="Z36" s="299"/>
+      <c r="AA36" s="299"/>
+      <c r="AB36" s="299"/>
+      <c r="AC36" s="300"/>
     </row>
     <row r="37" spans="2:29" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
@@ -7704,18 +7707,18 @@
       <c r="S37" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T37" s="284" t="s">
+      <c r="T37" s="298" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="285"/>
-      <c r="V37" s="285"/>
-      <c r="W37" s="285"/>
-      <c r="X37" s="285"/>
-      <c r="Y37" s="285"/>
-      <c r="Z37" s="285"/>
-      <c r="AA37" s="285"/>
-      <c r="AB37" s="285"/>
-      <c r="AC37" s="286"/>
+      <c r="U37" s="299"/>
+      <c r="V37" s="299"/>
+      <c r="W37" s="299"/>
+      <c r="X37" s="299"/>
+      <c r="Y37" s="299"/>
+      <c r="Z37" s="299"/>
+      <c r="AA37" s="299"/>
+      <c r="AB37" s="299"/>
+      <c r="AC37" s="300"/>
     </row>
     <row r="38" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
@@ -7736,21 +7739,21 @@
       <c r="R38" s="2">
         <v>7</v>
       </c>
-      <c r="S38" s="382" t="s">
+      <c r="S38" s="303" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="384" t="s">
+      <c r="T38" s="305" t="s">
         <v>144</v>
       </c>
-      <c r="U38" s="385"/>
-      <c r="V38" s="385"/>
-      <c r="W38" s="385"/>
-      <c r="X38" s="385"/>
-      <c r="Y38" s="385"/>
-      <c r="Z38" s="385"/>
-      <c r="AA38" s="385"/>
-      <c r="AB38" s="385"/>
-      <c r="AC38" s="386"/>
+      <c r="U38" s="306"/>
+      <c r="V38" s="306"/>
+      <c r="W38" s="306"/>
+      <c r="X38" s="306"/>
+      <c r="Y38" s="306"/>
+      <c r="Z38" s="306"/>
+      <c r="AA38" s="306"/>
+      <c r="AB38" s="306"/>
+      <c r="AC38" s="307"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
@@ -7768,26 +7771,26 @@
       <c r="F39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="G39" s="328" t="s">
+      <c r="G39" s="314" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="279"/>
-      <c r="I39" s="279"/>
-      <c r="J39" s="280"/>
+      <c r="H39" s="315"/>
+      <c r="I39" s="315"/>
+      <c r="J39" s="316"/>
       <c r="R39" s="2">
         <v>8</v>
       </c>
-      <c r="S39" s="383"/>
-      <c r="T39" s="387"/>
-      <c r="U39" s="388"/>
-      <c r="V39" s="388"/>
-      <c r="W39" s="388"/>
-      <c r="X39" s="388"/>
-      <c r="Y39" s="388"/>
-      <c r="Z39" s="388"/>
-      <c r="AA39" s="388"/>
-      <c r="AB39" s="388"/>
-      <c r="AC39" s="389"/>
+      <c r="S39" s="304"/>
+      <c r="T39" s="308"/>
+      <c r="U39" s="309"/>
+      <c r="V39" s="309"/>
+      <c r="W39" s="309"/>
+      <c r="X39" s="309"/>
+      <c r="Y39" s="309"/>
+      <c r="Z39" s="309"/>
+      <c r="AA39" s="309"/>
+      <c r="AB39" s="309"/>
+      <c r="AC39" s="310"/>
     </row>
     <row r="40" spans="2:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
@@ -7805,28 +7808,28 @@
       <c r="F40" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="329"/>
-      <c r="H40" s="330"/>
-      <c r="I40" s="330"/>
-      <c r="J40" s="331"/>
+      <c r="G40" s="320"/>
+      <c r="H40" s="321"/>
+      <c r="I40" s="321"/>
+      <c r="J40" s="322"/>
       <c r="R40" s="2">
         <v>9</v>
       </c>
       <c r="S40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="284" t="s">
+      <c r="T40" s="298" t="s">
         <v>321</v>
       </c>
-      <c r="U40" s="285"/>
-      <c r="V40" s="285"/>
-      <c r="W40" s="285"/>
-      <c r="X40" s="285"/>
-      <c r="Y40" s="285"/>
-      <c r="Z40" s="285"/>
-      <c r="AA40" s="285"/>
-      <c r="AB40" s="285"/>
-      <c r="AC40" s="286"/>
+      <c r="U40" s="299"/>
+      <c r="V40" s="299"/>
+      <c r="W40" s="299"/>
+      <c r="X40" s="299"/>
+      <c r="Y40" s="299"/>
+      <c r="Z40" s="299"/>
+      <c r="AA40" s="299"/>
+      <c r="AB40" s="299"/>
+      <c r="AC40" s="300"/>
     </row>
     <row r="41" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
@@ -7844,28 +7847,28 @@
       <c r="F41" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="329"/>
-      <c r="H41" s="330"/>
-      <c r="I41" s="330"/>
-      <c r="J41" s="331"/>
+      <c r="G41" s="320"/>
+      <c r="H41" s="321"/>
+      <c r="I41" s="321"/>
+      <c r="J41" s="322"/>
       <c r="R41" s="2">
         <v>10</v>
       </c>
       <c r="S41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T41" s="284" t="s">
+      <c r="T41" s="298" t="s">
         <v>324</v>
       </c>
-      <c r="U41" s="285"/>
-      <c r="V41" s="285"/>
-      <c r="W41" s="285"/>
-      <c r="X41" s="285"/>
-      <c r="Y41" s="285"/>
-      <c r="Z41" s="285"/>
-      <c r="AA41" s="285"/>
-      <c r="AB41" s="285"/>
-      <c r="AC41" s="286"/>
+      <c r="U41" s="299"/>
+      <c r="V41" s="299"/>
+      <c r="W41" s="299"/>
+      <c r="X41" s="299"/>
+      <c r="Y41" s="299"/>
+      <c r="Z41" s="299"/>
+      <c r="AA41" s="299"/>
+      <c r="AB41" s="299"/>
+      <c r="AC41" s="300"/>
     </row>
     <row r="42" spans="2:29" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
@@ -7883,28 +7886,28 @@
       <c r="F42" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="332"/>
-      <c r="H42" s="333"/>
-      <c r="I42" s="333"/>
-      <c r="J42" s="334"/>
+      <c r="G42" s="317"/>
+      <c r="H42" s="318"/>
+      <c r="I42" s="318"/>
+      <c r="J42" s="319"/>
       <c r="R42" s="2">
         <v>11</v>
       </c>
       <c r="S42" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="T42" s="284" t="s">
+      <c r="T42" s="298" t="s">
         <v>145</v>
       </c>
-      <c r="U42" s="285"/>
-      <c r="V42" s="285"/>
-      <c r="W42" s="285"/>
-      <c r="X42" s="285"/>
-      <c r="Y42" s="285"/>
-      <c r="Z42" s="285"/>
-      <c r="AA42" s="285"/>
-      <c r="AB42" s="285"/>
-      <c r="AC42" s="286"/>
+      <c r="U42" s="299"/>
+      <c r="V42" s="299"/>
+      <c r="W42" s="299"/>
+      <c r="X42" s="299"/>
+      <c r="Y42" s="299"/>
+      <c r="Z42" s="299"/>
+      <c r="AA42" s="299"/>
+      <c r="AB42" s="299"/>
+      <c r="AC42" s="300"/>
     </row>
     <row r="43" spans="2:29" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
@@ -7922,30 +7925,30 @@
       <c r="F43" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="257" t="s">
+      <c r="G43" s="374" t="s">
         <v>328</v>
       </c>
-      <c r="H43" s="258"/>
-      <c r="I43" s="258"/>
-      <c r="J43" s="259"/>
+      <c r="H43" s="301"/>
+      <c r="I43" s="301"/>
+      <c r="J43" s="302"/>
       <c r="R43" s="2">
         <v>12</v>
       </c>
       <c r="S43" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="T43" s="284" t="s">
+      <c r="T43" s="298" t="s">
         <v>146</v>
       </c>
-      <c r="U43" s="285"/>
-      <c r="V43" s="285"/>
-      <c r="W43" s="285"/>
-      <c r="X43" s="285"/>
-      <c r="Y43" s="285"/>
-      <c r="Z43" s="285"/>
-      <c r="AA43" s="285"/>
-      <c r="AB43" s="285"/>
-      <c r="AC43" s="286"/>
+      <c r="U43" s="299"/>
+      <c r="V43" s="299"/>
+      <c r="W43" s="299"/>
+      <c r="X43" s="299"/>
+      <c r="Y43" s="299"/>
+      <c r="Z43" s="299"/>
+      <c r="AA43" s="299"/>
+      <c r="AB43" s="299"/>
+      <c r="AC43" s="300"/>
     </row>
     <row r="44" spans="2:29" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
@@ -7966,21 +7969,21 @@
       <c r="R44" s="2">
         <v>13</v>
       </c>
-      <c r="S44" s="382" t="s">
+      <c r="S44" s="303" t="s">
         <v>71</v>
       </c>
-      <c r="T44" s="384" t="s">
+      <c r="T44" s="305" t="s">
         <v>330</v>
       </c>
-      <c r="U44" s="385"/>
-      <c r="V44" s="385"/>
-      <c r="W44" s="385"/>
-      <c r="X44" s="385"/>
-      <c r="Y44" s="385"/>
-      <c r="Z44" s="385"/>
-      <c r="AA44" s="385"/>
-      <c r="AB44" s="385"/>
-      <c r="AC44" s="386"/>
+      <c r="U44" s="306"/>
+      <c r="V44" s="306"/>
+      <c r="W44" s="306"/>
+      <c r="X44" s="306"/>
+      <c r="Y44" s="306"/>
+      <c r="Z44" s="306"/>
+      <c r="AA44" s="306"/>
+      <c r="AB44" s="306"/>
+      <c r="AC44" s="307"/>
     </row>
     <row r="45" spans="2:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
@@ -7998,26 +8001,26 @@
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="328" t="s">
+      <c r="G45" s="314" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="279"/>
-      <c r="I45" s="279"/>
-      <c r="J45" s="280"/>
+      <c r="H45" s="315"/>
+      <c r="I45" s="315"/>
+      <c r="J45" s="316"/>
       <c r="R45" s="2">
         <v>14</v>
       </c>
-      <c r="S45" s="383"/>
-      <c r="T45" s="387"/>
-      <c r="U45" s="388"/>
-      <c r="V45" s="388"/>
-      <c r="W45" s="388"/>
-      <c r="X45" s="388"/>
-      <c r="Y45" s="388"/>
-      <c r="Z45" s="388"/>
-      <c r="AA45" s="388"/>
-      <c r="AB45" s="388"/>
-      <c r="AC45" s="389"/>
+      <c r="S45" s="304"/>
+      <c r="T45" s="308"/>
+      <c r="U45" s="309"/>
+      <c r="V45" s="309"/>
+      <c r="W45" s="309"/>
+      <c r="X45" s="309"/>
+      <c r="Y45" s="309"/>
+      <c r="Z45" s="309"/>
+      <c r="AA45" s="309"/>
+      <c r="AB45" s="309"/>
+      <c r="AC45" s="310"/>
     </row>
     <row r="46" spans="2:29" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
@@ -8035,28 +8038,28 @@
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="332"/>
-      <c r="H46" s="333"/>
-      <c r="I46" s="333"/>
-      <c r="J46" s="334"/>
+      <c r="G46" s="317"/>
+      <c r="H46" s="318"/>
+      <c r="I46" s="318"/>
+      <c r="J46" s="319"/>
       <c r="R46" s="4">
         <v>15</v>
       </c>
       <c r="S46" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="T46" s="281" t="s">
+      <c r="T46" s="311" t="s">
         <v>147</v>
       </c>
-      <c r="U46" s="282"/>
-      <c r="V46" s="282"/>
-      <c r="W46" s="282"/>
-      <c r="X46" s="282"/>
-      <c r="Y46" s="282"/>
-      <c r="Z46" s="282"/>
-      <c r="AA46" s="282"/>
-      <c r="AB46" s="282"/>
-      <c r="AC46" s="283"/>
+      <c r="U46" s="312"/>
+      <c r="V46" s="312"/>
+      <c r="W46" s="312"/>
+      <c r="X46" s="312"/>
+      <c r="Y46" s="312"/>
+      <c r="Z46" s="312"/>
+      <c r="AA46" s="312"/>
+      <c r="AB46" s="312"/>
+      <c r="AC46" s="313"/>
     </row>
     <row r="47" spans="2:29" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
@@ -8074,12 +8077,12 @@
       <c r="F47" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="258" t="s">
+      <c r="G47" s="301" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="258"/>
-      <c r="I47" s="258"/>
-      <c r="J47" s="259"/>
+      <c r="H47" s="301"/>
+      <c r="I47" s="301"/>
+      <c r="J47" s="302"/>
     </row>
     <row r="48" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
@@ -8124,11 +8127,11 @@
       <c r="Z48" s="72">
         <v>0</v>
       </c>
-      <c r="AA48" s="298" t="s">
+      <c r="AA48" s="383" t="s">
         <v>334</v>
       </c>
-      <c r="AB48" s="299"/>
-      <c r="AC48" s="300"/>
+      <c r="AB48" s="384"/>
+      <c r="AC48" s="385"/>
     </row>
     <row r="49" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
@@ -8146,12 +8149,12 @@
       <c r="F49" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="328" t="s">
+      <c r="G49" s="314" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="279"/>
-      <c r="I49" s="279"/>
-      <c r="J49" s="280"/>
+      <c r="H49" s="315"/>
+      <c r="I49" s="315"/>
+      <c r="J49" s="316"/>
       <c r="R49" s="77" t="s">
         <v>61</v>
       </c>
@@ -8167,9 +8170,9 @@
       <c r="Z49" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="AA49" s="301"/>
-      <c r="AB49" s="302"/>
-      <c r="AC49" s="303"/>
+      <c r="AA49" s="386"/>
+      <c r="AB49" s="387"/>
+      <c r="AC49" s="388"/>
     </row>
     <row r="50" spans="2:29" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
@@ -8187,10 +8190,10 @@
       <c r="F50" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="329"/>
-      <c r="H50" s="330"/>
-      <c r="I50" s="330"/>
-      <c r="J50" s="331"/>
+      <c r="G50" s="320"/>
+      <c r="H50" s="321"/>
+      <c r="I50" s="321"/>
+      <c r="J50" s="322"/>
     </row>
     <row r="51" spans="2:29" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
@@ -8208,35 +8211,35 @@
       <c r="F51" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="332"/>
-      <c r="H51" s="333"/>
-      <c r="I51" s="333"/>
-      <c r="J51" s="334"/>
-      <c r="R51" s="316" t="s">
+      <c r="G51" s="317"/>
+      <c r="H51" s="318"/>
+      <c r="I51" s="318"/>
+      <c r="J51" s="319"/>
+      <c r="R51" s="379" t="s">
         <v>299</v>
       </c>
-      <c r="S51" s="318" t="s">
+      <c r="S51" s="362" t="s">
         <v>156</v>
       </c>
-      <c r="T51" s="320" t="s">
+      <c r="T51" s="375" t="s">
         <v>155</v>
       </c>
-      <c r="U51" s="320"/>
-      <c r="V51" s="321"/>
+      <c r="U51" s="375"/>
+      <c r="V51" s="376"/>
     </row>
     <row r="52" spans="2:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="273" t="s">
+      <c r="B52" s="285" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="274"/>
-      <c r="D52" s="274"/>
-      <c r="E52" s="274"/>
-      <c r="F52" s="275"/>
-      <c r="R52" s="317"/>
-      <c r="S52" s="319"/>
-      <c r="T52" s="322"/>
-      <c r="U52" s="322"/>
-      <c r="V52" s="323"/>
+      <c r="C52" s="286"/>
+      <c r="D52" s="286"/>
+      <c r="E52" s="286"/>
+      <c r="F52" s="289"/>
+      <c r="R52" s="400"/>
+      <c r="S52" s="363"/>
+      <c r="T52" s="377"/>
+      <c r="U52" s="377"/>
+      <c r="V52" s="378"/>
     </row>
     <row r="53" spans="2:29" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R53" s="164" t="s">
@@ -8245,67 +8248,67 @@
       <c r="S53" s="165" t="s">
         <v>300</v>
       </c>
-      <c r="T53" s="311" t="s">
+      <c r="T53" s="395" t="s">
         <v>338</v>
       </c>
-      <c r="U53" s="311"/>
-      <c r="V53" s="312"/>
+      <c r="U53" s="395"/>
+      <c r="V53" s="396"/>
     </row>
     <row r="54" spans="2:29" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="337" t="s">
+      <c r="B54" s="364" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="318" t="s">
+      <c r="C54" s="362" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="320" t="s">
+      <c r="D54" s="375" t="s">
         <v>155</v>
       </c>
-      <c r="E54" s="321"/>
-      <c r="H54" s="316" t="s">
+      <c r="E54" s="376"/>
+      <c r="H54" s="379" t="s">
         <v>290</v>
       </c>
-      <c r="I54" s="318" t="s">
+      <c r="I54" s="362" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="304" t="s">
+      <c r="J54" s="389" t="s">
         <v>155</v>
       </c>
-      <c r="K54" s="305"/>
-      <c r="L54" s="306"/>
+      <c r="K54" s="390"/>
+      <c r="L54" s="391"/>
       <c r="R54" s="162" t="s">
         <v>204</v>
       </c>
       <c r="S54" s="160" t="s">
         <v>301</v>
       </c>
-      <c r="T54" s="324" t="s">
+      <c r="T54" s="401" t="s">
         <v>307</v>
       </c>
-      <c r="U54" s="324"/>
-      <c r="V54" s="325"/>
+      <c r="U54" s="401"/>
+      <c r="V54" s="367"/>
     </row>
     <row r="55" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="338"/>
-      <c r="C55" s="319"/>
-      <c r="D55" s="322"/>
-      <c r="E55" s="323"/>
-      <c r="H55" s="335"/>
-      <c r="I55" s="336"/>
-      <c r="J55" s="307"/>
-      <c r="K55" s="308"/>
-      <c r="L55" s="309"/>
+      <c r="B55" s="365"/>
+      <c r="C55" s="363"/>
+      <c r="D55" s="377"/>
+      <c r="E55" s="378"/>
+      <c r="H55" s="380"/>
+      <c r="I55" s="381"/>
+      <c r="J55" s="353"/>
+      <c r="K55" s="392"/>
+      <c r="L55" s="393"/>
       <c r="R55" s="162" t="s">
         <v>190</v>
       </c>
       <c r="S55" s="160" t="s">
         <v>302</v>
       </c>
-      <c r="T55" s="324" t="s">
+      <c r="T55" s="401" t="s">
         <v>339</v>
       </c>
-      <c r="U55" s="324"/>
-      <c r="V55" s="325"/>
+      <c r="U55" s="401"/>
+      <c r="V55" s="367"/>
     </row>
     <row r="56" spans="2:29" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
@@ -8314,36 +8317,36 @@
       <c r="C56" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="287" t="s">
+      <c r="D56" s="295" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="289"/>
+      <c r="E56" s="297"/>
       <c r="H56" s="81" t="s">
         <v>293</v>
       </c>
       <c r="I56" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="310" t="s">
+      <c r="J56" s="394" t="s">
         <v>291</v>
       </c>
-      <c r="K56" s="311"/>
-      <c r="L56" s="312"/>
-      <c r="M56" s="257" t="s">
+      <c r="K56" s="395"/>
+      <c r="L56" s="396"/>
+      <c r="M56" s="374" t="s">
         <v>340</v>
       </c>
-      <c r="N56" s="259"/>
+      <c r="N56" s="302"/>
       <c r="R56" s="162" t="s">
         <v>215</v>
       </c>
       <c r="S56" s="160" t="s">
         <v>303</v>
       </c>
-      <c r="T56" s="324" t="s">
+      <c r="T56" s="401" t="s">
         <v>341</v>
       </c>
-      <c r="U56" s="324"/>
-      <c r="V56" s="325"/>
+      <c r="U56" s="401"/>
+      <c r="V56" s="367"/>
     </row>
     <row r="57" spans="2:29" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="82">
@@ -8352,36 +8355,36 @@
       <c r="C57" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="326" t="s">
+      <c r="D57" s="366" t="s">
         <v>287</v>
       </c>
-      <c r="E57" s="325"/>
-      <c r="F57" s="257" t="s">
+      <c r="E57" s="367"/>
+      <c r="F57" s="374" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="259"/>
+      <c r="G57" s="302"/>
       <c r="H57" s="82">
         <v>0</v>
       </c>
       <c r="I57" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="J57" s="313" t="s">
+      <c r="J57" s="397" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="314"/>
-      <c r="L57" s="315"/>
+      <c r="K57" s="398"/>
+      <c r="L57" s="399"/>
       <c r="R57" s="162" t="s">
         <v>228</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="T57" s="324" t="s">
+      <c r="T57" s="401" t="s">
         <v>344</v>
       </c>
-      <c r="U57" s="324"/>
-      <c r="V57" s="325"/>
+      <c r="U57" s="401"/>
+      <c r="V57" s="367"/>
     </row>
     <row r="58" spans="2:29" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="82">
@@ -8390,32 +8393,32 @@
       <c r="C58" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="D58" s="326" t="s">
+      <c r="D58" s="366" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="325"/>
+      <c r="E58" s="367"/>
       <c r="H58" s="82">
         <v>1</v>
       </c>
       <c r="I58" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="313" t="s">
+      <c r="J58" s="397" t="s">
         <v>347</v>
       </c>
-      <c r="K58" s="314"/>
-      <c r="L58" s="315"/>
+      <c r="K58" s="398"/>
+      <c r="L58" s="399"/>
       <c r="R58" s="162" t="s">
         <v>229</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="T58" s="324" t="s">
+      <c r="T58" s="401" t="s">
         <v>348</v>
       </c>
-      <c r="U58" s="324"/>
-      <c r="V58" s="325"/>
+      <c r="U58" s="401"/>
+      <c r="V58" s="367"/>
     </row>
     <row r="59" spans="2:29" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="82">
@@ -8424,32 +8427,32 @@
       <c r="C59" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="D59" s="326" t="s">
+      <c r="D59" s="366" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="325"/>
+      <c r="E59" s="367"/>
       <c r="H59" s="82">
         <v>2</v>
       </c>
       <c r="I59" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="313" t="s">
+      <c r="J59" s="397" t="s">
         <v>350</v>
       </c>
-      <c r="K59" s="314"/>
-      <c r="L59" s="315"/>
+      <c r="K59" s="398"/>
+      <c r="L59" s="399"/>
       <c r="R59" s="162" t="s">
         <v>230</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="T59" s="324" t="s">
+      <c r="T59" s="401" t="s">
         <v>351</v>
       </c>
-      <c r="U59" s="324"/>
-      <c r="V59" s="325"/>
+      <c r="U59" s="401"/>
+      <c r="V59" s="367"/>
       <c r="X59" s="166"/>
     </row>
     <row r="60" spans="2:29" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8459,32 +8462,32 @@
       <c r="C60" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="326" t="s">
+      <c r="D60" s="366" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="325"/>
+      <c r="E60" s="367"/>
       <c r="H60" s="82">
         <v>3</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="313" t="s">
+      <c r="J60" s="397" t="s">
         <v>309</v>
       </c>
-      <c r="K60" s="314"/>
-      <c r="L60" s="315"/>
+      <c r="K60" s="398"/>
+      <c r="L60" s="399"/>
       <c r="R60" s="162" t="s">
         <v>231</v>
       </c>
       <c r="S60" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T60" s="324" t="s">
+      <c r="T60" s="401" t="s">
         <v>459</v>
       </c>
-      <c r="U60" s="324"/>
-      <c r="V60" s="325"/>
+      <c r="U60" s="401"/>
+      <c r="V60" s="367"/>
     </row>
     <row r="61" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="82">
@@ -8493,101 +8496,101 @@
       <c r="C61" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="326" t="s">
+      <c r="D61" s="366" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="325"/>
+      <c r="E61" s="367"/>
       <c r="H61" s="82">
         <v>4</v>
       </c>
       <c r="I61" s="38"/>
-      <c r="J61" s="313"/>
-      <c r="K61" s="314"/>
-      <c r="L61" s="315"/>
+      <c r="J61" s="397"/>
+      <c r="K61" s="398"/>
+      <c r="L61" s="399"/>
       <c r="R61" s="162" t="s">
         <v>232</v>
       </c>
       <c r="S61" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T61" s="324"/>
-      <c r="U61" s="324"/>
-      <c r="V61" s="325"/>
+      <c r="T61" s="401"/>
+      <c r="U61" s="401"/>
+      <c r="V61" s="367"/>
     </row>
     <row r="62" spans="2:29" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="82">
         <v>6</v>
       </c>
       <c r="C62" s="38"/>
-      <c r="D62" s="326"/>
-      <c r="E62" s="325"/>
+      <c r="D62" s="366"/>
+      <c r="E62" s="367"/>
       <c r="H62" s="82">
         <v>5</v>
       </c>
       <c r="I62" s="38"/>
-      <c r="J62" s="313"/>
-      <c r="K62" s="314"/>
-      <c r="L62" s="315"/>
+      <c r="J62" s="397"/>
+      <c r="K62" s="398"/>
+      <c r="L62" s="399"/>
       <c r="R62" s="162" t="s">
         <v>264</v>
       </c>
       <c r="S62" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T62" s="324"/>
-      <c r="U62" s="324"/>
-      <c r="V62" s="325"/>
+      <c r="T62" s="401"/>
+      <c r="U62" s="401"/>
+      <c r="V62" s="367"/>
     </row>
     <row r="63" spans="2:29" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82">
         <v>7</v>
       </c>
       <c r="C63" s="85"/>
-      <c r="D63" s="326"/>
-      <c r="E63" s="325"/>
+      <c r="D63" s="366"/>
+      <c r="E63" s="367"/>
       <c r="H63" s="82">
         <v>6</v>
       </c>
       <c r="I63" s="85"/>
-      <c r="J63" s="313"/>
-      <c r="K63" s="314"/>
-      <c r="L63" s="315"/>
+      <c r="J63" s="397"/>
+      <c r="K63" s="398"/>
+      <c r="L63" s="399"/>
       <c r="R63" s="162" t="s">
         <v>352</v>
       </c>
       <c r="S63" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="T63" s="324"/>
-      <c r="U63" s="324"/>
-      <c r="V63" s="325"/>
+      <c r="T63" s="401"/>
+      <c r="U63" s="401"/>
+      <c r="V63" s="367"/>
     </row>
     <row r="64" spans="2:29" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="82">
         <v>8</v>
       </c>
       <c r="C64" s="85"/>
-      <c r="D64" s="326"/>
-      <c r="E64" s="325"/>
+      <c r="D64" s="366"/>
+      <c r="E64" s="367"/>
       <c r="R64" s="163" t="s">
         <v>456</v>
       </c>
       <c r="S64" s="161" t="s">
         <v>457</v>
       </c>
-      <c r="T64" s="296" t="s">
+      <c r="T64" s="382" t="s">
         <v>458</v>
       </c>
-      <c r="U64" s="296"/>
-      <c r="V64" s="297"/>
+      <c r="U64" s="382"/>
+      <c r="V64" s="373"/>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="82">
         <v>9</v>
       </c>
       <c r="C65" s="85"/>
-      <c r="D65" s="326"/>
-      <c r="E65" s="325"/>
+      <c r="D65" s="366"/>
+      <c r="E65" s="367"/>
       <c r="T65" s="166"/>
     </row>
     <row r="66" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8595,76 +8598,192 @@
         <v>10</v>
       </c>
       <c r="C66" s="85"/>
-      <c r="D66" s="326"/>
-      <c r="E66" s="325"/>
+      <c r="D66" s="366"/>
+      <c r="E66" s="367"/>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="82">
         <v>11</v>
       </c>
       <c r="C67" s="85"/>
-      <c r="D67" s="326"/>
-      <c r="E67" s="325"/>
+      <c r="D67" s="366"/>
+      <c r="E67" s="367"/>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="82">
         <v>12</v>
       </c>
       <c r="C68" s="85"/>
-      <c r="D68" s="326"/>
-      <c r="E68" s="325"/>
+      <c r="D68" s="366"/>
+      <c r="E68" s="367"/>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="82">
         <v>13</v>
       </c>
       <c r="C69" s="85"/>
-      <c r="D69" s="326"/>
-      <c r="E69" s="325"/>
+      <c r="D69" s="366"/>
+      <c r="E69" s="367"/>
     </row>
     <row r="70" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="82">
         <v>14</v>
       </c>
       <c r="C70" s="85"/>
-      <c r="D70" s="326"/>
-      <c r="E70" s="325"/>
+      <c r="D70" s="366"/>
+      <c r="E70" s="367"/>
     </row>
     <row r="71" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="83">
         <v>15</v>
       </c>
       <c r="C71" s="86"/>
-      <c r="D71" s="327"/>
-      <c r="E71" s="297"/>
+      <c r="D71" s="372"/>
+      <c r="E71" s="373"/>
     </row>
     <row r="75" spans="2:20" ht="72" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="T30:AC30"/>
-    <mergeCell ref="T31:AC31"/>
-    <mergeCell ref="T32:AC32"/>
-    <mergeCell ref="T33:AC33"/>
-    <mergeCell ref="T34:AC34"/>
-    <mergeCell ref="T35:AC35"/>
-    <mergeCell ref="T36:AC36"/>
-    <mergeCell ref="T37:AC37"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="T38:AC39"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="T44:AC45"/>
-    <mergeCell ref="T40:AC40"/>
-    <mergeCell ref="T41:AC41"/>
-    <mergeCell ref="T42:AC42"/>
-    <mergeCell ref="T43:AC43"/>
-    <mergeCell ref="T46:AC46"/>
-    <mergeCell ref="G45:J46"/>
-    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="T64:V64"/>
+    <mergeCell ref="AA48:AC49"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="T55:V55"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="T60:V63"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D54:E55"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G49:J51"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="N13:P13"/>
     <mergeCell ref="AA20:AB20"/>
     <mergeCell ref="AA21:AB21"/>
     <mergeCell ref="AA22:AB22"/>
@@ -8689,146 +8808,30 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D54:E55"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G49:J51"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="T64:V64"/>
-    <mergeCell ref="AA48:AC49"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R51:R52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="T55:V55"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="T57:V57"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="T59:V59"/>
-    <mergeCell ref="T60:V63"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="T35:AC35"/>
+    <mergeCell ref="T36:AC36"/>
+    <mergeCell ref="T37:AC37"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:AC39"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="T44:AC45"/>
+    <mergeCell ref="T40:AC40"/>
+    <mergeCell ref="T41:AC41"/>
+    <mergeCell ref="T42:AC42"/>
+    <mergeCell ref="T43:AC43"/>
+    <mergeCell ref="T46:AC46"/>
+    <mergeCell ref="G45:J46"/>
+    <mergeCell ref="G39:J42"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="T30:AC30"/>
+    <mergeCell ref="T31:AC31"/>
+    <mergeCell ref="T32:AC32"/>
+    <mergeCell ref="T33:AC33"/>
+    <mergeCell ref="T34:AC34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8883,35 +8886,35 @@
       <c r="F2" s="179" t="s">
         <v>358</v>
       </c>
-      <c r="G2" s="279" t="s">
+      <c r="G2" s="315" t="s">
         <v>171</v>
       </c>
-      <c r="H2" s="279"/>
-      <c r="I2" s="279"/>
-      <c r="J2" s="280"/>
-      <c r="L2" s="248" t="s">
+      <c r="H2" s="315"/>
+      <c r="I2" s="315"/>
+      <c r="J2" s="316"/>
+      <c r="L2" s="414" t="s">
         <v>274</v>
       </c>
-      <c r="M2" s="249"/>
-      <c r="N2" s="249"/>
-      <c r="O2" s="250"/>
+      <c r="M2" s="415"/>
+      <c r="N2" s="415"/>
+      <c r="O2" s="416"/>
       <c r="P2" s="114"/>
-      <c r="Q2" s="251" t="s">
+      <c r="Q2" s="417" t="s">
         <v>237</v>
       </c>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="253"/>
+      <c r="R2" s="418"/>
+      <c r="S2" s="418"/>
+      <c r="T2" s="419"/>
       <c r="U2" s="114"/>
-      <c r="V2" s="245" t="s">
+      <c r="V2" s="411" t="s">
         <v>260</v>
       </c>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="247"/>
+      <c r="W2" s="412"/>
+      <c r="X2" s="412"/>
+      <c r="Y2" s="412"/>
+      <c r="Z2" s="412"/>
+      <c r="AA2" s="412"/>
+      <c r="AB2" s="413"/>
     </row>
     <row r="3" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="186" t="s">
@@ -8932,11 +8935,11 @@
       <c r="G3" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="H3" s="287" t="s">
+      <c r="H3" s="295" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="288"/>
-      <c r="J3" s="289"/>
+      <c r="I3" s="296"/>
+      <c r="J3" s="297"/>
       <c r="L3" s="126" t="s">
         <v>223</v>
       </c>
@@ -8975,11 +8978,11 @@
       <c r="Y3" s="152" t="s">
         <v>226</v>
       </c>
-      <c r="Z3" s="264" t="s">
+      <c r="Z3" s="429" t="s">
         <v>265</v>
       </c>
-      <c r="AA3" s="265"/>
-      <c r="AB3" s="266"/>
+      <c r="AA3" s="430"/>
+      <c r="AB3" s="431"/>
     </row>
     <row r="4" spans="2:28" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="187" t="s">
@@ -9000,11 +9003,11 @@
       <c r="G4" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="284">
+      <c r="H4" s="298">
         <v>63</v>
       </c>
-      <c r="I4" s="285"/>
-      <c r="J4" s="286"/>
+      <c r="I4" s="299"/>
+      <c r="J4" s="300"/>
       <c r="L4" s="132" t="s">
         <v>195</v>
       </c>
@@ -9043,11 +9046,11 @@
       <c r="Y4" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="Z4" s="267" t="s">
+      <c r="Z4" s="432" t="s">
         <v>421</v>
       </c>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="269"/>
+      <c r="AA4" s="433"/>
+      <c r="AB4" s="434"/>
     </row>
     <row r="5" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="188" t="s">
@@ -9068,11 +9071,11 @@
       <c r="G5" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="284">
+      <c r="H5" s="298">
         <v>31</v>
       </c>
-      <c r="I5" s="285"/>
-      <c r="J5" s="286"/>
+      <c r="I5" s="299"/>
+      <c r="J5" s="300"/>
       <c r="L5" s="130" t="s">
         <v>204</v>
       </c>
@@ -9111,9 +9114,9 @@
       <c r="Y5" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="Z5" s="267"/>
-      <c r="AA5" s="268"/>
-      <c r="AB5" s="269"/>
+      <c r="Z5" s="432"/>
+      <c r="AA5" s="433"/>
+      <c r="AB5" s="434"/>
     </row>
     <row r="6" spans="2:28" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="187" t="s">
@@ -9134,11 +9137,11 @@
       <c r="G6" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="281">
+      <c r="H6" s="311">
         <v>7</v>
       </c>
-      <c r="I6" s="282"/>
-      <c r="J6" s="283"/>
+      <c r="I6" s="312"/>
+      <c r="J6" s="313"/>
       <c r="L6" s="133" t="s">
         <v>190</v>
       </c>
@@ -9177,9 +9180,9 @@
       <c r="Y6" s="125" t="s">
         <v>262</v>
       </c>
-      <c r="Z6" s="270"/>
-      <c r="AA6" s="271"/>
-      <c r="AB6" s="272"/>
+      <c r="Z6" s="435"/>
+      <c r="AA6" s="436"/>
+      <c r="AB6" s="437"/>
     </row>
     <row r="7" spans="2:28" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="188" t="s">
@@ -9200,12 +9203,12 @@
       <c r="G7" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="276" t="str">
+      <c r="H7" s="404" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12))</f>
         <v>E3FFF000</v>
       </c>
-      <c r="I7" s="277"/>
-      <c r="J7" s="278"/>
+      <c r="I7" s="405"/>
+      <c r="J7" s="406"/>
       <c r="L7" s="131" t="s">
         <v>190</v>
       </c>
@@ -9252,18 +9255,18 @@
       <c r="G8" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="276" t="str">
+      <c r="H8" s="404" t="str">
         <f>DEC2HEX(HEX2DEC($H$3)+_xlfn.BITLSHIFT(H4,20)+_xlfn.BITLSHIFT(H5,15)+_xlfn.BITLSHIFT(H6,12)+4095)</f>
         <v>E3FFFFFF</v>
       </c>
-      <c r="I8" s="277"/>
-      <c r="J8" s="278"/>
-      <c r="L8" s="257" t="s">
+      <c r="I8" s="405"/>
+      <c r="J8" s="406"/>
+      <c r="L8" s="374" t="s">
         <v>417</v>
       </c>
-      <c r="M8" s="258"/>
-      <c r="N8" s="258"/>
-      <c r="O8" s="259"/>
+      <c r="M8" s="301"/>
+      <c r="N8" s="301"/>
+      <c r="O8" s="302"/>
       <c r="P8" s="114"/>
       <c r="Q8" s="145" t="s">
         <v>232</v>
@@ -9281,10 +9284,10 @@
       <c r="V8" s="225" t="s">
         <v>451</v>
       </c>
-      <c r="W8" s="260" t="s">
+      <c r="W8" s="423" t="s">
         <v>452</v>
       </c>
-      <c r="X8" s="261"/>
+      <c r="X8" s="424"/>
       <c r="Y8" s="224"/>
     </row>
     <row r="9" spans="2:28" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9324,10 +9327,10 @@
       <c r="V9" s="67">
         <v>1</v>
       </c>
-      <c r="W9" s="262" t="s">
+      <c r="W9" s="425" t="s">
         <v>454</v>
       </c>
-      <c r="X9" s="263"/>
+      <c r="X9" s="426"/>
     </row>
     <row r="10" spans="2:28" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187" t="s">
@@ -9358,10 +9361,10 @@
       <c r="V10" s="2">
         <v>2</v>
       </c>
-      <c r="W10" s="243" t="s">
+      <c r="W10" s="427" t="s">
         <v>453</v>
       </c>
-      <c r="X10" s="244"/>
+      <c r="X10" s="428"/>
     </row>
     <row r="11" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="187" t="s">
@@ -9388,20 +9391,20 @@
       <c r="N11" s="114"/>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
-      <c r="Q11" s="254" t="s">
+      <c r="Q11" s="420" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="255"/>
-      <c r="S11" s="255"/>
-      <c r="T11" s="256"/>
+      <c r="R11" s="421"/>
+      <c r="S11" s="421"/>
+      <c r="T11" s="422"/>
       <c r="U11" s="114"/>
       <c r="V11" s="1">
         <v>3</v>
       </c>
-      <c r="W11" s="243" t="s">
+      <c r="W11" s="427" t="s">
         <v>425</v>
       </c>
-      <c r="X11" s="244"/>
+      <c r="X11" s="428"/>
     </row>
     <row r="12" spans="2:28" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="187" t="s">
@@ -9442,10 +9445,10 @@
       <c r="V12" s="2">
         <v>4</v>
       </c>
-      <c r="W12" s="243" t="s">
+      <c r="W12" s="427" t="s">
         <v>460</v>
       </c>
-      <c r="X12" s="244"/>
+      <c r="X12" s="428"/>
     </row>
     <row r="13" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="187" t="s">
@@ -9486,8 +9489,10 @@
       <c r="V13" s="1">
         <v>5</v>
       </c>
-      <c r="W13" s="243"/>
-      <c r="X13" s="244"/>
+      <c r="W13" s="427" t="s">
+        <v>466</v>
+      </c>
+      <c r="X13" s="428"/>
     </row>
     <row r="14" spans="2:28" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="187" t="s">
@@ -9528,8 +9533,8 @@
       <c r="V14" s="2">
         <v>6</v>
       </c>
-      <c r="W14" s="243"/>
-      <c r="X14" s="244"/>
+      <c r="W14" s="427"/>
+      <c r="X14" s="428"/>
     </row>
     <row r="15" spans="2:28" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="187" t="s">
@@ -9570,8 +9575,8 @@
       <c r="V15" s="1">
         <v>7</v>
       </c>
-      <c r="W15" s="243"/>
-      <c r="X15" s="244"/>
+      <c r="W15" s="427"/>
+      <c r="X15" s="428"/>
     </row>
     <row r="16" spans="2:28" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="187" t="s">
@@ -9602,8 +9607,8 @@
       <c r="V16" s="2">
         <v>8</v>
       </c>
-      <c r="W16" s="243"/>
-      <c r="X16" s="244"/>
+      <c r="W16" s="427"/>
+      <c r="X16" s="428"/>
     </row>
     <row r="17" spans="2:24" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="189" t="s">
@@ -9634,8 +9639,8 @@
       <c r="V17" s="226">
         <v>9</v>
       </c>
-      <c r="W17" s="241"/>
-      <c r="X17" s="242"/>
+      <c r="W17" s="438"/>
+      <c r="X17" s="439"/>
     </row>
     <row r="18" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9654,18 +9659,18 @@
       <c r="F19" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="273" t="s">
+      <c r="G19" s="285" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="274"/>
-      <c r="I19" s="274"/>
-      <c r="J19" s="275"/>
+      <c r="H19" s="286"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="289"/>
     </row>
     <row r="20" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="167" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="290" t="s">
+      <c r="C20" s="402" t="s">
         <v>184</v>
       </c>
       <c r="D20" s="106" t="s">
@@ -9677,16 +9682,16 @@
       <c r="F20" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="292" t="s">
+      <c r="G20" s="407" t="s">
         <v>455</v>
       </c>
-      <c r="H20" s="293"/>
-      <c r="I20" s="293"/>
-      <c r="J20" s="294"/>
+      <c r="H20" s="408"/>
+      <c r="I20" s="408"/>
+      <c r="J20" s="409"/>
     </row>
     <row r="21" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
-      <c r="C21" s="295"/>
+      <c r="C21" s="410"/>
       <c r="D21" s="94" t="s">
         <v>187</v>
       </c>
@@ -9696,16 +9701,16 @@
       <c r="F21" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="276" t="s">
+      <c r="G21" s="404" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="277"/>
-      <c r="I21" s="277"/>
-      <c r="J21" s="278"/>
+      <c r="H21" s="405"/>
+      <c r="I21" s="405"/>
+      <c r="J21" s="406"/>
     </row>
     <row r="22" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="168"/>
-      <c r="C22" s="291"/>
+      <c r="C22" s="403"/>
       <c r="D22" s="99" t="s">
         <v>190</v>
       </c>
@@ -9724,7 +9729,7 @@
       <c r="B23" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="290" t="s">
+      <c r="C23" s="402" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="106" t="s">
@@ -9743,7 +9748,7 @@
     </row>
     <row r="24" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="168"/>
-      <c r="C24" s="291"/>
+      <c r="C24" s="403"/>
       <c r="D24" s="99" t="s">
         <v>197</v>
       </c>
@@ -9762,7 +9767,7 @@
       <c r="B25" s="167" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="290" t="s">
+      <c r="C25" s="402" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="106" t="s">
@@ -9781,7 +9786,7 @@
     </row>
     <row r="26" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="168"/>
-      <c r="C26" s="291"/>
+      <c r="C26" s="403"/>
       <c r="D26" s="99" t="s">
         <v>193</v>
       </c>
@@ -9800,7 +9805,7 @@
       <c r="B27" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="290" t="s">
+      <c r="C27" s="402" t="s">
         <v>205</v>
       </c>
       <c r="D27" s="106" t="s">
@@ -9819,7 +9824,7 @@
     </row>
     <row r="28" spans="2:24" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="168"/>
-      <c r="C28" s="291"/>
+      <c r="C28" s="403"/>
       <c r="D28" s="99" t="s">
         <v>199</v>
       </c>
@@ -9859,7 +9864,7 @@
       <c r="B30" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="290" t="s">
+      <c r="C30" s="402" t="s">
         <v>211</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -9878,7 +9883,7 @@
     </row>
     <row r="31" spans="2:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="168"/>
-      <c r="C31" s="291"/>
+      <c r="C31" s="403"/>
       <c r="D31" s="99" t="s">
         <v>204</v>
       </c>
@@ -9897,7 +9902,7 @@
       <c r="B32" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="290" t="s">
+      <c r="C32" s="402" t="s">
         <v>216</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -9916,7 +9921,7 @@
     </row>
     <row r="33" spans="2:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="168"/>
-      <c r="C33" s="291"/>
+      <c r="C33" s="403"/>
       <c r="D33" s="99" t="s">
         <v>208</v>
       </c>
@@ -9933,22 +9938,12 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W16:X16"/>
     <mergeCell ref="V2:AB2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="Q2:T2"/>
@@ -9960,12 +9955,22 @@
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10005,22 +10010,22 @@
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="230"/>
-      <c r="B2" s="406" t="s">
+      <c r="B2" s="247" t="s">
         <v>425</v>
       </c>
-      <c r="C2" s="407"/>
-      <c r="D2" s="407"/>
-      <c r="E2" s="407"/>
-      <c r="F2" s="407"/>
-      <c r="G2" s="408"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
       <c r="I2" s="231"/>
       <c r="J2" s="230"/>
-      <c r="K2" s="406" t="s">
+      <c r="K2" s="247" t="s">
         <v>461</v>
       </c>
-      <c r="L2" s="407"/>
-      <c r="M2" s="407"/>
-      <c r="N2" s="408"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
+      <c r="N2" s="249"/>
       <c r="O2" s="231"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10037,10 +10042,10 @@
       <c r="E3" s="195" t="s">
         <v>429</v>
       </c>
-      <c r="F3" s="430" t="s">
+      <c r="F3" s="250" t="s">
         <v>428</v>
       </c>
-      <c r="G3" s="431"/>
+      <c r="G3" s="251"/>
       <c r="I3" s="231"/>
       <c r="J3" s="230"/>
       <c r="K3" s="194" t="s">
@@ -10049,10 +10054,10 @@
       <c r="L3" s="195" t="s">
         <v>429</v>
       </c>
-      <c r="M3" s="398" t="s">
+      <c r="M3" s="277" t="s">
         <v>428</v>
       </c>
-      <c r="N3" s="399"/>
+      <c r="N3" s="278"/>
       <c r="O3" s="231"/>
     </row>
     <row r="4" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10065,10 +10070,10 @@
       <c r="E4" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="436" t="s">
+      <c r="F4" s="252" t="s">
         <v>435</v>
       </c>
-      <c r="G4" s="437"/>
+      <c r="G4" s="253"/>
       <c r="I4" s="231"/>
       <c r="J4" s="230"/>
       <c r="K4" s="196">
@@ -10077,10 +10082,10 @@
       <c r="L4" s="236" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="400" t="s">
+      <c r="M4" s="279" t="s">
         <v>435</v>
       </c>
-      <c r="N4" s="401"/>
+      <c r="N4" s="280"/>
       <c r="O4" s="231"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10097,10 +10102,10 @@
       <c r="E5" s="219" t="s">
         <v>430</v>
       </c>
-      <c r="F5" s="438" t="s">
+      <c r="F5" s="241" t="s">
         <v>439</v>
       </c>
-      <c r="G5" s="439"/>
+      <c r="G5" s="242"/>
       <c r="I5" s="231"/>
       <c r="J5" s="230"/>
       <c r="K5" s="197">
@@ -10109,10 +10114,10 @@
       <c r="L5" s="237" t="s">
         <v>462</v>
       </c>
-      <c r="M5" s="402" t="s">
+      <c r="M5" s="281" t="s">
         <v>463</v>
       </c>
-      <c r="N5" s="403"/>
+      <c r="N5" s="282"/>
       <c r="O5" s="231"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10127,10 +10132,10 @@
       <c r="E6" s="219" t="s">
         <v>431</v>
       </c>
-      <c r="F6" s="438" t="s">
+      <c r="F6" s="241" t="s">
         <v>436</v>
       </c>
-      <c r="G6" s="439"/>
+      <c r="G6" s="242"/>
       <c r="I6" s="231"/>
       <c r="J6" s="230"/>
       <c r="K6" s="200">
@@ -10139,10 +10144,10 @@
       <c r="L6" s="238" t="s">
         <v>308</v>
       </c>
-      <c r="M6" s="404" t="s">
+      <c r="M6" s="283" t="s">
         <v>464</v>
       </c>
-      <c r="N6" s="405"/>
+      <c r="N6" s="284"/>
       <c r="O6" s="231"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10155,10 +10160,10 @@
       <c r="E7" s="219" t="s">
         <v>432</v>
       </c>
-      <c r="F7" s="438" t="s">
+      <c r="F7" s="241" t="s">
         <v>437</v>
       </c>
-      <c r="G7" s="439"/>
+      <c r="G7" s="242"/>
       <c r="I7" s="231"/>
       <c r="J7" s="230"/>
       <c r="O7" s="231"/>
@@ -10175,13 +10180,13 @@
       <c r="E8" s="219" t="s">
         <v>433</v>
       </c>
-      <c r="F8" s="438" t="s">
+      <c r="F8" s="241" t="s">
         <v>442</v>
       </c>
-      <c r="G8" s="439"/>
+      <c r="G8" s="242"/>
       <c r="I8" s="231"/>
       <c r="J8" s="230"/>
-      <c r="K8" s="396" t="s">
+      <c r="K8" s="254" t="s">
         <v>443</v>
       </c>
       <c r="L8" s="214">
@@ -10205,11 +10210,11 @@
       <c r="E9" s="220" t="s">
         <v>434</v>
       </c>
-      <c r="F9" s="432"/>
-      <c r="G9" s="433"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="244"/>
       <c r="I9" s="231"/>
       <c r="J9" s="230"/>
-      <c r="K9" s="397"/>
+      <c r="K9" s="255"/>
       <c r="L9" s="217"/>
       <c r="M9" s="217"/>
       <c r="N9" s="235" t="s">
@@ -10227,8 +10232,8 @@
       <c r="E10" s="221" t="s">
         <v>434</v>
       </c>
-      <c r="F10" s="432"/>
-      <c r="G10" s="433"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="244"/>
       <c r="I10" s="231"/>
       <c r="J10" s="230"/>
       <c r="O10" s="231"/>
@@ -10243,8 +10248,8 @@
       <c r="E11" s="222" t="s">
         <v>434</v>
       </c>
-      <c r="F11" s="434"/>
-      <c r="G11" s="435"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="246"/>
       <c r="I11" s="231"/>
       <c r="J11" s="232"/>
       <c r="K11" s="233"/>
@@ -10263,11 +10268,11 @@
       <c r="B13" s="208" t="s">
         <v>444</v>
       </c>
-      <c r="C13" s="427" t="s">
+      <c r="C13" s="274" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="428"/>
-      <c r="E13" s="429"/>
+      <c r="D13" s="275"/>
+      <c r="E13" s="276"/>
       <c r="I13" s="231"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -10275,11 +10280,11 @@
       <c r="B14" s="209">
         <v>0</v>
       </c>
-      <c r="C14" s="418" t="s">
+      <c r="C14" s="265" t="s">
         <v>449</v>
       </c>
-      <c r="D14" s="419"/>
-      <c r="E14" s="420"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="267"/>
       <c r="I14" s="231"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -10287,11 +10292,11 @@
       <c r="B15" s="210">
         <v>1</v>
       </c>
-      <c r="C15" s="421" t="s">
+      <c r="C15" s="268" t="s">
         <v>447</v>
       </c>
-      <c r="D15" s="422"/>
-      <c r="E15" s="423"/>
+      <c r="D15" s="269"/>
+      <c r="E15" s="270"/>
       <c r="I15" s="231"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -10299,11 +10304,11 @@
       <c r="B16" s="210">
         <v>2</v>
       </c>
-      <c r="C16" s="409" t="s">
+      <c r="C16" s="256" t="s">
         <v>448</v>
       </c>
-      <c r="D16" s="410"/>
-      <c r="E16" s="411"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="258"/>
       <c r="I16" s="231"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -10311,11 +10316,11 @@
       <c r="B17" s="210">
         <v>3</v>
       </c>
-      <c r="C17" s="424" t="s">
+      <c r="C17" s="271" t="s">
         <v>450</v>
       </c>
-      <c r="D17" s="425"/>
-      <c r="E17" s="426"/>
+      <c r="D17" s="272"/>
+      <c r="E17" s="273"/>
       <c r="I17" s="231"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -10323,9 +10328,9 @@
       <c r="B18" s="210">
         <v>4</v>
       </c>
-      <c r="C18" s="412"/>
-      <c r="D18" s="413"/>
-      <c r="E18" s="414"/>
+      <c r="C18" s="259"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="261"/>
       <c r="I18" s="231"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -10333,9 +10338,9 @@
       <c r="B19" s="210">
         <v>5</v>
       </c>
-      <c r="C19" s="412"/>
-      <c r="D19" s="413"/>
-      <c r="E19" s="414"/>
+      <c r="C19" s="259"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="261"/>
       <c r="I19" s="231"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -10343,9 +10348,9 @@
       <c r="B20" s="210">
         <v>6</v>
       </c>
-      <c r="C20" s="412"/>
-      <c r="D20" s="413"/>
-      <c r="E20" s="414"/>
+      <c r="C20" s="259"/>
+      <c r="D20" s="260"/>
+      <c r="E20" s="261"/>
       <c r="I20" s="231"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10353,9 +10358,9 @@
       <c r="B21" s="211">
         <v>7</v>
       </c>
-      <c r="C21" s="415"/>
-      <c r="D21" s="416"/>
-      <c r="E21" s="417"/>
+      <c r="C21" s="262"/>
+      <c r="D21" s="263"/>
+      <c r="E21" s="264"/>
       <c r="I21" s="231"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10364,7 +10369,7 @@
     </row>
     <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="230"/>
-      <c r="B23" s="396" t="s">
+      <c r="B23" s="254" t="s">
         <v>443</v>
       </c>
       <c r="C23" s="207">
@@ -10389,7 +10394,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="230"/>
-      <c r="B24" s="397"/>
+      <c r="B24" s="255"/>
       <c r="C24" s="216"/>
       <c r="D24" s="217"/>
       <c r="E24" s="217"/>
@@ -10415,16 +10420,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C16:E16"/>
@@ -10441,6 +10436,16 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
